--- a/output/2025-08-26.xlsx
+++ b/output/2025-08-26.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>4.01</v>
+        <v>3.67</v>
       </c>
       <c r="F14" t="n">
-        <v>10.2</v>
+        <v>10.89</v>
       </c>
       <c r="G14" t="n">
-        <v>241.1</v>
+        <v>235.7</v>
       </c>
       <c r="H14" t="n">
-        <v>96.8</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J14" t="n">
-        <v>20.09</v>
+        <v>137.98</v>
       </c>
       <c r="K14" t="n">
-        <v>-53.37</v>
+        <v>51.96</v>
       </c>
       <c r="L14" t="n">
-        <v>57.02</v>
+        <v>147.44</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06:08:55</t>
+          <t>06:09:07</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3.14</v>
+        <v>3.29</v>
       </c>
       <c r="F15" t="n">
-        <v>10.37</v>
+        <v>11.42</v>
       </c>
       <c r="G15" t="n">
-        <v>216.1</v>
+        <v>225.4</v>
       </c>
       <c r="H15" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J15" t="n">
-        <v>-97.65000000000001</v>
+        <v>-334.2</v>
       </c>
       <c r="K15" t="n">
-        <v>38.65</v>
+        <v>-240.52</v>
       </c>
       <c r="L15" t="n">
-        <v>105.02</v>
+        <v>411.75</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06:10:22</t>
+          <t>06:10:42</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>3.49</v>
+        <v>3.48</v>
       </c>
       <c r="F16" t="n">
-        <v>10.94</v>
+        <v>9.68</v>
       </c>
       <c r="G16" t="n">
-        <v>213.8</v>
+        <v>231.5</v>
       </c>
       <c r="H16" t="n">
-        <v>97.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="I16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J16" t="n">
-        <v>-27.56</v>
+        <v>-61.18</v>
       </c>
       <c r="K16" t="n">
-        <v>4.82</v>
+        <v>172.16</v>
       </c>
       <c r="L16" t="n">
-        <v>27.98</v>
+        <v>182.71</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06:15:23</t>
+          <t>06:14:38</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>3.71</v>
+        <v>3.86</v>
       </c>
       <c r="F17" t="n">
-        <v>11.17</v>
+        <v>10.63</v>
       </c>
       <c r="G17" t="n">
-        <v>225.3</v>
+        <v>214.5</v>
       </c>
       <c r="H17" t="n">
-        <v>93.40000000000001</v>
+        <v>91.8</v>
       </c>
       <c r="I17" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>-251.78</v>
+        <v>303.51</v>
       </c>
       <c r="K17" t="n">
-        <v>-17.52</v>
+        <v>10.82</v>
       </c>
       <c r="L17" t="n">
-        <v>252.39</v>
+        <v>303.71</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06:17:09</t>
+          <t>06:16:25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="F18" t="n">
-        <v>11.21</v>
+        <v>10.6</v>
       </c>
       <c r="G18" t="n">
-        <v>212.1</v>
+        <v>229.5</v>
       </c>
       <c r="H18" t="n">
-        <v>99.40000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="I18" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>321.68</v>
+        <v>293.95</v>
       </c>
       <c r="K18" t="n">
-        <v>-71.83</v>
+        <v>223.87</v>
       </c>
       <c r="L18" t="n">
-        <v>329.6</v>
+        <v>369.49</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06:18:25</t>
+          <t>06:17:17</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>3.67</v>
+        <v>4.16</v>
       </c>
       <c r="F19" t="n">
-        <v>10.3</v>
+        <v>10.45</v>
       </c>
       <c r="G19" t="n">
-        <v>222.9</v>
+        <v>230.4</v>
       </c>
       <c r="H19" t="n">
         <v>100</v>
       </c>
       <c r="I19" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J19" t="n">
-        <v>-18.77</v>
+        <v>-25.89</v>
       </c>
       <c r="K19" t="n">
-        <v>21.03</v>
+        <v>212.81</v>
       </c>
       <c r="L19" t="n">
-        <v>28.18</v>
+        <v>214.38</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06:22:16</t>
+          <t>06:22:53</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>3.48</v>
+        <v>3.75</v>
       </c>
       <c r="F20" t="n">
-        <v>10.92</v>
+        <v>10.23</v>
       </c>
       <c r="G20" t="n">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="H20" t="n">
-        <v>96.8</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J20" t="n">
-        <v>173.28</v>
+        <v>-296.7</v>
       </c>
       <c r="K20" t="n">
-        <v>-47.76</v>
+        <v>-0.27</v>
       </c>
       <c r="L20" t="n">
-        <v>179.74</v>
+        <v>296.7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06:24:12</t>
+          <t>06:25:15</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>3.61</v>
+        <v>3.58</v>
       </c>
       <c r="F21" t="n">
-        <v>10.85</v>
+        <v>10.37</v>
       </c>
       <c r="G21" t="n">
-        <v>213.6</v>
+        <v>232.7</v>
       </c>
       <c r="H21" t="n">
-        <v>89.59999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="I21" t="n">
         <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>-158.31</v>
+        <v>-39.64</v>
       </c>
       <c r="K21" t="n">
-        <v>-217.6</v>
+        <v>293.01</v>
       </c>
       <c r="L21" t="n">
-        <v>269.09</v>
+        <v>295.68</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06:25:55</t>
+          <t>06:27:12</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>4.43</v>
+        <v>3.48</v>
       </c>
       <c r="F22" t="n">
-        <v>10.53</v>
+        <v>10.67</v>
       </c>
       <c r="G22" t="n">
-        <v>226.8</v>
+        <v>225.9</v>
       </c>
       <c r="H22" t="n">
-        <v>88.2</v>
+        <v>94.5</v>
       </c>
       <c r="I22" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J22" t="n">
-        <v>68.03</v>
+        <v>-162.06</v>
       </c>
       <c r="K22" t="n">
-        <v>151.93</v>
+        <v>288.51</v>
       </c>
       <c r="L22" t="n">
-        <v>166.47</v>
+        <v>330.91</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06:30:47</t>
+          <t>06:32:00</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>4.67</v>
+        <v>4.3</v>
       </c>
       <c r="F23" t="n">
-        <v>10.98</v>
+        <v>11.41</v>
       </c>
       <c r="G23" t="n">
-        <v>239.1</v>
+        <v>223.8</v>
       </c>
       <c r="H23" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="I23" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>-385.62</v>
+        <v>510.16</v>
       </c>
       <c r="K23" t="n">
-        <v>296.42</v>
+        <v>-1.26</v>
       </c>
       <c r="L23" t="n">
-        <v>486.38</v>
+        <v>510.16</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06:32:46</t>
+          <t>06:34:17</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>4.23</v>
+        <v>3.78</v>
       </c>
       <c r="F24" t="n">
-        <v>10.89</v>
+        <v>10.41</v>
       </c>
       <c r="G24" t="n">
-        <v>216.4</v>
+        <v>231.9</v>
       </c>
       <c r="H24" t="n">
-        <v>94.40000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="I24" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>-577.09</v>
+        <v>470.22</v>
       </c>
       <c r="K24" t="n">
-        <v>-404.06</v>
+        <v>-239.5</v>
       </c>
       <c r="L24" t="n">
-        <v>704.48</v>
+        <v>527.7</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06:34:09</t>
+          <t>06:35:13</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>4.08</v>
+        <v>4.18</v>
       </c>
       <c r="F25" t="n">
-        <v>10.85</v>
+        <v>10.65</v>
       </c>
       <c r="G25" t="n">
-        <v>228.5</v>
+        <v>223.8</v>
       </c>
       <c r="H25" t="n">
-        <v>93.09999999999999</v>
+        <v>93.7</v>
       </c>
       <c r="I25" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J25" t="n">
-        <v>393.79</v>
+        <v>-59.46</v>
       </c>
       <c r="K25" t="n">
-        <v>-6.86</v>
+        <v>-149.91</v>
       </c>
       <c r="L25" t="n">
-        <v>393.85</v>
+        <v>161.27</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06:38:32</t>
+          <t>06:39:08</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>4.06</v>
+        <v>3.39</v>
       </c>
       <c r="F26" t="n">
-        <v>11.04</v>
+        <v>10.13</v>
       </c>
       <c r="G26" t="n">
         <v>227.7</v>
       </c>
       <c r="H26" t="n">
-        <v>98.40000000000001</v>
+        <v>93.5</v>
       </c>
       <c r="I26" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>-5.47</v>
+        <v>-777.29</v>
       </c>
       <c r="K26" t="n">
-        <v>163.52</v>
+        <v>505.13</v>
       </c>
       <c r="L26" t="n">
-        <v>163.61</v>
+        <v>927</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06:39:28</t>
+          <t>06:41:10</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>4.07</v>
+        <v>3.83</v>
       </c>
       <c r="F27" t="n">
-        <v>11.21</v>
+        <v>10.73</v>
       </c>
       <c r="G27" t="n">
-        <v>218.3</v>
+        <v>236.8</v>
       </c>
       <c r="H27" t="n">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="I27" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J27" t="n">
-        <v>-256.15</v>
+        <v>203.46</v>
       </c>
       <c r="K27" t="n">
-        <v>-413.87</v>
+        <v>325.74</v>
       </c>
       <c r="L27" t="n">
-        <v>486.72</v>
+        <v>384.06</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06:40:54</t>
+          <t>06:42:24</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>3.48</v>
+        <v>4.1</v>
       </c>
       <c r="F28" t="n">
-        <v>10.51</v>
+        <v>11.06</v>
       </c>
       <c r="G28" t="n">
-        <v>211.9</v>
+        <v>219.3</v>
       </c>
       <c r="H28" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="I28" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>-959.09</v>
+        <v>-1253.46</v>
       </c>
       <c r="K28" t="n">
-        <v>436.85</v>
+        <v>-294.23</v>
       </c>
       <c r="L28" t="n">
-        <v>1053.9</v>
+        <v>1287.53</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06:51:23</t>
+          <t>06:55:31</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>3.82</v>
+        <v>3.66</v>
       </c>
       <c r="F29" t="n">
-        <v>10.74</v>
+        <v>10.78</v>
       </c>
       <c r="G29" t="n">
-        <v>226.7</v>
+        <v>231.5</v>
       </c>
       <c r="H29" t="n">
-        <v>98.2</v>
+        <v>100</v>
       </c>
       <c r="I29" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J29" t="n">
-        <v>-79.52</v>
+        <v>-79.15000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>32.13</v>
+        <v>-290.47</v>
       </c>
       <c r="L29" t="n">
-        <v>85.77</v>
+        <v>301.06</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06:52:33</t>
+          <t>06:57:13</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>3.29</v>
+        <v>3.96</v>
       </c>
       <c r="F30" t="n">
-        <v>10.65</v>
+        <v>10.39</v>
       </c>
       <c r="G30" t="n">
-        <v>230.7</v>
+        <v>222.4</v>
       </c>
       <c r="H30" t="n">
-        <v>95.40000000000001</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J30" t="n">
-        <v>-91</v>
+        <v>250.63</v>
       </c>
       <c r="K30" t="n">
-        <v>73.26000000000001</v>
+        <v>17.13</v>
       </c>
       <c r="L30" t="n">
-        <v>116.82</v>
+        <v>251.22</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06:53:45</t>
+          <t>06:59:36</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>3.72</v>
+        <v>3.78</v>
       </c>
       <c r="F31" t="n">
-        <v>10.25</v>
+        <v>10.17</v>
       </c>
       <c r="G31" t="n">
-        <v>226.3</v>
+        <v>215</v>
       </c>
       <c r="H31" t="n">
-        <v>92.5</v>
+        <v>95</v>
       </c>
       <c r="I31" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J31" t="n">
-        <v>-121.87</v>
+        <v>-236.76</v>
       </c>
       <c r="K31" t="n">
-        <v>-151.81</v>
+        <v>-170.67</v>
       </c>
       <c r="L31" t="n">
-        <v>194.68</v>
+        <v>291.86</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06:57:39</t>
+          <t>07:03:14</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>4.12</v>
+        <v>3.76</v>
       </c>
       <c r="F32" t="n">
-        <v>11.06</v>
+        <v>10.7</v>
       </c>
       <c r="G32" t="n">
-        <v>219</v>
+        <v>230.1</v>
       </c>
       <c r="H32" t="n">
-        <v>95.2</v>
+        <v>100</v>
       </c>
       <c r="I32" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J32" t="n">
-        <v>233.38</v>
+        <v>63.84</v>
       </c>
       <c r="K32" t="n">
-        <v>160.07</v>
+        <v>317.04</v>
       </c>
       <c r="L32" t="n">
-        <v>283</v>
+        <v>323.4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06:59:33</t>
+          <t>07:04:10</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>3.66</v>
+        <v>3.94</v>
       </c>
       <c r="F33" t="n">
-        <v>10.6</v>
+        <v>10.39</v>
       </c>
       <c r="G33" t="n">
-        <v>224.7</v>
+        <v>229.2</v>
       </c>
       <c r="H33" t="n">
-        <v>99.59999999999999</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="I33" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J33" t="n">
-        <v>-62.17</v>
+        <v>112.27</v>
       </c>
       <c r="K33" t="n">
-        <v>153.66</v>
+        <v>65.98</v>
       </c>
       <c r="L33" t="n">
-        <v>165.76</v>
+        <v>130.22</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07:00:48</t>
+          <t>07:05:55</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>3.94</v>
+        <v>3.53</v>
       </c>
       <c r="F34" t="n">
-        <v>10.27</v>
+        <v>10.43</v>
       </c>
       <c r="G34" t="n">
-        <v>207.3</v>
+        <v>224.2</v>
       </c>
       <c r="H34" t="n">
-        <v>97.09999999999999</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="I34" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>-150.51</v>
+        <v>25.2</v>
       </c>
       <c r="K34" t="n">
-        <v>-54.73</v>
+        <v>-265.44</v>
       </c>
       <c r="L34" t="n">
-        <v>160.15</v>
+        <v>266.64</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07:05:14</t>
+          <t>07:10:33</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>4.35</v>
+        <v>3.46</v>
       </c>
       <c r="F35" t="n">
-        <v>10.54</v>
+        <v>10.64</v>
       </c>
       <c r="G35" t="n">
-        <v>212.6</v>
+        <v>233.8</v>
       </c>
       <c r="H35" t="n">
-        <v>100</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J35" t="n">
-        <v>408.43</v>
+        <v>-284.4</v>
       </c>
       <c r="K35" t="n">
-        <v>182.22</v>
+        <v>137.22</v>
       </c>
       <c r="L35" t="n">
-        <v>447.24</v>
+        <v>315.77</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07:07:17</t>
+          <t>07:12:40</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>3.46</v>
+        <v>4.62</v>
       </c>
       <c r="F36" t="n">
-        <v>10.41</v>
+        <v>10.72</v>
       </c>
       <c r="G36" t="n">
-        <v>220.6</v>
+        <v>223</v>
       </c>
       <c r="H36" t="n">
-        <v>98.2</v>
+        <v>94.7</v>
       </c>
       <c r="I36" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J36" t="n">
-        <v>119.17</v>
+        <v>-18.24</v>
       </c>
       <c r="K36" t="n">
-        <v>-264.6</v>
+        <v>168.91</v>
       </c>
       <c r="L36" t="n">
-        <v>290.2</v>
+        <v>169.89</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07:08:55</t>
+          <t>07:14:58</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>4.36</v>
+        <v>4.54</v>
       </c>
       <c r="F37" t="n">
-        <v>10.53</v>
+        <v>10.71</v>
       </c>
       <c r="G37" t="n">
-        <v>202.9</v>
+        <v>236</v>
       </c>
       <c r="H37" t="n">
-        <v>93.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="I37" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J37" t="n">
-        <v>-120.89</v>
+        <v>-513.55</v>
       </c>
       <c r="K37" t="n">
-        <v>106.27</v>
+        <v>19.77</v>
       </c>
       <c r="L37" t="n">
-        <v>160.96</v>
+        <v>513.9299999999999</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07:12:23</t>
+          <t>07:19:36</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>3.8</v>
+        <v>4.82</v>
       </c>
       <c r="F38" t="n">
-        <v>11.38</v>
+        <v>11.39</v>
       </c>
       <c r="G38" t="n">
-        <v>220.6</v>
+        <v>228</v>
       </c>
       <c r="H38" t="n">
-        <v>96.3</v>
+        <v>100</v>
       </c>
       <c r="I38" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J38" t="n">
-        <v>-31.62</v>
+        <v>522.09</v>
       </c>
       <c r="K38" t="n">
-        <v>36.45</v>
+        <v>440.93</v>
       </c>
       <c r="L38" t="n">
-        <v>48.25</v>
+        <v>683.37</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07:14:06</t>
+          <t>07:21:36</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>4.11</v>
+        <v>3.73</v>
       </c>
       <c r="F39" t="n">
-        <v>10.93</v>
+        <v>10.72</v>
       </c>
       <c r="G39" t="n">
-        <v>238</v>
+        <v>238.9</v>
       </c>
       <c r="H39" t="n">
-        <v>95.2</v>
+        <v>92.3</v>
       </c>
       <c r="I39" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J39" t="n">
-        <v>20.03</v>
+        <v>-480.68</v>
       </c>
       <c r="K39" t="n">
-        <v>-137.97</v>
+        <v>247.96</v>
       </c>
       <c r="L39" t="n">
-        <v>139.41</v>
+        <v>540.86</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07:15:30</t>
+          <t>07:22:51</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>4.1</v>
+        <v>3.83</v>
       </c>
       <c r="F40" t="n">
-        <v>10.62</v>
+        <v>11.08</v>
       </c>
       <c r="G40" t="n">
-        <v>231.8</v>
+        <v>235.5</v>
       </c>
       <c r="H40" t="n">
-        <v>94.90000000000001</v>
+        <v>93.5</v>
       </c>
       <c r="I40" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J40" t="n">
-        <v>-107.65</v>
+        <v>439.89</v>
       </c>
       <c r="K40" t="n">
-        <v>-446.03</v>
+        <v>361.26</v>
       </c>
       <c r="L40" t="n">
-        <v>458.84</v>
+        <v>569.22</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07:20:45</t>
+          <t>07:27:39</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>3.58</v>
+        <v>4.16</v>
       </c>
       <c r="F41" t="n">
-        <v>10.79</v>
+        <v>10.72</v>
       </c>
       <c r="G41" t="n">
-        <v>228</v>
+        <v>225.3</v>
       </c>
       <c r="H41" t="n">
-        <v>92.2</v>
+        <v>98.7</v>
       </c>
       <c r="I41" t="n">
         <v>18</v>
       </c>
       <c r="J41" t="n">
-        <v>-231.77</v>
+        <v>-88.56</v>
       </c>
       <c r="K41" t="n">
-        <v>304.84</v>
+        <v>-508.97</v>
       </c>
       <c r="L41" t="n">
-        <v>382.94</v>
+        <v>516.62</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07:22:52</t>
+          <t>07:29:30</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>3.61</v>
+        <v>3.48</v>
       </c>
       <c r="F42" t="n">
-        <v>10.7</v>
+        <v>10.99</v>
       </c>
       <c r="G42" t="n">
-        <v>228.3</v>
+        <v>205.4</v>
       </c>
       <c r="H42" t="n">
-        <v>91.3</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="I42" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J42" t="n">
-        <v>200.32</v>
+        <v>-164.53</v>
       </c>
       <c r="K42" t="n">
-        <v>-32.24</v>
+        <v>381.25</v>
       </c>
       <c r="L42" t="n">
-        <v>202.9</v>
+        <v>415.24</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07:24:56</t>
+          <t>07:30:25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>4.57</v>
+        <v>3.91</v>
       </c>
       <c r="F43" t="n">
-        <v>10.98</v>
+        <v>10.87</v>
       </c>
       <c r="G43" t="n">
-        <v>214.5</v>
+        <v>222.9</v>
       </c>
       <c r="H43" t="n">
-        <v>90.8</v>
+        <v>87.2</v>
       </c>
       <c r="I43" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J43" t="n">
-        <v>314.3</v>
+        <v>-203.77</v>
       </c>
       <c r="K43" t="n">
-        <v>-114.67</v>
+        <v>69.77</v>
       </c>
       <c r="L43" t="n">
-        <v>334.57</v>
+        <v>215.38</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07:35:48</t>
+          <t>07:41:31</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1888,31 +1888,31 @@
         <v>4.31</v>
       </c>
       <c r="F44" t="n">
-        <v>10.56</v>
+        <v>10.04</v>
       </c>
       <c r="G44" t="n">
-        <v>218.9</v>
+        <v>215.8</v>
       </c>
       <c r="H44" t="n">
-        <v>96.09999999999999</v>
+        <v>98.5</v>
       </c>
       <c r="I44" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>-63.21</v>
+        <v>149.24</v>
       </c>
       <c r="K44" t="n">
-        <v>85.34</v>
+        <v>-145.43</v>
       </c>
       <c r="L44" t="n">
-        <v>106.2</v>
+        <v>208.38</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07:36:56</t>
+          <t>07:43:47</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>4.33</v>
+        <v>4.28</v>
       </c>
       <c r="F45" t="n">
-        <v>11.01</v>
+        <v>10.5</v>
       </c>
       <c r="G45" t="n">
-        <v>221.8</v>
+        <v>219.5</v>
       </c>
       <c r="H45" t="n">
-        <v>91.59999999999999</v>
+        <v>97.2</v>
       </c>
       <c r="I45" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>157.1</v>
+        <v>166.7</v>
       </c>
       <c r="K45" t="n">
-        <v>22.07</v>
+        <v>-29.1</v>
       </c>
       <c r="L45" t="n">
-        <v>158.64</v>
+        <v>169.22</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07:38:17</t>
+          <t>07:45:18</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>4.19</v>
+        <v>3.73</v>
       </c>
       <c r="F46" t="n">
-        <v>10.44</v>
+        <v>10.32</v>
       </c>
       <c r="G46" t="n">
-        <v>231.2</v>
+        <v>220.7</v>
       </c>
       <c r="H46" t="n">
-        <v>99.8</v>
+        <v>93</v>
       </c>
       <c r="I46" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J46" t="n">
-        <v>-156.49</v>
+        <v>225.42</v>
       </c>
       <c r="K46" t="n">
-        <v>72.79000000000001</v>
+        <v>209.05</v>
       </c>
       <c r="L46" t="n">
-        <v>172.59</v>
+        <v>307.44</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07:43:39</t>
+          <t>07:50:55</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>4.18</v>
+        <v>4.53</v>
       </c>
       <c r="F47" t="n">
-        <v>11</v>
+        <v>10.53</v>
       </c>
       <c r="G47" t="n">
-        <v>228.3</v>
+        <v>212.5</v>
       </c>
       <c r="H47" t="n">
-        <v>96.5</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="I47" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-304.4</v>
+        <v>-160.23</v>
       </c>
       <c r="K47" t="n">
-        <v>-231.05</v>
+        <v>23.72</v>
       </c>
       <c r="L47" t="n">
-        <v>382.15</v>
+        <v>161.97</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07:44:46</t>
+          <t>07:52:55</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>3.8</v>
+        <v>4.27</v>
       </c>
       <c r="F48" t="n">
         <v>10.41</v>
       </c>
       <c r="G48" t="n">
-        <v>228.1</v>
+        <v>223.4</v>
       </c>
       <c r="H48" t="n">
-        <v>94.59999999999999</v>
+        <v>98.8</v>
       </c>
       <c r="I48" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>70.90000000000001</v>
+        <v>-168.1</v>
       </c>
       <c r="K48" t="n">
-        <v>-68.73999999999999</v>
+        <v>-325.11</v>
       </c>
       <c r="L48" t="n">
-        <v>98.75</v>
+        <v>366</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07:45:53</t>
+          <t>07:53:56</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>3.64</v>
+        <v>4.06</v>
       </c>
       <c r="F49" t="n">
-        <v>10.6</v>
+        <v>10.9</v>
       </c>
       <c r="G49" t="n">
-        <v>232.4</v>
+        <v>212.7</v>
       </c>
       <c r="H49" t="n">
-        <v>98.59999999999999</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="I49" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J49" t="n">
-        <v>-21.33</v>
+        <v>-45.2</v>
       </c>
       <c r="K49" t="n">
-        <v>19.47</v>
+        <v>-181.79</v>
       </c>
       <c r="L49" t="n">
-        <v>28.88</v>
+        <v>187.33</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07:50:55</t>
+          <t>07:57:19</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>3.83</v>
+        <v>3.8</v>
       </c>
       <c r="F50" t="n">
-        <v>10.68</v>
+        <v>10.26</v>
       </c>
       <c r="G50" t="n">
-        <v>228.1</v>
+        <v>229.2</v>
       </c>
       <c r="H50" t="n">
-        <v>92.59999999999999</v>
+        <v>96.3</v>
       </c>
       <c r="I50" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J50" t="n">
-        <v>-109.9</v>
+        <v>280.83</v>
       </c>
       <c r="K50" t="n">
-        <v>-239.99</v>
+        <v>-76.25</v>
       </c>
       <c r="L50" t="n">
-        <v>263.95</v>
+        <v>291</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07:52:19</t>
+          <t>07:58:46</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>4.72</v>
+        <v>4.24</v>
       </c>
       <c r="F51" t="n">
-        <v>10.76</v>
+        <v>10.52</v>
       </c>
       <c r="G51" t="n">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="H51" t="n">
-        <v>95.09999999999999</v>
+        <v>86.2</v>
       </c>
       <c r="I51" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J51" t="n">
-        <v>-65.47</v>
+        <v>-341.32</v>
       </c>
       <c r="K51" t="n">
-        <v>124.41</v>
+        <v>-96.7</v>
       </c>
       <c r="L51" t="n">
-        <v>140.59</v>
+        <v>354.76</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07:54:06</t>
+          <t>07:59:39</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>4.03</v>
+        <v>4.08</v>
       </c>
       <c r="F52" t="n">
-        <v>10.4</v>
+        <v>10.49</v>
       </c>
       <c r="G52" t="n">
-        <v>228.8</v>
+        <v>231.8</v>
       </c>
       <c r="H52" t="n">
-        <v>95.8</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="I52" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J52" t="n">
-        <v>-183.99</v>
+        <v>-99.03</v>
       </c>
       <c r="K52" t="n">
-        <v>545.79</v>
+        <v>194.93</v>
       </c>
       <c r="L52" t="n">
-        <v>575.97</v>
+        <v>218.65</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07:57:18</t>
+          <t>08:05:10</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>3.94</v>
+        <v>4.12</v>
       </c>
       <c r="F53" t="n">
-        <v>10.65</v>
+        <v>10.85</v>
       </c>
       <c r="G53" t="n">
-        <v>218.9</v>
+        <v>233.2</v>
       </c>
       <c r="H53" t="n">
-        <v>95.2</v>
+        <v>100</v>
       </c>
       <c r="I53" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>37.53</v>
+        <v>844.95</v>
       </c>
       <c r="K53" t="n">
-        <v>-199.29</v>
+        <v>143.56</v>
       </c>
       <c r="L53" t="n">
-        <v>202.79</v>
+        <v>857.0599999999999</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07:59:00</t>
+          <t>08:06:22</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>3.99</v>
+        <v>4.64</v>
       </c>
       <c r="F54" t="n">
-        <v>10.78</v>
+        <v>10.19</v>
       </c>
       <c r="G54" t="n">
-        <v>211.9</v>
+        <v>233</v>
       </c>
       <c r="H54" t="n">
-        <v>93.09999999999999</v>
+        <v>84</v>
       </c>
       <c r="I54" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J54" t="n">
-        <v>40.97</v>
+        <v>-669.11</v>
       </c>
       <c r="K54" t="n">
-        <v>-414.43</v>
+        <v>-365.47</v>
       </c>
       <c r="L54" t="n">
-        <v>416.45</v>
+        <v>762.42</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08:00:25</t>
+          <t>08:08:01</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>4.26</v>
+        <v>4.03</v>
       </c>
       <c r="F55" t="n">
         <v>10.61</v>
       </c>
       <c r="G55" t="n">
-        <v>223.6</v>
+        <v>225.6</v>
       </c>
       <c r="H55" t="n">
-        <v>97.5</v>
+        <v>100</v>
       </c>
       <c r="I55" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>14.29</v>
+        <v>-377.59</v>
       </c>
       <c r="K55" t="n">
-        <v>-68.18000000000001</v>
+        <v>-420.64</v>
       </c>
       <c r="L55" t="n">
-        <v>69.66</v>
+        <v>565.25</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08:04:03</t>
+          <t>08:13:10</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>4.62</v>
+        <v>4.9</v>
       </c>
       <c r="F56" t="n">
-        <v>10.52</v>
+        <v>11.02</v>
       </c>
       <c r="G56" t="n">
-        <v>211.5</v>
+        <v>226.7</v>
       </c>
       <c r="H56" t="n">
-        <v>92.8</v>
+        <v>100</v>
       </c>
       <c r="I56" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J56" t="n">
-        <v>422.88</v>
+        <v>-506.8</v>
       </c>
       <c r="K56" t="n">
-        <v>361.48</v>
+        <v>-531.27</v>
       </c>
       <c r="L56" t="n">
-        <v>556.3200000000001</v>
+        <v>734.23</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08:05:59</t>
+          <t>08:14:51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="F57" t="n">
-        <v>10.23</v>
+        <v>11.58</v>
       </c>
       <c r="G57" t="n">
-        <v>237.6</v>
+        <v>218.9</v>
       </c>
       <c r="H57" t="n">
-        <v>98.5</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="I57" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>-1052.17</v>
+        <v>-521.71</v>
       </c>
       <c r="K57" t="n">
-        <v>-81.03</v>
+        <v>-1030.84</v>
       </c>
       <c r="L57" t="n">
-        <v>1055.29</v>
+        <v>1155.34</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08:08:46</t>
+          <t>08:16:56</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>3.54</v>
+        <v>4.21</v>
       </c>
       <c r="F58" t="n">
-        <v>10.21</v>
+        <v>10.73</v>
       </c>
       <c r="G58" t="n">
-        <v>232</v>
+        <v>229.8</v>
       </c>
       <c r="H58" t="n">
-        <v>100</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="I58" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>-850.77</v>
+        <v>285.36</v>
       </c>
       <c r="K58" t="n">
-        <v>-142.53</v>
+        <v>-243.51</v>
       </c>
       <c r="L58" t="n">
-        <v>862.63</v>
+        <v>375.14</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08:19:39</t>
+          <t>08:25:59</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>3.95</v>
+        <v>3.83</v>
       </c>
       <c r="F59" t="n">
-        <v>11.34</v>
+        <v>10.78</v>
       </c>
       <c r="G59" t="n">
-        <v>215.2</v>
+        <v>227.1</v>
       </c>
       <c r="H59" t="n">
-        <v>89.90000000000001</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="I59" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J59" t="n">
-        <v>-1.16</v>
+        <v>-99.45999999999999</v>
       </c>
       <c r="K59" t="n">
-        <v>-43</v>
+        <v>-31.09</v>
       </c>
       <c r="L59" t="n">
-        <v>43.01</v>
+        <v>104.2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08:20:38</t>
+          <t>08:28:26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>3.94</v>
+        <v>4.54</v>
       </c>
       <c r="F60" t="n">
-        <v>10.51</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="G60" t="n">
-        <v>220</v>
+        <v>207.7</v>
       </c>
       <c r="H60" t="n">
-        <v>96.40000000000001</v>
+        <v>88.5</v>
       </c>
       <c r="I60" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J60" t="n">
-        <v>193.53</v>
+        <v>-138.9</v>
       </c>
       <c r="K60" t="n">
-        <v>44.25</v>
+        <v>-86.93000000000001</v>
       </c>
       <c r="L60" t="n">
-        <v>198.52</v>
+        <v>163.86</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08:22:04</t>
+          <t>08:30:06</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>4.01</v>
+        <v>4.2</v>
       </c>
       <c r="F61" t="n">
-        <v>10.68</v>
+        <v>10.83</v>
       </c>
       <c r="G61" t="n">
-        <v>220.1</v>
+        <v>211.4</v>
       </c>
       <c r="H61" t="n">
-        <v>99.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="I61" t="n">
         <v>20</v>
       </c>
       <c r="J61" t="n">
-        <v>21.5</v>
+        <v>-203.4</v>
       </c>
       <c r="K61" t="n">
-        <v>2.08</v>
+        <v>80.69</v>
       </c>
       <c r="L61" t="n">
-        <v>21.6</v>
+        <v>218.82</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08:27:25</t>
+          <t>08:33:04</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>4.7</v>
+        <v>4.36</v>
       </c>
       <c r="F62" t="n">
-        <v>10.82</v>
+        <v>10.79</v>
       </c>
       <c r="G62" t="n">
-        <v>235.9</v>
+        <v>232.5</v>
       </c>
       <c r="H62" t="n">
-        <v>93.09999999999999</v>
+        <v>86.5</v>
       </c>
       <c r="I62" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J62" t="n">
-        <v>-160.51</v>
+        <v>-655.01</v>
       </c>
       <c r="K62" t="n">
-        <v>-25.71</v>
+        <v>-107.64</v>
       </c>
       <c r="L62" t="n">
-        <v>162.56</v>
+        <v>663.8</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08:29:53</t>
+          <t>08:35:22</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>4.13</v>
+        <v>3.75</v>
       </c>
       <c r="F63" t="n">
-        <v>9.98</v>
+        <v>10.79</v>
       </c>
       <c r="G63" t="n">
-        <v>228.3</v>
+        <v>232.4</v>
       </c>
       <c r="H63" t="n">
-        <v>99.8</v>
+        <v>100</v>
       </c>
       <c r="I63" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>-39.06</v>
+        <v>-179.4</v>
       </c>
       <c r="K63" t="n">
-        <v>-22.99</v>
+        <v>-145.1</v>
       </c>
       <c r="L63" t="n">
-        <v>45.32</v>
+        <v>230.73</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>08:31:05</t>
+          <t>08:36:30</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>3.97</v>
+        <v>4.56</v>
       </c>
       <c r="F64" t="n">
-        <v>10.72</v>
+        <v>10.35</v>
       </c>
       <c r="G64" t="n">
-        <v>223.3</v>
+        <v>222.2</v>
       </c>
       <c r="H64" t="n">
-        <v>96.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="I64" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>182.95</v>
+        <v>168.37</v>
       </c>
       <c r="K64" t="n">
-        <v>12.62</v>
+        <v>-140.95</v>
       </c>
       <c r="L64" t="n">
-        <v>183.38</v>
+        <v>219.58</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>08:34:32</t>
+          <t>08:41:50</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>3.95</v>
+        <v>3.92</v>
       </c>
       <c r="F65" t="n">
-        <v>10.96</v>
+        <v>10.13</v>
       </c>
       <c r="G65" t="n">
-        <v>236.8</v>
+        <v>217.2</v>
       </c>
       <c r="H65" t="n">
-        <v>100</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="I65" t="n">
         <v>20</v>
       </c>
       <c r="J65" t="n">
-        <v>-214.25</v>
+        <v>72.38</v>
       </c>
       <c r="K65" t="n">
-        <v>-88.45999999999999</v>
+        <v>-153.83</v>
       </c>
       <c r="L65" t="n">
-        <v>231.8</v>
+        <v>170.01</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>08:36:40</t>
+          <t>08:44:06</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>4.3</v>
+        <v>4.62</v>
       </c>
       <c r="F66" t="n">
-        <v>10.55</v>
+        <v>10.14</v>
       </c>
       <c r="G66" t="n">
-        <v>224.1</v>
+        <v>228.9</v>
       </c>
       <c r="H66" t="n">
-        <v>100</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="I66" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>-58.23</v>
+        <v>-346.66</v>
       </c>
       <c r="K66" t="n">
-        <v>-145.19</v>
+        <v>95.33</v>
       </c>
       <c r="L66" t="n">
-        <v>156.43</v>
+        <v>359.53</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>08:39:15</t>
+          <t>08:44:49</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>4.64</v>
+        <v>3.93</v>
       </c>
       <c r="F67" t="n">
-        <v>10.48</v>
+        <v>10.88</v>
       </c>
       <c r="G67" t="n">
-        <v>234.3</v>
+        <v>215.2</v>
       </c>
       <c r="H67" t="n">
-        <v>91.5</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="I67" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J67" t="n">
-        <v>268.82</v>
+        <v>-284.29</v>
       </c>
       <c r="K67" t="n">
-        <v>270.93</v>
+        <v>-61.77</v>
       </c>
       <c r="L67" t="n">
-        <v>381.66</v>
+        <v>290.93</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>08:42:40</t>
+          <t>08:50:00</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>4.18</v>
+        <v>4.7</v>
       </c>
       <c r="F68" t="n">
-        <v>10.7</v>
+        <v>10.55</v>
       </c>
       <c r="G68" t="n">
-        <v>200.7</v>
+        <v>217.2</v>
       </c>
       <c r="H68" t="n">
-        <v>98.40000000000001</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="I68" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J68" t="n">
-        <v>82.09999999999999</v>
+        <v>119.82</v>
       </c>
       <c r="K68" t="n">
-        <v>-228.68</v>
+        <v>-376.89</v>
       </c>
       <c r="L68" t="n">
-        <v>242.97</v>
+        <v>395.48</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>08:43:40</t>
+          <t>08:50:54</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>4.77</v>
+        <v>4.25</v>
       </c>
       <c r="F69" t="n">
-        <v>10.83</v>
+        <v>10.61</v>
       </c>
       <c r="G69" t="n">
-        <v>228</v>
+        <v>222.9</v>
       </c>
       <c r="H69" t="n">
-        <v>91.7</v>
+        <v>97.8</v>
       </c>
       <c r="I69" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J69" t="n">
-        <v>-387.95</v>
+        <v>240.95</v>
       </c>
       <c r="K69" t="n">
-        <v>255.7</v>
+        <v>-261.85</v>
       </c>
       <c r="L69" t="n">
-        <v>464.63</v>
+        <v>355.84</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>08:46:08</t>
+          <t>08:52:01</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="F70" t="n">
-        <v>11.23</v>
+        <v>10.14</v>
       </c>
       <c r="G70" t="n">
-        <v>225.3</v>
+        <v>223</v>
       </c>
       <c r="H70" t="n">
-        <v>97.40000000000001</v>
+        <v>98.7</v>
       </c>
       <c r="I70" t="n">
         <v>20</v>
       </c>
       <c r="J70" t="n">
-        <v>266.95</v>
+        <v>-300.79</v>
       </c>
       <c r="K70" t="n">
-        <v>101.29</v>
+        <v>-346.36</v>
       </c>
       <c r="L70" t="n">
-        <v>285.52</v>
+        <v>458.74</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>08:51:42</t>
+          <t>08:57:24</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>3.97</v>
+        <v>4.24</v>
       </c>
       <c r="F71" t="n">
-        <v>10.26</v>
+        <v>11.38</v>
       </c>
       <c r="G71" t="n">
-        <v>221.3</v>
+        <v>217.1</v>
       </c>
       <c r="H71" t="n">
-        <v>97.40000000000001</v>
+        <v>90.7</v>
       </c>
       <c r="I71" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>-102.66</v>
+        <v>-536.49</v>
       </c>
       <c r="K71" t="n">
-        <v>-236.86</v>
+        <v>555.74</v>
       </c>
       <c r="L71" t="n">
-        <v>258.15</v>
+        <v>772.4400000000001</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>08:53:35</t>
+          <t>08:58:23</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>4.96</v>
+        <v>4.24</v>
       </c>
       <c r="F72" t="n">
-        <v>10.75</v>
+        <v>11.03</v>
       </c>
       <c r="G72" t="n">
-        <v>225</v>
+        <v>229.3</v>
       </c>
       <c r="H72" t="n">
-        <v>92.90000000000001</v>
+        <v>97.2</v>
       </c>
       <c r="I72" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>128.13</v>
+        <v>-299.1</v>
       </c>
       <c r="K72" t="n">
-        <v>-100.62</v>
+        <v>632.71</v>
       </c>
       <c r="L72" t="n">
-        <v>162.91</v>
+        <v>699.85</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>08:54:52</t>
+          <t>09:00:39</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>4.14</v>
+        <v>4.11</v>
       </c>
       <c r="F73" t="n">
-        <v>11.06</v>
+        <v>11.36</v>
       </c>
       <c r="G73" t="n">
-        <v>228.3</v>
+        <v>222.2</v>
       </c>
       <c r="H73" t="n">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="I73" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J73" t="n">
-        <v>188.53</v>
+        <v>-46.54</v>
       </c>
       <c r="K73" t="n">
-        <v>590.51</v>
+        <v>-539.17</v>
       </c>
       <c r="L73" t="n">
-        <v>619.88</v>
+        <v>541.17</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>09:06:32</t>
+          <t>09:11:44</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>4.55</v>
+        <v>4.71</v>
       </c>
       <c r="F74" t="n">
-        <v>10.44</v>
+        <v>11.2</v>
       </c>
       <c r="G74" t="n">
-        <v>231.2</v>
+        <v>218.2</v>
       </c>
       <c r="H74" t="n">
-        <v>98.2</v>
+        <v>99.2</v>
       </c>
       <c r="I74" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>125.95</v>
+        <v>-148.86</v>
       </c>
       <c r="K74" t="n">
-        <v>17.6</v>
+        <v>89.44</v>
       </c>
       <c r="L74" t="n">
-        <v>127.18</v>
+        <v>173.66</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09:07:52</t>
+          <t>09:14:04</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>3.59</v>
+        <v>4.58</v>
       </c>
       <c r="F75" t="n">
-        <v>10.31</v>
+        <v>10.56</v>
       </c>
       <c r="G75" t="n">
-        <v>228</v>
+        <v>232.9</v>
       </c>
       <c r="H75" t="n">
-        <v>98.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="I75" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J75" t="n">
-        <v>86.28</v>
+        <v>-262.14</v>
       </c>
       <c r="K75" t="n">
-        <v>-91.01000000000001</v>
+        <v>43.8</v>
       </c>
       <c r="L75" t="n">
-        <v>125.4</v>
+        <v>265.77</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09:09:27</t>
+          <t>09:15:38</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>4.29</v>
+        <v>4.65</v>
       </c>
       <c r="F76" t="n">
-        <v>10.66</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="G76" t="n">
-        <v>225.6</v>
+        <v>239.1</v>
       </c>
       <c r="H76" t="n">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="I76" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>-32.37</v>
+        <v>44.8</v>
       </c>
       <c r="K76" t="n">
-        <v>55.42</v>
+        <v>107.92</v>
       </c>
       <c r="L76" t="n">
-        <v>64.18000000000001</v>
+        <v>116.85</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09:12:41</t>
+          <t>09:18:51</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>4.5</v>
+        <v>4.12</v>
       </c>
       <c r="F77" t="n">
-        <v>11.24</v>
+        <v>11.39</v>
       </c>
       <c r="G77" t="n">
-        <v>234.7</v>
+        <v>210.4</v>
       </c>
       <c r="H77" t="n">
-        <v>97.90000000000001</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="I77" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>82.88</v>
+        <v>6.67</v>
       </c>
       <c r="K77" t="n">
-        <v>-354.35</v>
+        <v>41.34</v>
       </c>
       <c r="L77" t="n">
-        <v>363.91</v>
+        <v>41.87</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09:14:32</t>
+          <t>09:20:54</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>4.5</v>
+        <v>4.97</v>
       </c>
       <c r="F78" t="n">
-        <v>10.33</v>
+        <v>10.89</v>
       </c>
       <c r="G78" t="n">
-        <v>222.7</v>
+        <v>231.6</v>
       </c>
       <c r="H78" t="n">
-        <v>87.5</v>
+        <v>92.3</v>
       </c>
       <c r="I78" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>-58.14</v>
+        <v>243.9</v>
       </c>
       <c r="K78" t="n">
-        <v>7.45</v>
+        <v>60.22</v>
       </c>
       <c r="L78" t="n">
-        <v>58.61</v>
+        <v>251.23</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09:15:14</t>
+          <t>09:22:28</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>4.34</v>
+        <v>4.09</v>
       </c>
       <c r="F79" t="n">
-        <v>11.03</v>
+        <v>10.95</v>
       </c>
       <c r="G79" t="n">
-        <v>232.5</v>
+        <v>227.9</v>
       </c>
       <c r="H79" t="n">
-        <v>93.2</v>
+        <v>95.8</v>
       </c>
       <c r="I79" t="n">
         <v>19</v>
       </c>
       <c r="J79" t="n">
-        <v>229.25</v>
+        <v>18.59</v>
       </c>
       <c r="K79" t="n">
-        <v>-112.98</v>
+        <v>-80.88</v>
       </c>
       <c r="L79" t="n">
-        <v>255.58</v>
+        <v>82.98999999999999</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>09:19:42</t>
+          <t>09:27:16</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>4.67</v>
+        <v>4.49</v>
       </c>
       <c r="F80" t="n">
-        <v>10.81</v>
+        <v>10.72</v>
       </c>
       <c r="G80" t="n">
-        <v>218.9</v>
+        <v>222.2</v>
       </c>
       <c r="H80" t="n">
-        <v>94</v>
+        <v>98.7</v>
       </c>
       <c r="I80" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>159.34</v>
+        <v>233.01</v>
       </c>
       <c r="K80" t="n">
-        <v>-43.55</v>
+        <v>24.14</v>
       </c>
       <c r="L80" t="n">
-        <v>165.19</v>
+        <v>234.26</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>09:21:00</t>
+          <t>09:28:35</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>4.47</v>
+        <v>4.8</v>
       </c>
       <c r="F81" t="n">
-        <v>10.68</v>
+        <v>11.35</v>
       </c>
       <c r="G81" t="n">
-        <v>240.1</v>
+        <v>230</v>
       </c>
       <c r="H81" t="n">
-        <v>97.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="I81" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J81" t="n">
-        <v>339.74</v>
+        <v>-179.15</v>
       </c>
       <c r="K81" t="n">
-        <v>290.16</v>
+        <v>342.76</v>
       </c>
       <c r="L81" t="n">
-        <v>446.79</v>
+        <v>386.76</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>09:21:56</t>
+          <t>09:30:38</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>4.41</v>
+        <v>3.79</v>
       </c>
       <c r="F82" t="n">
-        <v>10.89</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="G82" t="n">
-        <v>217</v>
+        <v>229.3</v>
       </c>
       <c r="H82" t="n">
-        <v>94.7</v>
+        <v>100</v>
       </c>
       <c r="I82" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J82" t="n">
-        <v>-243.76</v>
+        <v>-57.19</v>
       </c>
       <c r="K82" t="n">
-        <v>246.02</v>
+        <v>127.92</v>
       </c>
       <c r="L82" t="n">
-        <v>346.34</v>
+        <v>140.13</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>09:26:37</t>
+          <t>09:35:49</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>4.44</v>
+        <v>4.61</v>
       </c>
       <c r="F83" t="n">
-        <v>10.8</v>
+        <v>10.92</v>
       </c>
       <c r="G83" t="n">
-        <v>221.7</v>
+        <v>223.8</v>
       </c>
       <c r="H83" t="n">
-        <v>93.09999999999999</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="I83" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>-223.77</v>
+        <v>211.27</v>
       </c>
       <c r="K83" t="n">
-        <v>1007.32</v>
+        <v>-394.75</v>
       </c>
       <c r="L83" t="n">
-        <v>1031.87</v>
+        <v>447.73</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>09:28:13</t>
+          <t>09:38:27</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>4.38</v>
+        <v>4.61</v>
       </c>
       <c r="F84" t="n">
-        <v>11.08</v>
+        <v>11.32</v>
       </c>
       <c r="G84" t="n">
-        <v>229.8</v>
+        <v>229.9</v>
       </c>
       <c r="H84" t="n">
-        <v>95.09999999999999</v>
+        <v>95</v>
       </c>
       <c r="I84" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J84" t="n">
-        <v>-88.84</v>
+        <v>329.13</v>
       </c>
       <c r="K84" t="n">
-        <v>-217.03</v>
+        <v>390.19</v>
       </c>
       <c r="L84" t="n">
-        <v>234.5</v>
+        <v>510.46</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>09:30:37</t>
+          <t>09:39:57</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>4.22</v>
+        <v>4.37</v>
       </c>
       <c r="F85" t="n">
-        <v>10.64</v>
+        <v>11.28</v>
       </c>
       <c r="G85" t="n">
-        <v>225.7</v>
+        <v>202.9</v>
       </c>
       <c r="H85" t="n">
-        <v>99.2</v>
+        <v>100</v>
       </c>
       <c r="I85" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J85" t="n">
-        <v>542.39</v>
+        <v>11.01</v>
       </c>
       <c r="K85" t="n">
-        <v>-455.13</v>
+        <v>-389.85</v>
       </c>
       <c r="L85" t="n">
-        <v>708.04</v>
+        <v>390</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>09:34:30</t>
+          <t>09:43:13</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>4.99</v>
+        <v>4.97</v>
       </c>
       <c r="F86" t="n">
-        <v>10.65</v>
+        <v>10.99</v>
       </c>
       <c r="G86" t="n">
-        <v>228.1</v>
+        <v>233.8</v>
       </c>
       <c r="H86" t="n">
-        <v>90.8</v>
+        <v>94</v>
       </c>
       <c r="I86" t="n">
         <v>20</v>
       </c>
       <c r="J86" t="n">
-        <v>-173.63</v>
+        <v>-622.6</v>
       </c>
       <c r="K86" t="n">
-        <v>-407.85</v>
+        <v>-665.61</v>
       </c>
       <c r="L86" t="n">
-        <v>443.27</v>
+        <v>911.41</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>09:35:50</t>
+          <t>09:45:41</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>4.69</v>
+        <v>4.9</v>
       </c>
       <c r="F87" t="n">
-        <v>10.98</v>
+        <v>10.57</v>
       </c>
       <c r="G87" t="n">
-        <v>223.5</v>
+        <v>209.2</v>
       </c>
       <c r="H87" t="n">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="I87" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J87" t="n">
-        <v>-23.84</v>
+        <v>465.03</v>
       </c>
       <c r="K87" t="n">
-        <v>-96.16</v>
+        <v>-904.36</v>
       </c>
       <c r="L87" t="n">
-        <v>99.06999999999999</v>
+        <v>1016.92</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>09:37:50</t>
+          <t>09:47:01</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>4.14</v>
+        <v>4.82</v>
       </c>
       <c r="F88" t="n">
-        <v>10.72</v>
+        <v>10.9</v>
       </c>
       <c r="G88" t="n">
-        <v>239.1</v>
+        <v>224.9</v>
       </c>
       <c r="H88" t="n">
-        <v>89.5</v>
+        <v>89.3</v>
       </c>
       <c r="I88" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J88" t="n">
-        <v>160.92</v>
+        <v>-1248.11</v>
       </c>
       <c r="K88" t="n">
-        <v>-91.06999999999999</v>
+        <v>90.73</v>
       </c>
       <c r="L88" t="n">
-        <v>184.9</v>
+        <v>1251.4</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-08-26.xlsx
+++ b/output/2025-08-26.xlsx
@@ -640,13 +640,13 @@
         <v>18</v>
       </c>
       <c r="J14" t="n">
-        <v>137.98</v>
+        <v>182.08</v>
       </c>
       <c r="K14" t="n">
-        <v>51.96</v>
+        <v>68.56</v>
       </c>
       <c r="L14" t="n">
-        <v>147.44</v>
+        <v>194.56</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>17</v>
       </c>
       <c r="J15" t="n">
-        <v>-334.2</v>
+        <v>-309.21</v>
       </c>
       <c r="K15" t="n">
-        <v>-240.52</v>
+        <v>-222.54</v>
       </c>
       <c r="L15" t="n">
-        <v>411.75</v>
+        <v>380.97</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>19</v>
       </c>
       <c r="J16" t="n">
-        <v>-61.18</v>
+        <v>-69.67</v>
       </c>
       <c r="K16" t="n">
-        <v>172.16</v>
+        <v>196.04</v>
       </c>
       <c r="L16" t="n">
-        <v>182.71</v>
+        <v>208.05</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>303.51</v>
+        <v>366.23</v>
       </c>
       <c r="K17" t="n">
-        <v>10.82</v>
+        <v>13.06</v>
       </c>
       <c r="L17" t="n">
-        <v>303.71</v>
+        <v>366.46</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>293.95</v>
+        <v>364.75</v>
       </c>
       <c r="K18" t="n">
-        <v>223.87</v>
+        <v>277.79</v>
       </c>
       <c r="L18" t="n">
-        <v>369.49</v>
+        <v>458.49</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>19</v>
       </c>
       <c r="J19" t="n">
-        <v>-25.89</v>
+        <v>-34.57</v>
       </c>
       <c r="K19" t="n">
-        <v>212.81</v>
+        <v>284.11</v>
       </c>
       <c r="L19" t="n">
-        <v>214.38</v>
+        <v>286.2</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>16</v>
       </c>
       <c r="J20" t="n">
-        <v>-296.7</v>
+        <v>-428.65</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.27</v>
+        <v>-0.39</v>
       </c>
       <c r="L20" t="n">
-        <v>296.7</v>
+        <v>428.65</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>-39.64</v>
+        <v>-50.55</v>
       </c>
       <c r="K21" t="n">
-        <v>293.01</v>
+        <v>373.62</v>
       </c>
       <c r="L21" t="n">
-        <v>295.68</v>
+        <v>377.02</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>19</v>
       </c>
       <c r="J22" t="n">
-        <v>-162.06</v>
+        <v>-200.8</v>
       </c>
       <c r="K22" t="n">
-        <v>288.51</v>
+        <v>357.48</v>
       </c>
       <c r="L22" t="n">
-        <v>330.91</v>
+        <v>410.02</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>510.16</v>
+        <v>786.4299999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.26</v>
+        <v>-1.94</v>
       </c>
       <c r="L23" t="n">
-        <v>510.16</v>
+        <v>786.4299999999999</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>470.22</v>
+        <v>662.65</v>
       </c>
       <c r="K24" t="n">
-        <v>-239.5</v>
+        <v>-337.51</v>
       </c>
       <c r="L24" t="n">
-        <v>527.7</v>
+        <v>743.65</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>18</v>
       </c>
       <c r="J25" t="n">
-        <v>-59.46</v>
+        <v>-148.24</v>
       </c>
       <c r="K25" t="n">
-        <v>-149.91</v>
+        <v>-373.73</v>
       </c>
       <c r="L25" t="n">
-        <v>161.27</v>
+        <v>402.06</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>-777.29</v>
+        <v>-916.92</v>
       </c>
       <c r="K26" t="n">
-        <v>505.13</v>
+        <v>595.86</v>
       </c>
       <c r="L26" t="n">
-        <v>927</v>
+        <v>1093.52</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>17</v>
       </c>
       <c r="J27" t="n">
-        <v>203.46</v>
+        <v>369.09</v>
       </c>
       <c r="K27" t="n">
-        <v>325.74</v>
+        <v>590.92</v>
       </c>
       <c r="L27" t="n">
-        <v>384.06</v>
+        <v>696.72</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>-1253.46</v>
+        <v>-1614.82</v>
       </c>
       <c r="K28" t="n">
-        <v>-294.23</v>
+        <v>-379.06</v>
       </c>
       <c r="L28" t="n">
-        <v>1287.53</v>
+        <v>1658.71</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>18</v>
       </c>
       <c r="J29" t="n">
-        <v>-79.15000000000001</v>
+        <v>-82.25</v>
       </c>
       <c r="K29" t="n">
-        <v>-290.47</v>
+        <v>-301.86</v>
       </c>
       <c r="L29" t="n">
-        <v>301.06</v>
+        <v>312.86</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>16</v>
       </c>
       <c r="J30" t="n">
-        <v>250.63</v>
+        <v>301.51</v>
       </c>
       <c r="K30" t="n">
-        <v>17.13</v>
+        <v>20.61</v>
       </c>
       <c r="L30" t="n">
-        <v>251.22</v>
+        <v>302.21</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>20</v>
       </c>
       <c r="J31" t="n">
-        <v>-236.76</v>
+        <v>-241.5</v>
       </c>
       <c r="K31" t="n">
-        <v>-170.67</v>
+        <v>-174.08</v>
       </c>
       <c r="L31" t="n">
-        <v>291.86</v>
+        <v>297.71</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>16</v>
       </c>
       <c r="J32" t="n">
-        <v>63.84</v>
+        <v>74.27</v>
       </c>
       <c r="K32" t="n">
-        <v>317.04</v>
+        <v>368.81</v>
       </c>
       <c r="L32" t="n">
-        <v>323.4</v>
+        <v>376.22</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>18</v>
       </c>
       <c r="J33" t="n">
-        <v>112.27</v>
+        <v>183.36</v>
       </c>
       <c r="K33" t="n">
-        <v>65.98</v>
+        <v>107.77</v>
       </c>
       <c r="L33" t="n">
-        <v>130.22</v>
+        <v>212.69</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>25.2</v>
+        <v>27.71</v>
       </c>
       <c r="K34" t="n">
-        <v>-265.44</v>
+        <v>-291.83</v>
       </c>
       <c r="L34" t="n">
-        <v>266.64</v>
+        <v>293.14</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>19</v>
       </c>
       <c r="J35" t="n">
-        <v>-284.4</v>
+        <v>-356.78</v>
       </c>
       <c r="K35" t="n">
-        <v>137.22</v>
+        <v>172.13</v>
       </c>
       <c r="L35" t="n">
-        <v>315.77</v>
+        <v>396.13</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>20</v>
       </c>
       <c r="J36" t="n">
-        <v>-18.24</v>
+        <v>-34.82</v>
       </c>
       <c r="K36" t="n">
-        <v>168.91</v>
+        <v>322.49</v>
       </c>
       <c r="L36" t="n">
-        <v>169.89</v>
+        <v>324.36</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>17</v>
       </c>
       <c r="J37" t="n">
-        <v>-513.55</v>
+        <v>-669.74</v>
       </c>
       <c r="K37" t="n">
-        <v>19.77</v>
+        <v>25.78</v>
       </c>
       <c r="L37" t="n">
-        <v>513.9299999999999</v>
+        <v>670.23</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>17</v>
       </c>
       <c r="J38" t="n">
-        <v>522.09</v>
+        <v>759.77</v>
       </c>
       <c r="K38" t="n">
-        <v>440.93</v>
+        <v>641.65</v>
       </c>
       <c r="L38" t="n">
-        <v>683.37</v>
+        <v>994.46</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>18</v>
       </c>
       <c r="J39" t="n">
-        <v>-480.68</v>
+        <v>-637.66</v>
       </c>
       <c r="K39" t="n">
-        <v>247.96</v>
+        <v>328.94</v>
       </c>
       <c r="L39" t="n">
-        <v>540.86</v>
+        <v>717.5</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>18</v>
       </c>
       <c r="J40" t="n">
-        <v>439.89</v>
+        <v>583.8099999999999</v>
       </c>
       <c r="K40" t="n">
-        <v>361.26</v>
+        <v>479.46</v>
       </c>
       <c r="L40" t="n">
-        <v>569.22</v>
+        <v>755.46</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>18</v>
       </c>
       <c r="J41" t="n">
-        <v>-88.56</v>
+        <v>-144.11</v>
       </c>
       <c r="K41" t="n">
-        <v>-508.97</v>
+        <v>-828.15</v>
       </c>
       <c r="L41" t="n">
-        <v>516.62</v>
+        <v>840.6</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>20</v>
       </c>
       <c r="J42" t="n">
-        <v>-164.53</v>
+        <v>-253.29</v>
       </c>
       <c r="K42" t="n">
-        <v>381.25</v>
+        <v>586.92</v>
       </c>
       <c r="L42" t="n">
-        <v>415.24</v>
+        <v>639.24</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>16</v>
       </c>
       <c r="J43" t="n">
-        <v>-203.77</v>
+        <v>-523.21</v>
       </c>
       <c r="K43" t="n">
-        <v>69.77</v>
+        <v>179.14</v>
       </c>
       <c r="L43" t="n">
-        <v>215.38</v>
+        <v>553.03</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>149.24</v>
+        <v>204.52</v>
       </c>
       <c r="K44" t="n">
-        <v>-145.43</v>
+        <v>-199.31</v>
       </c>
       <c r="L44" t="n">
-        <v>208.38</v>
+        <v>285.58</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>166.7</v>
+        <v>247.64</v>
       </c>
       <c r="K45" t="n">
-        <v>-29.1</v>
+        <v>-43.23</v>
       </c>
       <c r="L45" t="n">
-        <v>169.22</v>
+        <v>251.39</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>17</v>
       </c>
       <c r="J46" t="n">
-        <v>225.42</v>
+        <v>241.83</v>
       </c>
       <c r="K46" t="n">
-        <v>209.05</v>
+        <v>224.27</v>
       </c>
       <c r="L46" t="n">
-        <v>307.44</v>
+        <v>329.81</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-160.23</v>
+        <v>-252.38</v>
       </c>
       <c r="K47" t="n">
-        <v>23.72</v>
+        <v>37.35</v>
       </c>
       <c r="L47" t="n">
-        <v>161.97</v>
+        <v>255.13</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>-168.1</v>
+        <v>-206.21</v>
       </c>
       <c r="K48" t="n">
-        <v>-325.11</v>
+        <v>-398.83</v>
       </c>
       <c r="L48" t="n">
-        <v>366</v>
+        <v>448.99</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>19</v>
       </c>
       <c r="J49" t="n">
-        <v>-45.2</v>
+        <v>-63.17</v>
       </c>
       <c r="K49" t="n">
-        <v>-181.79</v>
+        <v>-254.04</v>
       </c>
       <c r="L49" t="n">
-        <v>187.33</v>
+        <v>261.77</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>20</v>
       </c>
       <c r="J50" t="n">
-        <v>280.83</v>
+        <v>376.01</v>
       </c>
       <c r="K50" t="n">
-        <v>-76.25</v>
+        <v>-102.09</v>
       </c>
       <c r="L50" t="n">
-        <v>291</v>
+        <v>389.62</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>18</v>
       </c>
       <c r="J51" t="n">
-        <v>-341.32</v>
+        <v>-476.02</v>
       </c>
       <c r="K51" t="n">
-        <v>-96.7</v>
+        <v>-134.86</v>
       </c>
       <c r="L51" t="n">
-        <v>354.76</v>
+        <v>494.76</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>17</v>
       </c>
       <c r="J52" t="n">
-        <v>-99.03</v>
+        <v>-169.6</v>
       </c>
       <c r="K52" t="n">
-        <v>194.93</v>
+        <v>333.84</v>
       </c>
       <c r="L52" t="n">
-        <v>218.65</v>
+        <v>374.45</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>844.95</v>
+        <v>1096.18</v>
       </c>
       <c r="K53" t="n">
-        <v>143.56</v>
+        <v>186.24</v>
       </c>
       <c r="L53" t="n">
-        <v>857.0599999999999</v>
+        <v>1111.89</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>16</v>
       </c>
       <c r="J54" t="n">
-        <v>-669.11</v>
+        <v>-951.0599999999999</v>
       </c>
       <c r="K54" t="n">
-        <v>-365.47</v>
+        <v>-519.47</v>
       </c>
       <c r="L54" t="n">
-        <v>762.42</v>
+        <v>1083.69</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>-377.59</v>
+        <v>-544.39</v>
       </c>
       <c r="K55" t="n">
-        <v>-420.64</v>
+        <v>-606.46</v>
       </c>
       <c r="L55" t="n">
-        <v>565.25</v>
+        <v>814.96</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>16</v>
       </c>
       <c r="J56" t="n">
-        <v>-506.8</v>
+        <v>-847.22</v>
       </c>
       <c r="K56" t="n">
-        <v>-531.27</v>
+        <v>-888.12</v>
       </c>
       <c r="L56" t="n">
-        <v>734.23</v>
+        <v>1227.41</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>-521.71</v>
+        <v>-689.7</v>
       </c>
       <c r="K57" t="n">
-        <v>-1030.84</v>
+        <v>-1362.78</v>
       </c>
       <c r="L57" t="n">
-        <v>1155.34</v>
+        <v>1527.37</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>285.36</v>
+        <v>573.67</v>
       </c>
       <c r="K58" t="n">
-        <v>-243.51</v>
+        <v>-489.53</v>
       </c>
       <c r="L58" t="n">
-        <v>375.14</v>
+        <v>754.15</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>16</v>
       </c>
       <c r="J59" t="n">
-        <v>-99.45999999999999</v>
+        <v>-166.96</v>
       </c>
       <c r="K59" t="n">
-        <v>-31.09</v>
+        <v>-52.19</v>
       </c>
       <c r="L59" t="n">
-        <v>104.2</v>
+        <v>174.93</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>20</v>
       </c>
       <c r="J60" t="n">
-        <v>-138.9</v>
+        <v>-193.44</v>
       </c>
       <c r="K60" t="n">
-        <v>-86.93000000000001</v>
+        <v>-121.07</v>
       </c>
       <c r="L60" t="n">
-        <v>163.86</v>
+        <v>228.21</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>20</v>
       </c>
       <c r="J61" t="n">
-        <v>-203.4</v>
+        <v>-241.1</v>
       </c>
       <c r="K61" t="n">
-        <v>80.69</v>
+        <v>95.64</v>
       </c>
       <c r="L61" t="n">
-        <v>218.82</v>
+        <v>259.38</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>17</v>
       </c>
       <c r="J62" t="n">
-        <v>-655.01</v>
+        <v>-693.16</v>
       </c>
       <c r="K62" t="n">
-        <v>-107.64</v>
+        <v>-113.9</v>
       </c>
       <c r="L62" t="n">
-        <v>663.8</v>
+        <v>702.45</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>-179.4</v>
+        <v>-231.2</v>
       </c>
       <c r="K63" t="n">
-        <v>-145.1</v>
+        <v>-187</v>
       </c>
       <c r="L63" t="n">
-        <v>230.73</v>
+        <v>297.36</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>168.37</v>
+        <v>254.19</v>
       </c>
       <c r="K64" t="n">
-        <v>-140.95</v>
+        <v>-212.81</v>
       </c>
       <c r="L64" t="n">
-        <v>219.58</v>
+        <v>331.52</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>20</v>
       </c>
       <c r="J65" t="n">
-        <v>72.38</v>
+        <v>122.94</v>
       </c>
       <c r="K65" t="n">
-        <v>-153.83</v>
+        <v>-261.31</v>
       </c>
       <c r="L65" t="n">
-        <v>170.01</v>
+        <v>288.79</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>-346.66</v>
+        <v>-522.5700000000001</v>
       </c>
       <c r="K66" t="n">
-        <v>95.33</v>
+        <v>143.7</v>
       </c>
       <c r="L66" t="n">
-        <v>359.53</v>
+        <v>541.97</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>16</v>
       </c>
       <c r="J67" t="n">
-        <v>-284.29</v>
+        <v>-423.55</v>
       </c>
       <c r="K67" t="n">
-        <v>-61.77</v>
+        <v>-92.03</v>
       </c>
       <c r="L67" t="n">
-        <v>290.93</v>
+        <v>433.43</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>18</v>
       </c>
       <c r="J68" t="n">
-        <v>119.82</v>
+        <v>203.42</v>
       </c>
       <c r="K68" t="n">
-        <v>-376.89</v>
+        <v>-639.87</v>
       </c>
       <c r="L68" t="n">
-        <v>395.48</v>
+        <v>671.4299999999999</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>16</v>
       </c>
       <c r="J69" t="n">
-        <v>240.95</v>
+        <v>422.05</v>
       </c>
       <c r="K69" t="n">
-        <v>-261.85</v>
+        <v>-458.65</v>
       </c>
       <c r="L69" t="n">
-        <v>355.84</v>
+        <v>623.29</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>20</v>
       </c>
       <c r="J70" t="n">
-        <v>-300.79</v>
+        <v>-452.08</v>
       </c>
       <c r="K70" t="n">
-        <v>-346.36</v>
+        <v>-520.5700000000001</v>
       </c>
       <c r="L70" t="n">
-        <v>458.74</v>
+        <v>689.47</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>-536.49</v>
+        <v>-798.78</v>
       </c>
       <c r="K71" t="n">
-        <v>555.74</v>
+        <v>827.4299999999999</v>
       </c>
       <c r="L71" t="n">
-        <v>772.4400000000001</v>
+        <v>1150.08</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>-299.1</v>
+        <v>-459.61</v>
       </c>
       <c r="K72" t="n">
-        <v>632.71</v>
+        <v>972.26</v>
       </c>
       <c r="L72" t="n">
-        <v>699.85</v>
+        <v>1075.42</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>18</v>
       </c>
       <c r="J73" t="n">
-        <v>-46.54</v>
+        <v>-73.64</v>
       </c>
       <c r="K73" t="n">
-        <v>-539.17</v>
+        <v>-853.16</v>
       </c>
       <c r="L73" t="n">
-        <v>541.17</v>
+        <v>856.33</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>-148.86</v>
+        <v>-233.01</v>
       </c>
       <c r="K74" t="n">
-        <v>89.44</v>
+        <v>140.01</v>
       </c>
       <c r="L74" t="n">
-        <v>173.66</v>
+        <v>271.84</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>18</v>
       </c>
       <c r="J75" t="n">
-        <v>-262.14</v>
+        <v>-325.77</v>
       </c>
       <c r="K75" t="n">
-        <v>43.8</v>
+        <v>54.43</v>
       </c>
       <c r="L75" t="n">
-        <v>265.77</v>
+        <v>330.29</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>44.8</v>
+        <v>84.39</v>
       </c>
       <c r="K76" t="n">
-        <v>107.92</v>
+        <v>203.28</v>
       </c>
       <c r="L76" t="n">
-        <v>116.85</v>
+        <v>220.1</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>6.67</v>
+        <v>25.32</v>
       </c>
       <c r="K77" t="n">
-        <v>41.34</v>
+        <v>156.93</v>
       </c>
       <c r="L77" t="n">
-        <v>41.87</v>
+        <v>158.96</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>243.9</v>
+        <v>333.33</v>
       </c>
       <c r="K78" t="n">
-        <v>60.22</v>
+        <v>82.3</v>
       </c>
       <c r="L78" t="n">
-        <v>251.23</v>
+        <v>343.34</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>19</v>
       </c>
       <c r="J79" t="n">
-        <v>18.59</v>
+        <v>39.53</v>
       </c>
       <c r="K79" t="n">
-        <v>-80.88</v>
+        <v>-172.03</v>
       </c>
       <c r="L79" t="n">
-        <v>82.98999999999999</v>
+        <v>176.52</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>233.01</v>
+        <v>417.85</v>
       </c>
       <c r="K80" t="n">
-        <v>24.14</v>
+        <v>43.29</v>
       </c>
       <c r="L80" t="n">
-        <v>234.26</v>
+        <v>420.09</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>18</v>
       </c>
       <c r="J81" t="n">
-        <v>-179.15</v>
+        <v>-258.25</v>
       </c>
       <c r="K81" t="n">
-        <v>342.76</v>
+        <v>494.09</v>
       </c>
       <c r="L81" t="n">
-        <v>386.76</v>
+        <v>557.51</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>20</v>
       </c>
       <c r="J82" t="n">
-        <v>-57.19</v>
+        <v>-106.74</v>
       </c>
       <c r="K82" t="n">
-        <v>127.92</v>
+        <v>238.75</v>
       </c>
       <c r="L82" t="n">
-        <v>140.13</v>
+        <v>261.52</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>211.27</v>
+        <v>323.33</v>
       </c>
       <c r="K83" t="n">
-        <v>-394.75</v>
+        <v>-604.13</v>
       </c>
       <c r="L83" t="n">
-        <v>447.73</v>
+        <v>685.21</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>20</v>
       </c>
       <c r="J84" t="n">
-        <v>329.13</v>
+        <v>480.26</v>
       </c>
       <c r="K84" t="n">
-        <v>390.19</v>
+        <v>569.35</v>
       </c>
       <c r="L84" t="n">
-        <v>510.46</v>
+        <v>744.85</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>19</v>
       </c>
       <c r="J85" t="n">
-        <v>11.01</v>
+        <v>17.71</v>
       </c>
       <c r="K85" t="n">
-        <v>-389.85</v>
+        <v>-627.15</v>
       </c>
       <c r="L85" t="n">
-        <v>390</v>
+        <v>627.4</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>20</v>
       </c>
       <c r="J86" t="n">
-        <v>-622.6</v>
+        <v>-888.15</v>
       </c>
       <c r="K86" t="n">
-        <v>-665.61</v>
+        <v>-949.51</v>
       </c>
       <c r="L86" t="n">
-        <v>911.41</v>
+        <v>1300.15</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>18</v>
       </c>
       <c r="J87" t="n">
-        <v>465.03</v>
+        <v>668.76</v>
       </c>
       <c r="K87" t="n">
-        <v>-904.36</v>
+        <v>-1300.57</v>
       </c>
       <c r="L87" t="n">
-        <v>1016.92</v>
+        <v>1462.44</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>17</v>
       </c>
       <c r="J88" t="n">
-        <v>-1248.11</v>
+        <v>-1721.89</v>
       </c>
       <c r="K88" t="n">
-        <v>90.73</v>
+        <v>125.18</v>
       </c>
       <c r="L88" t="n">
-        <v>1251.4</v>
+        <v>1726.43</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-08-26.xlsx
+++ b/output/2025-08-26.xlsx
@@ -640,13 +640,13 @@
         <v>18</v>
       </c>
       <c r="J14" t="n">
-        <v>182.08</v>
+        <v>118.63</v>
       </c>
       <c r="K14" t="n">
-        <v>68.56</v>
+        <v>44.67</v>
       </c>
       <c r="L14" t="n">
-        <v>194.56</v>
+        <v>126.77</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>17</v>
       </c>
       <c r="J15" t="n">
-        <v>-309.21</v>
+        <v>-201.84</v>
       </c>
       <c r="K15" t="n">
-        <v>-222.54</v>
+        <v>-145.27</v>
       </c>
       <c r="L15" t="n">
-        <v>380.97</v>
+        <v>248.68</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>19</v>
       </c>
       <c r="J16" t="n">
-        <v>-69.67</v>
+        <v>-47.13</v>
       </c>
       <c r="K16" t="n">
-        <v>196.04</v>
+        <v>132.61</v>
       </c>
       <c r="L16" t="n">
-        <v>208.05</v>
+        <v>140.74</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>366.23</v>
+        <v>214.46</v>
       </c>
       <c r="K17" t="n">
-        <v>13.06</v>
+        <v>7.65</v>
       </c>
       <c r="L17" t="n">
-        <v>366.46</v>
+        <v>214.59</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>364.75</v>
+        <v>208.2</v>
       </c>
       <c r="K18" t="n">
-        <v>277.79</v>
+        <v>158.57</v>
       </c>
       <c r="L18" t="n">
-        <v>458.49</v>
+        <v>261.71</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>19</v>
       </c>
       <c r="J19" t="n">
-        <v>-34.57</v>
+        <v>-21.43</v>
       </c>
       <c r="K19" t="n">
-        <v>284.11</v>
+        <v>176.15</v>
       </c>
       <c r="L19" t="n">
-        <v>286.2</v>
+        <v>177.45</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>16</v>
       </c>
       <c r="J20" t="n">
-        <v>-428.65</v>
+        <v>-220.42</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.39</v>
+        <v>-0.2</v>
       </c>
       <c r="L20" t="n">
-        <v>428.65</v>
+        <v>220.42</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>-50.55</v>
+        <v>-28.94</v>
       </c>
       <c r="K21" t="n">
-        <v>373.62</v>
+        <v>213.89</v>
       </c>
       <c r="L21" t="n">
-        <v>377.02</v>
+        <v>215.84</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>19</v>
       </c>
       <c r="J22" t="n">
-        <v>-200.8</v>
+        <v>-112.49</v>
       </c>
       <c r="K22" t="n">
-        <v>357.48</v>
+        <v>200.27</v>
       </c>
       <c r="L22" t="n">
-        <v>410.02</v>
+        <v>229.7</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>786.4299999999999</v>
+        <v>349.12</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.94</v>
+        <v>-0.86</v>
       </c>
       <c r="L23" t="n">
-        <v>786.4299999999999</v>
+        <v>349.12</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>662.65</v>
+        <v>300.8</v>
       </c>
       <c r="K24" t="n">
-        <v>-337.51</v>
+        <v>-153.21</v>
       </c>
       <c r="L24" t="n">
-        <v>743.65</v>
+        <v>337.56</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>18</v>
       </c>
       <c r="J25" t="n">
-        <v>-148.24</v>
+        <v>-69.29000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>-373.73</v>
+        <v>-174.7</v>
       </c>
       <c r="L25" t="n">
-        <v>402.06</v>
+        <v>187.94</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>-916.92</v>
+        <v>-429.33</v>
       </c>
       <c r="K26" t="n">
-        <v>595.86</v>
+        <v>279</v>
       </c>
       <c r="L26" t="n">
-        <v>1093.52</v>
+        <v>512.02</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>17</v>
       </c>
       <c r="J27" t="n">
-        <v>369.09</v>
+        <v>157.41</v>
       </c>
       <c r="K27" t="n">
-        <v>590.92</v>
+        <v>252.02</v>
       </c>
       <c r="L27" t="n">
-        <v>696.72</v>
+        <v>297.14</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>-1614.82</v>
+        <v>-666.9299999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>-379.06</v>
+        <v>-156.55</v>
       </c>
       <c r="L28" t="n">
-        <v>1658.71</v>
+        <v>685.0599999999999</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>18</v>
       </c>
       <c r="J29" t="n">
-        <v>-82.25</v>
+        <v>-53.62</v>
       </c>
       <c r="K29" t="n">
-        <v>-301.86</v>
+        <v>-196.8</v>
       </c>
       <c r="L29" t="n">
-        <v>312.86</v>
+        <v>203.97</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>16</v>
       </c>
       <c r="J30" t="n">
-        <v>301.51</v>
+        <v>184.49</v>
       </c>
       <c r="K30" t="n">
-        <v>20.61</v>
+        <v>12.61</v>
       </c>
       <c r="L30" t="n">
-        <v>302.21</v>
+        <v>184.92</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>20</v>
       </c>
       <c r="J31" t="n">
-        <v>-241.5</v>
+        <v>-164.73</v>
       </c>
       <c r="K31" t="n">
-        <v>-174.08</v>
+        <v>-118.74</v>
       </c>
       <c r="L31" t="n">
-        <v>297.71</v>
+        <v>203.06</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>16</v>
       </c>
       <c r="J32" t="n">
-        <v>74.27</v>
+        <v>43.74</v>
       </c>
       <c r="K32" t="n">
-        <v>368.81</v>
+        <v>217.21</v>
       </c>
       <c r="L32" t="n">
-        <v>376.22</v>
+        <v>221.58</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>18</v>
       </c>
       <c r="J33" t="n">
-        <v>183.36</v>
+        <v>112.05</v>
       </c>
       <c r="K33" t="n">
-        <v>107.77</v>
+        <v>65.86</v>
       </c>
       <c r="L33" t="n">
-        <v>212.69</v>
+        <v>129.97</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>27.71</v>
+        <v>17.8</v>
       </c>
       <c r="K34" t="n">
-        <v>-291.83</v>
+        <v>-187.52</v>
       </c>
       <c r="L34" t="n">
-        <v>293.14</v>
+        <v>188.36</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>19</v>
       </c>
       <c r="J35" t="n">
-        <v>-356.78</v>
+        <v>-200.09</v>
       </c>
       <c r="K35" t="n">
-        <v>172.13</v>
+        <v>96.54000000000001</v>
       </c>
       <c r="L35" t="n">
-        <v>396.13</v>
+        <v>222.16</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>20</v>
       </c>
       <c r="J36" t="n">
-        <v>-34.82</v>
+        <v>-19.12</v>
       </c>
       <c r="K36" t="n">
-        <v>322.49</v>
+        <v>177.07</v>
       </c>
       <c r="L36" t="n">
-        <v>324.36</v>
+        <v>178.1</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>17</v>
       </c>
       <c r="J37" t="n">
-        <v>-669.74</v>
+        <v>-341.69</v>
       </c>
       <c r="K37" t="n">
-        <v>25.78</v>
+        <v>13.15</v>
       </c>
       <c r="L37" t="n">
-        <v>670.23</v>
+        <v>341.95</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>17</v>
       </c>
       <c r="J38" t="n">
-        <v>759.77</v>
+        <v>340.96</v>
       </c>
       <c r="K38" t="n">
-        <v>641.65</v>
+        <v>287.95</v>
       </c>
       <c r="L38" t="n">
-        <v>994.46</v>
+        <v>446.29</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>18</v>
       </c>
       <c r="J39" t="n">
-        <v>-637.66</v>
+        <v>-304.12</v>
       </c>
       <c r="K39" t="n">
-        <v>328.94</v>
+        <v>156.88</v>
       </c>
       <c r="L39" t="n">
-        <v>717.5</v>
+        <v>342.2</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>18</v>
       </c>
       <c r="J40" t="n">
-        <v>583.8099999999999</v>
+        <v>277.08</v>
       </c>
       <c r="K40" t="n">
-        <v>479.46</v>
+        <v>227.56</v>
       </c>
       <c r="L40" t="n">
-        <v>755.46</v>
+        <v>358.55</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>18</v>
       </c>
       <c r="J41" t="n">
-        <v>-144.11</v>
+        <v>-62.26</v>
       </c>
       <c r="K41" t="n">
-        <v>-828.15</v>
+        <v>-357.79</v>
       </c>
       <c r="L41" t="n">
-        <v>840.6</v>
+        <v>363.16</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>20</v>
       </c>
       <c r="J42" t="n">
-        <v>-253.29</v>
+        <v>-118.15</v>
       </c>
       <c r="K42" t="n">
-        <v>586.92</v>
+        <v>273.78</v>
       </c>
       <c r="L42" t="n">
-        <v>639.24</v>
+        <v>298.19</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>16</v>
       </c>
       <c r="J43" t="n">
-        <v>-523.21</v>
+        <v>-217.47</v>
       </c>
       <c r="K43" t="n">
-        <v>179.14</v>
+        <v>74.45999999999999</v>
       </c>
       <c r="L43" t="n">
-        <v>553.03</v>
+        <v>229.87</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>204.52</v>
+        <v>123.18</v>
       </c>
       <c r="K44" t="n">
-        <v>-199.31</v>
+        <v>-120.04</v>
       </c>
       <c r="L44" t="n">
-        <v>285.58</v>
+        <v>171.99</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>247.64</v>
+        <v>149.33</v>
       </c>
       <c r="K45" t="n">
-        <v>-43.23</v>
+        <v>-26.07</v>
       </c>
       <c r="L45" t="n">
-        <v>251.39</v>
+        <v>151.59</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>17</v>
       </c>
       <c r="J46" t="n">
-        <v>241.83</v>
+        <v>153.28</v>
       </c>
       <c r="K46" t="n">
-        <v>224.27</v>
+        <v>142.15</v>
       </c>
       <c r="L46" t="n">
-        <v>329.81</v>
+        <v>209.05</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-252.38</v>
+        <v>-158.68</v>
       </c>
       <c r="K47" t="n">
-        <v>37.35</v>
+        <v>23.49</v>
       </c>
       <c r="L47" t="n">
-        <v>255.13</v>
+        <v>160.41</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>-206.21</v>
+        <v>-118.35</v>
       </c>
       <c r="K48" t="n">
-        <v>-398.83</v>
+        <v>-228.9</v>
       </c>
       <c r="L48" t="n">
-        <v>448.99</v>
+        <v>257.68</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>19</v>
       </c>
       <c r="J49" t="n">
-        <v>-63.17</v>
+        <v>-39.35</v>
       </c>
       <c r="K49" t="n">
-        <v>-254.04</v>
+        <v>-158.26</v>
       </c>
       <c r="L49" t="n">
-        <v>261.77</v>
+        <v>163.08</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>20</v>
       </c>
       <c r="J50" t="n">
-        <v>376.01</v>
+        <v>213.01</v>
       </c>
       <c r="K50" t="n">
-        <v>-102.09</v>
+        <v>-57.84</v>
       </c>
       <c r="L50" t="n">
-        <v>389.62</v>
+        <v>220.72</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>18</v>
       </c>
       <c r="J51" t="n">
-        <v>-476.02</v>
+        <v>-251.42</v>
       </c>
       <c r="K51" t="n">
-        <v>-134.86</v>
+        <v>-71.23</v>
       </c>
       <c r="L51" t="n">
-        <v>494.76</v>
+        <v>261.32</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>17</v>
       </c>
       <c r="J52" t="n">
-        <v>-169.6</v>
+        <v>-87.98999999999999</v>
       </c>
       <c r="K52" t="n">
-        <v>333.84</v>
+        <v>173.19</v>
       </c>
       <c r="L52" t="n">
-        <v>374.45</v>
+        <v>194.26</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>1096.18</v>
+        <v>490.08</v>
       </c>
       <c r="K53" t="n">
-        <v>186.24</v>
+        <v>83.27</v>
       </c>
       <c r="L53" t="n">
-        <v>1111.89</v>
+        <v>497.1</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>16</v>
       </c>
       <c r="J54" t="n">
-        <v>-951.0599999999999</v>
+        <v>-418.64</v>
       </c>
       <c r="K54" t="n">
-        <v>-519.47</v>
+        <v>-228.66</v>
       </c>
       <c r="L54" t="n">
-        <v>1083.69</v>
+        <v>477.02</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>-544.39</v>
+        <v>-244.31</v>
       </c>
       <c r="K55" t="n">
-        <v>-606.46</v>
+        <v>-272.16</v>
       </c>
       <c r="L55" t="n">
-        <v>814.96</v>
+        <v>365.73</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>16</v>
       </c>
       <c r="J56" t="n">
-        <v>-847.22</v>
+        <v>-336.78</v>
       </c>
       <c r="K56" t="n">
-        <v>-888.12</v>
+        <v>-353.04</v>
       </c>
       <c r="L56" t="n">
-        <v>1227.41</v>
+        <v>487.92</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>-689.7</v>
+        <v>-284.85</v>
       </c>
       <c r="K57" t="n">
-        <v>-1362.78</v>
+        <v>-562.84</v>
       </c>
       <c r="L57" t="n">
-        <v>1527.37</v>
+        <v>630.8099999999999</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>573.67</v>
+        <v>236.1</v>
       </c>
       <c r="K58" t="n">
-        <v>-489.53</v>
+        <v>-201.47</v>
       </c>
       <c r="L58" t="n">
-        <v>754.15</v>
+        <v>310.38</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>16</v>
       </c>
       <c r="J59" t="n">
-        <v>-166.96</v>
+        <v>-102.86</v>
       </c>
       <c r="K59" t="n">
-        <v>-52.19</v>
+        <v>-32.15</v>
       </c>
       <c r="L59" t="n">
-        <v>174.93</v>
+        <v>107.76</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>20</v>
       </c>
       <c r="J60" t="n">
-        <v>-193.44</v>
+        <v>-127.47</v>
       </c>
       <c r="K60" t="n">
-        <v>-121.07</v>
+        <v>-79.78</v>
       </c>
       <c r="L60" t="n">
-        <v>228.21</v>
+        <v>150.37</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>20</v>
       </c>
       <c r="J61" t="n">
-        <v>-241.1</v>
+        <v>-161.08</v>
       </c>
       <c r="K61" t="n">
-        <v>95.64</v>
+        <v>63.9</v>
       </c>
       <c r="L61" t="n">
-        <v>259.38</v>
+        <v>173.29</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>17</v>
       </c>
       <c r="J62" t="n">
-        <v>-693.16</v>
+        <v>-405.48</v>
       </c>
       <c r="K62" t="n">
-        <v>-113.9</v>
+        <v>-66.63</v>
       </c>
       <c r="L62" t="n">
-        <v>702.45</v>
+        <v>410.91</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>-231.2</v>
+        <v>-136.25</v>
       </c>
       <c r="K63" t="n">
-        <v>-187</v>
+        <v>-110.2</v>
       </c>
       <c r="L63" t="n">
-        <v>297.36</v>
+        <v>175.23</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>254.19</v>
+        <v>144.74</v>
       </c>
       <c r="K64" t="n">
-        <v>-212.81</v>
+        <v>-121.18</v>
       </c>
       <c r="L64" t="n">
-        <v>331.52</v>
+        <v>188.77</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>20</v>
       </c>
       <c r="J65" t="n">
-        <v>122.94</v>
+        <v>69.28</v>
       </c>
       <c r="K65" t="n">
-        <v>-261.31</v>
+        <v>-147.26</v>
       </c>
       <c r="L65" t="n">
-        <v>288.79</v>
+        <v>162.74</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>-522.5700000000001</v>
+        <v>-259.87</v>
       </c>
       <c r="K66" t="n">
-        <v>143.7</v>
+        <v>71.45999999999999</v>
       </c>
       <c r="L66" t="n">
-        <v>541.97</v>
+        <v>269.51</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>16</v>
       </c>
       <c r="J67" t="n">
-        <v>-423.55</v>
+        <v>-216.08</v>
       </c>
       <c r="K67" t="n">
-        <v>-92.03</v>
+        <v>-46.95</v>
       </c>
       <c r="L67" t="n">
-        <v>433.43</v>
+        <v>221.12</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>18</v>
       </c>
       <c r="J68" t="n">
-        <v>203.42</v>
+        <v>93.77</v>
       </c>
       <c r="K68" t="n">
-        <v>-639.87</v>
+        <v>-294.96</v>
       </c>
       <c r="L68" t="n">
-        <v>671.4299999999999</v>
+        <v>309.5</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>16</v>
       </c>
       <c r="J69" t="n">
-        <v>422.05</v>
+        <v>187.72</v>
       </c>
       <c r="K69" t="n">
-        <v>-458.65</v>
+        <v>-204</v>
       </c>
       <c r="L69" t="n">
-        <v>623.29</v>
+        <v>277.22</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>20</v>
       </c>
       <c r="J70" t="n">
-        <v>-452.08</v>
+        <v>-219.86</v>
       </c>
       <c r="K70" t="n">
-        <v>-520.5700000000001</v>
+        <v>-253.16</v>
       </c>
       <c r="L70" t="n">
-        <v>689.47</v>
+        <v>335.3</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>-798.78</v>
+        <v>-328.44</v>
       </c>
       <c r="K71" t="n">
-        <v>827.4299999999999</v>
+        <v>340.22</v>
       </c>
       <c r="L71" t="n">
-        <v>1150.08</v>
+        <v>472.89</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>-459.61</v>
+        <v>-188.98</v>
       </c>
       <c r="K72" t="n">
-        <v>972.26</v>
+        <v>399.77</v>
       </c>
       <c r="L72" t="n">
-        <v>1075.42</v>
+        <v>442.19</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>18</v>
       </c>
       <c r="J73" t="n">
-        <v>-73.64</v>
+        <v>-31.86</v>
       </c>
       <c r="K73" t="n">
-        <v>-853.16</v>
+        <v>-369.18</v>
       </c>
       <c r="L73" t="n">
-        <v>856.33</v>
+        <v>370.55</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>-233.01</v>
+        <v>-138.16</v>
       </c>
       <c r="K74" t="n">
-        <v>140.01</v>
+        <v>83.01000000000001</v>
       </c>
       <c r="L74" t="n">
-        <v>271.84</v>
+        <v>161.18</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>18</v>
       </c>
       <c r="J75" t="n">
-        <v>-325.77</v>
+        <v>-203.44</v>
       </c>
       <c r="K75" t="n">
-        <v>54.43</v>
+        <v>33.99</v>
       </c>
       <c r="L75" t="n">
-        <v>330.29</v>
+        <v>206.26</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>84.39</v>
+        <v>50.15</v>
       </c>
       <c r="K76" t="n">
-        <v>203.28</v>
+        <v>120.8</v>
       </c>
       <c r="L76" t="n">
-        <v>220.1</v>
+        <v>130.79</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>25.32</v>
+        <v>14.63</v>
       </c>
       <c r="K77" t="n">
-        <v>156.93</v>
+        <v>90.68000000000001</v>
       </c>
       <c r="L77" t="n">
-        <v>158.96</v>
+        <v>91.84999999999999</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>333.33</v>
+        <v>208.17</v>
       </c>
       <c r="K78" t="n">
-        <v>82.3</v>
+        <v>51.4</v>
       </c>
       <c r="L78" t="n">
-        <v>343.34</v>
+        <v>214.42</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>19</v>
       </c>
       <c r="J79" t="n">
-        <v>39.53</v>
+        <v>24.59</v>
       </c>
       <c r="K79" t="n">
-        <v>-172.03</v>
+        <v>-107.01</v>
       </c>
       <c r="L79" t="n">
-        <v>176.52</v>
+        <v>109.8</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>417.85</v>
+        <v>208.73</v>
       </c>
       <c r="K80" t="n">
-        <v>43.29</v>
+        <v>21.62</v>
       </c>
       <c r="L80" t="n">
-        <v>420.09</v>
+        <v>209.85</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>18</v>
       </c>
       <c r="J81" t="n">
-        <v>-258.25</v>
+        <v>-133.82</v>
       </c>
       <c r="K81" t="n">
-        <v>494.09</v>
+        <v>256.03</v>
       </c>
       <c r="L81" t="n">
-        <v>557.51</v>
+        <v>288.9</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>20</v>
       </c>
       <c r="J82" t="n">
-        <v>-106.74</v>
+        <v>-60.5</v>
       </c>
       <c r="K82" t="n">
-        <v>238.75</v>
+        <v>135.31</v>
       </c>
       <c r="L82" t="n">
-        <v>261.52</v>
+        <v>148.22</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>323.33</v>
+        <v>157.22</v>
       </c>
       <c r="K83" t="n">
-        <v>-604.13</v>
+        <v>-293.76</v>
       </c>
       <c r="L83" t="n">
-        <v>685.21</v>
+        <v>333.18</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>20</v>
       </c>
       <c r="J84" t="n">
-        <v>480.26</v>
+        <v>233.52</v>
       </c>
       <c r="K84" t="n">
-        <v>569.35</v>
+        <v>276.84</v>
       </c>
       <c r="L84" t="n">
-        <v>744.85</v>
+        <v>362.18</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>19</v>
       </c>
       <c r="J85" t="n">
-        <v>17.71</v>
+        <v>8.43</v>
       </c>
       <c r="K85" t="n">
-        <v>-627.15</v>
+        <v>-298.51</v>
       </c>
       <c r="L85" t="n">
-        <v>627.4</v>
+        <v>298.63</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>20</v>
       </c>
       <c r="J86" t="n">
-        <v>-888.15</v>
+        <v>-389.06</v>
       </c>
       <c r="K86" t="n">
-        <v>-949.51</v>
+        <v>-415.94</v>
       </c>
       <c r="L86" t="n">
-        <v>1300.15</v>
+        <v>569.54</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>18</v>
       </c>
       <c r="J87" t="n">
-        <v>668.76</v>
+        <v>278.63</v>
       </c>
       <c r="K87" t="n">
-        <v>-1300.57</v>
+        <v>-541.85</v>
       </c>
       <c r="L87" t="n">
-        <v>1462.44</v>
+        <v>609.29</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>17</v>
       </c>
       <c r="J88" t="n">
-        <v>-1721.89</v>
+        <v>-701.96</v>
       </c>
       <c r="K88" t="n">
-        <v>125.18</v>
+        <v>51.03</v>
       </c>
       <c r="L88" t="n">
-        <v>1726.43</v>
+        <v>703.8099999999999</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-08-26.xlsx
+++ b/output/2025-08-26.xlsx
@@ -640,13 +640,13 @@
         <v>18</v>
       </c>
       <c r="J14" t="n">
-        <v>118.63</v>
+        <v>128.79</v>
       </c>
       <c r="K14" t="n">
-        <v>44.67</v>
+        <v>48.5</v>
       </c>
       <c r="L14" t="n">
-        <v>126.77</v>
+        <v>137.62</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>17</v>
       </c>
       <c r="J15" t="n">
-        <v>-201.84</v>
+        <v>-218.81</v>
       </c>
       <c r="K15" t="n">
-        <v>-145.27</v>
+        <v>-157.48</v>
       </c>
       <c r="L15" t="n">
-        <v>248.68</v>
+        <v>269.59</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>19</v>
       </c>
       <c r="J16" t="n">
-        <v>-47.13</v>
+        <v>-51.14</v>
       </c>
       <c r="K16" t="n">
-        <v>132.61</v>
+        <v>143.9</v>
       </c>
       <c r="L16" t="n">
-        <v>140.74</v>
+        <v>152.71</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>214.46</v>
+        <v>240.66</v>
       </c>
       <c r="K17" t="n">
-        <v>7.65</v>
+        <v>8.58</v>
       </c>
       <c r="L17" t="n">
-        <v>214.59</v>
+        <v>240.81</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>208.2</v>
+        <v>233.34</v>
       </c>
       <c r="K18" t="n">
-        <v>158.57</v>
+        <v>177.71</v>
       </c>
       <c r="L18" t="n">
-        <v>261.71</v>
+        <v>293.3</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>19</v>
       </c>
       <c r="J19" t="n">
-        <v>-21.43</v>
+        <v>-23.96</v>
       </c>
       <c r="K19" t="n">
-        <v>176.15</v>
+        <v>196.94</v>
       </c>
       <c r="L19" t="n">
-        <v>177.45</v>
+        <v>198.39</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>16</v>
       </c>
       <c r="J20" t="n">
-        <v>-220.42</v>
+        <v>-257.45</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.2</v>
+        <v>-0.23</v>
       </c>
       <c r="L20" t="n">
-        <v>220.42</v>
+        <v>257.45</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>-28.94</v>
+        <v>-33.1</v>
       </c>
       <c r="K21" t="n">
-        <v>213.89</v>
+        <v>244.66</v>
       </c>
       <c r="L21" t="n">
-        <v>215.84</v>
+        <v>246.89</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>19</v>
       </c>
       <c r="J22" t="n">
-        <v>-112.49</v>
+        <v>-129.62</v>
       </c>
       <c r="K22" t="n">
-        <v>200.27</v>
+        <v>230.77</v>
       </c>
       <c r="L22" t="n">
-        <v>229.7</v>
+        <v>264.68</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>349.12</v>
+        <v>419.62</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.86</v>
+        <v>-1.04</v>
       </c>
       <c r="L23" t="n">
-        <v>349.12</v>
+        <v>419.62</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>300.8</v>
+        <v>359.75</v>
       </c>
       <c r="K24" t="n">
-        <v>-153.21</v>
+        <v>-183.23</v>
       </c>
       <c r="L24" t="n">
-        <v>337.56</v>
+        <v>403.72</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>18</v>
       </c>
       <c r="J25" t="n">
-        <v>-69.29000000000001</v>
+        <v>-82.31</v>
       </c>
       <c r="K25" t="n">
-        <v>-174.7</v>
+        <v>-207.52</v>
       </c>
       <c r="L25" t="n">
-        <v>187.94</v>
+        <v>223.25</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>-429.33</v>
+        <v>-509.35</v>
       </c>
       <c r="K26" t="n">
-        <v>279</v>
+        <v>331</v>
       </c>
       <c r="L26" t="n">
-        <v>512.02</v>
+        <v>607.45</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>17</v>
       </c>
       <c r="J27" t="n">
-        <v>157.41</v>
+        <v>192.42</v>
       </c>
       <c r="K27" t="n">
-        <v>252.02</v>
+        <v>308.07</v>
       </c>
       <c r="L27" t="n">
-        <v>297.14</v>
+        <v>363.23</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>-666.9299999999999</v>
+        <v>-822.4299999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>-156.55</v>
+        <v>-193.05</v>
       </c>
       <c r="L28" t="n">
-        <v>685.0599999999999</v>
+        <v>844.79</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>18</v>
       </c>
       <c r="J29" t="n">
-        <v>-53.62</v>
+        <v>-58.69</v>
       </c>
       <c r="K29" t="n">
-        <v>-196.8</v>
+        <v>-215.39</v>
       </c>
       <c r="L29" t="n">
-        <v>203.97</v>
+        <v>223.24</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>16</v>
       </c>
       <c r="J30" t="n">
-        <v>184.49</v>
+        <v>202.68</v>
       </c>
       <c r="K30" t="n">
-        <v>12.61</v>
+        <v>13.86</v>
       </c>
       <c r="L30" t="n">
-        <v>184.92</v>
+        <v>203.15</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>20</v>
       </c>
       <c r="J31" t="n">
-        <v>-164.73</v>
+        <v>-178.09</v>
       </c>
       <c r="K31" t="n">
-        <v>-118.74</v>
+        <v>-128.37</v>
       </c>
       <c r="L31" t="n">
-        <v>203.06</v>
+        <v>219.53</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>16</v>
       </c>
       <c r="J32" t="n">
-        <v>43.74</v>
+        <v>49.65</v>
       </c>
       <c r="K32" t="n">
-        <v>217.21</v>
+        <v>246.59</v>
       </c>
       <c r="L32" t="n">
-        <v>221.58</v>
+        <v>251.54</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>18</v>
       </c>
       <c r="J33" t="n">
-        <v>112.05</v>
+        <v>125.2</v>
       </c>
       <c r="K33" t="n">
-        <v>65.86</v>
+        <v>73.59</v>
       </c>
       <c r="L33" t="n">
-        <v>129.97</v>
+        <v>145.23</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>17.8</v>
+        <v>19.86</v>
       </c>
       <c r="K34" t="n">
-        <v>-187.52</v>
+        <v>-209.16</v>
       </c>
       <c r="L34" t="n">
-        <v>188.36</v>
+        <v>210.1</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>19</v>
       </c>
       <c r="J35" t="n">
-        <v>-200.09</v>
+        <v>-230.59</v>
       </c>
       <c r="K35" t="n">
-        <v>96.54000000000001</v>
+        <v>111.25</v>
       </c>
       <c r="L35" t="n">
-        <v>222.16</v>
+        <v>256.02</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>20</v>
       </c>
       <c r="J36" t="n">
-        <v>-19.12</v>
+        <v>-21.94</v>
       </c>
       <c r="K36" t="n">
-        <v>177.07</v>
+        <v>203.21</v>
       </c>
       <c r="L36" t="n">
-        <v>178.1</v>
+        <v>204.39</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>17</v>
       </c>
       <c r="J37" t="n">
-        <v>-341.69</v>
+        <v>-399.82</v>
       </c>
       <c r="K37" t="n">
-        <v>13.15</v>
+        <v>15.39</v>
       </c>
       <c r="L37" t="n">
-        <v>341.95</v>
+        <v>400.11</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>17</v>
       </c>
       <c r="J38" t="n">
-        <v>340.96</v>
+        <v>411.27</v>
       </c>
       <c r="K38" t="n">
-        <v>287.95</v>
+        <v>347.34</v>
       </c>
       <c r="L38" t="n">
-        <v>446.29</v>
+        <v>538.3200000000001</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>18</v>
       </c>
       <c r="J39" t="n">
-        <v>-304.12</v>
+        <v>-359.32</v>
       </c>
       <c r="K39" t="n">
-        <v>156.88</v>
+        <v>185.36</v>
       </c>
       <c r="L39" t="n">
-        <v>342.2</v>
+        <v>404.31</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>18</v>
       </c>
       <c r="J40" t="n">
-        <v>277.08</v>
+        <v>328.18</v>
       </c>
       <c r="K40" t="n">
-        <v>227.56</v>
+        <v>269.52</v>
       </c>
       <c r="L40" t="n">
-        <v>358.55</v>
+        <v>424.66</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>18</v>
       </c>
       <c r="J41" t="n">
-        <v>-62.26</v>
+        <v>-76.12</v>
       </c>
       <c r="K41" t="n">
-        <v>-357.79</v>
+        <v>-437.42</v>
       </c>
       <c r="L41" t="n">
-        <v>363.16</v>
+        <v>444</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>20</v>
       </c>
       <c r="J42" t="n">
-        <v>-118.15</v>
+        <v>-141.16</v>
       </c>
       <c r="K42" t="n">
-        <v>273.78</v>
+        <v>327.11</v>
       </c>
       <c r="L42" t="n">
-        <v>298.19</v>
+        <v>356.27</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>16</v>
       </c>
       <c r="J43" t="n">
-        <v>-217.47</v>
+        <v>-262.84</v>
       </c>
       <c r="K43" t="n">
-        <v>74.45999999999999</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="L43" t="n">
-        <v>229.87</v>
+        <v>277.82</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>123.18</v>
+        <v>137.34</v>
       </c>
       <c r="K44" t="n">
-        <v>-120.04</v>
+        <v>-133.84</v>
       </c>
       <c r="L44" t="n">
-        <v>171.99</v>
+        <v>191.77</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>149.33</v>
+        <v>166.14</v>
       </c>
       <c r="K45" t="n">
-        <v>-26.07</v>
+        <v>-29</v>
       </c>
       <c r="L45" t="n">
-        <v>151.59</v>
+        <v>168.65</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>17</v>
       </c>
       <c r="J46" t="n">
-        <v>153.28</v>
+        <v>167.17</v>
       </c>
       <c r="K46" t="n">
-        <v>142.15</v>
+        <v>155.03</v>
       </c>
       <c r="L46" t="n">
-        <v>209.05</v>
+        <v>227.99</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-158.68</v>
+        <v>-175.18</v>
       </c>
       <c r="K47" t="n">
-        <v>23.49</v>
+        <v>25.93</v>
       </c>
       <c r="L47" t="n">
-        <v>160.41</v>
+        <v>177.08</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>-118.35</v>
+        <v>-133.62</v>
       </c>
       <c r="K48" t="n">
-        <v>-228.9</v>
+        <v>-258.43</v>
       </c>
       <c r="L48" t="n">
-        <v>257.68</v>
+        <v>290.93</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>19</v>
       </c>
       <c r="J49" t="n">
-        <v>-39.35</v>
+        <v>-43.33</v>
       </c>
       <c r="K49" t="n">
-        <v>-158.26</v>
+        <v>-174.28</v>
       </c>
       <c r="L49" t="n">
-        <v>163.08</v>
+        <v>179.59</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>20</v>
       </c>
       <c r="J50" t="n">
-        <v>213.01</v>
+        <v>244.97</v>
       </c>
       <c r="K50" t="n">
-        <v>-57.84</v>
+        <v>-66.51000000000001</v>
       </c>
       <c r="L50" t="n">
-        <v>220.72</v>
+        <v>253.84</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>18</v>
       </c>
       <c r="J51" t="n">
-        <v>-251.42</v>
+        <v>-287.75</v>
       </c>
       <c r="K51" t="n">
-        <v>-71.23</v>
+        <v>-81.52</v>
       </c>
       <c r="L51" t="n">
-        <v>261.32</v>
+        <v>299.08</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>17</v>
       </c>
       <c r="J52" t="n">
-        <v>-87.98999999999999</v>
+        <v>-101.8</v>
       </c>
       <c r="K52" t="n">
-        <v>173.19</v>
+        <v>200.38</v>
       </c>
       <c r="L52" t="n">
-        <v>194.26</v>
+        <v>224.76</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>490.08</v>
+        <v>591.38</v>
       </c>
       <c r="K53" t="n">
-        <v>83.27</v>
+        <v>100.48</v>
       </c>
       <c r="L53" t="n">
-        <v>497.1</v>
+        <v>599.86</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>16</v>
       </c>
       <c r="J54" t="n">
-        <v>-418.64</v>
+        <v>-496.35</v>
       </c>
       <c r="K54" t="n">
-        <v>-228.66</v>
+        <v>-271.11</v>
       </c>
       <c r="L54" t="n">
-        <v>477.02</v>
+        <v>565.5599999999999</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>-244.31</v>
+        <v>-294.61</v>
       </c>
       <c r="K55" t="n">
-        <v>-272.16</v>
+        <v>-328.2</v>
       </c>
       <c r="L55" t="n">
-        <v>365.73</v>
+        <v>441.04</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>16</v>
       </c>
       <c r="J56" t="n">
-        <v>-336.78</v>
+        <v>-418.61</v>
       </c>
       <c r="K56" t="n">
-        <v>-353.04</v>
+        <v>-438.82</v>
       </c>
       <c r="L56" t="n">
-        <v>487.92</v>
+        <v>606.47</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>-284.85</v>
+        <v>-349.72</v>
       </c>
       <c r="K57" t="n">
-        <v>-562.84</v>
+        <v>-691</v>
       </c>
       <c r="L57" t="n">
-        <v>630.8099999999999</v>
+        <v>774.46</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>236.1</v>
+        <v>288.5</v>
       </c>
       <c r="K58" t="n">
-        <v>-201.47</v>
+        <v>-246.19</v>
       </c>
       <c r="L58" t="n">
-        <v>310.38</v>
+        <v>379.27</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>16</v>
       </c>
       <c r="J59" t="n">
-        <v>-102.86</v>
+        <v>-112.65</v>
       </c>
       <c r="K59" t="n">
-        <v>-32.15</v>
+        <v>-35.22</v>
       </c>
       <c r="L59" t="n">
-        <v>107.76</v>
+        <v>118.03</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>20</v>
       </c>
       <c r="J60" t="n">
-        <v>-127.47</v>
+        <v>-138.48</v>
       </c>
       <c r="K60" t="n">
-        <v>-79.78</v>
+        <v>-86.67</v>
       </c>
       <c r="L60" t="n">
-        <v>150.37</v>
+        <v>163.36</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>20</v>
       </c>
       <c r="J61" t="n">
-        <v>-161.08</v>
+        <v>-176.7</v>
       </c>
       <c r="K61" t="n">
-        <v>63.9</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="L61" t="n">
-        <v>173.29</v>
+        <v>190.1</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>17</v>
       </c>
       <c r="J62" t="n">
-        <v>-405.48</v>
+        <v>-448.44</v>
       </c>
       <c r="K62" t="n">
-        <v>-66.63</v>
+        <v>-73.69</v>
       </c>
       <c r="L62" t="n">
-        <v>410.91</v>
+        <v>454.46</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>-136.25</v>
+        <v>-154.68</v>
       </c>
       <c r="K63" t="n">
-        <v>-110.2</v>
+        <v>-125.11</v>
       </c>
       <c r="L63" t="n">
-        <v>175.23</v>
+        <v>198.95</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>144.74</v>
+        <v>161.45</v>
       </c>
       <c r="K64" t="n">
-        <v>-121.18</v>
+        <v>-135.16</v>
       </c>
       <c r="L64" t="n">
-        <v>188.77</v>
+        <v>210.56</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>20</v>
       </c>
       <c r="J65" t="n">
-        <v>69.28</v>
+        <v>79.79000000000001</v>
       </c>
       <c r="K65" t="n">
-        <v>-147.26</v>
+        <v>-169.59</v>
       </c>
       <c r="L65" t="n">
-        <v>162.74</v>
+        <v>187.43</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>-259.87</v>
+        <v>-304.11</v>
       </c>
       <c r="K66" t="n">
-        <v>71.45999999999999</v>
+        <v>83.63</v>
       </c>
       <c r="L66" t="n">
-        <v>269.51</v>
+        <v>315.4</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>16</v>
       </c>
       <c r="J67" t="n">
-        <v>-216.08</v>
+        <v>-253.36</v>
       </c>
       <c r="K67" t="n">
-        <v>-46.95</v>
+        <v>-55.05</v>
       </c>
       <c r="L67" t="n">
-        <v>221.12</v>
+        <v>259.27</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>18</v>
       </c>
       <c r="J68" t="n">
-        <v>93.77</v>
+        <v>111.08</v>
       </c>
       <c r="K68" t="n">
-        <v>-294.96</v>
+        <v>-349.4</v>
       </c>
       <c r="L68" t="n">
-        <v>309.5</v>
+        <v>366.64</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>16</v>
       </c>
       <c r="J69" t="n">
-        <v>187.72</v>
+        <v>226.08</v>
       </c>
       <c r="K69" t="n">
-        <v>-204</v>
+        <v>-245.69</v>
       </c>
       <c r="L69" t="n">
-        <v>277.22</v>
+        <v>333.88</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>20</v>
       </c>
       <c r="J70" t="n">
-        <v>-219.86</v>
+        <v>-261.37</v>
       </c>
       <c r="K70" t="n">
-        <v>-253.16</v>
+        <v>-300.96</v>
       </c>
       <c r="L70" t="n">
-        <v>335.3</v>
+        <v>398.61</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>-328.44</v>
+        <v>-401.06</v>
       </c>
       <c r="K71" t="n">
-        <v>340.22</v>
+        <v>415.45</v>
       </c>
       <c r="L71" t="n">
-        <v>472.89</v>
+        <v>577.45</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>-188.98</v>
+        <v>-232.74</v>
       </c>
       <c r="K72" t="n">
-        <v>399.77</v>
+        <v>492.34</v>
       </c>
       <c r="L72" t="n">
-        <v>442.19</v>
+        <v>544.58</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>18</v>
       </c>
       <c r="J73" t="n">
-        <v>-31.86</v>
+        <v>-38.98</v>
       </c>
       <c r="K73" t="n">
-        <v>-369.18</v>
+        <v>-451.68</v>
       </c>
       <c r="L73" t="n">
-        <v>370.55</v>
+        <v>453.36</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>-138.16</v>
+        <v>-155.09</v>
       </c>
       <c r="K74" t="n">
-        <v>83.01000000000001</v>
+        <v>93.19</v>
       </c>
       <c r="L74" t="n">
-        <v>161.18</v>
+        <v>180.94</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>18</v>
       </c>
       <c r="J75" t="n">
-        <v>-203.44</v>
+        <v>-226.4</v>
       </c>
       <c r="K75" t="n">
-        <v>33.99</v>
+        <v>37.83</v>
       </c>
       <c r="L75" t="n">
-        <v>206.26</v>
+        <v>229.54</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>50.15</v>
+        <v>55.76</v>
       </c>
       <c r="K76" t="n">
-        <v>120.8</v>
+        <v>134.32</v>
       </c>
       <c r="L76" t="n">
-        <v>130.79</v>
+        <v>145.43</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>14.63</v>
+        <v>16.48</v>
       </c>
       <c r="K77" t="n">
-        <v>90.68000000000001</v>
+        <v>102.09</v>
       </c>
       <c r="L77" t="n">
-        <v>91.84999999999999</v>
+        <v>103.42</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>208.17</v>
+        <v>229.11</v>
       </c>
       <c r="K78" t="n">
-        <v>51.4</v>
+        <v>56.57</v>
       </c>
       <c r="L78" t="n">
-        <v>214.42</v>
+        <v>235.99</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>19</v>
       </c>
       <c r="J79" t="n">
-        <v>24.59</v>
+        <v>27.36</v>
       </c>
       <c r="K79" t="n">
-        <v>-107.01</v>
+        <v>-119.05</v>
       </c>
       <c r="L79" t="n">
-        <v>109.8</v>
+        <v>122.15</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>208.73</v>
+        <v>244.78</v>
       </c>
       <c r="K80" t="n">
-        <v>21.62</v>
+        <v>25.36</v>
       </c>
       <c r="L80" t="n">
-        <v>209.85</v>
+        <v>246.09</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>18</v>
       </c>
       <c r="J81" t="n">
-        <v>-133.82</v>
+        <v>-155.95</v>
       </c>
       <c r="K81" t="n">
-        <v>256.03</v>
+        <v>298.38</v>
       </c>
       <c r="L81" t="n">
-        <v>288.9</v>
+        <v>336.68</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>20</v>
       </c>
       <c r="J82" t="n">
-        <v>-60.5</v>
+        <v>-69.91</v>
       </c>
       <c r="K82" t="n">
-        <v>135.31</v>
+        <v>156.37</v>
       </c>
       <c r="L82" t="n">
-        <v>148.22</v>
+        <v>171.28</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>157.22</v>
+        <v>186.72</v>
       </c>
       <c r="K83" t="n">
-        <v>-293.76</v>
+        <v>-348.88</v>
       </c>
       <c r="L83" t="n">
-        <v>333.18</v>
+        <v>395.7</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>20</v>
       </c>
       <c r="J84" t="n">
-        <v>233.52</v>
+        <v>276.29</v>
       </c>
       <c r="K84" t="n">
-        <v>276.84</v>
+        <v>327.55</v>
       </c>
       <c r="L84" t="n">
-        <v>362.18</v>
+        <v>428.51</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>19</v>
       </c>
       <c r="J85" t="n">
-        <v>8.43</v>
+        <v>10.07</v>
       </c>
       <c r="K85" t="n">
-        <v>-298.51</v>
+        <v>-356.5</v>
       </c>
       <c r="L85" t="n">
-        <v>298.63</v>
+        <v>356.64</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>20</v>
       </c>
       <c r="J86" t="n">
-        <v>-389.06</v>
+        <v>-471.58</v>
       </c>
       <c r="K86" t="n">
-        <v>-415.94</v>
+        <v>-504.16</v>
       </c>
       <c r="L86" t="n">
-        <v>569.54</v>
+        <v>690.34</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>18</v>
       </c>
       <c r="J87" t="n">
-        <v>278.63</v>
+        <v>342.78</v>
       </c>
       <c r="K87" t="n">
-        <v>-541.85</v>
+        <v>-666.62</v>
       </c>
       <c r="L87" t="n">
-        <v>609.29</v>
+        <v>749.59</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>17</v>
       </c>
       <c r="J88" t="n">
-        <v>-701.96</v>
+        <v>-857.96</v>
       </c>
       <c r="K88" t="n">
-        <v>51.03</v>
+        <v>62.37</v>
       </c>
       <c r="L88" t="n">
-        <v>703.8099999999999</v>
+        <v>860.23</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-08-26.xlsx
+++ b/output/2025-08-26.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>3.67</v>
+        <v>3.06</v>
       </c>
       <c r="F14" t="n">
-        <v>10.89</v>
+        <v>10.92</v>
       </c>
       <c r="G14" t="n">
-        <v>235.7</v>
+        <v>231.2</v>
       </c>
       <c r="H14" t="n">
-        <v>93.59999999999999</v>
+        <v>90.5</v>
       </c>
       <c r="I14" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>128.79</v>
+        <v>63.28</v>
       </c>
       <c r="K14" t="n">
-        <v>48.5</v>
+        <v>-46.04</v>
       </c>
       <c r="L14" t="n">
-        <v>137.62</v>
+        <v>78.26000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06:09:07</t>
+          <t>06:08:52</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3.29</v>
+        <v>3.78</v>
       </c>
       <c r="F15" t="n">
-        <v>11.42</v>
+        <v>10.84</v>
       </c>
       <c r="G15" t="n">
-        <v>225.4</v>
+        <v>223.6</v>
       </c>
       <c r="H15" t="n">
-        <v>97</v>
+        <v>99.8</v>
       </c>
       <c r="I15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>-218.81</v>
+        <v>-113.35</v>
       </c>
       <c r="K15" t="n">
-        <v>-157.48</v>
+        <v>-8.630000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>269.59</v>
+        <v>113.68</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06:10:42</t>
+          <t>06:11:27</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>3.48</v>
+        <v>3.36</v>
       </c>
       <c r="F16" t="n">
-        <v>9.68</v>
+        <v>10.63</v>
       </c>
       <c r="G16" t="n">
-        <v>231.5</v>
+        <v>234.6</v>
       </c>
       <c r="H16" t="n">
-        <v>100</v>
+        <v>90.7</v>
       </c>
       <c r="I16" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J16" t="n">
-        <v>-51.14</v>
+        <v>-88.79000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>143.9</v>
+        <v>-20.49</v>
       </c>
       <c r="L16" t="n">
-        <v>152.71</v>
+        <v>91.12</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06:14:38</t>
+          <t>06:14:49</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,28 +751,28 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>3.86</v>
+        <v>3.45</v>
       </c>
       <c r="F17" t="n">
-        <v>10.63</v>
+        <v>11.16</v>
       </c>
       <c r="G17" t="n">
-        <v>214.5</v>
+        <v>234.1</v>
       </c>
       <c r="H17" t="n">
-        <v>91.8</v>
+        <v>100</v>
       </c>
       <c r="I17" t="n">
         <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>240.66</v>
+        <v>109.47</v>
       </c>
       <c r="K17" t="n">
-        <v>8.58</v>
+        <v>122.87</v>
       </c>
       <c r="L17" t="n">
-        <v>240.81</v>
+        <v>164.56</v>
       </c>
     </row>
     <row r="18">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>4.4</v>
+        <v>3.81</v>
       </c>
       <c r="F18" t="n">
-        <v>10.6</v>
+        <v>10.73</v>
       </c>
       <c r="G18" t="n">
-        <v>229.5</v>
+        <v>228.6</v>
       </c>
       <c r="H18" t="n">
-        <v>93.8</v>
+        <v>92.8</v>
       </c>
       <c r="I18" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J18" t="n">
-        <v>233.34</v>
+        <v>-101.81</v>
       </c>
       <c r="K18" t="n">
-        <v>177.71</v>
+        <v>0.14</v>
       </c>
       <c r="L18" t="n">
-        <v>293.3</v>
+        <v>101.81</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06:17:17</t>
+          <t>06:18:31</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>4.16</v>
+        <v>4.09</v>
       </c>
       <c r="F19" t="n">
-        <v>10.45</v>
+        <v>10.43</v>
       </c>
       <c r="G19" t="n">
-        <v>230.4</v>
+        <v>213.1</v>
       </c>
       <c r="H19" t="n">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="I19" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>-23.96</v>
+        <v>58.27</v>
       </c>
       <c r="K19" t="n">
-        <v>196.94</v>
+        <v>-71.98999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>198.39</v>
+        <v>92.62</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06:22:53</t>
+          <t>06:23:48</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>3.75</v>
+        <v>3.36</v>
       </c>
       <c r="F20" t="n">
-        <v>10.23</v>
+        <v>11.02</v>
       </c>
       <c r="G20" t="n">
-        <v>222</v>
+        <v>218.1</v>
       </c>
       <c r="H20" t="n">
-        <v>95.59999999999999</v>
+        <v>94.5</v>
       </c>
       <c r="I20" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J20" t="n">
-        <v>-257.45</v>
+        <v>-45.02</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.23</v>
+        <v>-72.51000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>257.45</v>
+        <v>85.34</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06:25:15</t>
+          <t>06:26:04</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>3.58</v>
+        <v>3.86</v>
       </c>
       <c r="F21" t="n">
-        <v>10.37</v>
+        <v>10.48</v>
       </c>
       <c r="G21" t="n">
-        <v>232.7</v>
+        <v>219.9</v>
       </c>
       <c r="H21" t="n">
-        <v>92.2</v>
+        <v>96.7</v>
       </c>
       <c r="I21" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J21" t="n">
-        <v>-33.1</v>
+        <v>-112.98</v>
       </c>
       <c r="K21" t="n">
-        <v>244.66</v>
+        <v>-127.22</v>
       </c>
       <c r="L21" t="n">
-        <v>246.89</v>
+        <v>170.14</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06:27:12</t>
+          <t>06:27:33</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>3.48</v>
+        <v>3.7</v>
       </c>
       <c r="F22" t="n">
-        <v>10.67</v>
+        <v>10.81</v>
       </c>
       <c r="G22" t="n">
-        <v>225.9</v>
+        <v>221.7</v>
       </c>
       <c r="H22" t="n">
-        <v>94.5</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J22" t="n">
-        <v>-129.62</v>
+        <v>169.84</v>
       </c>
       <c r="K22" t="n">
-        <v>230.77</v>
+        <v>-31.82</v>
       </c>
       <c r="L22" t="n">
-        <v>264.68</v>
+        <v>172.79</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06:32:00</t>
+          <t>06:32:30</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>4.3</v>
+        <v>4.43</v>
       </c>
       <c r="F23" t="n">
-        <v>11.41</v>
+        <v>11.06</v>
       </c>
       <c r="G23" t="n">
-        <v>223.8</v>
+        <v>228.4</v>
       </c>
       <c r="H23" t="n">
-        <v>96</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J23" t="n">
-        <v>419.62</v>
+        <v>-320.94</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.04</v>
+        <v>4.75</v>
       </c>
       <c r="L23" t="n">
-        <v>419.62</v>
+        <v>320.98</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06:34:17</t>
+          <t>06:33:56</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>3.78</v>
+        <v>3.69</v>
       </c>
       <c r="F24" t="n">
-        <v>10.41</v>
+        <v>10.23</v>
       </c>
       <c r="G24" t="n">
-        <v>231.9</v>
+        <v>219.2</v>
       </c>
       <c r="H24" t="n">
-        <v>95.2</v>
+        <v>94</v>
       </c>
       <c r="I24" t="n">
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>359.75</v>
+        <v>301.51</v>
       </c>
       <c r="K24" t="n">
-        <v>-183.23</v>
+        <v>-197.7</v>
       </c>
       <c r="L24" t="n">
-        <v>403.72</v>
+        <v>360.55</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06:35:13</t>
+          <t>06:36:19</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>4.18</v>
+        <v>3.31</v>
       </c>
       <c r="F25" t="n">
-        <v>10.65</v>
+        <v>10.55</v>
       </c>
       <c r="G25" t="n">
-        <v>223.8</v>
+        <v>237.2</v>
       </c>
       <c r="H25" t="n">
-        <v>93.7</v>
+        <v>99.2</v>
       </c>
       <c r="I25" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J25" t="n">
-        <v>-82.31</v>
+        <v>-126.72</v>
       </c>
       <c r="K25" t="n">
-        <v>-207.52</v>
+        <v>-43.83</v>
       </c>
       <c r="L25" t="n">
-        <v>223.25</v>
+        <v>134.08</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06:39:08</t>
+          <t>06:42:14</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>3.39</v>
+        <v>3.8</v>
       </c>
       <c r="F26" t="n">
-        <v>10.13</v>
+        <v>10.33</v>
       </c>
       <c r="G26" t="n">
-        <v>227.7</v>
+        <v>219.1</v>
       </c>
       <c r="H26" t="n">
-        <v>93.5</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J26" t="n">
-        <v>-509.35</v>
+        <v>32.06</v>
       </c>
       <c r="K26" t="n">
-        <v>331</v>
+        <v>-14.52</v>
       </c>
       <c r="L26" t="n">
-        <v>607.45</v>
+        <v>35.2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06:41:10</t>
+          <t>06:44:17</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>3.83</v>
+        <v>4.18</v>
       </c>
       <c r="F27" t="n">
-        <v>10.73</v>
+        <v>10.09</v>
       </c>
       <c r="G27" t="n">
-        <v>236.8</v>
+        <v>223.2</v>
       </c>
       <c r="H27" t="n">
-        <v>100</v>
+        <v>96.3</v>
       </c>
       <c r="I27" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J27" t="n">
-        <v>192.42</v>
+        <v>279.92</v>
       </c>
       <c r="K27" t="n">
-        <v>308.07</v>
+        <v>-153.67</v>
       </c>
       <c r="L27" t="n">
-        <v>363.23</v>
+        <v>319.32</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06:42:24</t>
+          <t>06:45:27</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>4.1</v>
+        <v>3.54</v>
       </c>
       <c r="F28" t="n">
-        <v>11.06</v>
+        <v>10.75</v>
       </c>
       <c r="G28" t="n">
-        <v>219.3</v>
+        <v>222.4</v>
       </c>
       <c r="H28" t="n">
-        <v>100</v>
+        <v>99.8</v>
       </c>
       <c r="I28" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J28" t="n">
-        <v>-822.4299999999999</v>
+        <v>158.46</v>
       </c>
       <c r="K28" t="n">
-        <v>-193.05</v>
+        <v>32.21</v>
       </c>
       <c r="L28" t="n">
-        <v>844.79</v>
+        <v>161.7</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06:55:31</t>
+          <t>06:55:16</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>3.66</v>
+        <v>4.16</v>
       </c>
       <c r="F29" t="n">
-        <v>10.78</v>
+        <v>10.72</v>
       </c>
       <c r="G29" t="n">
-        <v>231.5</v>
+        <v>220.3</v>
       </c>
       <c r="H29" t="n">
         <v>100</v>
       </c>
       <c r="I29" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>-58.69</v>
+        <v>-29.1</v>
       </c>
       <c r="K29" t="n">
-        <v>-215.39</v>
+        <v>82.18000000000001</v>
       </c>
       <c r="L29" t="n">
-        <v>223.24</v>
+        <v>87.18000000000001</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06:57:13</t>
+          <t>06:56:30</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>3.96</v>
+        <v>3.37</v>
       </c>
       <c r="F30" t="n">
-        <v>10.39</v>
+        <v>10.65</v>
       </c>
       <c r="G30" t="n">
-        <v>222.4</v>
+        <v>232.3</v>
       </c>
       <c r="H30" t="n">
-        <v>91.90000000000001</v>
+        <v>97.2</v>
       </c>
       <c r="I30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J30" t="n">
-        <v>202.68</v>
+        <v>-9.609999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>13.86</v>
+        <v>13.5</v>
       </c>
       <c r="L30" t="n">
-        <v>203.15</v>
+        <v>16.57</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06:59:36</t>
+          <t>06:57:39</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>3.78</v>
+        <v>3.89</v>
       </c>
       <c r="F31" t="n">
-        <v>10.17</v>
+        <v>10.92</v>
       </c>
       <c r="G31" t="n">
-        <v>215</v>
+        <v>226.5</v>
       </c>
       <c r="H31" t="n">
-        <v>95</v>
+        <v>91.7</v>
       </c>
       <c r="I31" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>-178.09</v>
+        <v>-73.29000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>-128.37</v>
+        <v>36.92</v>
       </c>
       <c r="L31" t="n">
-        <v>219.53</v>
+        <v>82.06999999999999</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07:03:14</t>
+          <t>07:02:57</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>3.76</v>
+        <v>3.77</v>
       </c>
       <c r="F32" t="n">
-        <v>10.7</v>
+        <v>10.83</v>
       </c>
       <c r="G32" t="n">
-        <v>230.1</v>
+        <v>224.7</v>
       </c>
       <c r="H32" t="n">
-        <v>100</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="I32" t="n">
         <v>16</v>
       </c>
       <c r="J32" t="n">
-        <v>49.65</v>
+        <v>93.59</v>
       </c>
       <c r="K32" t="n">
-        <v>246.59</v>
+        <v>-104.23</v>
       </c>
       <c r="L32" t="n">
-        <v>251.54</v>
+        <v>140.08</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07:04:10</t>
+          <t>07:05:19</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>3.94</v>
+        <v>4.08</v>
       </c>
       <c r="F33" t="n">
-        <v>10.39</v>
+        <v>10.66</v>
       </c>
       <c r="G33" t="n">
-        <v>229.2</v>
+        <v>230.5</v>
       </c>
       <c r="H33" t="n">
-        <v>95.09999999999999</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="I33" t="n">
         <v>18</v>
       </c>
       <c r="J33" t="n">
-        <v>125.2</v>
+        <v>45.95</v>
       </c>
       <c r="K33" t="n">
-        <v>73.59</v>
+        <v>79.84999999999999</v>
       </c>
       <c r="L33" t="n">
-        <v>145.23</v>
+        <v>92.12</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07:05:55</t>
+          <t>07:06:24</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>3.53</v>
+        <v>4.37</v>
       </c>
       <c r="F34" t="n">
-        <v>10.43</v>
+        <v>10.15</v>
       </c>
       <c r="G34" t="n">
-        <v>224.2</v>
+        <v>207.3</v>
       </c>
       <c r="H34" t="n">
-        <v>94.09999999999999</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J34" t="n">
-        <v>19.86</v>
+        <v>78.69</v>
       </c>
       <c r="K34" t="n">
-        <v>-209.16</v>
+        <v>-49.51</v>
       </c>
       <c r="L34" t="n">
-        <v>210.1</v>
+        <v>92.97</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07:10:33</t>
+          <t>07:11:01</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>3.46</v>
+        <v>3.82</v>
       </c>
       <c r="F35" t="n">
-        <v>10.64</v>
+        <v>10.65</v>
       </c>
       <c r="G35" t="n">
-        <v>233.8</v>
+        <v>218.8</v>
       </c>
       <c r="H35" t="n">
-        <v>94.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="I35" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J35" t="n">
-        <v>-230.59</v>
+        <v>-49.51</v>
       </c>
       <c r="K35" t="n">
-        <v>111.25</v>
+        <v>70.64</v>
       </c>
       <c r="L35" t="n">
-        <v>256.02</v>
+        <v>86.27</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07:12:40</t>
+          <t>07:13:20</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>4.62</v>
+        <v>4.25</v>
       </c>
       <c r="F36" t="n">
-        <v>10.72</v>
+        <v>10.2</v>
       </c>
       <c r="G36" t="n">
-        <v>223</v>
+        <v>215.7</v>
       </c>
       <c r="H36" t="n">
-        <v>94.7</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J36" t="n">
-        <v>-21.94</v>
+        <v>-148.39</v>
       </c>
       <c r="K36" t="n">
-        <v>203.21</v>
+        <v>1.89</v>
       </c>
       <c r="L36" t="n">
-        <v>204.39</v>
+        <v>148.4</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07:14:58</t>
+          <t>07:14:28</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>4.54</v>
+        <v>4.58</v>
       </c>
       <c r="F37" t="n">
-        <v>10.71</v>
+        <v>11.12</v>
       </c>
       <c r="G37" t="n">
-        <v>236</v>
+        <v>218.2</v>
       </c>
       <c r="H37" t="n">
         <v>100</v>
       </c>
       <c r="I37" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>-399.82</v>
+        <v>-1.19</v>
       </c>
       <c r="K37" t="n">
-        <v>15.39</v>
+        <v>221.94</v>
       </c>
       <c r="L37" t="n">
-        <v>400.11</v>
+        <v>221.94</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07:19:36</t>
+          <t>07:18:50</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>4.82</v>
+        <v>4.33</v>
       </c>
       <c r="F38" t="n">
-        <v>11.39</v>
+        <v>10.65</v>
       </c>
       <c r="G38" t="n">
-        <v>228</v>
+        <v>221.3</v>
       </c>
       <c r="H38" t="n">
-        <v>100</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="I38" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J38" t="n">
-        <v>411.27</v>
+        <v>-101.53</v>
       </c>
       <c r="K38" t="n">
-        <v>347.34</v>
+        <v>-79.81</v>
       </c>
       <c r="L38" t="n">
-        <v>538.3200000000001</v>
+        <v>129.14</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07:21:36</t>
+          <t>07:21:01</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>3.73</v>
+        <v>3.55</v>
       </c>
       <c r="F39" t="n">
-        <v>10.72</v>
+        <v>10.65</v>
       </c>
       <c r="G39" t="n">
-        <v>238.9</v>
+        <v>225.4</v>
       </c>
       <c r="H39" t="n">
-        <v>92.3</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="I39" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J39" t="n">
-        <v>-359.32</v>
+        <v>-143.89</v>
       </c>
       <c r="K39" t="n">
-        <v>185.36</v>
+        <v>-120.73</v>
       </c>
       <c r="L39" t="n">
-        <v>404.31</v>
+        <v>187.83</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07:22:51</t>
+          <t>07:22:06</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>3.83</v>
+        <v>3.46</v>
       </c>
       <c r="F40" t="n">
-        <v>11.08</v>
+        <v>11.33</v>
       </c>
       <c r="G40" t="n">
-        <v>235.5</v>
+        <v>235.4</v>
       </c>
       <c r="H40" t="n">
-        <v>93.5</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="I40" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>328.18</v>
+        <v>-103.5</v>
       </c>
       <c r="K40" t="n">
-        <v>269.52</v>
+        <v>-236.85</v>
       </c>
       <c r="L40" t="n">
-        <v>424.66</v>
+        <v>258.48</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07:27:39</t>
+          <t>07:26:04</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>4.16</v>
+        <v>3.61</v>
       </c>
       <c r="F41" t="n">
-        <v>10.72</v>
+        <v>11.06</v>
       </c>
       <c r="G41" t="n">
-        <v>225.3</v>
+        <v>224.1</v>
       </c>
       <c r="H41" t="n">
-        <v>98.7</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="I41" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>-76.12</v>
+        <v>0.79</v>
       </c>
       <c r="K41" t="n">
-        <v>-437.42</v>
+        <v>317.78</v>
       </c>
       <c r="L41" t="n">
-        <v>444</v>
+        <v>317.78</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07:29:30</t>
+          <t>07:27:20</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>3.48</v>
+        <v>3.37</v>
       </c>
       <c r="F42" t="n">
-        <v>10.99</v>
+        <v>11.09</v>
       </c>
       <c r="G42" t="n">
-        <v>205.4</v>
+        <v>234.9</v>
       </c>
       <c r="H42" t="n">
-        <v>97.40000000000001</v>
+        <v>97.7</v>
       </c>
       <c r="I42" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J42" t="n">
-        <v>-141.16</v>
+        <v>-24.67</v>
       </c>
       <c r="K42" t="n">
-        <v>327.11</v>
+        <v>-286.56</v>
       </c>
       <c r="L42" t="n">
-        <v>356.27</v>
+        <v>287.62</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07:30:25</t>
+          <t>07:29:53</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>3.91</v>
+        <v>3.82</v>
       </c>
       <c r="F43" t="n">
-        <v>10.87</v>
+        <v>10.53</v>
       </c>
       <c r="G43" t="n">
-        <v>222.9</v>
+        <v>237.5</v>
       </c>
       <c r="H43" t="n">
-        <v>87.2</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="I43" t="n">
         <v>16</v>
       </c>
       <c r="J43" t="n">
-        <v>-262.84</v>
+        <v>22.47</v>
       </c>
       <c r="K43" t="n">
-        <v>89.98999999999999</v>
+        <v>-291.12</v>
       </c>
       <c r="L43" t="n">
-        <v>277.82</v>
+        <v>291.99</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07:41:31</t>
+          <t>07:40:11</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>4.31</v>
+        <v>3.99</v>
       </c>
       <c r="F44" t="n">
-        <v>10.04</v>
+        <v>10.27</v>
       </c>
       <c r="G44" t="n">
-        <v>215.8</v>
+        <v>216.5</v>
       </c>
       <c r="H44" t="n">
-        <v>98.5</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="I44" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>137.34</v>
+        <v>-53.76</v>
       </c>
       <c r="K44" t="n">
-        <v>-133.84</v>
+        <v>73.53</v>
       </c>
       <c r="L44" t="n">
-        <v>191.77</v>
+        <v>91.09</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07:43:47</t>
+          <t>07:42:36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>4.28</v>
+        <v>3.21</v>
       </c>
       <c r="F45" t="n">
-        <v>10.5</v>
+        <v>10.56</v>
       </c>
       <c r="G45" t="n">
-        <v>219.5</v>
+        <v>222.9</v>
       </c>
       <c r="H45" t="n">
-        <v>97.2</v>
+        <v>92.3</v>
       </c>
       <c r="I45" t="n">
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>166.14</v>
+        <v>51</v>
       </c>
       <c r="K45" t="n">
-        <v>-29</v>
+        <v>43.84</v>
       </c>
       <c r="L45" t="n">
-        <v>168.65</v>
+        <v>67.25</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07:45:18</t>
+          <t>07:44:31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>3.73</v>
+        <v>3.85</v>
       </c>
       <c r="F46" t="n">
-        <v>10.32</v>
+        <v>10.49</v>
       </c>
       <c r="G46" t="n">
-        <v>220.7</v>
+        <v>219.5</v>
       </c>
       <c r="H46" t="n">
-        <v>93</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="I46" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J46" t="n">
-        <v>167.17</v>
+        <v>-49.97</v>
       </c>
       <c r="K46" t="n">
-        <v>155.03</v>
+        <v>31.4</v>
       </c>
       <c r="L46" t="n">
-        <v>227.99</v>
+        <v>59.02</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07:50:55</t>
+          <t>07:48:51</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>4.53</v>
+        <v>4.93</v>
       </c>
       <c r="F47" t="n">
-        <v>10.53</v>
+        <v>10.91</v>
       </c>
       <c r="G47" t="n">
-        <v>212.5</v>
+        <v>225.4</v>
       </c>
       <c r="H47" t="n">
-        <v>95.40000000000001</v>
+        <v>98.2</v>
       </c>
       <c r="I47" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J47" t="n">
-        <v>-175.18</v>
+        <v>95.36</v>
       </c>
       <c r="K47" t="n">
-        <v>25.93</v>
+        <v>1.95</v>
       </c>
       <c r="L47" t="n">
-        <v>177.08</v>
+        <v>95.38</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07:52:55</t>
+          <t>07:49:58</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>4.27</v>
+        <v>3.63</v>
       </c>
       <c r="F48" t="n">
-        <v>10.41</v>
+        <v>10.97</v>
       </c>
       <c r="G48" t="n">
-        <v>223.4</v>
+        <v>215.8</v>
       </c>
       <c r="H48" t="n">
-        <v>98.8</v>
+        <v>98</v>
       </c>
       <c r="I48" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>-133.62</v>
+        <v>-19.63</v>
       </c>
       <c r="K48" t="n">
-        <v>-258.43</v>
+        <v>93.47</v>
       </c>
       <c r="L48" t="n">
-        <v>290.93</v>
+        <v>95.51000000000001</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07:53:56</t>
+          <t>07:51:13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>4.06</v>
+        <v>4.66</v>
       </c>
       <c r="F49" t="n">
-        <v>10.9</v>
+        <v>10.41</v>
       </c>
       <c r="G49" t="n">
-        <v>212.7</v>
+        <v>211.6</v>
       </c>
       <c r="H49" t="n">
-        <v>87.90000000000001</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="I49" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J49" t="n">
-        <v>-43.33</v>
+        <v>-112.79</v>
       </c>
       <c r="K49" t="n">
-        <v>-174.28</v>
+        <v>-90.72</v>
       </c>
       <c r="L49" t="n">
-        <v>179.59</v>
+        <v>144.75</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07:57:19</t>
+          <t>07:54:56</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="F50" t="n">
-        <v>10.26</v>
+        <v>10.62</v>
       </c>
       <c r="G50" t="n">
-        <v>229.2</v>
+        <v>219.9</v>
       </c>
       <c r="H50" t="n">
-        <v>96.3</v>
+        <v>97.3</v>
       </c>
       <c r="I50" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>244.97</v>
+        <v>-98.31999999999999</v>
       </c>
       <c r="K50" t="n">
-        <v>-66.51000000000001</v>
+        <v>-24.2</v>
       </c>
       <c r="L50" t="n">
-        <v>253.84</v>
+        <v>101.26</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07:58:46</t>
+          <t>07:56:21</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>4.24</v>
+        <v>4.06</v>
       </c>
       <c r="F51" t="n">
-        <v>10.52</v>
+        <v>10.8</v>
       </c>
       <c r="G51" t="n">
-        <v>234</v>
+        <v>204.8</v>
       </c>
       <c r="H51" t="n">
-        <v>86.2</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="I51" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J51" t="n">
-        <v>-287.75</v>
+        <v>96.47</v>
       </c>
       <c r="K51" t="n">
-        <v>-81.52</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="L51" t="n">
-        <v>299.08</v>
+        <v>96.97</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07:59:39</t>
+          <t>07:58:22</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>4.08</v>
+        <v>4.38</v>
       </c>
       <c r="F52" t="n">
-        <v>10.49</v>
+        <v>10.33</v>
       </c>
       <c r="G52" t="n">
-        <v>231.8</v>
+        <v>230.2</v>
       </c>
       <c r="H52" t="n">
-        <v>91.40000000000001</v>
+        <v>96.3</v>
       </c>
       <c r="I52" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>-101.8</v>
+        <v>99.76000000000001</v>
       </c>
       <c r="K52" t="n">
-        <v>200.38</v>
+        <v>-42.25</v>
       </c>
       <c r="L52" t="n">
-        <v>224.76</v>
+        <v>108.34</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08:05:10</t>
+          <t>08:04:09</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>4.12</v>
+        <v>5.53</v>
       </c>
       <c r="F53" t="n">
-        <v>10.85</v>
+        <v>10.82</v>
       </c>
       <c r="G53" t="n">
-        <v>233.2</v>
+        <v>231.2</v>
       </c>
       <c r="H53" t="n">
-        <v>100</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="I53" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J53" t="n">
-        <v>591.38</v>
+        <v>129.82</v>
       </c>
       <c r="K53" t="n">
-        <v>100.48</v>
+        <v>-101.82</v>
       </c>
       <c r="L53" t="n">
-        <v>599.86</v>
+        <v>164.99</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08:06:22</t>
+          <t>08:05:52</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>4.64</v>
+        <v>3.98</v>
       </c>
       <c r="F54" t="n">
-        <v>10.19</v>
+        <v>11.15</v>
       </c>
       <c r="G54" t="n">
-        <v>233</v>
+        <v>217.4</v>
       </c>
       <c r="H54" t="n">
-        <v>84</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="I54" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>-496.35</v>
+        <v>41.68</v>
       </c>
       <c r="K54" t="n">
-        <v>-271.11</v>
+        <v>132.4</v>
       </c>
       <c r="L54" t="n">
-        <v>565.5599999999999</v>
+        <v>138.8</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08:08:01</t>
+          <t>08:06:44</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>4.03</v>
+        <v>4.4</v>
       </c>
       <c r="F55" t="n">
-        <v>10.61</v>
+        <v>10.43</v>
       </c>
       <c r="G55" t="n">
-        <v>225.6</v>
+        <v>215</v>
       </c>
       <c r="H55" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="I55" t="n">
         <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>-294.61</v>
+        <v>-165.67</v>
       </c>
       <c r="K55" t="n">
-        <v>-328.2</v>
+        <v>227.15</v>
       </c>
       <c r="L55" t="n">
-        <v>441.04</v>
+        <v>281.15</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08:13:10</t>
+          <t>08:11:17</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>4.9</v>
+        <v>3.57</v>
       </c>
       <c r="F56" t="n">
-        <v>11.02</v>
+        <v>10.28</v>
       </c>
       <c r="G56" t="n">
-        <v>226.7</v>
+        <v>216.6</v>
       </c>
       <c r="H56" t="n">
-        <v>100</v>
+        <v>91.3</v>
       </c>
       <c r="I56" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J56" t="n">
-        <v>-418.61</v>
+        <v>193.41</v>
       </c>
       <c r="K56" t="n">
-        <v>-438.82</v>
+        <v>105.75</v>
       </c>
       <c r="L56" t="n">
-        <v>606.47</v>
+        <v>220.43</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08:14:51</t>
+          <t>08:13:16</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>4.1</v>
+        <v>4.09</v>
       </c>
       <c r="F57" t="n">
-        <v>11.58</v>
+        <v>10.43</v>
       </c>
       <c r="G57" t="n">
-        <v>218.9</v>
+        <v>225.3</v>
       </c>
       <c r="H57" t="n">
-        <v>96.59999999999999</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="I57" t="n">
         <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>-349.72</v>
+        <v>-173.51</v>
       </c>
       <c r="K57" t="n">
-        <v>-691</v>
+        <v>182.2</v>
       </c>
       <c r="L57" t="n">
-        <v>774.46</v>
+        <v>251.6</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08:16:56</t>
+          <t>08:15:20</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>4.21</v>
+        <v>4.37</v>
       </c>
       <c r="F58" t="n">
-        <v>10.73</v>
+        <v>10.82</v>
       </c>
       <c r="G58" t="n">
-        <v>229.8</v>
+        <v>229.5</v>
       </c>
       <c r="H58" t="n">
-        <v>91.59999999999999</v>
+        <v>93.3</v>
       </c>
       <c r="I58" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J58" t="n">
-        <v>288.5</v>
+        <v>-220.07</v>
       </c>
       <c r="K58" t="n">
-        <v>-246.19</v>
+        <v>-252.44</v>
       </c>
       <c r="L58" t="n">
-        <v>379.27</v>
+        <v>334.9</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08:25:59</t>
+          <t>08:26:53</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>3.83</v>
+        <v>4.4</v>
       </c>
       <c r="F59" t="n">
-        <v>10.78</v>
+        <v>10.56</v>
       </c>
       <c r="G59" t="n">
-        <v>227.1</v>
+        <v>234.4</v>
       </c>
       <c r="H59" t="n">
-        <v>91.59999999999999</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="I59" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J59" t="n">
-        <v>-112.65</v>
+        <v>-82.17</v>
       </c>
       <c r="K59" t="n">
-        <v>-35.22</v>
+        <v>-42.64</v>
       </c>
       <c r="L59" t="n">
-        <v>118.03</v>
+        <v>92.56999999999999</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08:28:26</t>
+          <t>08:27:38</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>4.54</v>
+        <v>4.06</v>
       </c>
       <c r="F60" t="n">
-        <v>9.960000000000001</v>
+        <v>10.97</v>
       </c>
       <c r="G60" t="n">
-        <v>207.7</v>
+        <v>222.6</v>
       </c>
       <c r="H60" t="n">
-        <v>88.5</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="I60" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J60" t="n">
-        <v>-138.48</v>
+        <v>77.48</v>
       </c>
       <c r="K60" t="n">
-        <v>-86.67</v>
+        <v>57.16</v>
       </c>
       <c r="L60" t="n">
-        <v>163.36</v>
+        <v>96.28</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08:30:06</t>
+          <t>08:28:50</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>4.2</v>
+        <v>4.52</v>
       </c>
       <c r="F61" t="n">
-        <v>10.83</v>
+        <v>10.42</v>
       </c>
       <c r="G61" t="n">
-        <v>211.4</v>
+        <v>223.2</v>
       </c>
       <c r="H61" t="n">
-        <v>100</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="I61" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>-176.7</v>
+        <v>28.09</v>
       </c>
       <c r="K61" t="n">
-        <v>70.09999999999999</v>
+        <v>-64.69</v>
       </c>
       <c r="L61" t="n">
-        <v>190.1</v>
+        <v>70.53</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08:33:04</t>
+          <t>08:34:56</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>4.36</v>
+        <v>3.85</v>
       </c>
       <c r="F62" t="n">
-        <v>10.79</v>
+        <v>10.94</v>
       </c>
       <c r="G62" t="n">
-        <v>232.5</v>
+        <v>217</v>
       </c>
       <c r="H62" t="n">
-        <v>86.5</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="I62" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J62" t="n">
-        <v>-448.44</v>
+        <v>-48.37</v>
       </c>
       <c r="K62" t="n">
-        <v>-73.69</v>
+        <v>45.46</v>
       </c>
       <c r="L62" t="n">
-        <v>454.46</v>
+        <v>66.38</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08:35:22</t>
+          <t>08:35:34</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="F63" t="n">
-        <v>10.79</v>
+        <v>10.9</v>
       </c>
       <c r="G63" t="n">
-        <v>232.4</v>
+        <v>220</v>
       </c>
       <c r="H63" t="n">
-        <v>100</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="I63" t="n">
         <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>-154.68</v>
+        <v>-78.73999999999999</v>
       </c>
       <c r="K63" t="n">
-        <v>-125.11</v>
+        <v>-93.13</v>
       </c>
       <c r="L63" t="n">
-        <v>198.95</v>
+        <v>121.96</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>08:36:30</t>
+          <t>08:37:04</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>4.56</v>
+        <v>4.37</v>
       </c>
       <c r="F64" t="n">
-        <v>10.35</v>
+        <v>10.49</v>
       </c>
       <c r="G64" t="n">
-        <v>222.2</v>
+        <v>215.1</v>
       </c>
       <c r="H64" t="n">
-        <v>90.90000000000001</v>
+        <v>93.3</v>
       </c>
       <c r="I64" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J64" t="n">
-        <v>161.45</v>
+        <v>-29.26</v>
       </c>
       <c r="K64" t="n">
-        <v>-135.16</v>
+        <v>90.58</v>
       </c>
       <c r="L64" t="n">
-        <v>210.56</v>
+        <v>95.19</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>08:41:50</t>
+          <t>08:40:04</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>3.92</v>
+        <v>4.21</v>
       </c>
       <c r="F65" t="n">
-        <v>10.13</v>
+        <v>10.21</v>
       </c>
       <c r="G65" t="n">
-        <v>217.2</v>
+        <v>231.5</v>
       </c>
       <c r="H65" t="n">
-        <v>97.40000000000001</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="I65" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J65" t="n">
-        <v>79.79000000000001</v>
+        <v>-89.95</v>
       </c>
       <c r="K65" t="n">
-        <v>-169.59</v>
+        <v>57.61</v>
       </c>
       <c r="L65" t="n">
-        <v>187.43</v>
+        <v>106.82</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>08:44:06</t>
+          <t>08:41:03</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>4.62</v>
+        <v>4.48</v>
       </c>
       <c r="F66" t="n">
-        <v>10.14</v>
+        <v>10.08</v>
       </c>
       <c r="G66" t="n">
-        <v>228.9</v>
+        <v>225.4</v>
       </c>
       <c r="H66" t="n">
-        <v>97.09999999999999</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="I66" t="n">
         <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>-304.11</v>
+        <v>-216.85</v>
       </c>
       <c r="K66" t="n">
-        <v>83.63</v>
+        <v>94.72</v>
       </c>
       <c r="L66" t="n">
-        <v>315.4</v>
+        <v>236.64</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>08:44:49</t>
+          <t>08:43:44</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>3.93</v>
+        <v>4.2</v>
       </c>
       <c r="F67" t="n">
-        <v>10.88</v>
+        <v>10.39</v>
       </c>
       <c r="G67" t="n">
-        <v>215.2</v>
+        <v>227.1</v>
       </c>
       <c r="H67" t="n">
-        <v>98.59999999999999</v>
+        <v>97.5</v>
       </c>
       <c r="I67" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J67" t="n">
-        <v>-253.36</v>
+        <v>-140.18</v>
       </c>
       <c r="K67" t="n">
-        <v>-55.05</v>
+        <v>-38.25</v>
       </c>
       <c r="L67" t="n">
-        <v>259.27</v>
+        <v>145.31</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>08:50:00</t>
+          <t>08:47:58</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>4.7</v>
+        <v>4.79</v>
       </c>
       <c r="F68" t="n">
-        <v>10.55</v>
+        <v>10.87</v>
       </c>
       <c r="G68" t="n">
-        <v>217.2</v>
+        <v>223.1</v>
       </c>
       <c r="H68" t="n">
-        <v>89.09999999999999</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="I68" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J68" t="n">
-        <v>111.08</v>
+        <v>-229.12</v>
       </c>
       <c r="K68" t="n">
-        <v>-349.4</v>
+        <v>-159.1</v>
       </c>
       <c r="L68" t="n">
-        <v>366.64</v>
+        <v>278.94</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>08:50:54</t>
+          <t>08:50:04</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="F69" t="n">
-        <v>10.61</v>
+        <v>10.66</v>
       </c>
       <c r="G69" t="n">
-        <v>222.9</v>
+        <v>225.2</v>
       </c>
       <c r="H69" t="n">
-        <v>97.8</v>
+        <v>100</v>
       </c>
       <c r="I69" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J69" t="n">
-        <v>226.08</v>
+        <v>155.09</v>
       </c>
       <c r="K69" t="n">
-        <v>-245.69</v>
+        <v>19.96</v>
       </c>
       <c r="L69" t="n">
-        <v>333.88</v>
+        <v>156.37</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>08:52:01</t>
+          <t>08:52:00</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>4.6</v>
+        <v>4.32</v>
       </c>
       <c r="F70" t="n">
-        <v>10.14</v>
+        <v>10.86</v>
       </c>
       <c r="G70" t="n">
-        <v>223</v>
+        <v>223.6</v>
       </c>
       <c r="H70" t="n">
-        <v>98.7</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="I70" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J70" t="n">
-        <v>-261.37</v>
+        <v>-229.16</v>
       </c>
       <c r="K70" t="n">
-        <v>-300.96</v>
+        <v>-53.99</v>
       </c>
       <c r="L70" t="n">
-        <v>398.61</v>
+        <v>235.43</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>08:57:24</t>
+          <t>08:57:37</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>4.24</v>
+        <v>4.82</v>
       </c>
       <c r="F71" t="n">
-        <v>11.38</v>
+        <v>10.85</v>
       </c>
       <c r="G71" t="n">
-        <v>217.1</v>
+        <v>231.4</v>
       </c>
       <c r="H71" t="n">
-        <v>90.7</v>
+        <v>91.8</v>
       </c>
       <c r="I71" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J71" t="n">
-        <v>-401.06</v>
+        <v>-380</v>
       </c>
       <c r="K71" t="n">
-        <v>415.45</v>
+        <v>323.94</v>
       </c>
       <c r="L71" t="n">
-        <v>577.45</v>
+        <v>499.34</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>08:58:23</t>
+          <t>08:58:20</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>4.24</v>
+        <v>4.18</v>
       </c>
       <c r="F72" t="n">
-        <v>11.03</v>
+        <v>11.52</v>
       </c>
       <c r="G72" t="n">
-        <v>229.3</v>
+        <v>222.9</v>
       </c>
       <c r="H72" t="n">
-        <v>97.2</v>
+        <v>99.2</v>
       </c>
       <c r="I72" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J72" t="n">
-        <v>-232.74</v>
+        <v>-114.25</v>
       </c>
       <c r="K72" t="n">
-        <v>492.34</v>
+        <v>-168.03</v>
       </c>
       <c r="L72" t="n">
-        <v>544.58</v>
+        <v>203.2</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>09:00:39</t>
+          <t>09:00:01</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>4.11</v>
+        <v>4.68</v>
       </c>
       <c r="F73" t="n">
-        <v>11.36</v>
+        <v>10.42</v>
       </c>
       <c r="G73" t="n">
-        <v>222.2</v>
+        <v>218.8</v>
       </c>
       <c r="H73" t="n">
-        <v>99.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="I73" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J73" t="n">
-        <v>-38.98</v>
+        <v>236.74</v>
       </c>
       <c r="K73" t="n">
-        <v>-451.68</v>
+        <v>15.3</v>
       </c>
       <c r="L73" t="n">
-        <v>453.36</v>
+        <v>237.24</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>09:11:44</t>
+          <t>09:11:01</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>4.71</v>
+        <v>4.17</v>
       </c>
       <c r="F74" t="n">
-        <v>11.2</v>
+        <v>10.82</v>
       </c>
       <c r="G74" t="n">
-        <v>218.2</v>
+        <v>239.1</v>
       </c>
       <c r="H74" t="n">
-        <v>99.2</v>
+        <v>94.7</v>
       </c>
       <c r="I74" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J74" t="n">
-        <v>-155.09</v>
+        <v>14.48</v>
       </c>
       <c r="K74" t="n">
-        <v>93.19</v>
+        <v>-75.25</v>
       </c>
       <c r="L74" t="n">
-        <v>180.94</v>
+        <v>76.63</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09:14:04</t>
+          <t>09:12:19</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>4.58</v>
+        <v>4.4</v>
       </c>
       <c r="F75" t="n">
-        <v>10.56</v>
+        <v>11.03</v>
       </c>
       <c r="G75" t="n">
-        <v>232.9</v>
+        <v>220.2</v>
       </c>
       <c r="H75" t="n">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="I75" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J75" t="n">
-        <v>-226.4</v>
+        <v>-12.86</v>
       </c>
       <c r="K75" t="n">
-        <v>37.83</v>
+        <v>-142.62</v>
       </c>
       <c r="L75" t="n">
-        <v>229.54</v>
+        <v>143.2</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09:15:38</t>
+          <t>09:13:41</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>4.65</v>
+        <v>5.15</v>
       </c>
       <c r="F76" t="n">
-        <v>9.859999999999999</v>
+        <v>11.14</v>
       </c>
       <c r="G76" t="n">
-        <v>239.1</v>
+        <v>224.7</v>
       </c>
       <c r="H76" t="n">
-        <v>92.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="I76" t="n">
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>55.76</v>
+        <v>-21.14</v>
       </c>
       <c r="K76" t="n">
-        <v>134.32</v>
+        <v>-117.92</v>
       </c>
       <c r="L76" t="n">
-        <v>145.43</v>
+        <v>119.8</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09:18:51</t>
+          <t>09:17:57</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>4.12</v>
+        <v>4.35</v>
       </c>
       <c r="F77" t="n">
-        <v>11.39</v>
+        <v>10.43</v>
       </c>
       <c r="G77" t="n">
-        <v>210.4</v>
+        <v>221.4</v>
       </c>
       <c r="H77" t="n">
-        <v>95.90000000000001</v>
+        <v>93.7</v>
       </c>
       <c r="I77" t="n">
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>16.48</v>
+        <v>122.11</v>
       </c>
       <c r="K77" t="n">
-        <v>102.09</v>
+        <v>-221.2</v>
       </c>
       <c r="L77" t="n">
-        <v>103.42</v>
+        <v>252.66</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09:20:54</t>
+          <t>09:19:13</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>4.97</v>
+        <v>4.37</v>
       </c>
       <c r="F78" t="n">
-        <v>10.89</v>
+        <v>11.17</v>
       </c>
       <c r="G78" t="n">
-        <v>231.6</v>
+        <v>229</v>
       </c>
       <c r="H78" t="n">
-        <v>92.3</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="I78" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>229.11</v>
+        <v>-64.51000000000001</v>
       </c>
       <c r="K78" t="n">
-        <v>56.57</v>
+        <v>83.77</v>
       </c>
       <c r="L78" t="n">
-        <v>235.99</v>
+        <v>105.73</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09:22:28</t>
+          <t>09:20:40</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>4.09</v>
+        <v>4.56</v>
       </c>
       <c r="F79" t="n">
-        <v>10.95</v>
+        <v>11.08</v>
       </c>
       <c r="G79" t="n">
-        <v>227.9</v>
+        <v>229.7</v>
       </c>
       <c r="H79" t="n">
-        <v>95.8</v>
+        <v>96</v>
       </c>
       <c r="I79" t="n">
         <v>19</v>
       </c>
       <c r="J79" t="n">
-        <v>27.36</v>
+        <v>35.03</v>
       </c>
       <c r="K79" t="n">
-        <v>-119.05</v>
+        <v>64.84</v>
       </c>
       <c r="L79" t="n">
-        <v>122.15</v>
+        <v>73.7</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>09:27:16</t>
+          <t>09:25:07</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>4.49</v>
+        <v>4.24</v>
       </c>
       <c r="F80" t="n">
-        <v>10.72</v>
+        <v>11.01</v>
       </c>
       <c r="G80" t="n">
-        <v>222.2</v>
+        <v>223.7</v>
       </c>
       <c r="H80" t="n">
-        <v>98.7</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="I80" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J80" t="n">
-        <v>244.78</v>
+        <v>123.54</v>
       </c>
       <c r="K80" t="n">
-        <v>25.36</v>
+        <v>17.75</v>
       </c>
       <c r="L80" t="n">
-        <v>246.09</v>
+        <v>124.81</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>09:28:35</t>
+          <t>09:26:16</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>4.8</v>
+        <v>4.86</v>
       </c>
       <c r="F81" t="n">
-        <v>11.35</v>
+        <v>10.79</v>
       </c>
       <c r="G81" t="n">
-        <v>230</v>
+        <v>223.5</v>
       </c>
       <c r="H81" t="n">
-        <v>100</v>
+        <v>98.7</v>
       </c>
       <c r="I81" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>-155.95</v>
+        <v>236.35</v>
       </c>
       <c r="K81" t="n">
-        <v>298.38</v>
+        <v>-0.25</v>
       </c>
       <c r="L81" t="n">
-        <v>336.68</v>
+        <v>236.35</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>09:30:38</t>
+          <t>09:27:50</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>3.79</v>
+        <v>4.36</v>
       </c>
       <c r="F82" t="n">
-        <v>9.859999999999999</v>
+        <v>10.55</v>
       </c>
       <c r="G82" t="n">
-        <v>229.3</v>
+        <v>215.7</v>
       </c>
       <c r="H82" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I82" t="n">
         <v>20</v>
       </c>
       <c r="J82" t="n">
-        <v>-69.91</v>
+        <v>-119.44</v>
       </c>
       <c r="K82" t="n">
-        <v>156.37</v>
+        <v>90.7</v>
       </c>
       <c r="L82" t="n">
-        <v>171.28</v>
+        <v>149.97</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>09:35:49</t>
+          <t>09:32:03</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>4.61</v>
+        <v>4.43</v>
       </c>
       <c r="F83" t="n">
-        <v>10.92</v>
+        <v>10.1</v>
       </c>
       <c r="G83" t="n">
-        <v>223.8</v>
+        <v>225.2</v>
       </c>
       <c r="H83" t="n">
-        <v>97.90000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="I83" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>186.72</v>
+        <v>-225.9</v>
       </c>
       <c r="K83" t="n">
-        <v>-348.88</v>
+        <v>-147.19</v>
       </c>
       <c r="L83" t="n">
-        <v>395.7</v>
+        <v>269.62</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>09:38:27</t>
+          <t>09:34:22</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>4.61</v>
+        <v>4.18</v>
       </c>
       <c r="F84" t="n">
-        <v>11.32</v>
+        <v>11.03</v>
       </c>
       <c r="G84" t="n">
-        <v>229.9</v>
+        <v>239.5</v>
       </c>
       <c r="H84" t="n">
-        <v>95</v>
+        <v>99.3</v>
       </c>
       <c r="I84" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J84" t="n">
-        <v>276.29</v>
+        <v>27.13</v>
       </c>
       <c r="K84" t="n">
-        <v>327.55</v>
+        <v>-50.86</v>
       </c>
       <c r="L84" t="n">
-        <v>428.51</v>
+        <v>57.65</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>09:39:57</t>
+          <t>09:35:08</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>4.37</v>
+        <v>4.22</v>
       </c>
       <c r="F85" t="n">
-        <v>11.28</v>
+        <v>10.46</v>
       </c>
       <c r="G85" t="n">
-        <v>202.9</v>
+        <v>236.3</v>
       </c>
       <c r="H85" t="n">
-        <v>100</v>
+        <v>90.3</v>
       </c>
       <c r="I85" t="n">
         <v>19</v>
       </c>
       <c r="J85" t="n">
-        <v>10.07</v>
+        <v>22.46</v>
       </c>
       <c r="K85" t="n">
-        <v>-356.5</v>
+        <v>214.44</v>
       </c>
       <c r="L85" t="n">
-        <v>356.64</v>
+        <v>215.61</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>09:43:13</t>
+          <t>09:41:10</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>4.97</v>
+        <v>4.54</v>
       </c>
       <c r="F86" t="n">
-        <v>10.99</v>
+        <v>10.9</v>
       </c>
       <c r="G86" t="n">
-        <v>233.8</v>
+        <v>232.9</v>
       </c>
       <c r="H86" t="n">
-        <v>94</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="I86" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J86" t="n">
-        <v>-471.58</v>
+        <v>-155.71</v>
       </c>
       <c r="K86" t="n">
-        <v>-504.16</v>
+        <v>-375.02</v>
       </c>
       <c r="L86" t="n">
-        <v>690.34</v>
+        <v>406.06</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>09:45:41</t>
+          <t>09:43:27</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>4.9</v>
+        <v>5.08</v>
       </c>
       <c r="F87" t="n">
-        <v>10.57</v>
+        <v>10.41</v>
       </c>
       <c r="G87" t="n">
-        <v>209.2</v>
+        <v>220.8</v>
       </c>
       <c r="H87" t="n">
-        <v>98.2</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="I87" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>342.78</v>
+        <v>137.63</v>
       </c>
       <c r="K87" t="n">
-        <v>-666.62</v>
+        <v>190.68</v>
       </c>
       <c r="L87" t="n">
-        <v>749.59</v>
+        <v>235.16</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>09:47:01</t>
+          <t>09:45:35</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>4.82</v>
+        <v>4.65</v>
       </c>
       <c r="F88" t="n">
-        <v>10.9</v>
+        <v>10.49</v>
       </c>
       <c r="G88" t="n">
-        <v>224.9</v>
+        <v>233.8</v>
       </c>
       <c r="H88" t="n">
-        <v>89.3</v>
+        <v>94.5</v>
       </c>
       <c r="I88" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>-857.96</v>
+        <v>243.2</v>
       </c>
       <c r="K88" t="n">
-        <v>62.37</v>
+        <v>-50.22</v>
       </c>
       <c r="L88" t="n">
-        <v>860.23</v>
+        <v>248.33</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-08-26.xlsx
+++ b/output/2025-08-26.xlsx
@@ -640,13 +640,13 @@
         <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>63.28</v>
+        <v>63.43</v>
       </c>
       <c r="K14" t="n">
-        <v>-46.04</v>
+        <v>-46.15</v>
       </c>
       <c r="L14" t="n">
-        <v>78.26000000000001</v>
+        <v>78.44</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>-113.35</v>
+        <v>-108.35</v>
       </c>
       <c r="K15" t="n">
-        <v>-8.630000000000001</v>
+        <v>-8.25</v>
       </c>
       <c r="L15" t="n">
-        <v>113.68</v>
+        <v>108.66</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>16</v>
       </c>
       <c r="J16" t="n">
-        <v>-88.79000000000001</v>
+        <v>-87.63</v>
       </c>
       <c r="K16" t="n">
-        <v>-20.49</v>
+        <v>-20.22</v>
       </c>
       <c r="L16" t="n">
-        <v>91.12</v>
+        <v>89.93000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>109.47</v>
+        <v>103.53</v>
       </c>
       <c r="K17" t="n">
-        <v>122.87</v>
+        <v>116.2</v>
       </c>
       <c r="L17" t="n">
-        <v>164.56</v>
+        <v>155.63</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>20</v>
       </c>
       <c r="J18" t="n">
-        <v>-101.81</v>
+        <v>-99.3</v>
       </c>
       <c r="K18" t="n">
         <v>0.14</v>
       </c>
       <c r="L18" t="n">
-        <v>101.81</v>
+        <v>99.3</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>58.27</v>
+        <v>57.81</v>
       </c>
       <c r="K19" t="n">
-        <v>-71.98999999999999</v>
+        <v>-71.42</v>
       </c>
       <c r="L19" t="n">
-        <v>92.62</v>
+        <v>91.88</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>19</v>
       </c>
       <c r="J20" t="n">
-        <v>-45.02</v>
+        <v>-47.89</v>
       </c>
       <c r="K20" t="n">
-        <v>-72.51000000000001</v>
+        <v>-77.13</v>
       </c>
       <c r="L20" t="n">
-        <v>85.34</v>
+        <v>90.79000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>16</v>
       </c>
       <c r="J21" t="n">
-        <v>-112.98</v>
+        <v>-110.59</v>
       </c>
       <c r="K21" t="n">
-        <v>-127.22</v>
+        <v>-124.54</v>
       </c>
       <c r="L21" t="n">
-        <v>170.14</v>
+        <v>166.56</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>18</v>
       </c>
       <c r="J22" t="n">
-        <v>169.84</v>
+        <v>164.98</v>
       </c>
       <c r="K22" t="n">
-        <v>-31.82</v>
+        <v>-30.91</v>
       </c>
       <c r="L22" t="n">
-        <v>172.79</v>
+        <v>167.85</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>20</v>
       </c>
       <c r="J23" t="n">
-        <v>-320.94</v>
+        <v>-307.89</v>
       </c>
       <c r="K23" t="n">
-        <v>4.75</v>
+        <v>4.56</v>
       </c>
       <c r="L23" t="n">
-        <v>320.98</v>
+        <v>307.92</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>301.51</v>
+        <v>285.67</v>
       </c>
       <c r="K24" t="n">
-        <v>-197.7</v>
+        <v>-187.31</v>
       </c>
       <c r="L24" t="n">
-        <v>360.55</v>
+        <v>341.61</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>16</v>
       </c>
       <c r="J25" t="n">
-        <v>-126.72</v>
+        <v>-133.59</v>
       </c>
       <c r="K25" t="n">
-        <v>-43.83</v>
+        <v>-46.21</v>
       </c>
       <c r="L25" t="n">
-        <v>134.08</v>
+        <v>141.36</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>19</v>
       </c>
       <c r="J26" t="n">
-        <v>32.06</v>
+        <v>32.49</v>
       </c>
       <c r="K26" t="n">
-        <v>-14.52</v>
+        <v>-14.72</v>
       </c>
       <c r="L26" t="n">
-        <v>35.2</v>
+        <v>35.67</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>20</v>
       </c>
       <c r="J27" t="n">
-        <v>279.92</v>
+        <v>288.44</v>
       </c>
       <c r="K27" t="n">
-        <v>-153.67</v>
+        <v>-158.35</v>
       </c>
       <c r="L27" t="n">
-        <v>319.32</v>
+        <v>329.04</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>19</v>
       </c>
       <c r="J28" t="n">
-        <v>158.46</v>
+        <v>172.19</v>
       </c>
       <c r="K28" t="n">
-        <v>32.21</v>
+        <v>35</v>
       </c>
       <c r="L28" t="n">
-        <v>161.7</v>
+        <v>175.71</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>-29.1</v>
+        <v>-28.34</v>
       </c>
       <c r="K29" t="n">
-        <v>82.18000000000001</v>
+        <v>80.04000000000001</v>
       </c>
       <c r="L29" t="n">
-        <v>87.18000000000001</v>
+        <v>84.91</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>17</v>
       </c>
       <c r="J30" t="n">
-        <v>-9.609999999999999</v>
+        <v>-9.390000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>13.5</v>
+        <v>13.18</v>
       </c>
       <c r="L30" t="n">
-        <v>16.57</v>
+        <v>16.19</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>-73.29000000000001</v>
+        <v>-72.23</v>
       </c>
       <c r="K31" t="n">
-        <v>36.92</v>
+        <v>36.39</v>
       </c>
       <c r="L31" t="n">
-        <v>82.06999999999999</v>
+        <v>80.88</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>16</v>
       </c>
       <c r="J32" t="n">
-        <v>93.59</v>
+        <v>88.83</v>
       </c>
       <c r="K32" t="n">
-        <v>-104.23</v>
+        <v>-98.94</v>
       </c>
       <c r="L32" t="n">
-        <v>140.08</v>
+        <v>132.96</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>18</v>
       </c>
       <c r="J33" t="n">
-        <v>45.95</v>
+        <v>45.29</v>
       </c>
       <c r="K33" t="n">
-        <v>79.84999999999999</v>
+        <v>78.7</v>
       </c>
       <c r="L33" t="n">
-        <v>92.12</v>
+        <v>90.81</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>17</v>
       </c>
       <c r="J34" t="n">
-        <v>78.69</v>
+        <v>77.28</v>
       </c>
       <c r="K34" t="n">
-        <v>-49.51</v>
+        <v>-48.62</v>
       </c>
       <c r="L34" t="n">
-        <v>92.97</v>
+        <v>91.31</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>20</v>
       </c>
       <c r="J35" t="n">
-        <v>-49.51</v>
+        <v>-52.58</v>
       </c>
       <c r="K35" t="n">
-        <v>70.64</v>
+        <v>75.02</v>
       </c>
       <c r="L35" t="n">
-        <v>86.27</v>
+        <v>91.61</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>16</v>
       </c>
       <c r="J36" t="n">
-        <v>-148.39</v>
+        <v>-147.79</v>
       </c>
       <c r="K36" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="L36" t="n">
-        <v>148.4</v>
+        <v>147.8</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>-1.19</v>
+        <v>-1.13</v>
       </c>
       <c r="K37" t="n">
-        <v>221.94</v>
+        <v>212.04</v>
       </c>
       <c r="L37" t="n">
-        <v>221.94</v>
+        <v>212.04</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>19</v>
       </c>
       <c r="J38" t="n">
-        <v>-101.53</v>
+        <v>-108.41</v>
       </c>
       <c r="K38" t="n">
-        <v>-79.81</v>
+        <v>-85.20999999999999</v>
       </c>
       <c r="L38" t="n">
-        <v>129.14</v>
+        <v>137.89</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>17</v>
       </c>
       <c r="J39" t="n">
-        <v>-143.89</v>
+        <v>-144.27</v>
       </c>
       <c r="K39" t="n">
-        <v>-120.73</v>
+        <v>-121.05</v>
       </c>
       <c r="L39" t="n">
-        <v>187.83</v>
+        <v>188.32</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>-103.5</v>
+        <v>-100.33</v>
       </c>
       <c r="K40" t="n">
-        <v>-236.85</v>
+        <v>-229.58</v>
       </c>
       <c r="L40" t="n">
-        <v>258.48</v>
+        <v>250.55</v>
       </c>
     </row>
     <row r="41">
@@ -1777,10 +1777,10 @@
         <v>0.79</v>
       </c>
       <c r="K41" t="n">
-        <v>317.78</v>
+        <v>317.14</v>
       </c>
       <c r="L41" t="n">
-        <v>317.78</v>
+        <v>317.14</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>16</v>
       </c>
       <c r="J42" t="n">
-        <v>-24.67</v>
+        <v>-24.47</v>
       </c>
       <c r="K42" t="n">
-        <v>-286.56</v>
+        <v>-284.24</v>
       </c>
       <c r="L42" t="n">
-        <v>287.62</v>
+        <v>285.29</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>16</v>
       </c>
       <c r="J43" t="n">
-        <v>22.47</v>
+        <v>22.98</v>
       </c>
       <c r="K43" t="n">
-        <v>-291.12</v>
+        <v>-297.83</v>
       </c>
       <c r="L43" t="n">
-        <v>291.99</v>
+        <v>298.72</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>-53.76</v>
+        <v>-51.87</v>
       </c>
       <c r="K44" t="n">
-        <v>73.53</v>
+        <v>70.95</v>
       </c>
       <c r="L44" t="n">
-        <v>91.09</v>
+        <v>87.89</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>51</v>
+        <v>52.4</v>
       </c>
       <c r="K45" t="n">
-        <v>43.84</v>
+        <v>45.04</v>
       </c>
       <c r="L45" t="n">
-        <v>67.25</v>
+        <v>69.09</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>16</v>
       </c>
       <c r="J46" t="n">
-        <v>-49.97</v>
+        <v>-51.94</v>
       </c>
       <c r="K46" t="n">
-        <v>31.4</v>
+        <v>32.64</v>
       </c>
       <c r="L46" t="n">
-        <v>59.02</v>
+        <v>61.35</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>16</v>
       </c>
       <c r="J47" t="n">
-        <v>95.36</v>
+        <v>90.84999999999999</v>
       </c>
       <c r="K47" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="L47" t="n">
-        <v>95.38</v>
+        <v>90.87</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>-19.63</v>
+        <v>-19.45</v>
       </c>
       <c r="K48" t="n">
-        <v>93.47</v>
+        <v>92.59</v>
       </c>
       <c r="L48" t="n">
-        <v>95.51000000000001</v>
+        <v>94.61</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>17</v>
       </c>
       <c r="J49" t="n">
-        <v>-112.79</v>
+        <v>-104.9</v>
       </c>
       <c r="K49" t="n">
-        <v>-90.72</v>
+        <v>-84.38</v>
       </c>
       <c r="L49" t="n">
-        <v>144.75</v>
+        <v>134.63</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>-98.31999999999999</v>
+        <v>-103.3</v>
       </c>
       <c r="K50" t="n">
-        <v>-24.2</v>
+        <v>-25.42</v>
       </c>
       <c r="L50" t="n">
-        <v>101.26</v>
+        <v>106.38</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>19</v>
       </c>
       <c r="J51" t="n">
-        <v>96.47</v>
+        <v>101.56</v>
       </c>
       <c r="K51" t="n">
-        <v>9.779999999999999</v>
+        <v>10.3</v>
       </c>
       <c r="L51" t="n">
-        <v>96.97</v>
+        <v>102.08</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>99.76000000000001</v>
+        <v>104.58</v>
       </c>
       <c r="K52" t="n">
-        <v>-42.25</v>
+        <v>-44.29</v>
       </c>
       <c r="L52" t="n">
-        <v>108.34</v>
+        <v>113.57</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>19</v>
       </c>
       <c r="J53" t="n">
-        <v>129.82</v>
+        <v>147.4</v>
       </c>
       <c r="K53" t="n">
-        <v>-101.82</v>
+        <v>-115.61</v>
       </c>
       <c r="L53" t="n">
-        <v>164.99</v>
+        <v>187.33</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>41.68</v>
+        <v>43.71</v>
       </c>
       <c r="K54" t="n">
-        <v>132.4</v>
+        <v>138.82</v>
       </c>
       <c r="L54" t="n">
-        <v>138.8</v>
+        <v>145.54</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>-165.67</v>
+        <v>-161.59</v>
       </c>
       <c r="K55" t="n">
-        <v>227.15</v>
+        <v>221.55</v>
       </c>
       <c r="L55" t="n">
-        <v>281.15</v>
+        <v>274.22</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>17</v>
       </c>
       <c r="J56" t="n">
-        <v>193.41</v>
+        <v>201.1</v>
       </c>
       <c r="K56" t="n">
-        <v>105.75</v>
+        <v>109.95</v>
       </c>
       <c r="L56" t="n">
-        <v>220.43</v>
+        <v>229.2</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>-173.51</v>
+        <v>-184.46</v>
       </c>
       <c r="K57" t="n">
-        <v>182.2</v>
+        <v>193.69</v>
       </c>
       <c r="L57" t="n">
-        <v>251.6</v>
+        <v>267.47</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>17</v>
       </c>
       <c r="J58" t="n">
-        <v>-220.07</v>
+        <v>-230.64</v>
       </c>
       <c r="K58" t="n">
-        <v>-252.44</v>
+        <v>-264.55</v>
       </c>
       <c r="L58" t="n">
-        <v>334.9</v>
+        <v>350.97</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>20</v>
       </c>
       <c r="J59" t="n">
-        <v>-82.17</v>
+        <v>-78.27</v>
       </c>
       <c r="K59" t="n">
-        <v>-42.64</v>
+        <v>-40.62</v>
       </c>
       <c r="L59" t="n">
-        <v>92.56999999999999</v>
+        <v>88.19</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>17</v>
       </c>
       <c r="J60" t="n">
-        <v>77.48</v>
+        <v>74.43000000000001</v>
       </c>
       <c r="K60" t="n">
-        <v>57.16</v>
+        <v>54.91</v>
       </c>
       <c r="L60" t="n">
-        <v>96.28</v>
+        <v>92.48999999999999</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>28.09</v>
+        <v>27.93</v>
       </c>
       <c r="K61" t="n">
-        <v>-64.69</v>
+        <v>-64.31999999999999</v>
       </c>
       <c r="L61" t="n">
-        <v>70.53</v>
+        <v>70.12</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>16</v>
       </c>
       <c r="J62" t="n">
-        <v>-48.37</v>
+        <v>-50.35</v>
       </c>
       <c r="K62" t="n">
-        <v>45.46</v>
+        <v>47.32</v>
       </c>
       <c r="L62" t="n">
-        <v>66.38</v>
+        <v>69.09999999999999</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>-78.73999999999999</v>
+        <v>-74.48999999999999</v>
       </c>
       <c r="K63" t="n">
-        <v>-93.13</v>
+        <v>-88.09999999999999</v>
       </c>
       <c r="L63" t="n">
-        <v>121.96</v>
+        <v>115.37</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>20</v>
       </c>
       <c r="J64" t="n">
-        <v>-29.26</v>
+        <v>-28.38</v>
       </c>
       <c r="K64" t="n">
-        <v>90.58</v>
+        <v>87.86</v>
       </c>
       <c r="L64" t="n">
-        <v>95.19</v>
+        <v>92.33</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>16</v>
       </c>
       <c r="J65" t="n">
-        <v>-89.95</v>
+        <v>-93.76000000000001</v>
       </c>
       <c r="K65" t="n">
-        <v>57.61</v>
+        <v>60.05</v>
       </c>
       <c r="L65" t="n">
-        <v>106.82</v>
+        <v>111.34</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>-216.85</v>
+        <v>-205.44</v>
       </c>
       <c r="K66" t="n">
-        <v>94.72</v>
+        <v>89.73999999999999</v>
       </c>
       <c r="L66" t="n">
-        <v>236.64</v>
+        <v>224.19</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>19</v>
       </c>
       <c r="J67" t="n">
-        <v>-140.18</v>
+        <v>-138.76</v>
       </c>
       <c r="K67" t="n">
-        <v>-38.25</v>
+        <v>-37.86</v>
       </c>
       <c r="L67" t="n">
-        <v>145.31</v>
+        <v>143.83</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>20</v>
       </c>
       <c r="J68" t="n">
-        <v>-229.12</v>
+        <v>-233.57</v>
       </c>
       <c r="K68" t="n">
-        <v>-159.1</v>
+        <v>-162.19</v>
       </c>
       <c r="L68" t="n">
-        <v>278.94</v>
+        <v>284.36</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>19</v>
       </c>
       <c r="J69" t="n">
-        <v>155.09</v>
+        <v>158.16</v>
       </c>
       <c r="K69" t="n">
-        <v>19.96</v>
+        <v>20.36</v>
       </c>
       <c r="L69" t="n">
-        <v>156.37</v>
+        <v>159.47</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>19</v>
       </c>
       <c r="J70" t="n">
-        <v>-229.16</v>
+        <v>-225.46</v>
       </c>
       <c r="K70" t="n">
-        <v>-53.99</v>
+        <v>-53.12</v>
       </c>
       <c r="L70" t="n">
-        <v>235.43</v>
+        <v>231.64</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>19</v>
       </c>
       <c r="J71" t="n">
-        <v>-380</v>
+        <v>-408.48</v>
       </c>
       <c r="K71" t="n">
-        <v>323.94</v>
+        <v>348.22</v>
       </c>
       <c r="L71" t="n">
-        <v>499.34</v>
+        <v>536.77</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>17</v>
       </c>
       <c r="J72" t="n">
-        <v>-114.25</v>
+        <v>-125.37</v>
       </c>
       <c r="K72" t="n">
-        <v>-168.03</v>
+        <v>-184.38</v>
       </c>
       <c r="L72" t="n">
-        <v>203.2</v>
+        <v>222.96</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>19</v>
       </c>
       <c r="J73" t="n">
-        <v>236.74</v>
+        <v>271.3</v>
       </c>
       <c r="K73" t="n">
-        <v>15.3</v>
+        <v>17.53</v>
       </c>
       <c r="L73" t="n">
-        <v>237.24</v>
+        <v>271.86</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>17</v>
       </c>
       <c r="J74" t="n">
-        <v>14.48</v>
+        <v>14.37</v>
       </c>
       <c r="K74" t="n">
-        <v>-75.25</v>
+        <v>-74.72</v>
       </c>
       <c r="L74" t="n">
-        <v>76.63</v>
+        <v>76.09</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>20</v>
       </c>
       <c r="J75" t="n">
-        <v>-12.86</v>
+        <v>-11.81</v>
       </c>
       <c r="K75" t="n">
-        <v>-142.62</v>
+        <v>-131</v>
       </c>
       <c r="L75" t="n">
-        <v>143.2</v>
+        <v>131.53</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>-21.14</v>
+        <v>-18.36</v>
       </c>
       <c r="K76" t="n">
-        <v>-117.92</v>
+        <v>-102.41</v>
       </c>
       <c r="L76" t="n">
-        <v>119.8</v>
+        <v>104.05</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>122.11</v>
+        <v>109.94</v>
       </c>
       <c r="K77" t="n">
-        <v>-221.2</v>
+        <v>-199.15</v>
       </c>
       <c r="L77" t="n">
-        <v>252.66</v>
+        <v>227.48</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>-64.51000000000001</v>
+        <v>-62.76</v>
       </c>
       <c r="K78" t="n">
-        <v>83.77</v>
+        <v>81.5</v>
       </c>
       <c r="L78" t="n">
-        <v>105.73</v>
+        <v>102.86</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>19</v>
       </c>
       <c r="J79" t="n">
-        <v>35.03</v>
+        <v>35.6</v>
       </c>
       <c r="K79" t="n">
-        <v>64.84</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="L79" t="n">
-        <v>73.7</v>
+        <v>74.90000000000001</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>18</v>
       </c>
       <c r="J80" t="n">
-        <v>123.54</v>
+        <v>126.03</v>
       </c>
       <c r="K80" t="n">
-        <v>17.75</v>
+        <v>18.11</v>
       </c>
       <c r="L80" t="n">
-        <v>124.81</v>
+        <v>127.32</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>236.35</v>
+        <v>224.69</v>
       </c>
       <c r="K81" t="n">
-        <v>-0.25</v>
+        <v>-0.24</v>
       </c>
       <c r="L81" t="n">
-        <v>236.35</v>
+        <v>224.69</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>20</v>
       </c>
       <c r="J82" t="n">
-        <v>-119.44</v>
+        <v>-118.48</v>
       </c>
       <c r="K82" t="n">
-        <v>90.7</v>
+        <v>89.98</v>
       </c>
       <c r="L82" t="n">
-        <v>149.97</v>
+        <v>148.78</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>-225.9</v>
+        <v>-221.9</v>
       </c>
       <c r="K83" t="n">
-        <v>-147.19</v>
+        <v>-144.58</v>
       </c>
       <c r="L83" t="n">
-        <v>269.62</v>
+        <v>264.85</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>19</v>
       </c>
       <c r="J84" t="n">
-        <v>27.13</v>
+        <v>26.74</v>
       </c>
       <c r="K84" t="n">
-        <v>-50.86</v>
+        <v>-50.13</v>
       </c>
       <c r="L84" t="n">
-        <v>57.65</v>
+        <v>56.82</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>19</v>
       </c>
       <c r="J85" t="n">
-        <v>22.46</v>
+        <v>22.38</v>
       </c>
       <c r="K85" t="n">
-        <v>214.44</v>
+        <v>213.68</v>
       </c>
       <c r="L85" t="n">
-        <v>215.61</v>
+        <v>214.85</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>19</v>
       </c>
       <c r="J86" t="n">
-        <v>-155.71</v>
+        <v>-164.83</v>
       </c>
       <c r="K86" t="n">
-        <v>-375.02</v>
+        <v>-396.97</v>
       </c>
       <c r="L86" t="n">
-        <v>406.06</v>
+        <v>429.83</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>137.63</v>
+        <v>167.15</v>
       </c>
       <c r="K87" t="n">
-        <v>190.68</v>
+        <v>231.58</v>
       </c>
       <c r="L87" t="n">
-        <v>235.16</v>
+        <v>285.6</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>243.2</v>
+        <v>279.95</v>
       </c>
       <c r="K88" t="n">
-        <v>-50.22</v>
+        <v>-57.81</v>
       </c>
       <c r="L88" t="n">
-        <v>248.33</v>
+        <v>285.85</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-08-26.xlsx
+++ b/output/2025-08-26.xlsx
@@ -640,13 +640,13 @@
         <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>63.43</v>
+        <v>63.6</v>
       </c>
       <c r="K14" t="n">
-        <v>-46.15</v>
+        <v>-46.28</v>
       </c>
       <c r="L14" t="n">
-        <v>78.44</v>
+        <v>78.66</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>-108.35</v>
+        <v>-104.64</v>
       </c>
       <c r="K15" t="n">
-        <v>-8.25</v>
+        <v>-7.97</v>
       </c>
       <c r="L15" t="n">
-        <v>108.66</v>
+        <v>104.94</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>16</v>
       </c>
       <c r="J16" t="n">
-        <v>-87.63</v>
+        <v>-86.64</v>
       </c>
       <c r="K16" t="n">
-        <v>-20.22</v>
+        <v>-20</v>
       </c>
       <c r="L16" t="n">
-        <v>89.93000000000001</v>
+        <v>88.92</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>103.53</v>
+        <v>97.5</v>
       </c>
       <c r="K17" t="n">
-        <v>116.2</v>
+        <v>109.44</v>
       </c>
       <c r="L17" t="n">
-        <v>155.63</v>
+        <v>146.57</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>20</v>
       </c>
       <c r="J18" t="n">
-        <v>-99.3</v>
+        <v>-98.34</v>
       </c>
       <c r="K18" t="n">
         <v>0.14</v>
       </c>
       <c r="L18" t="n">
-        <v>99.3</v>
+        <v>98.34</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>57.81</v>
+        <v>58.86</v>
       </c>
       <c r="K19" t="n">
-        <v>-71.42</v>
+        <v>-72.72</v>
       </c>
       <c r="L19" t="n">
-        <v>91.88</v>
+        <v>93.56</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>19</v>
       </c>
       <c r="J20" t="n">
-        <v>-47.89</v>
+        <v>-51.24</v>
       </c>
       <c r="K20" t="n">
-        <v>-77.13</v>
+        <v>-82.52</v>
       </c>
       <c r="L20" t="n">
-        <v>90.79000000000001</v>
+        <v>97.14</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>16</v>
       </c>
       <c r="J21" t="n">
-        <v>-110.59</v>
+        <v>-108.71</v>
       </c>
       <c r="K21" t="n">
-        <v>-124.54</v>
+        <v>-122.41</v>
       </c>
       <c r="L21" t="n">
-        <v>166.56</v>
+        <v>163.71</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>18</v>
       </c>
       <c r="J22" t="n">
-        <v>164.98</v>
+        <v>160.39</v>
       </c>
       <c r="K22" t="n">
-        <v>-30.91</v>
+        <v>-30.05</v>
       </c>
       <c r="L22" t="n">
-        <v>167.85</v>
+        <v>163.18</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>20</v>
       </c>
       <c r="J23" t="n">
-        <v>-307.89</v>
+        <v>-289.9</v>
       </c>
       <c r="K23" t="n">
-        <v>4.56</v>
+        <v>4.29</v>
       </c>
       <c r="L23" t="n">
-        <v>307.92</v>
+        <v>289.93</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>285.67</v>
+        <v>266.46</v>
       </c>
       <c r="K24" t="n">
-        <v>-187.31</v>
+        <v>-174.72</v>
       </c>
       <c r="L24" t="n">
-        <v>341.61</v>
+        <v>318.63</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>16</v>
       </c>
       <c r="J25" t="n">
-        <v>-133.59</v>
+        <v>-141.38</v>
       </c>
       <c r="K25" t="n">
-        <v>-46.21</v>
+        <v>-48.9</v>
       </c>
       <c r="L25" t="n">
-        <v>141.36</v>
+        <v>149.6</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>19</v>
       </c>
       <c r="J26" t="n">
-        <v>32.49</v>
+        <v>34.78</v>
       </c>
       <c r="K26" t="n">
-        <v>-14.72</v>
+        <v>-15.76</v>
       </c>
       <c r="L26" t="n">
-        <v>35.67</v>
+        <v>38.18</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>20</v>
       </c>
       <c r="J27" t="n">
-        <v>288.44</v>
+        <v>283.78</v>
       </c>
       <c r="K27" t="n">
-        <v>-158.35</v>
+        <v>-155.79</v>
       </c>
       <c r="L27" t="n">
-        <v>329.04</v>
+        <v>323.73</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>19</v>
       </c>
       <c r="J28" t="n">
-        <v>172.19</v>
+        <v>185.15</v>
       </c>
       <c r="K28" t="n">
-        <v>35</v>
+        <v>37.63</v>
       </c>
       <c r="L28" t="n">
-        <v>175.71</v>
+        <v>188.94</v>
       </c>
     </row>
     <row r="29">
@@ -1273,10 +1273,10 @@
         <v>-28.34</v>
       </c>
       <c r="K29" t="n">
-        <v>80.04000000000001</v>
+        <v>80.02</v>
       </c>
       <c r="L29" t="n">
-        <v>84.91</v>
+        <v>84.89</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>17</v>
       </c>
       <c r="J30" t="n">
-        <v>-9.390000000000001</v>
+        <v>-10.12</v>
       </c>
       <c r="K30" t="n">
-        <v>13.18</v>
+        <v>14.2</v>
       </c>
       <c r="L30" t="n">
-        <v>16.19</v>
+        <v>17.44</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>-72.23</v>
+        <v>-72.56</v>
       </c>
       <c r="K31" t="n">
-        <v>36.39</v>
+        <v>36.56</v>
       </c>
       <c r="L31" t="n">
-        <v>80.88</v>
+        <v>81.25</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>16</v>
       </c>
       <c r="J32" t="n">
-        <v>88.83</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="K32" t="n">
-        <v>-98.94</v>
+        <v>-94.70999999999999</v>
       </c>
       <c r="L32" t="n">
-        <v>132.96</v>
+        <v>127.28</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>18</v>
       </c>
       <c r="J33" t="n">
-        <v>45.29</v>
+        <v>45.78</v>
       </c>
       <c r="K33" t="n">
-        <v>78.7</v>
+        <v>79.55</v>
       </c>
       <c r="L33" t="n">
-        <v>90.81</v>
+        <v>91.78</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>17</v>
       </c>
       <c r="J34" t="n">
-        <v>77.28</v>
+        <v>78.44</v>
       </c>
       <c r="K34" t="n">
-        <v>-48.62</v>
+        <v>-49.35</v>
       </c>
       <c r="L34" t="n">
-        <v>91.31</v>
+        <v>92.67</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>20</v>
       </c>
       <c r="J35" t="n">
-        <v>-52.58</v>
+        <v>-56.42</v>
       </c>
       <c r="K35" t="n">
-        <v>75.02</v>
+        <v>80.5</v>
       </c>
       <c r="L35" t="n">
-        <v>91.61</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>16</v>
       </c>
       <c r="J36" t="n">
-        <v>-147.79</v>
+        <v>-148.79</v>
       </c>
       <c r="K36" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="L36" t="n">
-        <v>147.8</v>
+        <v>148.8</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>-1.13</v>
+        <v>-1.09</v>
       </c>
       <c r="K37" t="n">
-        <v>212.04</v>
+        <v>203.93</v>
       </c>
       <c r="L37" t="n">
-        <v>212.04</v>
+        <v>203.93</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>19</v>
       </c>
       <c r="J38" t="n">
-        <v>-108.41</v>
+        <v>-115.39</v>
       </c>
       <c r="K38" t="n">
-        <v>-85.20999999999999</v>
+        <v>-90.70999999999999</v>
       </c>
       <c r="L38" t="n">
-        <v>137.89</v>
+        <v>146.78</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>17</v>
       </c>
       <c r="J39" t="n">
-        <v>-144.27</v>
+        <v>-144.34</v>
       </c>
       <c r="K39" t="n">
-        <v>-121.05</v>
+        <v>-121.11</v>
       </c>
       <c r="L39" t="n">
-        <v>188.32</v>
+        <v>188.42</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>-100.33</v>
+        <v>-96.51000000000001</v>
       </c>
       <c r="K40" t="n">
-        <v>-229.58</v>
+        <v>-220.86</v>
       </c>
       <c r="L40" t="n">
-        <v>250.55</v>
+        <v>241.02</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
       <c r="K41" t="n">
-        <v>317.14</v>
+        <v>309.57</v>
       </c>
       <c r="L41" t="n">
-        <v>317.14</v>
+        <v>309.57</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>16</v>
       </c>
       <c r="J42" t="n">
-        <v>-24.47</v>
+        <v>-24.06</v>
       </c>
       <c r="K42" t="n">
-        <v>-284.24</v>
+        <v>-279.45</v>
       </c>
       <c r="L42" t="n">
-        <v>285.29</v>
+        <v>280.49</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>16</v>
       </c>
       <c r="J43" t="n">
-        <v>22.98</v>
+        <v>22.83</v>
       </c>
       <c r="K43" t="n">
-        <v>-297.83</v>
+        <v>-295.89</v>
       </c>
       <c r="L43" t="n">
-        <v>298.72</v>
+        <v>296.77</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>-51.87</v>
+        <v>-51.02</v>
       </c>
       <c r="K44" t="n">
-        <v>70.95</v>
+        <v>69.79000000000001</v>
       </c>
       <c r="L44" t="n">
-        <v>87.89</v>
+        <v>86.45</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>52.4</v>
+        <v>53.99</v>
       </c>
       <c r="K45" t="n">
-        <v>45.04</v>
+        <v>46.41</v>
       </c>
       <c r="L45" t="n">
-        <v>69.09</v>
+        <v>71.2</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>16</v>
       </c>
       <c r="J46" t="n">
-        <v>-51.94</v>
+        <v>-55.17</v>
       </c>
       <c r="K46" t="n">
-        <v>32.64</v>
+        <v>34.67</v>
       </c>
       <c r="L46" t="n">
-        <v>61.35</v>
+        <v>65.16</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>16</v>
       </c>
       <c r="J47" t="n">
-        <v>90.84999999999999</v>
+        <v>93.41</v>
       </c>
       <c r="K47" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="L47" t="n">
-        <v>90.87</v>
+        <v>93.43000000000001</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>-19.45</v>
+        <v>-19.49</v>
       </c>
       <c r="K48" t="n">
-        <v>92.59</v>
+        <v>92.8</v>
       </c>
       <c r="L48" t="n">
-        <v>94.61</v>
+        <v>94.81999999999999</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>17</v>
       </c>
       <c r="J49" t="n">
-        <v>-104.9</v>
+        <v>-100.8</v>
       </c>
       <c r="K49" t="n">
-        <v>-84.38</v>
+        <v>-81.08</v>
       </c>
       <c r="L49" t="n">
-        <v>134.63</v>
+        <v>129.36</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>-103.3</v>
+        <v>-109.65</v>
       </c>
       <c r="K50" t="n">
-        <v>-25.42</v>
+        <v>-26.99</v>
       </c>
       <c r="L50" t="n">
-        <v>106.38</v>
+        <v>112.92</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>19</v>
       </c>
       <c r="J51" t="n">
-        <v>101.56</v>
+        <v>108.28</v>
       </c>
       <c r="K51" t="n">
-        <v>10.3</v>
+        <v>10.98</v>
       </c>
       <c r="L51" t="n">
-        <v>102.08</v>
+        <v>108.84</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>104.58</v>
+        <v>111.33</v>
       </c>
       <c r="K52" t="n">
-        <v>-44.29</v>
+        <v>-47.15</v>
       </c>
       <c r="L52" t="n">
-        <v>113.57</v>
+        <v>120.9</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>19</v>
       </c>
       <c r="J53" t="n">
-        <v>147.4</v>
+        <v>157.4</v>
       </c>
       <c r="K53" t="n">
-        <v>-115.61</v>
+        <v>-123.45</v>
       </c>
       <c r="L53" t="n">
-        <v>187.33</v>
+        <v>200.03</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>43.71</v>
+        <v>45.77</v>
       </c>
       <c r="K54" t="n">
-        <v>138.82</v>
+        <v>145.38</v>
       </c>
       <c r="L54" t="n">
-        <v>145.54</v>
+        <v>152.42</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>-161.59</v>
+        <v>-155.39</v>
       </c>
       <c r="K55" t="n">
-        <v>221.55</v>
+        <v>213.05</v>
       </c>
       <c r="L55" t="n">
-        <v>274.22</v>
+        <v>263.69</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>17</v>
       </c>
       <c r="J56" t="n">
-        <v>201.1</v>
+        <v>206.2</v>
       </c>
       <c r="K56" t="n">
-        <v>109.95</v>
+        <v>112.74</v>
       </c>
       <c r="L56" t="n">
-        <v>229.2</v>
+        <v>235.01</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>-184.46</v>
+        <v>-188.87</v>
       </c>
       <c r="K57" t="n">
-        <v>193.69</v>
+        <v>198.32</v>
       </c>
       <c r="L57" t="n">
-        <v>267.47</v>
+        <v>273.87</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>17</v>
       </c>
       <c r="J58" t="n">
-        <v>-230.64</v>
+        <v>-228.71</v>
       </c>
       <c r="K58" t="n">
-        <v>-264.55</v>
+        <v>-262.34</v>
       </c>
       <c r="L58" t="n">
-        <v>350.97</v>
+        <v>348.04</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>20</v>
       </c>
       <c r="J59" t="n">
-        <v>-78.27</v>
+        <v>-76.83</v>
       </c>
       <c r="K59" t="n">
-        <v>-40.62</v>
+        <v>-39.87</v>
       </c>
       <c r="L59" t="n">
-        <v>88.19</v>
+        <v>86.56</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>17</v>
       </c>
       <c r="J60" t="n">
-        <v>74.43000000000001</v>
+        <v>73</v>
       </c>
       <c r="K60" t="n">
-        <v>54.91</v>
+        <v>53.85</v>
       </c>
       <c r="L60" t="n">
-        <v>92.48999999999999</v>
+        <v>90.70999999999999</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>27.93</v>
+        <v>28.86</v>
       </c>
       <c r="K61" t="n">
-        <v>-64.31999999999999</v>
+        <v>-66.45</v>
       </c>
       <c r="L61" t="n">
-        <v>70.12</v>
+        <v>72.44</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>16</v>
       </c>
       <c r="J62" t="n">
-        <v>-50.35</v>
+        <v>-53.57</v>
       </c>
       <c r="K62" t="n">
-        <v>47.32</v>
+        <v>50.34</v>
       </c>
       <c r="L62" t="n">
-        <v>69.09999999999999</v>
+        <v>73.51000000000001</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>-74.48999999999999</v>
+        <v>-72.92</v>
       </c>
       <c r="K63" t="n">
-        <v>-88.09999999999999</v>
+        <v>-86.23999999999999</v>
       </c>
       <c r="L63" t="n">
-        <v>115.37</v>
+        <v>112.94</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>20</v>
       </c>
       <c r="J64" t="n">
-        <v>-28.38</v>
+        <v>-28.41</v>
       </c>
       <c r="K64" t="n">
-        <v>87.86</v>
+        <v>87.95</v>
       </c>
       <c r="L64" t="n">
-        <v>92.33</v>
+        <v>92.43000000000001</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>16</v>
       </c>
       <c r="J65" t="n">
-        <v>-93.76000000000001</v>
+        <v>-99.06999999999999</v>
       </c>
       <c r="K65" t="n">
-        <v>60.05</v>
+        <v>63.45</v>
       </c>
       <c r="L65" t="n">
-        <v>111.34</v>
+        <v>117.65</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>-205.44</v>
+        <v>-195.35</v>
       </c>
       <c r="K66" t="n">
-        <v>89.73999999999999</v>
+        <v>85.33</v>
       </c>
       <c r="L66" t="n">
-        <v>224.19</v>
+        <v>213.17</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>19</v>
       </c>
       <c r="J67" t="n">
-        <v>-138.76</v>
+        <v>-138.65</v>
       </c>
       <c r="K67" t="n">
-        <v>-37.86</v>
+        <v>-37.83</v>
       </c>
       <c r="L67" t="n">
-        <v>143.83</v>
+        <v>143.72</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>20</v>
       </c>
       <c r="J68" t="n">
-        <v>-233.57</v>
+        <v>-224.26</v>
       </c>
       <c r="K68" t="n">
-        <v>-162.19</v>
+        <v>-155.72</v>
       </c>
       <c r="L68" t="n">
-        <v>284.36</v>
+        <v>273.02</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>19</v>
       </c>
       <c r="J69" t="n">
-        <v>158.16</v>
+        <v>161.34</v>
       </c>
       <c r="K69" t="n">
-        <v>20.36</v>
+        <v>20.77</v>
       </c>
       <c r="L69" t="n">
-        <v>159.47</v>
+        <v>162.67</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>19</v>
       </c>
       <c r="J70" t="n">
-        <v>-225.46</v>
+        <v>-219.26</v>
       </c>
       <c r="K70" t="n">
-        <v>-53.12</v>
+        <v>-51.66</v>
       </c>
       <c r="L70" t="n">
-        <v>231.64</v>
+        <v>225.26</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>19</v>
       </c>
       <c r="J71" t="n">
-        <v>-408.48</v>
+        <v>-388.26</v>
       </c>
       <c r="K71" t="n">
-        <v>348.22</v>
+        <v>330.98</v>
       </c>
       <c r="L71" t="n">
-        <v>536.77</v>
+        <v>510.19</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>17</v>
       </c>
       <c r="J72" t="n">
-        <v>-125.37</v>
+        <v>-132.27</v>
       </c>
       <c r="K72" t="n">
-        <v>-184.38</v>
+        <v>-194.53</v>
       </c>
       <c r="L72" t="n">
-        <v>222.96</v>
+        <v>235.23</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>19</v>
       </c>
       <c r="J73" t="n">
-        <v>271.3</v>
+        <v>282.33</v>
       </c>
       <c r="K73" t="n">
-        <v>17.53</v>
+        <v>18.24</v>
       </c>
       <c r="L73" t="n">
-        <v>271.86</v>
+        <v>282.92</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>17</v>
       </c>
       <c r="J74" t="n">
-        <v>14.37</v>
+        <v>14.69</v>
       </c>
       <c r="K74" t="n">
-        <v>-74.72</v>
+        <v>-76.34</v>
       </c>
       <c r="L74" t="n">
-        <v>76.09</v>
+        <v>77.73999999999999</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>20</v>
       </c>
       <c r="J75" t="n">
-        <v>-11.81</v>
+        <v>-11.09</v>
       </c>
       <c r="K75" t="n">
-        <v>-131</v>
+        <v>-122.97</v>
       </c>
       <c r="L75" t="n">
-        <v>131.53</v>
+        <v>123.47</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>-18.36</v>
+        <v>-17.97</v>
       </c>
       <c r="K76" t="n">
-        <v>-102.41</v>
+        <v>-100.25</v>
       </c>
       <c r="L76" t="n">
-        <v>104.05</v>
+        <v>101.85</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>109.94</v>
+        <v>100.33</v>
       </c>
       <c r="K77" t="n">
-        <v>-199.15</v>
+        <v>-181.74</v>
       </c>
       <c r="L77" t="n">
-        <v>227.48</v>
+        <v>207.59</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>-62.76</v>
+        <v>-63.03</v>
       </c>
       <c r="K78" t="n">
-        <v>81.5</v>
+        <v>81.84999999999999</v>
       </c>
       <c r="L78" t="n">
-        <v>102.86</v>
+        <v>103.3</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>19</v>
       </c>
       <c r="J79" t="n">
-        <v>35.6</v>
+        <v>37.66</v>
       </c>
       <c r="K79" t="n">
-        <v>65.90000000000001</v>
+        <v>69.70999999999999</v>
       </c>
       <c r="L79" t="n">
-        <v>74.90000000000001</v>
+        <v>79.23</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>18</v>
       </c>
       <c r="J80" t="n">
-        <v>126.03</v>
+        <v>130.25</v>
       </c>
       <c r="K80" t="n">
-        <v>18.11</v>
+        <v>18.72</v>
       </c>
       <c r="L80" t="n">
-        <v>127.32</v>
+        <v>131.59</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>224.69</v>
+        <v>216.6</v>
       </c>
       <c r="K81" t="n">
-        <v>-0.24</v>
+        <v>-0.23</v>
       </c>
       <c r="L81" t="n">
-        <v>224.69</v>
+        <v>216.6</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>20</v>
       </c>
       <c r="J82" t="n">
-        <v>-118.48</v>
+        <v>-118.87</v>
       </c>
       <c r="K82" t="n">
-        <v>89.98</v>
+        <v>90.27</v>
       </c>
       <c r="L82" t="n">
-        <v>148.78</v>
+        <v>149.26</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>-221.9</v>
+        <v>-215.18</v>
       </c>
       <c r="K83" t="n">
-        <v>-144.58</v>
+        <v>-140.21</v>
       </c>
       <c r="L83" t="n">
-        <v>264.85</v>
+        <v>256.83</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>19</v>
       </c>
       <c r="J84" t="n">
-        <v>26.74</v>
+        <v>29.07</v>
       </c>
       <c r="K84" t="n">
-        <v>-50.13</v>
+        <v>-54.51</v>
       </c>
       <c r="L84" t="n">
-        <v>56.82</v>
+        <v>61.77</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>19</v>
       </c>
       <c r="J85" t="n">
-        <v>22.38</v>
+        <v>22.11</v>
       </c>
       <c r="K85" t="n">
-        <v>213.68</v>
+        <v>211.13</v>
       </c>
       <c r="L85" t="n">
-        <v>214.85</v>
+        <v>212.28</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>19</v>
       </c>
       <c r="J86" t="n">
-        <v>-164.83</v>
+        <v>-160.26</v>
       </c>
       <c r="K86" t="n">
-        <v>-396.97</v>
+        <v>-385.98</v>
       </c>
       <c r="L86" t="n">
-        <v>429.83</v>
+        <v>417.93</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>167.15</v>
+        <v>180.24</v>
       </c>
       <c r="K87" t="n">
-        <v>231.58</v>
+        <v>249.71</v>
       </c>
       <c r="L87" t="n">
-        <v>285.6</v>
+        <v>307.96</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>279.95</v>
+        <v>294.07</v>
       </c>
       <c r="K88" t="n">
-        <v>-57.81</v>
+        <v>-60.72</v>
       </c>
       <c r="L88" t="n">
-        <v>285.85</v>
+        <v>300.27</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-08-26.xlsx
+++ b/output/2025-08-26.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>3.06</v>
+        <v>3.32</v>
       </c>
       <c r="F14" t="n">
-        <v>10.92</v>
+        <v>5.42</v>
       </c>
       <c r="G14" t="n">
-        <v>231.2</v>
+        <v>213.4</v>
       </c>
       <c r="H14" t="n">
-        <v>90.5</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J14" t="n">
-        <v>63.6</v>
+        <v>34.25</v>
       </c>
       <c r="K14" t="n">
-        <v>-46.28</v>
+        <v>-83.20999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>78.66</v>
+        <v>89.98999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06:08:52</t>
+          <t>06:08:59</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3.78</v>
+        <v>3.99</v>
       </c>
       <c r="F15" t="n">
-        <v>10.84</v>
+        <v>10.34</v>
       </c>
       <c r="G15" t="n">
-        <v>223.6</v>
+        <v>232.1</v>
       </c>
       <c r="H15" t="n">
-        <v>99.8</v>
+        <v>95.2</v>
       </c>
       <c r="I15" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>-104.64</v>
+        <v>49.43</v>
       </c>
       <c r="K15" t="n">
-        <v>-7.97</v>
+        <v>-50.66</v>
       </c>
       <c r="L15" t="n">
-        <v>104.94</v>
+        <v>70.78</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06:11:27</t>
+          <t>06:09:52</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -712,7 +712,7 @@
         <v>3.36</v>
       </c>
       <c r="F16" t="n">
-        <v>10.63</v>
+        <v>10.39</v>
       </c>
       <c r="G16" t="n">
         <v>234.6</v>
@@ -721,22 +721,22 @@
         <v>90.7</v>
       </c>
       <c r="I16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J16" t="n">
-        <v>-86.64</v>
+        <v>26.97</v>
       </c>
       <c r="K16" t="n">
-        <v>-20</v>
+        <v>-102.14</v>
       </c>
       <c r="L16" t="n">
-        <v>88.92</v>
+        <v>105.64</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06:14:49</t>
+          <t>06:16:02</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,10 +751,10 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>3.45</v>
+        <v>3.58</v>
       </c>
       <c r="F17" t="n">
-        <v>11.16</v>
+        <v>12.09</v>
       </c>
       <c r="G17" t="n">
         <v>234.1</v>
@@ -763,22 +763,22 @@
         <v>100</v>
       </c>
       <c r="I17" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J17" t="n">
-        <v>97.5</v>
+        <v>-50.69</v>
       </c>
       <c r="K17" t="n">
-        <v>109.44</v>
+        <v>133.3</v>
       </c>
       <c r="L17" t="n">
-        <v>146.57</v>
+        <v>142.61</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06:16:25</t>
+          <t>06:17:10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,10 +793,10 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>3.81</v>
+        <v>4.38</v>
       </c>
       <c r="F18" t="n">
-        <v>10.73</v>
+        <v>10.02</v>
       </c>
       <c r="G18" t="n">
         <v>228.6</v>
@@ -805,22 +805,22 @@
         <v>92.8</v>
       </c>
       <c r="I18" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J18" t="n">
-        <v>-98.34</v>
+        <v>7.9</v>
       </c>
       <c r="K18" t="n">
-        <v>0.14</v>
+        <v>-111.55</v>
       </c>
       <c r="L18" t="n">
-        <v>98.34</v>
+        <v>111.83</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06:18:31</t>
+          <t>06:18:47</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,10 +835,10 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>4.09</v>
+        <v>3.71</v>
       </c>
       <c r="F19" t="n">
-        <v>10.43</v>
+        <v>10.4</v>
       </c>
       <c r="G19" t="n">
         <v>213.1</v>
@@ -847,22 +847,22 @@
         <v>95.8</v>
       </c>
       <c r="I19" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J19" t="n">
-        <v>58.86</v>
+        <v>-54.98</v>
       </c>
       <c r="K19" t="n">
-        <v>-72.72</v>
+        <v>78.22</v>
       </c>
       <c r="L19" t="n">
-        <v>93.56</v>
+        <v>95.61</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06:23:48</t>
+          <t>06:23:41</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>3.36</v>
+        <v>3.47</v>
       </c>
       <c r="F20" t="n">
-        <v>11.02</v>
+        <v>9.75</v>
       </c>
       <c r="G20" t="n">
         <v>218.1</v>
@@ -889,22 +889,22 @@
         <v>94.5</v>
       </c>
       <c r="I20" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J20" t="n">
-        <v>-51.24</v>
+        <v>77.25</v>
       </c>
       <c r="K20" t="n">
-        <v>-82.52</v>
+        <v>-88.70999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>97.14</v>
+        <v>117.63</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06:26:04</t>
+          <t>06:25:58</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,10 +919,10 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>3.86</v>
+        <v>3.61</v>
       </c>
       <c r="F21" t="n">
-        <v>10.48</v>
+        <v>9.77</v>
       </c>
       <c r="G21" t="n">
         <v>219.9</v>
@@ -931,22 +931,22 @@
         <v>96.7</v>
       </c>
       <c r="I21" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J21" t="n">
-        <v>-108.71</v>
+        <v>-42.49</v>
       </c>
       <c r="K21" t="n">
-        <v>-122.41</v>
+        <v>-152.97</v>
       </c>
       <c r="L21" t="n">
-        <v>163.71</v>
+        <v>158.77</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06:27:33</t>
+          <t>06:28:14</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,10 +961,10 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>3.7</v>
+        <v>3.37</v>
       </c>
       <c r="F22" t="n">
-        <v>10.81</v>
+        <v>9.9</v>
       </c>
       <c r="G22" t="n">
         <v>221.7</v>
@@ -973,22 +973,22 @@
         <v>87.90000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J22" t="n">
-        <v>160.39</v>
+        <v>89.3</v>
       </c>
       <c r="K22" t="n">
-        <v>-30.05</v>
+        <v>157.23</v>
       </c>
       <c r="L22" t="n">
-        <v>163.18</v>
+        <v>180.82</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06:32:30</t>
+          <t>06:33:13</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,10 +1003,10 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>4.43</v>
+        <v>3.67</v>
       </c>
       <c r="F23" t="n">
-        <v>11.06</v>
+        <v>9.84</v>
       </c>
       <c r="G23" t="n">
         <v>228.4</v>
@@ -1015,22 +1015,22 @@
         <v>91.90000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J23" t="n">
-        <v>-289.9</v>
+        <v>-101.2</v>
       </c>
       <c r="K23" t="n">
-        <v>4.29</v>
+        <v>-296.68</v>
       </c>
       <c r="L23" t="n">
-        <v>289.93</v>
+        <v>313.46</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06:33:56</t>
+          <t>06:35:35</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,10 +1045,10 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>3.69</v>
+        <v>3.82</v>
       </c>
       <c r="F24" t="n">
-        <v>10.23</v>
+        <v>11.62</v>
       </c>
       <c r="G24" t="n">
         <v>219.2</v>
@@ -1060,19 +1060,19 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>266.46</v>
+        <v>-115.71</v>
       </c>
       <c r="K24" t="n">
-        <v>-174.72</v>
+        <v>309.49</v>
       </c>
       <c r="L24" t="n">
-        <v>318.63</v>
+        <v>330.41</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06:36:19</t>
+          <t>06:37:01</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,10 +1087,10 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>3.31</v>
+        <v>3.23</v>
       </c>
       <c r="F25" t="n">
-        <v>10.55</v>
+        <v>7.96</v>
       </c>
       <c r="G25" t="n">
         <v>237.2</v>
@@ -1099,22 +1099,22 @@
         <v>99.2</v>
       </c>
       <c r="I25" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J25" t="n">
-        <v>-141.38</v>
+        <v>-229.4</v>
       </c>
       <c r="K25" t="n">
-        <v>-48.9</v>
+        <v>-86.59999999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>149.6</v>
+        <v>245.2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06:42:14</t>
+          <t>06:42:56</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,10 +1129,10 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>3.8</v>
+        <v>3.76</v>
       </c>
       <c r="F26" t="n">
-        <v>10.33</v>
+        <v>9.07</v>
       </c>
       <c r="G26" t="n">
         <v>219.1</v>
@@ -1141,22 +1141,22 @@
         <v>98.59999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J26" t="n">
-        <v>34.78</v>
+        <v>-71.90000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>-15.76</v>
+        <v>-314.14</v>
       </c>
       <c r="L26" t="n">
-        <v>38.18</v>
+        <v>322.27</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06:44:17</t>
+          <t>06:45:18</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>4.18</v>
+        <v>3.88</v>
       </c>
       <c r="F27" t="n">
-        <v>10.09</v>
+        <v>11.44</v>
       </c>
       <c r="G27" t="n">
-        <v>223.2</v>
+        <v>225</v>
       </c>
       <c r="H27" t="n">
-        <v>96.3</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J27" t="n">
-        <v>283.78</v>
+        <v>-384.28</v>
       </c>
       <c r="K27" t="n">
-        <v>-155.79</v>
+        <v>-171.28</v>
       </c>
       <c r="L27" t="n">
-        <v>323.73</v>
+        <v>420.72</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06:45:27</t>
+          <t>06:47:21</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>3.54</v>
+        <v>4.36</v>
       </c>
       <c r="F28" t="n">
-        <v>10.75</v>
+        <v>9.69</v>
       </c>
       <c r="G28" t="n">
-        <v>222.4</v>
+        <v>232.1</v>
       </c>
       <c r="H28" t="n">
-        <v>99.8</v>
+        <v>96</v>
       </c>
       <c r="I28" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J28" t="n">
-        <v>185.15</v>
+        <v>-36.35</v>
       </c>
       <c r="K28" t="n">
-        <v>37.63</v>
+        <v>-489.33</v>
       </c>
       <c r="L28" t="n">
-        <v>188.94</v>
+        <v>490.68</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06:55:16</t>
+          <t>06:58:47</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>4.16</v>
+        <v>4.06</v>
       </c>
       <c r="F29" t="n">
-        <v>10.72</v>
+        <v>11.67</v>
       </c>
       <c r="G29" t="n">
-        <v>220.3</v>
+        <v>232.5</v>
       </c>
       <c r="H29" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I29" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J29" t="n">
-        <v>-28.34</v>
+        <v>1.65</v>
       </c>
       <c r="K29" t="n">
-        <v>80.02</v>
+        <v>-75.84999999999999</v>
       </c>
       <c r="L29" t="n">
-        <v>84.89</v>
+        <v>75.86</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06:56:30</t>
+          <t>07:00:10</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>3.37</v>
+        <v>3.74</v>
       </c>
       <c r="F30" t="n">
-        <v>10.65</v>
+        <v>7.24</v>
       </c>
       <c r="G30" t="n">
-        <v>232.3</v>
+        <v>226.8</v>
       </c>
       <c r="H30" t="n">
-        <v>97.2</v>
+        <v>96</v>
       </c>
       <c r="I30" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J30" t="n">
-        <v>-10.12</v>
+        <v>-12.89</v>
       </c>
       <c r="K30" t="n">
-        <v>14.2</v>
+        <v>76.83</v>
       </c>
       <c r="L30" t="n">
-        <v>17.44</v>
+        <v>77.90000000000001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06:57:39</t>
+          <t>07:01:24</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>3.89</v>
+        <v>3.86</v>
       </c>
       <c r="F31" t="n">
-        <v>10.92</v>
+        <v>9.92</v>
       </c>
       <c r="G31" t="n">
-        <v>226.5</v>
+        <v>215.9</v>
       </c>
       <c r="H31" t="n">
-        <v>91.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J31" t="n">
-        <v>-72.56</v>
+        <v>34.6</v>
       </c>
       <c r="K31" t="n">
-        <v>36.56</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="L31" t="n">
-        <v>81.25</v>
+        <v>102.18</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07:02:57</t>
+          <t>07:06:21</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>3.77</v>
+        <v>3.55</v>
       </c>
       <c r="F32" t="n">
-        <v>10.83</v>
+        <v>8.49</v>
       </c>
       <c r="G32" t="n">
-        <v>224.7</v>
+        <v>216.2</v>
       </c>
       <c r="H32" t="n">
-        <v>91.90000000000001</v>
+        <v>97</v>
       </c>
       <c r="I32" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J32" t="n">
-        <v>85.04000000000001</v>
+        <v>23.51</v>
       </c>
       <c r="K32" t="n">
-        <v>-94.70999999999999</v>
+        <v>-91.90000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>127.28</v>
+        <v>94.86</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07:05:19</t>
+          <t>07:07:59</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>4.08</v>
+        <v>4.4</v>
       </c>
       <c r="F33" t="n">
-        <v>10.66</v>
+        <v>12.06</v>
       </c>
       <c r="G33" t="n">
-        <v>230.5</v>
+        <v>228.6</v>
       </c>
       <c r="H33" t="n">
-        <v>98.09999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="I33" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J33" t="n">
-        <v>45.78</v>
+        <v>-42.23</v>
       </c>
       <c r="K33" t="n">
-        <v>79.55</v>
+        <v>-70.66</v>
       </c>
       <c r="L33" t="n">
-        <v>91.78</v>
+        <v>82.31</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07:06:24</t>
+          <t>07:10:20</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>4.37</v>
+        <v>4.11</v>
       </c>
       <c r="F34" t="n">
-        <v>10.15</v>
+        <v>12.3</v>
       </c>
       <c r="G34" t="n">
-        <v>207.3</v>
+        <v>223.2</v>
       </c>
       <c r="H34" t="n">
-        <v>95.40000000000001</v>
+        <v>91</v>
       </c>
       <c r="I34" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J34" t="n">
-        <v>78.44</v>
+        <v>-108.75</v>
       </c>
       <c r="K34" t="n">
-        <v>-49.35</v>
+        <v>-58.92</v>
       </c>
       <c r="L34" t="n">
-        <v>92.67</v>
+        <v>123.68</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07:11:01</t>
+          <t>07:14:07</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>3.82</v>
+        <v>4.23</v>
       </c>
       <c r="F35" t="n">
-        <v>10.65</v>
+        <v>10.37</v>
       </c>
       <c r="G35" t="n">
-        <v>218.8</v>
+        <v>208.8</v>
       </c>
       <c r="H35" t="n">
-        <v>88.2</v>
+        <v>93.5</v>
       </c>
       <c r="I35" t="n">
         <v>20</v>
       </c>
       <c r="J35" t="n">
-        <v>-56.42</v>
+        <v>-86.06999999999999</v>
       </c>
       <c r="K35" t="n">
-        <v>80.5</v>
+        <v>84.05</v>
       </c>
       <c r="L35" t="n">
-        <v>98.3</v>
+        <v>120.3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07:13:20</t>
+          <t>07:15:56</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>4.25</v>
+        <v>3.87</v>
       </c>
       <c r="F36" t="n">
-        <v>10.2</v>
+        <v>11.37</v>
       </c>
       <c r="G36" t="n">
-        <v>215.7</v>
+        <v>226.2</v>
       </c>
       <c r="H36" t="n">
-        <v>96.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="I36" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J36" t="n">
-        <v>-148.79</v>
+        <v>-147.16</v>
       </c>
       <c r="K36" t="n">
-        <v>1.89</v>
+        <v>-136.76</v>
       </c>
       <c r="L36" t="n">
-        <v>148.8</v>
+        <v>200.9</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07:14:28</t>
+          <t>07:18:15</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>4.58</v>
+        <v>3.58</v>
       </c>
       <c r="F37" t="n">
-        <v>11.12</v>
+        <v>12.16</v>
       </c>
       <c r="G37" t="n">
-        <v>218.2</v>
+        <v>232.5</v>
       </c>
       <c r="H37" t="n">
-        <v>100</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="I37" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J37" t="n">
-        <v>-1.09</v>
+        <v>121.75</v>
       </c>
       <c r="K37" t="n">
-        <v>203.93</v>
+        <v>117.06</v>
       </c>
       <c r="L37" t="n">
-        <v>203.93</v>
+        <v>168.9</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07:18:50</t>
+          <t>07:22:21</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>4.33</v>
+        <v>3.99</v>
       </c>
       <c r="F38" t="n">
-        <v>10.65</v>
+        <v>12.02</v>
       </c>
       <c r="G38" t="n">
-        <v>221.3</v>
+        <v>223.7</v>
       </c>
       <c r="H38" t="n">
-        <v>95.59999999999999</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="I38" t="n">
         <v>19</v>
       </c>
       <c r="J38" t="n">
-        <v>-115.39</v>
+        <v>-130.48</v>
       </c>
       <c r="K38" t="n">
-        <v>-90.70999999999999</v>
+        <v>-125.32</v>
       </c>
       <c r="L38" t="n">
-        <v>146.78</v>
+        <v>180.91</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07:21:01</t>
+          <t>07:23:16</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>3.55</v>
+        <v>3.86</v>
       </c>
       <c r="F39" t="n">
-        <v>10.65</v>
+        <v>8.06</v>
       </c>
       <c r="G39" t="n">
-        <v>225.4</v>
+        <v>228.1</v>
       </c>
       <c r="H39" t="n">
-        <v>97.90000000000001</v>
+        <v>89.8</v>
       </c>
       <c r="I39" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J39" t="n">
-        <v>-144.34</v>
+        <v>-99.75</v>
       </c>
       <c r="K39" t="n">
-        <v>-121.11</v>
+        <v>146.93</v>
       </c>
       <c r="L39" t="n">
-        <v>188.42</v>
+        <v>177.59</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07:22:06</t>
+          <t>07:25:27</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>3.46</v>
+        <v>3.68</v>
       </c>
       <c r="F40" t="n">
-        <v>11.33</v>
+        <v>7.16</v>
       </c>
       <c r="G40" t="n">
-        <v>235.4</v>
+        <v>229.6</v>
       </c>
       <c r="H40" t="n">
-        <v>98.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="I40" t="n">
         <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>-96.51000000000001</v>
+        <v>200.23</v>
       </c>
       <c r="K40" t="n">
-        <v>-220.86</v>
+        <v>-104.42</v>
       </c>
       <c r="L40" t="n">
-        <v>241.02</v>
+        <v>225.82</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07:26:04</t>
+          <t>07:29:31</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>3.61</v>
+        <v>3.75</v>
       </c>
       <c r="F41" t="n">
-        <v>11.06</v>
+        <v>7.97</v>
       </c>
       <c r="G41" t="n">
-        <v>224.1</v>
+        <v>216.2</v>
       </c>
       <c r="H41" t="n">
-        <v>91.90000000000001</v>
+        <v>88</v>
       </c>
       <c r="I41" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J41" t="n">
-        <v>0.77</v>
+        <v>158.87</v>
       </c>
       <c r="K41" t="n">
-        <v>309.57</v>
+        <v>-251.37</v>
       </c>
       <c r="L41" t="n">
-        <v>309.57</v>
+        <v>297.37</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07:27:20</t>
+          <t>07:30:31</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>3.37</v>
+        <v>4.04</v>
       </c>
       <c r="F42" t="n">
-        <v>11.09</v>
+        <v>7.61</v>
       </c>
       <c r="G42" t="n">
-        <v>234.9</v>
+        <v>227.8</v>
       </c>
       <c r="H42" t="n">
-        <v>97.7</v>
+        <v>100</v>
       </c>
       <c r="I42" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>-24.06</v>
+        <v>166.33</v>
       </c>
       <c r="K42" t="n">
-        <v>-279.45</v>
+        <v>-231.14</v>
       </c>
       <c r="L42" t="n">
-        <v>280.49</v>
+        <v>284.77</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07:29:53</t>
+          <t>07:31:47</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>3.82</v>
+        <v>4.01</v>
       </c>
       <c r="F43" t="n">
-        <v>10.53</v>
+        <v>9.56</v>
       </c>
       <c r="G43" t="n">
-        <v>237.5</v>
+        <v>231.1</v>
       </c>
       <c r="H43" t="n">
-        <v>99.40000000000001</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="I43" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J43" t="n">
-        <v>22.83</v>
+        <v>-186.95</v>
       </c>
       <c r="K43" t="n">
-        <v>-295.89</v>
+        <v>223.68</v>
       </c>
       <c r="L43" t="n">
-        <v>296.77</v>
+        <v>291.52</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07:40:11</t>
+          <t>07:45:11</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>3.99</v>
+        <v>4.15</v>
       </c>
       <c r="F44" t="n">
-        <v>10.27</v>
+        <v>10.61</v>
       </c>
       <c r="G44" t="n">
-        <v>216.5</v>
+        <v>218.1</v>
       </c>
       <c r="H44" t="n">
-        <v>92.90000000000001</v>
+        <v>96.7</v>
       </c>
       <c r="I44" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>-51.02</v>
+        <v>-84.84999999999999</v>
       </c>
       <c r="K44" t="n">
-        <v>69.79000000000001</v>
+        <v>-44.88</v>
       </c>
       <c r="L44" t="n">
-        <v>86.45</v>
+        <v>95.98999999999999</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07:42:36</t>
+          <t>07:46:54</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>3.21</v>
+        <v>3.77</v>
       </c>
       <c r="F45" t="n">
-        <v>10.56</v>
+        <v>6.01</v>
       </c>
       <c r="G45" t="n">
-        <v>222.9</v>
+        <v>217.1</v>
       </c>
       <c r="H45" t="n">
-        <v>92.3</v>
+        <v>98.3</v>
       </c>
       <c r="I45" t="n">
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>53.99</v>
+        <v>-64.73</v>
       </c>
       <c r="K45" t="n">
-        <v>46.41</v>
+        <v>-20.23</v>
       </c>
       <c r="L45" t="n">
-        <v>71.2</v>
+        <v>67.81999999999999</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07:44:31</t>
+          <t>07:49:19</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="F46" t="n">
-        <v>10.49</v>
+        <v>10.32</v>
       </c>
       <c r="G46" t="n">
-        <v>219.5</v>
+        <v>226.1</v>
       </c>
       <c r="H46" t="n">
-        <v>96.90000000000001</v>
+        <v>90.2</v>
       </c>
       <c r="I46" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J46" t="n">
-        <v>-55.17</v>
+        <v>-71.09999999999999</v>
       </c>
       <c r="K46" t="n">
-        <v>34.67</v>
+        <v>23.19</v>
       </c>
       <c r="L46" t="n">
-        <v>65.16</v>
+        <v>74.79000000000001</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07:48:51</t>
+          <t>07:54:28</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>4.93</v>
+        <v>3.95</v>
       </c>
       <c r="F47" t="n">
-        <v>10.91</v>
+        <v>12.3</v>
       </c>
       <c r="G47" t="n">
-        <v>225.4</v>
+        <v>228.9</v>
       </c>
       <c r="H47" t="n">
-        <v>98.2</v>
+        <v>100</v>
       </c>
       <c r="I47" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>93.41</v>
+        <v>69.89</v>
       </c>
       <c r="K47" t="n">
-        <v>1.91</v>
+        <v>63.81</v>
       </c>
       <c r="L47" t="n">
-        <v>93.43000000000001</v>
+        <v>94.64</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07:49:58</t>
+          <t>07:56:45</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>3.63</v>
+        <v>4.4</v>
       </c>
       <c r="F48" t="n">
-        <v>10.97</v>
+        <v>9.52</v>
       </c>
       <c r="G48" t="n">
-        <v>215.8</v>
+        <v>228.5</v>
       </c>
       <c r="H48" t="n">
-        <v>98</v>
+        <v>90.3</v>
       </c>
       <c r="I48" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>-19.49</v>
+        <v>47.28</v>
       </c>
       <c r="K48" t="n">
-        <v>92.8</v>
+        <v>99.06999999999999</v>
       </c>
       <c r="L48" t="n">
-        <v>94.81999999999999</v>
+        <v>109.77</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07:51:13</t>
+          <t>07:57:52</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>4.66</v>
+        <v>4.03</v>
       </c>
       <c r="F49" t="n">
-        <v>10.41</v>
+        <v>11.02</v>
       </c>
       <c r="G49" t="n">
-        <v>211.6</v>
+        <v>218.2</v>
       </c>
       <c r="H49" t="n">
-        <v>92.40000000000001</v>
+        <v>96.5</v>
       </c>
       <c r="I49" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J49" t="n">
-        <v>-100.8</v>
+        <v>-125.75</v>
       </c>
       <c r="K49" t="n">
-        <v>-81.08</v>
+        <v>-59.86</v>
       </c>
       <c r="L49" t="n">
-        <v>129.36</v>
+        <v>139.27</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07:54:56</t>
+          <t>08:01:26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>3.82</v>
+        <v>4.85</v>
       </c>
       <c r="F50" t="n">
-        <v>10.62</v>
+        <v>10.95</v>
       </c>
       <c r="G50" t="n">
-        <v>219.9</v>
+        <v>218.7</v>
       </c>
       <c r="H50" t="n">
-        <v>97.3</v>
+        <v>93</v>
       </c>
       <c r="I50" t="n">
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>-109.65</v>
+        <v>-152.11</v>
       </c>
       <c r="K50" t="n">
-        <v>-26.99</v>
+        <v>-82.19</v>
       </c>
       <c r="L50" t="n">
-        <v>112.92</v>
+        <v>172.89</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07:56:21</t>
+          <t>08:02:36</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>4.06</v>
+        <v>3.83</v>
       </c>
       <c r="F51" t="n">
-        <v>10.8</v>
+        <v>10.02</v>
       </c>
       <c r="G51" t="n">
-        <v>204.8</v>
+        <v>224.6</v>
       </c>
       <c r="H51" t="n">
-        <v>95.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="I51" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>108.28</v>
+        <v>-245.95</v>
       </c>
       <c r="K51" t="n">
-        <v>10.98</v>
+        <v>6.66</v>
       </c>
       <c r="L51" t="n">
-        <v>108.84</v>
+        <v>246.04</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07:58:22</t>
+          <t>08:04:00</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>4.38</v>
+        <v>3.45</v>
       </c>
       <c r="F52" t="n">
-        <v>10.33</v>
+        <v>9.35</v>
       </c>
       <c r="G52" t="n">
-        <v>230.2</v>
+        <v>219.7</v>
       </c>
       <c r="H52" t="n">
-        <v>96.3</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="I52" t="n">
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>111.33</v>
+        <v>72.31999999999999</v>
       </c>
       <c r="K52" t="n">
-        <v>-47.15</v>
+        <v>-146.32</v>
       </c>
       <c r="L52" t="n">
-        <v>120.9</v>
+        <v>163.22</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08:04:09</t>
+          <t>08:08:33</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>5.53</v>
+        <v>4.36</v>
       </c>
       <c r="F53" t="n">
-        <v>10.82</v>
+        <v>11.35</v>
       </c>
       <c r="G53" t="n">
-        <v>231.2</v>
+        <v>211.4</v>
       </c>
       <c r="H53" t="n">
-        <v>93.59999999999999</v>
+        <v>98.3</v>
       </c>
       <c r="I53" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>157.4</v>
+        <v>-183.88</v>
       </c>
       <c r="K53" t="n">
-        <v>-123.45</v>
+        <v>96.81999999999999</v>
       </c>
       <c r="L53" t="n">
-        <v>200.03</v>
+        <v>207.82</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08:05:52</t>
+          <t>08:11:03</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>3.98</v>
+        <v>4.26</v>
       </c>
       <c r="F54" t="n">
-        <v>11.15</v>
+        <v>12.26</v>
       </c>
       <c r="G54" t="n">
-        <v>217.4</v>
+        <v>221.1</v>
       </c>
       <c r="H54" t="n">
-        <v>99.40000000000001</v>
+        <v>95.3</v>
       </c>
       <c r="I54" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J54" t="n">
-        <v>45.77</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="K54" t="n">
-        <v>145.38</v>
+        <v>-219.21</v>
       </c>
       <c r="L54" t="n">
-        <v>152.42</v>
+        <v>238.63</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08:06:44</t>
+          <t>08:12:46</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>4.4</v>
+        <v>4.54</v>
       </c>
       <c r="F55" t="n">
-        <v>10.43</v>
+        <v>12.3</v>
       </c>
       <c r="G55" t="n">
-        <v>215</v>
+        <v>226.3</v>
       </c>
       <c r="H55" t="n">
-        <v>94</v>
+        <v>99.2</v>
       </c>
       <c r="I55" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J55" t="n">
-        <v>-155.39</v>
+        <v>-129.28</v>
       </c>
       <c r="K55" t="n">
-        <v>213.05</v>
+        <v>-230.9</v>
       </c>
       <c r="L55" t="n">
-        <v>263.69</v>
+        <v>264.63</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08:11:17</t>
+          <t>08:16:25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>3.57</v>
+        <v>3.94</v>
       </c>
       <c r="F56" t="n">
-        <v>10.28</v>
+        <v>8.73</v>
       </c>
       <c r="G56" t="n">
-        <v>216.6</v>
+        <v>211</v>
       </c>
       <c r="H56" t="n">
-        <v>91.3</v>
+        <v>100</v>
       </c>
       <c r="I56" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J56" t="n">
-        <v>206.2</v>
+        <v>-267.55</v>
       </c>
       <c r="K56" t="n">
-        <v>112.74</v>
+        <v>-253.17</v>
       </c>
       <c r="L56" t="n">
-        <v>235.01</v>
+        <v>368.35</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08:13:16</t>
+          <t>08:18:22</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>4.09</v>
+        <v>3.83</v>
       </c>
       <c r="F57" t="n">
-        <v>10.43</v>
+        <v>11.67</v>
       </c>
       <c r="G57" t="n">
-        <v>225.3</v>
+        <v>246.5</v>
       </c>
       <c r="H57" t="n">
-        <v>96.09999999999999</v>
+        <v>95.3</v>
       </c>
       <c r="I57" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J57" t="n">
-        <v>-188.87</v>
+        <v>-106.44</v>
       </c>
       <c r="K57" t="n">
-        <v>198.32</v>
+        <v>-293.06</v>
       </c>
       <c r="L57" t="n">
-        <v>273.87</v>
+        <v>311.79</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08:15:20</t>
+          <t>08:20:20</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>4.37</v>
+        <v>3.92</v>
       </c>
       <c r="F58" t="n">
-        <v>10.82</v>
+        <v>11.81</v>
       </c>
       <c r="G58" t="n">
-        <v>229.5</v>
+        <v>235.1</v>
       </c>
       <c r="H58" t="n">
-        <v>93.3</v>
+        <v>98.5</v>
       </c>
       <c r="I58" t="n">
         <v>17</v>
       </c>
       <c r="J58" t="n">
-        <v>-228.71</v>
+        <v>233.21</v>
       </c>
       <c r="K58" t="n">
-        <v>-262.34</v>
+        <v>68.37</v>
       </c>
       <c r="L58" t="n">
-        <v>348.04</v>
+        <v>243.02</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08:26:53</t>
+          <t>08:31:24</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>4.4</v>
+        <v>4.38</v>
       </c>
       <c r="F59" t="n">
-        <v>10.56</v>
+        <v>10.13</v>
       </c>
       <c r="G59" t="n">
-        <v>234.4</v>
+        <v>219.9</v>
       </c>
       <c r="H59" t="n">
-        <v>98.59999999999999</v>
+        <v>99.7</v>
       </c>
       <c r="I59" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J59" t="n">
-        <v>-76.83</v>
+        <v>87.52</v>
       </c>
       <c r="K59" t="n">
-        <v>-39.87</v>
+        <v>-30.47</v>
       </c>
       <c r="L59" t="n">
-        <v>86.56</v>
+        <v>92.68000000000001</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08:27:38</t>
+          <t>08:33:12</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>4.06</v>
+        <v>3.74</v>
       </c>
       <c r="F60" t="n">
-        <v>10.97</v>
+        <v>8.99</v>
       </c>
       <c r="G60" t="n">
-        <v>222.6</v>
+        <v>224.5</v>
       </c>
       <c r="H60" t="n">
-        <v>96.09999999999999</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="I60" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J60" t="n">
-        <v>73</v>
+        <v>-30.93</v>
       </c>
       <c r="K60" t="n">
-        <v>53.85</v>
+        <v>65.17</v>
       </c>
       <c r="L60" t="n">
-        <v>90.70999999999999</v>
+        <v>72.14</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08:28:50</t>
+          <t>08:33:57</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>4.52</v>
+        <v>3.98</v>
       </c>
       <c r="F61" t="n">
-        <v>10.42</v>
+        <v>12.19</v>
       </c>
       <c r="G61" t="n">
-        <v>223.2</v>
+        <v>223.9</v>
       </c>
       <c r="H61" t="n">
-        <v>99.09999999999999</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="I61" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J61" t="n">
-        <v>28.86</v>
+        <v>-25.87</v>
       </c>
       <c r="K61" t="n">
-        <v>-66.45</v>
+        <v>-80.88</v>
       </c>
       <c r="L61" t="n">
-        <v>72.44</v>
+        <v>84.92</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08:34:56</t>
+          <t>08:37:33</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="F62" t="n">
-        <v>10.94</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="G62" t="n">
-        <v>217</v>
+        <v>209.2</v>
       </c>
       <c r="H62" t="n">
-        <v>88.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="I62" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J62" t="n">
-        <v>-53.57</v>
+        <v>54.88</v>
       </c>
       <c r="K62" t="n">
-        <v>50.34</v>
+        <v>-77.08</v>
       </c>
       <c r="L62" t="n">
-        <v>73.51000000000001</v>
+        <v>94.62</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08:35:34</t>
+          <t>08:39:59</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>4.6</v>
+        <v>4.14</v>
       </c>
       <c r="F63" t="n">
-        <v>10.9</v>
+        <v>12.3</v>
       </c>
       <c r="G63" t="n">
-        <v>220</v>
+        <v>211.2</v>
       </c>
       <c r="H63" t="n">
-        <v>89.40000000000001</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="I63" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J63" t="n">
-        <v>-72.92</v>
+        <v>31.92</v>
       </c>
       <c r="K63" t="n">
-        <v>-86.23999999999999</v>
+        <v>136.34</v>
       </c>
       <c r="L63" t="n">
-        <v>112.94</v>
+        <v>140.02</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>08:37:04</t>
+          <t>08:40:36</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>4.37</v>
+        <v>3.93</v>
       </c>
       <c r="F64" t="n">
-        <v>10.49</v>
+        <v>11.15</v>
       </c>
       <c r="G64" t="n">
-        <v>215.1</v>
+        <v>219.1</v>
       </c>
       <c r="H64" t="n">
-        <v>93.3</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="I64" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J64" t="n">
-        <v>-28.41</v>
+        <v>-78.28</v>
       </c>
       <c r="K64" t="n">
-        <v>87.95</v>
+        <v>60.5</v>
       </c>
       <c r="L64" t="n">
-        <v>92.43000000000001</v>
+        <v>98.94</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>08:40:04</t>
+          <t>08:44:29</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>4.21</v>
+        <v>4.16</v>
       </c>
       <c r="F65" t="n">
-        <v>10.21</v>
+        <v>11.04</v>
       </c>
       <c r="G65" t="n">
-        <v>231.5</v>
+        <v>221.6</v>
       </c>
       <c r="H65" t="n">
-        <v>94.59999999999999</v>
+        <v>97.3</v>
       </c>
       <c r="I65" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J65" t="n">
-        <v>-99.06999999999999</v>
+        <v>-163.44</v>
       </c>
       <c r="K65" t="n">
-        <v>63.45</v>
+        <v>-87.78</v>
       </c>
       <c r="L65" t="n">
-        <v>117.65</v>
+        <v>185.52</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>08:41:03</t>
+          <t>08:45:32</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>4.48</v>
+        <v>4.14</v>
       </c>
       <c r="F66" t="n">
-        <v>10.08</v>
+        <v>12.2</v>
       </c>
       <c r="G66" t="n">
-        <v>225.4</v>
+        <v>217.2</v>
       </c>
       <c r="H66" t="n">
-        <v>92.40000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="I66" t="n">
         <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>-195.35</v>
+        <v>-194.22</v>
       </c>
       <c r="K66" t="n">
-        <v>85.33</v>
+        <v>92.41</v>
       </c>
       <c r="L66" t="n">
-        <v>213.17</v>
+        <v>215.08</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>08:43:44</t>
+          <t>08:46:31</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>4.2</v>
+        <v>4.21</v>
       </c>
       <c r="F67" t="n">
-        <v>10.39</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="G67" t="n">
-        <v>227.1</v>
+        <v>218.7</v>
       </c>
       <c r="H67" t="n">
-        <v>97.5</v>
+        <v>97.3</v>
       </c>
       <c r="I67" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>-138.65</v>
+        <v>-151.76</v>
       </c>
       <c r="K67" t="n">
-        <v>-37.83</v>
+        <v>-54.14</v>
       </c>
       <c r="L67" t="n">
-        <v>143.72</v>
+        <v>161.13</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>08:47:58</t>
+          <t>08:53:05</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>4.79</v>
+        <v>4.81</v>
       </c>
       <c r="F68" t="n">
-        <v>10.87</v>
+        <v>12.3</v>
       </c>
       <c r="G68" t="n">
-        <v>223.1</v>
+        <v>228.3</v>
       </c>
       <c r="H68" t="n">
-        <v>95.90000000000001</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="I68" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J68" t="n">
-        <v>-224.26</v>
+        <v>-279.08</v>
       </c>
       <c r="K68" t="n">
-        <v>-155.72</v>
+        <v>-195.65</v>
       </c>
       <c r="L68" t="n">
-        <v>273.02</v>
+        <v>340.83</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>08:50:04</t>
+          <t>08:54:00</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>3.5</v>
+        <v>3.51</v>
       </c>
       <c r="F69" t="n">
-        <v>10.66</v>
+        <v>12.3</v>
       </c>
       <c r="G69" t="n">
-        <v>225.2</v>
+        <v>224</v>
       </c>
       <c r="H69" t="n">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="I69" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J69" t="n">
-        <v>161.34</v>
+        <v>204.55</v>
       </c>
       <c r="K69" t="n">
-        <v>20.77</v>
+        <v>-12.08</v>
       </c>
       <c r="L69" t="n">
-        <v>162.67</v>
+        <v>204.91</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>08:52:00</t>
+          <t>08:56:06</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>4.32</v>
+        <v>4.34</v>
       </c>
       <c r="F70" t="n">
-        <v>10.86</v>
+        <v>12.3</v>
       </c>
       <c r="G70" t="n">
-        <v>223.6</v>
+        <v>228</v>
       </c>
       <c r="H70" t="n">
-        <v>98.59999999999999</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="I70" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J70" t="n">
-        <v>-219.26</v>
+        <v>-264.32</v>
       </c>
       <c r="K70" t="n">
-        <v>-51.66</v>
+        <v>-77.05</v>
       </c>
       <c r="L70" t="n">
-        <v>225.26</v>
+        <v>275.32</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>08:57:37</t>
+          <t>09:01:29</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>4.82</v>
+        <v>4.84</v>
       </c>
       <c r="F71" t="n">
-        <v>10.85</v>
+        <v>12.07</v>
       </c>
       <c r="G71" t="n">
-        <v>231.4</v>
+        <v>227.8</v>
       </c>
       <c r="H71" t="n">
-        <v>91.8</v>
+        <v>99.5</v>
       </c>
       <c r="I71" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J71" t="n">
-        <v>-388.26</v>
+        <v>-481.27</v>
       </c>
       <c r="K71" t="n">
-        <v>330.98</v>
+        <v>363.7</v>
       </c>
       <c r="L71" t="n">
-        <v>510.19</v>
+        <v>603.24</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>08:58:20</t>
+          <t>09:04:07</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>4.18</v>
+        <v>4.2</v>
       </c>
       <c r="F72" t="n">
-        <v>11.52</v>
+        <v>12.3</v>
       </c>
       <c r="G72" t="n">
-        <v>222.9</v>
+        <v>241.1</v>
       </c>
       <c r="H72" t="n">
-        <v>99.2</v>
+        <v>95.3</v>
       </c>
       <c r="I72" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>-132.27</v>
+        <v>-222.84</v>
       </c>
       <c r="K72" t="n">
-        <v>-194.53</v>
+        <v>-225.11</v>
       </c>
       <c r="L72" t="n">
-        <v>235.23</v>
+        <v>316.75</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>09:00:01</t>
+          <t>09:04:49</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>4.68</v>
+        <v>4.69</v>
       </c>
       <c r="F73" t="n">
-        <v>10.42</v>
+        <v>12.23</v>
       </c>
       <c r="G73" t="n">
-        <v>218.8</v>
+        <v>219.2</v>
       </c>
       <c r="H73" t="n">
-        <v>93.8</v>
+        <v>93.2</v>
       </c>
       <c r="I73" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J73" t="n">
-        <v>282.33</v>
+        <v>332.65</v>
       </c>
       <c r="K73" t="n">
-        <v>18.24</v>
+        <v>-32.9</v>
       </c>
       <c r="L73" t="n">
-        <v>282.92</v>
+        <v>334.27</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>09:11:01</t>
+          <t>09:14:23</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>4.17</v>
+        <v>4.18</v>
       </c>
       <c r="F74" t="n">
-        <v>10.82</v>
+        <v>10.91</v>
       </c>
       <c r="G74" t="n">
-        <v>239.1</v>
+        <v>227.1</v>
       </c>
       <c r="H74" t="n">
-        <v>94.7</v>
+        <v>100</v>
       </c>
       <c r="I74" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J74" t="n">
-        <v>14.69</v>
+        <v>15.25</v>
       </c>
       <c r="K74" t="n">
-        <v>-76.34</v>
+        <v>-87.67</v>
       </c>
       <c r="L74" t="n">
-        <v>77.73999999999999</v>
+        <v>88.98</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09:12:19</t>
+          <t>09:16:15</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>4.4</v>
+        <v>4.41</v>
       </c>
       <c r="F75" t="n">
-        <v>11.03</v>
+        <v>12.3</v>
       </c>
       <c r="G75" t="n">
-        <v>220.2</v>
+        <v>231.3</v>
       </c>
       <c r="H75" t="n">
-        <v>93.2</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="I75" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>-11.09</v>
+        <v>-13.2</v>
       </c>
       <c r="K75" t="n">
-        <v>-122.97</v>
+        <v>-134</v>
       </c>
       <c r="L75" t="n">
-        <v>123.47</v>
+        <v>134.65</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09:13:41</t>
+          <t>09:17:33</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>5.15</v>
+        <v>5.16</v>
       </c>
       <c r="F76" t="n">
-        <v>11.14</v>
+        <v>12.3</v>
       </c>
       <c r="G76" t="n">
-        <v>224.7</v>
+        <v>233.5</v>
       </c>
       <c r="H76" t="n">
-        <v>98.40000000000001</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="I76" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J76" t="n">
-        <v>-17.97</v>
+        <v>-20.02</v>
       </c>
       <c r="K76" t="n">
-        <v>-100.25</v>
+        <v>-102.46</v>
       </c>
       <c r="L76" t="n">
-        <v>101.85</v>
+        <v>104.4</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09:17:57</t>
+          <t>09:22:26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>4.35</v>
+        <v>4.36</v>
       </c>
       <c r="F77" t="n">
-        <v>10.43</v>
+        <v>12.3</v>
       </c>
       <c r="G77" t="n">
-        <v>221.4</v>
+        <v>219.4</v>
       </c>
       <c r="H77" t="n">
-        <v>93.7</v>
+        <v>94.5</v>
       </c>
       <c r="I77" t="n">
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>100.33</v>
+        <v>107.23</v>
       </c>
       <c r="K77" t="n">
-        <v>-181.74</v>
+        <v>-200.11</v>
       </c>
       <c r="L77" t="n">
-        <v>207.59</v>
+        <v>227.02</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09:19:13</t>
+          <t>09:24:27</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>4.37</v>
+        <v>4.38</v>
       </c>
       <c r="F78" t="n">
-        <v>11.17</v>
+        <v>11.28</v>
       </c>
       <c r="G78" t="n">
-        <v>229</v>
+        <v>234.2</v>
       </c>
       <c r="H78" t="n">
-        <v>94.09999999999999</v>
+        <v>98.3</v>
       </c>
       <c r="I78" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J78" t="n">
-        <v>-63.03</v>
+        <v>-72.64</v>
       </c>
       <c r="K78" t="n">
-        <v>81.84999999999999</v>
+        <v>85.38</v>
       </c>
       <c r="L78" t="n">
-        <v>103.3</v>
+        <v>112.1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09:20:40</t>
+          <t>09:25:42</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>4.56</v>
+        <v>4.57</v>
       </c>
       <c r="F79" t="n">
-        <v>11.08</v>
+        <v>9.43</v>
       </c>
       <c r="G79" t="n">
-        <v>229.7</v>
+        <v>232.5</v>
       </c>
       <c r="H79" t="n">
-        <v>96</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="I79" t="n">
         <v>19</v>
       </c>
       <c r="J79" t="n">
-        <v>37.66</v>
+        <v>37.33</v>
       </c>
       <c r="K79" t="n">
-        <v>69.70999999999999</v>
+        <v>78.7</v>
       </c>
       <c r="L79" t="n">
-        <v>79.23</v>
+        <v>87.09999999999999</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>09:25:07</t>
+          <t>09:30:07</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>4.24</v>
+        <v>4.26</v>
       </c>
       <c r="F80" t="n">
-        <v>11.01</v>
+        <v>10.17</v>
       </c>
       <c r="G80" t="n">
-        <v>223.7</v>
+        <v>230.9</v>
       </c>
       <c r="H80" t="n">
-        <v>92.09999999999999</v>
+        <v>95.7</v>
       </c>
       <c r="I80" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>130.25</v>
+        <v>148.14</v>
       </c>
       <c r="K80" t="n">
-        <v>18.72</v>
+        <v>5.54</v>
       </c>
       <c r="L80" t="n">
-        <v>131.59</v>
+        <v>148.25</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>09:26:16</t>
+          <t>09:31:17</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>4.86</v>
+        <v>4.87</v>
       </c>
       <c r="F81" t="n">
-        <v>10.79</v>
+        <v>12.3</v>
       </c>
       <c r="G81" t="n">
-        <v>223.5</v>
+        <v>226.7</v>
       </c>
       <c r="H81" t="n">
-        <v>98.7</v>
+        <v>95.5</v>
       </c>
       <c r="I81" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J81" t="n">
-        <v>216.6</v>
+        <v>225.2</v>
       </c>
       <c r="K81" t="n">
-        <v>-0.23</v>
+        <v>-15.08</v>
       </c>
       <c r="L81" t="n">
-        <v>216.6</v>
+        <v>225.71</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>09:27:50</t>
+          <t>09:32:26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>4.36</v>
+        <v>4.38</v>
       </c>
       <c r="F82" t="n">
-        <v>10.55</v>
+        <v>12.3</v>
       </c>
       <c r="G82" t="n">
-        <v>215.7</v>
+        <v>221.7</v>
       </c>
       <c r="H82" t="n">
-        <v>97</v>
+        <v>91.7</v>
       </c>
       <c r="I82" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J82" t="n">
-        <v>-118.87</v>
+        <v>-162.13</v>
       </c>
       <c r="K82" t="n">
-        <v>90.27</v>
+        <v>92.14</v>
       </c>
       <c r="L82" t="n">
-        <v>149.26</v>
+        <v>186.48</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>09:32:03</t>
+          <t>09:36:16</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>4.43</v>
+        <v>4.44</v>
       </c>
       <c r="F83" t="n">
-        <v>10.1</v>
+        <v>12.08</v>
       </c>
       <c r="G83" t="n">
-        <v>225.2</v>
+        <v>212.7</v>
       </c>
       <c r="H83" t="n">
-        <v>95.2</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="I83" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J83" t="n">
-        <v>-215.18</v>
+        <v>-235.01</v>
       </c>
       <c r="K83" t="n">
-        <v>-140.21</v>
+        <v>-175.27</v>
       </c>
       <c r="L83" t="n">
-        <v>256.83</v>
+        <v>293.17</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>09:34:22</t>
+          <t>09:38:07</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>4.18</v>
+        <v>4.19</v>
       </c>
       <c r="F84" t="n">
-        <v>11.03</v>
+        <v>12.3</v>
       </c>
       <c r="G84" t="n">
-        <v>239.5</v>
+        <v>231.4</v>
       </c>
       <c r="H84" t="n">
-        <v>99.3</v>
+        <v>100</v>
       </c>
       <c r="I84" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J84" t="n">
-        <v>29.07</v>
+        <v>-54.26</v>
       </c>
       <c r="K84" t="n">
-        <v>-54.51</v>
+        <v>-167.38</v>
       </c>
       <c r="L84" t="n">
-        <v>61.77</v>
+        <v>175.96</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>09:35:08</t>
+          <t>09:40:26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>4.22</v>
+        <v>4.24</v>
       </c>
       <c r="F85" t="n">
-        <v>10.46</v>
+        <v>12.3</v>
       </c>
       <c r="G85" t="n">
-        <v>236.3</v>
+        <v>220.1</v>
       </c>
       <c r="H85" t="n">
-        <v>90.3</v>
+        <v>100</v>
       </c>
       <c r="I85" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J85" t="n">
-        <v>22.11</v>
+        <v>4.6</v>
       </c>
       <c r="K85" t="n">
-        <v>211.13</v>
+        <v>228.32</v>
       </c>
       <c r="L85" t="n">
-        <v>212.28</v>
+        <v>228.37</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>09:41:10</t>
+          <t>09:44:23</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>4.54</v>
+        <v>4.55</v>
       </c>
       <c r="F86" t="n">
-        <v>10.9</v>
+        <v>12.3</v>
       </c>
       <c r="G86" t="n">
-        <v>232.9</v>
+        <v>228.9</v>
       </c>
       <c r="H86" t="n">
-        <v>99.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="I86" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>-160.26</v>
+        <v>-188.65</v>
       </c>
       <c r="K86" t="n">
-        <v>-385.98</v>
+        <v>-419.01</v>
       </c>
       <c r="L86" t="n">
-        <v>417.93</v>
+        <v>459.52</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>09:43:27</t>
+          <t>09:46:20</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>5.08</v>
+        <v>5.09</v>
       </c>
       <c r="F87" t="n">
-        <v>10.41</v>
+        <v>12.3</v>
       </c>
       <c r="G87" t="n">
-        <v>220.8</v>
+        <v>219</v>
       </c>
       <c r="H87" t="n">
-        <v>94.90000000000001</v>
+        <v>94.2</v>
       </c>
       <c r="I87" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J87" t="n">
-        <v>180.24</v>
+        <v>186.3</v>
       </c>
       <c r="K87" t="n">
-        <v>249.71</v>
+        <v>258.79</v>
       </c>
       <c r="L87" t="n">
-        <v>307.96</v>
+        <v>318.87</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>09:45:35</t>
+          <t>09:48:37</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>4.65</v>
+        <v>4.66</v>
       </c>
       <c r="F88" t="n">
-        <v>10.49</v>
+        <v>12.3</v>
       </c>
       <c r="G88" t="n">
-        <v>233.8</v>
+        <v>220.6</v>
       </c>
       <c r="H88" t="n">
-        <v>94.5</v>
+        <v>100</v>
       </c>
       <c r="I88" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>294.07</v>
+        <v>288.5</v>
       </c>
       <c r="K88" t="n">
-        <v>-60.72</v>
+        <v>-138.95</v>
       </c>
       <c r="L88" t="n">
-        <v>300.27</v>
+        <v>320.21</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-08-26.xlsx
+++ b/output/2025-08-26.xlsx
@@ -640,13 +640,13 @@
         <v>17</v>
       </c>
       <c r="J14" t="n">
-        <v>34.25</v>
+        <v>38.44</v>
       </c>
       <c r="K14" t="n">
-        <v>-83.20999999999999</v>
+        <v>-93.40000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>89.98999999999999</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>49.43</v>
+        <v>52.9</v>
       </c>
       <c r="K15" t="n">
-        <v>-50.66</v>
+        <v>-54.22</v>
       </c>
       <c r="L15" t="n">
-        <v>70.78</v>
+        <v>75.75</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>17</v>
       </c>
       <c r="J16" t="n">
-        <v>26.97</v>
+        <v>30.26</v>
       </c>
       <c r="K16" t="n">
-        <v>-102.14</v>
+        <v>-114.62</v>
       </c>
       <c r="L16" t="n">
-        <v>105.64</v>
+        <v>118.54</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>18</v>
       </c>
       <c r="J17" t="n">
-        <v>-50.69</v>
+        <v>-56.02</v>
       </c>
       <c r="K17" t="n">
-        <v>133.3</v>
+        <v>147.34</v>
       </c>
       <c r="L17" t="n">
-        <v>142.61</v>
+        <v>157.63</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>22</v>
       </c>
       <c r="J18" t="n">
-        <v>7.9</v>
+        <v>8.16</v>
       </c>
       <c r="K18" t="n">
-        <v>-111.55</v>
+        <v>-115.23</v>
       </c>
       <c r="L18" t="n">
-        <v>111.83</v>
+        <v>115.52</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>18</v>
       </c>
       <c r="J19" t="n">
-        <v>-54.98</v>
+        <v>-60.74</v>
       </c>
       <c r="K19" t="n">
-        <v>78.22</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>95.61</v>
+        <v>105.61</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>21</v>
       </c>
       <c r="J20" t="n">
-        <v>77.25</v>
+        <v>81.59</v>
       </c>
       <c r="K20" t="n">
-        <v>-88.70999999999999</v>
+        <v>-93.69</v>
       </c>
       <c r="L20" t="n">
-        <v>117.63</v>
+        <v>124.24</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>18</v>
       </c>
       <c r="J21" t="n">
-        <v>-42.49</v>
+        <v>-47.02</v>
       </c>
       <c r="K21" t="n">
-        <v>-152.97</v>
+        <v>-169.25</v>
       </c>
       <c r="L21" t="n">
-        <v>158.77</v>
+        <v>175.66</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>20</v>
       </c>
       <c r="J22" t="n">
-        <v>89.3</v>
+        <v>95.89</v>
       </c>
       <c r="K22" t="n">
-        <v>157.23</v>
+        <v>168.84</v>
       </c>
       <c r="L22" t="n">
-        <v>180.82</v>
+        <v>194.17</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>22</v>
       </c>
       <c r="J23" t="n">
-        <v>-101.2</v>
+        <v>-105.15</v>
       </c>
       <c r="K23" t="n">
-        <v>-296.68</v>
+        <v>-308.24</v>
       </c>
       <c r="L23" t="n">
-        <v>313.46</v>
+        <v>325.68</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>-115.71</v>
+        <v>-131.76</v>
       </c>
       <c r="K24" t="n">
-        <v>309.49</v>
+        <v>352.41</v>
       </c>
       <c r="L24" t="n">
-        <v>330.41</v>
+        <v>376.24</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>18</v>
       </c>
       <c r="J25" t="n">
-        <v>-229.4</v>
+        <v>-253.98</v>
       </c>
       <c r="K25" t="n">
-        <v>-86.59999999999999</v>
+        <v>-95.88</v>
       </c>
       <c r="L25" t="n">
-        <v>245.2</v>
+        <v>271.47</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>21</v>
       </c>
       <c r="J26" t="n">
-        <v>-71.90000000000001</v>
+        <v>-76.29000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>-314.14</v>
+        <v>-333.3</v>
       </c>
       <c r="L26" t="n">
-        <v>322.27</v>
+        <v>341.92</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>16</v>
       </c>
       <c r="J27" t="n">
-        <v>-384.28</v>
+        <v>-439.47</v>
       </c>
       <c r="K27" t="n">
-        <v>-171.28</v>
+        <v>-195.88</v>
       </c>
       <c r="L27" t="n">
-        <v>420.72</v>
+        <v>481.15</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>17</v>
       </c>
       <c r="J28" t="n">
-        <v>-36.35</v>
+        <v>-41.38</v>
       </c>
       <c r="K28" t="n">
-        <v>-489.33</v>
+        <v>-557.0599999999999</v>
       </c>
       <c r="L28" t="n">
-        <v>490.68</v>
+        <v>558.59</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>17</v>
       </c>
       <c r="J29" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="K29" t="n">
-        <v>-75.84999999999999</v>
+        <v>-84.83</v>
       </c>
       <c r="L29" t="n">
-        <v>75.86</v>
+        <v>84.84999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>20</v>
       </c>
       <c r="J30" t="n">
-        <v>-12.89</v>
+        <v>-13.81</v>
       </c>
       <c r="K30" t="n">
-        <v>76.83</v>
+        <v>82.31999999999999</v>
       </c>
       <c r="L30" t="n">
-        <v>77.90000000000001</v>
+        <v>83.47</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>18</v>
       </c>
       <c r="J31" t="n">
-        <v>34.6</v>
+        <v>38.19</v>
       </c>
       <c r="K31" t="n">
-        <v>96.15000000000001</v>
+        <v>106.13</v>
       </c>
       <c r="L31" t="n">
-        <v>102.18</v>
+        <v>112.8</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>22</v>
       </c>
       <c r="J32" t="n">
-        <v>23.51</v>
+        <v>24.38</v>
       </c>
       <c r="K32" t="n">
-        <v>-91.90000000000001</v>
+        <v>-95.29000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>94.86</v>
+        <v>98.36</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>21</v>
       </c>
       <c r="J33" t="n">
-        <v>-42.23</v>
+        <v>-44.37</v>
       </c>
       <c r="K33" t="n">
-        <v>-70.66</v>
+        <v>-74.25</v>
       </c>
       <c r="L33" t="n">
-        <v>82.31</v>
+        <v>86.5</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>21</v>
       </c>
       <c r="J34" t="n">
-        <v>-108.75</v>
+        <v>-114.43</v>
       </c>
       <c r="K34" t="n">
-        <v>-58.92</v>
+        <v>-62</v>
       </c>
       <c r="L34" t="n">
-        <v>123.68</v>
+        <v>130.15</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>20</v>
       </c>
       <c r="J35" t="n">
-        <v>-86.06999999999999</v>
+        <v>-92.29000000000001</v>
       </c>
       <c r="K35" t="n">
-        <v>84.05</v>
+        <v>90.13</v>
       </c>
       <c r="L35" t="n">
-        <v>120.3</v>
+        <v>129</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>19</v>
       </c>
       <c r="J36" t="n">
-        <v>-147.16</v>
+        <v>-160.37</v>
       </c>
       <c r="K36" t="n">
-        <v>-136.76</v>
+        <v>-149.03</v>
       </c>
       <c r="L36" t="n">
-        <v>200.9</v>
+        <v>218.92</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>17</v>
       </c>
       <c r="J37" t="n">
-        <v>121.75</v>
+        <v>136.62</v>
       </c>
       <c r="K37" t="n">
-        <v>117.06</v>
+        <v>131.35</v>
       </c>
       <c r="L37" t="n">
-        <v>168.9</v>
+        <v>189.53</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>19</v>
       </c>
       <c r="J38" t="n">
-        <v>-130.48</v>
+        <v>-142.46</v>
       </c>
       <c r="K38" t="n">
-        <v>-125.32</v>
+        <v>-136.83</v>
       </c>
       <c r="L38" t="n">
-        <v>180.91</v>
+        <v>197.53</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>18</v>
       </c>
       <c r="J39" t="n">
-        <v>-99.75</v>
+        <v>-110.52</v>
       </c>
       <c r="K39" t="n">
-        <v>146.93</v>
+        <v>162.79</v>
       </c>
       <c r="L39" t="n">
-        <v>177.59</v>
+        <v>196.76</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>200.23</v>
+        <v>227.96</v>
       </c>
       <c r="K40" t="n">
-        <v>-104.42</v>
+        <v>-118.89</v>
       </c>
       <c r="L40" t="n">
-        <v>225.82</v>
+        <v>257.1</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>17</v>
       </c>
       <c r="J41" t="n">
-        <v>158.87</v>
+        <v>179.1</v>
       </c>
       <c r="K41" t="n">
-        <v>-251.37</v>
+        <v>-283.39</v>
       </c>
       <c r="L41" t="n">
-        <v>297.37</v>
+        <v>335.25</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>166.33</v>
+        <v>176.81</v>
       </c>
       <c r="K42" t="n">
-        <v>-231.14</v>
+        <v>-245.72</v>
       </c>
       <c r="L42" t="n">
-        <v>284.77</v>
+        <v>302.72</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>22</v>
       </c>
       <c r="J43" t="n">
-        <v>-186.95</v>
+        <v>-195.28</v>
       </c>
       <c r="K43" t="n">
-        <v>223.68</v>
+        <v>233.65</v>
       </c>
       <c r="L43" t="n">
-        <v>291.52</v>
+        <v>304.51</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>-84.84999999999999</v>
+        <v>-92.16</v>
       </c>
       <c r="K44" t="n">
-        <v>-44.88</v>
+        <v>-48.75</v>
       </c>
       <c r="L44" t="n">
-        <v>95.98999999999999</v>
+        <v>104.26</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>-64.73</v>
+        <v>-73.48</v>
       </c>
       <c r="K45" t="n">
-        <v>-20.23</v>
+        <v>-22.96</v>
       </c>
       <c r="L45" t="n">
-        <v>67.81999999999999</v>
+        <v>76.98</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>20</v>
       </c>
       <c r="J46" t="n">
-        <v>-71.09999999999999</v>
+        <v>-75.98999999999999</v>
       </c>
       <c r="K46" t="n">
-        <v>23.19</v>
+        <v>24.78</v>
       </c>
       <c r="L46" t="n">
-        <v>74.79000000000001</v>
+        <v>79.93000000000001</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>69.89</v>
+        <v>74.81</v>
       </c>
       <c r="K47" t="n">
-        <v>63.81</v>
+        <v>68.31</v>
       </c>
       <c r="L47" t="n">
-        <v>94.64</v>
+        <v>101.3</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>47.28</v>
+        <v>48.83</v>
       </c>
       <c r="K48" t="n">
-        <v>99.06999999999999</v>
+        <v>102.32</v>
       </c>
       <c r="L48" t="n">
-        <v>109.77</v>
+        <v>113.38</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>18</v>
       </c>
       <c r="J49" t="n">
-        <v>-125.75</v>
+        <v>-138.7</v>
       </c>
       <c r="K49" t="n">
-        <v>-59.86</v>
+        <v>-66.02</v>
       </c>
       <c r="L49" t="n">
-        <v>139.27</v>
+        <v>153.61</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>-152.11</v>
+        <v>-172.67</v>
       </c>
       <c r="K50" t="n">
-        <v>-82.19</v>
+        <v>-93.3</v>
       </c>
       <c r="L50" t="n">
-        <v>172.89</v>
+        <v>196.26</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>-245.95</v>
+        <v>-279.58</v>
       </c>
       <c r="K51" t="n">
-        <v>6.66</v>
+        <v>7.57</v>
       </c>
       <c r="L51" t="n">
-        <v>246.04</v>
+        <v>279.69</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>72.31999999999999</v>
+        <v>82.26000000000001</v>
       </c>
       <c r="K52" t="n">
-        <v>-146.32</v>
+        <v>-166.44</v>
       </c>
       <c r="L52" t="n">
-        <v>163.22</v>
+        <v>185.66</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>-183.88</v>
+        <v>-197.75</v>
       </c>
       <c r="K53" t="n">
-        <v>96.81999999999999</v>
+        <v>104.13</v>
       </c>
       <c r="L53" t="n">
-        <v>207.82</v>
+        <v>223.49</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>19</v>
       </c>
       <c r="J54" t="n">
-        <v>94.29000000000001</v>
+        <v>102.98</v>
       </c>
       <c r="K54" t="n">
-        <v>-219.21</v>
+        <v>-239.42</v>
       </c>
       <c r="L54" t="n">
-        <v>238.63</v>
+        <v>260.63</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>20</v>
       </c>
       <c r="J55" t="n">
-        <v>-129.28</v>
+        <v>-139.91</v>
       </c>
       <c r="K55" t="n">
-        <v>-230.9</v>
+        <v>-249.88</v>
       </c>
       <c r="L55" t="n">
-        <v>264.63</v>
+        <v>286.38</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>21</v>
       </c>
       <c r="J56" t="n">
-        <v>-267.55</v>
+        <v>-284.23</v>
       </c>
       <c r="K56" t="n">
-        <v>-253.17</v>
+        <v>-268.95</v>
       </c>
       <c r="L56" t="n">
-        <v>368.35</v>
+        <v>391.31</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>22</v>
       </c>
       <c r="J57" t="n">
-        <v>-106.44</v>
+        <v>-111.04</v>
       </c>
       <c r="K57" t="n">
-        <v>-293.06</v>
+        <v>-305.74</v>
       </c>
       <c r="L57" t="n">
-        <v>311.79</v>
+        <v>325.28</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>17</v>
       </c>
       <c r="J58" t="n">
-        <v>233.21</v>
+        <v>263.23</v>
       </c>
       <c r="K58" t="n">
-        <v>68.37</v>
+        <v>77.17</v>
       </c>
       <c r="L58" t="n">
-        <v>243.02</v>
+        <v>274.31</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>19</v>
       </c>
       <c r="J59" t="n">
-        <v>87.52</v>
+        <v>94.97</v>
       </c>
       <c r="K59" t="n">
-        <v>-30.47</v>
+        <v>-33.07</v>
       </c>
       <c r="L59" t="n">
-        <v>92.68000000000001</v>
+        <v>100.56</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>22</v>
       </c>
       <c r="J60" t="n">
-        <v>-30.93</v>
+        <v>-32.04</v>
       </c>
       <c r="K60" t="n">
-        <v>65.17</v>
+        <v>67.52</v>
       </c>
       <c r="L60" t="n">
-        <v>72.14</v>
+        <v>74.73999999999999</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>18</v>
       </c>
       <c r="J61" t="n">
-        <v>-25.87</v>
+        <v>-28.54</v>
       </c>
       <c r="K61" t="n">
-        <v>-80.88</v>
+        <v>-89.23</v>
       </c>
       <c r="L61" t="n">
-        <v>84.92</v>
+        <v>93.69</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>21</v>
       </c>
       <c r="J62" t="n">
-        <v>54.88</v>
+        <v>57.78</v>
       </c>
       <c r="K62" t="n">
-        <v>-77.08</v>
+        <v>-81.15000000000001</v>
       </c>
       <c r="L62" t="n">
-        <v>94.62</v>
+        <v>99.62</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>19</v>
       </c>
       <c r="J63" t="n">
-        <v>31.92</v>
+        <v>34.67</v>
       </c>
       <c r="K63" t="n">
-        <v>136.34</v>
+        <v>148.1</v>
       </c>
       <c r="L63" t="n">
-        <v>140.02</v>
+        <v>152.1</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>17</v>
       </c>
       <c r="J64" t="n">
-        <v>-78.28</v>
+        <v>-87.61</v>
       </c>
       <c r="K64" t="n">
-        <v>60.5</v>
+        <v>67.7</v>
       </c>
       <c r="L64" t="n">
-        <v>98.94</v>
+        <v>110.72</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>19</v>
       </c>
       <c r="J65" t="n">
-        <v>-163.44</v>
+        <v>-178.03</v>
       </c>
       <c r="K65" t="n">
-        <v>-87.78</v>
+        <v>-95.61</v>
       </c>
       <c r="L65" t="n">
-        <v>185.52</v>
+        <v>202.08</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>-194.22</v>
+        <v>-220.67</v>
       </c>
       <c r="K66" t="n">
-        <v>92.41</v>
+        <v>105</v>
       </c>
       <c r="L66" t="n">
-        <v>215.08</v>
+        <v>244.38</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>-151.76</v>
+        <v>-157.35</v>
       </c>
       <c r="K67" t="n">
-        <v>-54.14</v>
+        <v>-56.13</v>
       </c>
       <c r="L67" t="n">
-        <v>161.13</v>
+        <v>167.06</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>18</v>
       </c>
       <c r="J68" t="n">
-        <v>-279.08</v>
+        <v>-311.6</v>
       </c>
       <c r="K68" t="n">
-        <v>-195.65</v>
+        <v>-218.45</v>
       </c>
       <c r="L68" t="n">
-        <v>340.83</v>
+        <v>380.55</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>17</v>
       </c>
       <c r="J69" t="n">
-        <v>204.55</v>
+        <v>229.75</v>
       </c>
       <c r="K69" t="n">
-        <v>-12.08</v>
+        <v>-13.56</v>
       </c>
       <c r="L69" t="n">
-        <v>204.91</v>
+        <v>230.15</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>20</v>
       </c>
       <c r="J70" t="n">
-        <v>-264.32</v>
+        <v>-284.25</v>
       </c>
       <c r="K70" t="n">
-        <v>-77.05</v>
+        <v>-82.87</v>
       </c>
       <c r="L70" t="n">
-        <v>275.32</v>
+        <v>296.09</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>17</v>
       </c>
       <c r="J71" t="n">
-        <v>-481.27</v>
+        <v>-549.77</v>
       </c>
       <c r="K71" t="n">
-        <v>363.7</v>
+        <v>415.47</v>
       </c>
       <c r="L71" t="n">
-        <v>603.24</v>
+        <v>689.1</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>-222.84</v>
+        <v>-255.38</v>
       </c>
       <c r="K72" t="n">
-        <v>-225.11</v>
+        <v>-257.98</v>
       </c>
       <c r="L72" t="n">
-        <v>316.75</v>
+        <v>363.01</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>18</v>
       </c>
       <c r="J73" t="n">
-        <v>332.65</v>
+        <v>374.33</v>
       </c>
       <c r="K73" t="n">
-        <v>-32.9</v>
+        <v>-37.02</v>
       </c>
       <c r="L73" t="n">
-        <v>334.27</v>
+        <v>376.16</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>18</v>
       </c>
       <c r="J74" t="n">
-        <v>15.25</v>
+        <v>16.81</v>
       </c>
       <c r="K74" t="n">
-        <v>-87.67</v>
+        <v>-96.63</v>
       </c>
       <c r="L74" t="n">
-        <v>88.98</v>
+        <v>98.08</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>-13.2</v>
+        <v>-13.87</v>
       </c>
       <c r="K75" t="n">
-        <v>-134</v>
+        <v>-140.81</v>
       </c>
       <c r="L75" t="n">
-        <v>134.65</v>
+        <v>141.49</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>20</v>
       </c>
       <c r="J76" t="n">
-        <v>-20.02</v>
+        <v>-21.32</v>
       </c>
       <c r="K76" t="n">
-        <v>-102.46</v>
+        <v>-109.09</v>
       </c>
       <c r="L76" t="n">
-        <v>104.4</v>
+        <v>111.15</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>107.23</v>
+        <v>121.38</v>
       </c>
       <c r="K77" t="n">
-        <v>-200.11</v>
+        <v>-226.52</v>
       </c>
       <c r="L77" t="n">
-        <v>227.02</v>
+        <v>256.99</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>19</v>
       </c>
       <c r="J78" t="n">
-        <v>-72.64</v>
+        <v>-78.81999999999999</v>
       </c>
       <c r="K78" t="n">
-        <v>85.38</v>
+        <v>92.65000000000001</v>
       </c>
       <c r="L78" t="n">
-        <v>112.1</v>
+        <v>121.64</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>19</v>
       </c>
       <c r="J79" t="n">
-        <v>37.33</v>
+        <v>40.47</v>
       </c>
       <c r="K79" t="n">
-        <v>78.7</v>
+        <v>85.33</v>
       </c>
       <c r="L79" t="n">
-        <v>87.09999999999999</v>
+        <v>94.44</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>148.14</v>
+        <v>168.3</v>
       </c>
       <c r="K80" t="n">
-        <v>5.54</v>
+        <v>6.29</v>
       </c>
       <c r="L80" t="n">
-        <v>148.25</v>
+        <v>168.41</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>17</v>
       </c>
       <c r="J81" t="n">
-        <v>225.2</v>
+        <v>252.24</v>
       </c>
       <c r="K81" t="n">
-        <v>-15.08</v>
+        <v>-16.89</v>
       </c>
       <c r="L81" t="n">
-        <v>225.71</v>
+        <v>252.8</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>16</v>
       </c>
       <c r="J82" t="n">
-        <v>-162.13</v>
+        <v>-184.15</v>
       </c>
       <c r="K82" t="n">
-        <v>92.14</v>
+        <v>104.66</v>
       </c>
       <c r="L82" t="n">
-        <v>186.48</v>
+        <v>211.81</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>18</v>
       </c>
       <c r="J83" t="n">
-        <v>-235.01</v>
+        <v>-260.54</v>
       </c>
       <c r="K83" t="n">
-        <v>-175.27</v>
+        <v>-194.31</v>
       </c>
       <c r="L83" t="n">
-        <v>293.17</v>
+        <v>325.02</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>17</v>
       </c>
       <c r="J84" t="n">
-        <v>-54.26</v>
+        <v>-60.99</v>
       </c>
       <c r="K84" t="n">
-        <v>-167.38</v>
+        <v>-188.14</v>
       </c>
       <c r="L84" t="n">
-        <v>175.96</v>
+        <v>197.78</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>20</v>
       </c>
       <c r="J85" t="n">
-        <v>4.6</v>
+        <v>4.95</v>
       </c>
       <c r="K85" t="n">
-        <v>228.32</v>
+        <v>245.52</v>
       </c>
       <c r="L85" t="n">
-        <v>228.37</v>
+        <v>245.57</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>-188.65</v>
+        <v>-198.93</v>
       </c>
       <c r="K86" t="n">
-        <v>-419.01</v>
+        <v>-441.82</v>
       </c>
       <c r="L86" t="n">
-        <v>459.52</v>
+        <v>484.54</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>19</v>
       </c>
       <c r="J87" t="n">
-        <v>186.3</v>
+        <v>207.08</v>
       </c>
       <c r="K87" t="n">
-        <v>258.79</v>
+        <v>287.65</v>
       </c>
       <c r="L87" t="n">
-        <v>318.87</v>
+        <v>354.43</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>288.5</v>
+        <v>309.76</v>
       </c>
       <c r="K88" t="n">
-        <v>-138.95</v>
+        <v>-149.19</v>
       </c>
       <c r="L88" t="n">
-        <v>320.21</v>
+        <v>343.82</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-08-26.xlsx
+++ b/output/2025-08-26.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>3.32</v>
+        <v>3.38</v>
       </c>
       <c r="F14" t="n">
-        <v>5.42</v>
+        <v>9.99</v>
       </c>
       <c r="G14" t="n">
-        <v>213.4</v>
+        <v>246.1</v>
       </c>
       <c r="H14" t="n">
-        <v>93.40000000000001</v>
+        <v>48.9</v>
       </c>
       <c r="I14" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J14" t="n">
-        <v>38.44</v>
+        <v>-84.14</v>
       </c>
       <c r="K14" t="n">
-        <v>-93.40000000000001</v>
+        <v>-25.99</v>
       </c>
       <c r="L14" t="n">
-        <v>101</v>
+        <v>88.06999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06:08:59</t>
+          <t>06:10:07</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3.99</v>
+        <v>3.57</v>
       </c>
       <c r="F15" t="n">
-        <v>10.34</v>
+        <v>7.78</v>
       </c>
       <c r="G15" t="n">
-        <v>232.1</v>
+        <v>232.6</v>
       </c>
       <c r="H15" t="n">
-        <v>95.2</v>
+        <v>62.4</v>
       </c>
       <c r="I15" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J15" t="n">
-        <v>52.9</v>
+        <v>-66.79000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>-54.22</v>
+        <v>-18.22</v>
       </c>
       <c r="L15" t="n">
-        <v>75.75</v>
+        <v>69.23</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06:09:52</t>
+          <t>06:11:36</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>3.36</v>
+        <v>3.8</v>
       </c>
       <c r="F16" t="n">
-        <v>10.39</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>234.6</v>
+        <v>219.4</v>
       </c>
       <c r="H16" t="n">
-        <v>90.7</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="J16" t="n">
-        <v>30.26</v>
+        <v>6.87</v>
       </c>
       <c r="K16" t="n">
-        <v>-114.62</v>
+        <v>-62.93</v>
       </c>
       <c r="L16" t="n">
-        <v>118.54</v>
+        <v>63.3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06:16:02</t>
+          <t>06:15:19</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="F17" t="n">
+        <v>6.69</v>
+      </c>
+      <c r="G17" t="n">
+        <v>227</v>
+      </c>
+      <c r="H17" t="n">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="I17" t="n">
+        <v>21</v>
+      </c>
+      <c r="J17" t="n">
         <v>3.58</v>
       </c>
-      <c r="F17" t="n">
-        <v>12.09</v>
-      </c>
-      <c r="G17" t="n">
-        <v>234.1</v>
-      </c>
-      <c r="H17" t="n">
-        <v>100</v>
-      </c>
-      <c r="I17" t="n">
-        <v>18</v>
-      </c>
-      <c r="J17" t="n">
-        <v>-56.02</v>
-      </c>
       <c r="K17" t="n">
-        <v>147.34</v>
+        <v>-91.62</v>
       </c>
       <c r="L17" t="n">
-        <v>157.63</v>
+        <v>91.69</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06:17:10</t>
+          <t>06:16:56</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>4.38</v>
+        <v>3.76</v>
       </c>
       <c r="F18" t="n">
-        <v>10.02</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>228.6</v>
+        <v>233.4</v>
       </c>
       <c r="H18" t="n">
-        <v>92.8</v>
+        <v>55.1</v>
       </c>
       <c r="I18" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="J18" t="n">
-        <v>8.16</v>
+        <v>-58.27</v>
       </c>
       <c r="K18" t="n">
-        <v>-115.23</v>
+        <v>-82.38</v>
       </c>
       <c r="L18" t="n">
-        <v>115.52</v>
+        <v>100.91</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06:18:47</t>
+          <t>06:19:28</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>3.71</v>
+        <v>3.92</v>
       </c>
       <c r="F19" t="n">
-        <v>10.4</v>
+        <v>9.9</v>
       </c>
       <c r="G19" t="n">
-        <v>213.1</v>
+        <v>217.6</v>
       </c>
       <c r="H19" t="n">
-        <v>95.8</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>-60.74</v>
+        <v>-17.74</v>
       </c>
       <c r="K19" t="n">
-        <v>86.40000000000001</v>
+        <v>-90.33</v>
       </c>
       <c r="L19" t="n">
-        <v>105.61</v>
+        <v>92.05</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06:23:41</t>
+          <t>06:25:13</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>3.47</v>
+        <v>3.91</v>
       </c>
       <c r="F20" t="n">
-        <v>9.75</v>
+        <v>10.39</v>
       </c>
       <c r="G20" t="n">
-        <v>218.1</v>
+        <v>211</v>
       </c>
       <c r="H20" t="n">
-        <v>94.5</v>
+        <v>81.2</v>
       </c>
       <c r="I20" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J20" t="n">
-        <v>81.59</v>
+        <v>-57.64</v>
       </c>
       <c r="K20" t="n">
-        <v>-93.69</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>124.24</v>
+        <v>106.42</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06:25:58</t>
+          <t>06:26:50</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>3.61</v>
+        <v>4.2</v>
       </c>
       <c r="F21" t="n">
-        <v>9.77</v>
+        <v>9.91</v>
       </c>
       <c r="G21" t="n">
-        <v>219.9</v>
+        <v>231</v>
       </c>
       <c r="H21" t="n">
-        <v>96.7</v>
+        <v>87</v>
       </c>
       <c r="I21" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="J21" t="n">
-        <v>-47.02</v>
+        <v>-63.02</v>
       </c>
       <c r="K21" t="n">
-        <v>-169.25</v>
+        <v>30.15</v>
       </c>
       <c r="L21" t="n">
-        <v>175.66</v>
+        <v>69.86</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06:28:14</t>
+          <t>06:28:12</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>3.37</v>
+        <v>3.96</v>
       </c>
       <c r="F22" t="n">
-        <v>9.9</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>221.7</v>
+        <v>209.3</v>
       </c>
       <c r="H22" t="n">
-        <v>87.90000000000001</v>
+        <v>61.7</v>
       </c>
       <c r="I22" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="J22" t="n">
-        <v>95.89</v>
+        <v>-97.06999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>168.84</v>
+        <v>-105.81</v>
       </c>
       <c r="L22" t="n">
-        <v>194.17</v>
+        <v>143.59</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06:33:13</t>
+          <t>06:32:32</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>3.67</v>
+        <v>3.72</v>
       </c>
       <c r="F23" t="n">
-        <v>9.84</v>
+        <v>10.17</v>
       </c>
       <c r="G23" t="n">
-        <v>228.4</v>
+        <v>219.4</v>
       </c>
       <c r="H23" t="n">
-        <v>91.90000000000001</v>
+        <v>62.3</v>
       </c>
       <c r="I23" t="n">
         <v>22</v>
       </c>
       <c r="J23" t="n">
-        <v>-105.15</v>
+        <v>-181.34</v>
       </c>
       <c r="K23" t="n">
-        <v>-308.24</v>
+        <v>-73.42</v>
       </c>
       <c r="L23" t="n">
-        <v>325.68</v>
+        <v>195.64</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06:35:35</t>
+          <t>06:33:38</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>3.82</v>
+        <v>3.57</v>
       </c>
       <c r="F24" t="n">
-        <v>11.62</v>
+        <v>10.35</v>
       </c>
       <c r="G24" t="n">
-        <v>219.2</v>
+        <v>226.3</v>
       </c>
       <c r="H24" t="n">
-        <v>94</v>
+        <v>31.8</v>
       </c>
       <c r="I24" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J24" t="n">
-        <v>-131.76</v>
+        <v>-154.33</v>
       </c>
       <c r="K24" t="n">
-        <v>352.41</v>
+        <v>-107.9</v>
       </c>
       <c r="L24" t="n">
-        <v>376.24</v>
+        <v>188.31</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06:37:01</t>
+          <t>06:35:07</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>3.23</v>
+        <v>3.95</v>
       </c>
       <c r="F25" t="n">
-        <v>7.96</v>
+        <v>9.74</v>
       </c>
       <c r="G25" t="n">
-        <v>237.2</v>
+        <v>222</v>
       </c>
       <c r="H25" t="n">
-        <v>99.2</v>
+        <v>58.2</v>
       </c>
       <c r="I25" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J25" t="n">
-        <v>-253.98</v>
+        <v>117.06</v>
       </c>
       <c r="K25" t="n">
-        <v>-95.88</v>
+        <v>-181.39</v>
       </c>
       <c r="L25" t="n">
-        <v>271.47</v>
+        <v>215.88</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06:42:56</t>
+          <t>06:39:48</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>3.76</v>
+        <v>3.47</v>
       </c>
       <c r="F26" t="n">
-        <v>9.07</v>
+        <v>7.85</v>
       </c>
       <c r="G26" t="n">
-        <v>219.1</v>
+        <v>225.6</v>
       </c>
       <c r="H26" t="n">
-        <v>98.59999999999999</v>
+        <v>61.2</v>
       </c>
       <c r="I26" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>-76.29000000000001</v>
+        <v>71.2</v>
       </c>
       <c r="K26" t="n">
-        <v>-333.3</v>
+        <v>215.64</v>
       </c>
       <c r="L26" t="n">
-        <v>341.92</v>
+        <v>227.09</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06:45:18</t>
+          <t>06:40:36</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>3.88</v>
+        <v>3.48</v>
       </c>
       <c r="F27" t="n">
-        <v>11.44</v>
+        <v>6.67</v>
       </c>
       <c r="G27" t="n">
-        <v>225</v>
+        <v>225.8</v>
       </c>
       <c r="H27" t="n">
-        <v>91.40000000000001</v>
+        <v>57.5</v>
       </c>
       <c r="I27" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>-439.47</v>
+        <v>-30.92</v>
       </c>
       <c r="K27" t="n">
-        <v>-195.88</v>
+        <v>-264.48</v>
       </c>
       <c r="L27" t="n">
-        <v>481.15</v>
+        <v>266.28</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06:47:21</t>
+          <t>06:41:44</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>4.36</v>
+        <v>3.68</v>
       </c>
       <c r="F28" t="n">
-        <v>9.69</v>
+        <v>11.94</v>
       </c>
       <c r="G28" t="n">
-        <v>232.1</v>
+        <v>219.7</v>
       </c>
       <c r="H28" t="n">
-        <v>96</v>
+        <v>33.3</v>
       </c>
       <c r="I28" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J28" t="n">
-        <v>-41.38</v>
+        <v>-225.24</v>
       </c>
       <c r="K28" t="n">
-        <v>-557.0599999999999</v>
+        <v>-35.67</v>
       </c>
       <c r="L28" t="n">
-        <v>558.59</v>
+        <v>228.05</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06:58:47</t>
+          <t>06:50:46</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>4.06</v>
+        <v>4.08</v>
       </c>
       <c r="F29" t="n">
-        <v>11.67</v>
+        <v>10.41</v>
       </c>
       <c r="G29" t="n">
-        <v>232.5</v>
+        <v>238.7</v>
       </c>
       <c r="H29" t="n">
-        <v>95</v>
+        <v>44.6</v>
       </c>
       <c r="I29" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J29" t="n">
-        <v>1.85</v>
+        <v>-1.7</v>
       </c>
       <c r="K29" t="n">
-        <v>-84.83</v>
+        <v>-48.85</v>
       </c>
       <c r="L29" t="n">
-        <v>84.84999999999999</v>
+        <v>48.88</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07:00:10</t>
+          <t>06:52:47</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>3.74</v>
+        <v>4.01</v>
       </c>
       <c r="F30" t="n">
-        <v>7.24</v>
+        <v>10.14</v>
       </c>
       <c r="G30" t="n">
-        <v>226.8</v>
+        <v>210.7</v>
       </c>
       <c r="H30" t="n">
-        <v>96</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="I30" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J30" t="n">
-        <v>-13.81</v>
+        <v>-63.62</v>
       </c>
       <c r="K30" t="n">
-        <v>82.31999999999999</v>
+        <v>35.14</v>
       </c>
       <c r="L30" t="n">
-        <v>83.47</v>
+        <v>72.68000000000001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07:01:24</t>
+          <t>06:54:48</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>3.86</v>
+        <v>3.41</v>
       </c>
       <c r="F31" t="n">
-        <v>9.92</v>
+        <v>11.79</v>
       </c>
       <c r="G31" t="n">
-        <v>215.9</v>
+        <v>212.5</v>
       </c>
       <c r="H31" t="n">
-        <v>98.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="I31" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>38.19</v>
+        <v>13.5</v>
       </c>
       <c r="K31" t="n">
-        <v>106.13</v>
+        <v>-60.85</v>
       </c>
       <c r="L31" t="n">
-        <v>112.8</v>
+        <v>62.33</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07:06:21</t>
+          <t>06:59:34</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1384,31 +1384,31 @@
         <v>3.55</v>
       </c>
       <c r="F32" t="n">
-        <v>8.49</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="G32" t="n">
-        <v>216.2</v>
+        <v>220.8</v>
       </c>
       <c r="H32" t="n">
-        <v>97</v>
+        <v>79.2</v>
       </c>
       <c r="I32" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J32" t="n">
-        <v>24.38</v>
+        <v>-7.2</v>
       </c>
       <c r="K32" t="n">
-        <v>-95.29000000000001</v>
+        <v>-83.45999999999999</v>
       </c>
       <c r="L32" t="n">
-        <v>98.36</v>
+        <v>83.77</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07:07:59</t>
+          <t>07:01:09</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>4.4</v>
+        <v>3.61</v>
       </c>
       <c r="F33" t="n">
-        <v>12.06</v>
+        <v>7.84</v>
       </c>
       <c r="G33" t="n">
-        <v>228.6</v>
+        <v>224.4</v>
       </c>
       <c r="H33" t="n">
-        <v>95.2</v>
+        <v>65</v>
       </c>
       <c r="I33" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="J33" t="n">
-        <v>-44.37</v>
+        <v>-97.98</v>
       </c>
       <c r="K33" t="n">
-        <v>-74.25</v>
+        <v>1.37</v>
       </c>
       <c r="L33" t="n">
-        <v>86.5</v>
+        <v>97.98999999999999</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07:10:20</t>
+          <t>07:03:05</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,7 +1465,7 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>4.11</v>
+        <v>4.32</v>
       </c>
       <c r="F34" t="n">
         <v>12.3</v>
@@ -1474,25 +1474,25 @@
         <v>223.2</v>
       </c>
       <c r="H34" t="n">
-        <v>91</v>
+        <v>40.2</v>
       </c>
       <c r="I34" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="J34" t="n">
-        <v>-114.43</v>
+        <v>-91.78</v>
       </c>
       <c r="K34" t="n">
-        <v>-62</v>
+        <v>22.57</v>
       </c>
       <c r="L34" t="n">
-        <v>130.15</v>
+        <v>94.51000000000001</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07:14:07</t>
+          <t>07:07:26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>4.23</v>
+        <v>3.49</v>
       </c>
       <c r="F35" t="n">
-        <v>10.37</v>
+        <v>6.88</v>
       </c>
       <c r="G35" t="n">
-        <v>208.8</v>
+        <v>219.7</v>
       </c>
       <c r="H35" t="n">
-        <v>93.5</v>
+        <v>88.5</v>
       </c>
       <c r="I35" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J35" t="n">
-        <v>-92.29000000000001</v>
+        <v>82.65000000000001</v>
       </c>
       <c r="K35" t="n">
-        <v>90.13</v>
+        <v>-66.08</v>
       </c>
       <c r="L35" t="n">
-        <v>129</v>
+        <v>105.82</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07:15:56</t>
+          <t>07:09:39</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>3.87</v>
+        <v>4.48</v>
       </c>
       <c r="F36" t="n">
-        <v>11.37</v>
+        <v>12.3</v>
       </c>
       <c r="G36" t="n">
-        <v>226.2</v>
+        <v>225.3</v>
       </c>
       <c r="H36" t="n">
-        <v>100</v>
+        <v>43.8</v>
       </c>
       <c r="I36" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="J36" t="n">
-        <v>-160.37</v>
+        <v>-44.79</v>
       </c>
       <c r="K36" t="n">
-        <v>-149.03</v>
+        <v>-93.41</v>
       </c>
       <c r="L36" t="n">
-        <v>218.92</v>
+        <v>103.59</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07:18:15</t>
+          <t>07:10:44</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>3.58</v>
+        <v>3.75</v>
       </c>
       <c r="F37" t="n">
-        <v>12.16</v>
+        <v>8.51</v>
       </c>
       <c r="G37" t="n">
-        <v>232.5</v>
+        <v>227.7</v>
       </c>
       <c r="H37" t="n">
-        <v>95.90000000000001</v>
+        <v>98.2</v>
       </c>
       <c r="I37" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J37" t="n">
-        <v>136.62</v>
+        <v>-112.54</v>
       </c>
       <c r="K37" t="n">
-        <v>131.35</v>
+        <v>-29.37</v>
       </c>
       <c r="L37" t="n">
-        <v>189.53</v>
+        <v>116.31</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07:22:21</t>
+          <t>07:16:36</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>3.99</v>
+        <v>4.63</v>
       </c>
       <c r="F38" t="n">
-        <v>12.02</v>
+        <v>12.3</v>
       </c>
       <c r="G38" t="n">
-        <v>223.7</v>
+        <v>221.7</v>
       </c>
       <c r="H38" t="n">
-        <v>96.40000000000001</v>
+        <v>66.8</v>
       </c>
       <c r="I38" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="J38" t="n">
-        <v>-142.46</v>
+        <v>-240.16</v>
       </c>
       <c r="K38" t="n">
-        <v>-136.83</v>
+        <v>123.18</v>
       </c>
       <c r="L38" t="n">
-        <v>197.53</v>
+        <v>269.91</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07:23:16</t>
+          <t>07:18:56</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>3.86</v>
+        <v>3.76</v>
       </c>
       <c r="F39" t="n">
-        <v>8.06</v>
+        <v>10.31</v>
       </c>
       <c r="G39" t="n">
-        <v>228.1</v>
+        <v>224</v>
       </c>
       <c r="H39" t="n">
-        <v>89.8</v>
+        <v>47.2</v>
       </c>
       <c r="I39" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="J39" t="n">
-        <v>-110.52</v>
+        <v>8.16</v>
       </c>
       <c r="K39" t="n">
-        <v>162.79</v>
+        <v>-173.93</v>
       </c>
       <c r="L39" t="n">
-        <v>196.76</v>
+        <v>174.12</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07:25:27</t>
+          <t>07:20:39</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>3.68</v>
+        <v>4.2</v>
       </c>
       <c r="F40" t="n">
-        <v>7.16</v>
+        <v>10.56</v>
       </c>
       <c r="G40" t="n">
-        <v>229.6</v>
+        <v>226.5</v>
       </c>
       <c r="H40" t="n">
-        <v>100</v>
+        <v>61.5</v>
       </c>
       <c r="I40" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>227.96</v>
+        <v>180.26</v>
       </c>
       <c r="K40" t="n">
-        <v>-118.89</v>
+        <v>-180.32</v>
       </c>
       <c r="L40" t="n">
-        <v>257.1</v>
+        <v>254.97</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07:29:31</t>
+          <t>07:24:43</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>3.75</v>
+        <v>3.67</v>
       </c>
       <c r="F41" t="n">
-        <v>7.97</v>
+        <v>6.61</v>
       </c>
       <c r="G41" t="n">
-        <v>216.2</v>
+        <v>220.4</v>
       </c>
       <c r="H41" t="n">
-        <v>88</v>
+        <v>37.2</v>
       </c>
       <c r="I41" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>179.1</v>
+        <v>-223.54</v>
       </c>
       <c r="K41" t="n">
-        <v>-283.39</v>
+        <v>53.62</v>
       </c>
       <c r="L41" t="n">
-        <v>335.25</v>
+        <v>229.88</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07:30:31</t>
+          <t>07:25:40</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>4.04</v>
+        <v>3.85</v>
       </c>
       <c r="F42" t="n">
-        <v>7.61</v>
+        <v>6.21</v>
       </c>
       <c r="G42" t="n">
-        <v>227.8</v>
+        <v>229.3</v>
       </c>
       <c r="H42" t="n">
-        <v>100</v>
+        <v>96.3</v>
       </c>
       <c r="I42" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="J42" t="n">
-        <v>176.81</v>
+        <v>64.34999999999999</v>
       </c>
       <c r="K42" t="n">
-        <v>-245.72</v>
+        <v>-274.48</v>
       </c>
       <c r="L42" t="n">
-        <v>302.72</v>
+        <v>281.92</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07:31:47</t>
+          <t>07:27:43</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>4.01</v>
+        <v>4.11</v>
       </c>
       <c r="F43" t="n">
-        <v>9.56</v>
+        <v>9.35</v>
       </c>
       <c r="G43" t="n">
-        <v>231.1</v>
+        <v>212.4</v>
       </c>
       <c r="H43" t="n">
-        <v>97.40000000000001</v>
+        <v>25.3</v>
       </c>
       <c r="I43" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>-195.28</v>
+        <v>62.82</v>
       </c>
       <c r="K43" t="n">
-        <v>233.65</v>
+        <v>-211.37</v>
       </c>
       <c r="L43" t="n">
-        <v>304.51</v>
+        <v>220.51</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07:45:11</t>
+          <t>07:38:46</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>4.15</v>
+        <v>3.94</v>
       </c>
       <c r="F44" t="n">
-        <v>10.61</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="G44" t="n">
-        <v>218.1</v>
+        <v>230.1</v>
       </c>
       <c r="H44" t="n">
-        <v>96.7</v>
+        <v>83.3</v>
       </c>
       <c r="I44" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="J44" t="n">
-        <v>-92.16</v>
+        <v>-52.56</v>
       </c>
       <c r="K44" t="n">
-        <v>-48.75</v>
+        <v>26.56</v>
       </c>
       <c r="L44" t="n">
-        <v>104.26</v>
+        <v>58.89</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07:46:54</t>
+          <t>07:39:52</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>3.77</v>
+        <v>4.14</v>
       </c>
       <c r="F45" t="n">
-        <v>6.01</v>
+        <v>10.45</v>
       </c>
       <c r="G45" t="n">
-        <v>217.1</v>
+        <v>216.4</v>
       </c>
       <c r="H45" t="n">
-        <v>98.3</v>
+        <v>64.5</v>
       </c>
       <c r="I45" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J45" t="n">
-        <v>-73.48</v>
+        <v>-50.52</v>
       </c>
       <c r="K45" t="n">
-        <v>-22.96</v>
+        <v>-60.37</v>
       </c>
       <c r="L45" t="n">
-        <v>76.98</v>
+        <v>78.72</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07:49:19</t>
+          <t>07:40:40</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="F46" t="n">
-        <v>10.32</v>
+        <v>6.16</v>
       </c>
       <c r="G46" t="n">
-        <v>226.1</v>
+        <v>233.6</v>
       </c>
       <c r="H46" t="n">
-        <v>90.2</v>
+        <v>26.3</v>
       </c>
       <c r="I46" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J46" t="n">
-        <v>-75.98999999999999</v>
+        <v>-39.73</v>
       </c>
       <c r="K46" t="n">
-        <v>24.78</v>
+        <v>-55.54</v>
       </c>
       <c r="L46" t="n">
-        <v>79.93000000000001</v>
+        <v>68.29000000000001</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07:54:28</t>
+          <t>07:46:02</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>3.95</v>
+        <v>3.73</v>
       </c>
       <c r="F47" t="n">
-        <v>12.3</v>
+        <v>10.39</v>
       </c>
       <c r="G47" t="n">
-        <v>228.9</v>
+        <v>235.1</v>
       </c>
       <c r="H47" t="n">
-        <v>100</v>
+        <v>48.5</v>
       </c>
       <c r="I47" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J47" t="n">
-        <v>74.81</v>
+        <v>-75.36</v>
       </c>
       <c r="K47" t="n">
-        <v>68.31</v>
+        <v>-16.32</v>
       </c>
       <c r="L47" t="n">
-        <v>101.3</v>
+        <v>77.09999999999999</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07:56:45</t>
+          <t>07:46:56</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>4.4</v>
+        <v>3.78</v>
       </c>
       <c r="F48" t="n">
-        <v>9.52</v>
+        <v>10.26</v>
       </c>
       <c r="G48" t="n">
-        <v>228.5</v>
+        <v>223.6</v>
       </c>
       <c r="H48" t="n">
-        <v>90.3</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="I48" t="n">
         <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>48.83</v>
+        <v>-73.44</v>
       </c>
       <c r="K48" t="n">
-        <v>102.32</v>
+        <v>4.21</v>
       </c>
       <c r="L48" t="n">
-        <v>113.38</v>
+        <v>73.56</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07:57:52</t>
+          <t>07:48:55</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>4.03</v>
+        <v>3.78</v>
       </c>
       <c r="F49" t="n">
-        <v>11.02</v>
+        <v>9.83</v>
       </c>
       <c r="G49" t="n">
-        <v>218.2</v>
+        <v>215.7</v>
       </c>
       <c r="H49" t="n">
-        <v>96.5</v>
+        <v>29.1</v>
       </c>
       <c r="I49" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J49" t="n">
-        <v>-138.7</v>
+        <v>87.56</v>
       </c>
       <c r="K49" t="n">
-        <v>-66.02</v>
+        <v>36.03</v>
       </c>
       <c r="L49" t="n">
-        <v>153.61</v>
+        <v>94.68000000000001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08:01:26</t>
+          <t>07:52:47</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>4.85</v>
+        <v>3.9</v>
       </c>
       <c r="F50" t="n">
-        <v>10.95</v>
+        <v>9.17</v>
       </c>
       <c r="G50" t="n">
-        <v>218.7</v>
+        <v>229.4</v>
       </c>
       <c r="H50" t="n">
-        <v>93</v>
+        <v>60</v>
       </c>
       <c r="I50" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="J50" t="n">
-        <v>-172.67</v>
+        <v>-158.63</v>
       </c>
       <c r="K50" t="n">
-        <v>-93.3</v>
+        <v>-13.59</v>
       </c>
       <c r="L50" t="n">
-        <v>196.26</v>
+        <v>159.21</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08:02:36</t>
+          <t>07:53:48</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>3.83</v>
+        <v>4.22</v>
       </c>
       <c r="F51" t="n">
-        <v>10.02</v>
+        <v>12.3</v>
       </c>
       <c r="G51" t="n">
-        <v>224.6</v>
+        <v>221.5</v>
       </c>
       <c r="H51" t="n">
-        <v>100</v>
+        <v>54.6</v>
       </c>
       <c r="I51" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>-279.58</v>
+        <v>-31.62</v>
       </c>
       <c r="K51" t="n">
-        <v>7.57</v>
+        <v>163.19</v>
       </c>
       <c r="L51" t="n">
-        <v>279.69</v>
+        <v>166.22</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08:04:00</t>
+          <t>07:54:55</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>3.45</v>
+        <v>4.42</v>
       </c>
       <c r="F52" t="n">
-        <v>9.35</v>
+        <v>8.51</v>
       </c>
       <c r="G52" t="n">
-        <v>219.7</v>
+        <v>224.9</v>
       </c>
       <c r="H52" t="n">
-        <v>99.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="I52" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>82.26000000000001</v>
+        <v>-146.95</v>
       </c>
       <c r="K52" t="n">
-        <v>-166.44</v>
+        <v>118.16</v>
       </c>
       <c r="L52" t="n">
-        <v>185.66</v>
+        <v>188.56</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08:08:33</t>
+          <t>07:59:52</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>4.36</v>
+        <v>3.61</v>
       </c>
       <c r="F53" t="n">
-        <v>11.35</v>
+        <v>7.81</v>
       </c>
       <c r="G53" t="n">
-        <v>211.4</v>
+        <v>227.2</v>
       </c>
       <c r="H53" t="n">
-        <v>98.3</v>
+        <v>66.5</v>
       </c>
       <c r="I53" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J53" t="n">
-        <v>-197.75</v>
+        <v>-112.53</v>
       </c>
       <c r="K53" t="n">
-        <v>104.13</v>
+        <v>-80.94</v>
       </c>
       <c r="L53" t="n">
-        <v>223.49</v>
+        <v>138.62</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08:11:03</t>
+          <t>08:02:02</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>4.26</v>
+        <v>4.19</v>
       </c>
       <c r="F54" t="n">
-        <v>12.26</v>
+        <v>12.3</v>
       </c>
       <c r="G54" t="n">
-        <v>221.1</v>
+        <v>224</v>
       </c>
       <c r="H54" t="n">
-        <v>95.3</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="I54" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="J54" t="n">
-        <v>102.98</v>
+        <v>-19.25</v>
       </c>
       <c r="K54" t="n">
-        <v>-239.42</v>
+        <v>-188.49</v>
       </c>
       <c r="L54" t="n">
-        <v>260.63</v>
+        <v>189.47</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08:12:46</t>
+          <t>08:03:21</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>4.54</v>
+        <v>4.57</v>
       </c>
       <c r="F55" t="n">
-        <v>12.3</v>
+        <v>10.63</v>
       </c>
       <c r="G55" t="n">
-        <v>226.3</v>
+        <v>218.2</v>
       </c>
       <c r="H55" t="n">
-        <v>99.2</v>
+        <v>39.7</v>
       </c>
       <c r="I55" t="n">
         <v>20</v>
       </c>
       <c r="J55" t="n">
-        <v>-139.91</v>
+        <v>-189.36</v>
       </c>
       <c r="K55" t="n">
-        <v>-249.88</v>
+        <v>-90.76000000000001</v>
       </c>
       <c r="L55" t="n">
-        <v>286.38</v>
+        <v>209.99</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08:16:25</t>
+          <t>08:08:43</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>3.94</v>
+        <v>4.03</v>
       </c>
       <c r="F56" t="n">
-        <v>8.73</v>
+        <v>8.98</v>
       </c>
       <c r="G56" t="n">
-        <v>211</v>
+        <v>219.7</v>
       </c>
       <c r="H56" t="n">
-        <v>100</v>
+        <v>56.2</v>
       </c>
       <c r="I56" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="J56" t="n">
-        <v>-284.23</v>
+        <v>-90.36</v>
       </c>
       <c r="K56" t="n">
-        <v>-268.95</v>
+        <v>203.66</v>
       </c>
       <c r="L56" t="n">
-        <v>391.31</v>
+        <v>222.81</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08:18:22</t>
+          <t>08:09:53</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>3.83</v>
+        <v>3.77</v>
       </c>
       <c r="F57" t="n">
-        <v>11.67</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="G57" t="n">
-        <v>246.5</v>
+        <v>226.9</v>
       </c>
       <c r="H57" t="n">
-        <v>95.3</v>
+        <v>61</v>
       </c>
       <c r="I57" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J57" t="n">
-        <v>-111.04</v>
+        <v>104.81</v>
       </c>
       <c r="K57" t="n">
-        <v>-305.74</v>
+        <v>-263.1</v>
       </c>
       <c r="L57" t="n">
-        <v>325.28</v>
+        <v>283.21</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08:20:20</t>
+          <t>08:11:20</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>3.92</v>
+        <v>3.72</v>
       </c>
       <c r="F58" t="n">
-        <v>11.81</v>
+        <v>12.04</v>
       </c>
       <c r="G58" t="n">
-        <v>235.1</v>
+        <v>234.1</v>
       </c>
       <c r="H58" t="n">
-        <v>98.5</v>
+        <v>61.4</v>
       </c>
       <c r="I58" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="J58" t="n">
-        <v>263.23</v>
+        <v>-109.89</v>
       </c>
       <c r="K58" t="n">
-        <v>77.17</v>
+        <v>-229</v>
       </c>
       <c r="L58" t="n">
-        <v>274.31</v>
+        <v>254</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08:31:24</t>
+          <t>08:23:50</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>4.38</v>
+        <v>3.73</v>
       </c>
       <c r="F59" t="n">
-        <v>10.13</v>
+        <v>10.85</v>
       </c>
       <c r="G59" t="n">
-        <v>219.9</v>
+        <v>233.5</v>
       </c>
       <c r="H59" t="n">
-        <v>99.7</v>
+        <v>99.8</v>
       </c>
       <c r="I59" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J59" t="n">
-        <v>94.97</v>
+        <v>-52.1</v>
       </c>
       <c r="K59" t="n">
-        <v>-33.07</v>
+        <v>1</v>
       </c>
       <c r="L59" t="n">
-        <v>100.56</v>
+        <v>52.11</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08:33:12</t>
+          <t>08:25:36</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>3.74</v>
+        <v>4.4</v>
       </c>
       <c r="F60" t="n">
-        <v>8.99</v>
+        <v>11.3</v>
       </c>
       <c r="G60" t="n">
-        <v>224.5</v>
+        <v>224.9</v>
       </c>
       <c r="H60" t="n">
-        <v>94.40000000000001</v>
+        <v>54.3</v>
       </c>
       <c r="I60" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J60" t="n">
-        <v>-32.04</v>
+        <v>-20.09</v>
       </c>
       <c r="K60" t="n">
-        <v>67.52</v>
+        <v>-74.48999999999999</v>
       </c>
       <c r="L60" t="n">
-        <v>74.73999999999999</v>
+        <v>77.15000000000001</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08:33:57</t>
+          <t>08:26:41</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>3.98</v>
+        <v>4.31</v>
       </c>
       <c r="F61" t="n">
-        <v>12.19</v>
+        <v>12.3</v>
       </c>
       <c r="G61" t="n">
-        <v>223.9</v>
+        <v>217.3</v>
       </c>
       <c r="H61" t="n">
-        <v>93.59999999999999</v>
+        <v>4.4</v>
       </c>
       <c r="I61" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J61" t="n">
-        <v>-28.54</v>
+        <v>44.8</v>
       </c>
       <c r="K61" t="n">
-        <v>-89.23</v>
+        <v>81.79000000000001</v>
       </c>
       <c r="L61" t="n">
-        <v>93.69</v>
+        <v>93.26000000000001</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08:37:33</t>
+          <t>08:30:46</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="F62" t="n">
-        <v>8.960000000000001</v>
+        <v>11.13</v>
       </c>
       <c r="G62" t="n">
-        <v>209.2</v>
+        <v>228.2</v>
       </c>
       <c r="H62" t="n">
-        <v>100</v>
+        <v>34</v>
       </c>
       <c r="I62" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="J62" t="n">
-        <v>57.78</v>
+        <v>18.12</v>
       </c>
       <c r="K62" t="n">
-        <v>-81.15000000000001</v>
+        <v>-125.48</v>
       </c>
       <c r="L62" t="n">
-        <v>99.62</v>
+        <v>126.78</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08:39:59</t>
+          <t>08:31:27</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>4.14</v>
+        <v>4.54</v>
       </c>
       <c r="F63" t="n">
-        <v>12.3</v>
+        <v>11.61</v>
       </c>
       <c r="G63" t="n">
-        <v>211.2</v>
+        <v>224.7</v>
       </c>
       <c r="H63" t="n">
-        <v>99.90000000000001</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="I63" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>34.67</v>
+        <v>-105.43</v>
       </c>
       <c r="K63" t="n">
-        <v>148.1</v>
+        <v>21.66</v>
       </c>
       <c r="L63" t="n">
-        <v>152.1</v>
+        <v>107.63</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>08:40:36</t>
+          <t>08:32:48</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>3.93</v>
+        <v>3.8</v>
       </c>
       <c r="F64" t="n">
-        <v>11.15</v>
+        <v>10.67</v>
       </c>
       <c r="G64" t="n">
-        <v>219.1</v>
+        <v>223.3</v>
       </c>
       <c r="H64" t="n">
-        <v>96.40000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="I64" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J64" t="n">
-        <v>-87.61</v>
+        <v>-41.81</v>
       </c>
       <c r="K64" t="n">
-        <v>67.7</v>
+        <v>-70.41</v>
       </c>
       <c r="L64" t="n">
-        <v>110.72</v>
+        <v>81.89</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>08:44:29</t>
+          <t>08:37:42</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>4.16</v>
+        <v>4.1</v>
       </c>
       <c r="F65" t="n">
-        <v>11.04</v>
+        <v>10.23</v>
       </c>
       <c r="G65" t="n">
-        <v>221.6</v>
+        <v>214.2</v>
       </c>
       <c r="H65" t="n">
-        <v>97.3</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="I65" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="J65" t="n">
-        <v>-178.03</v>
+        <v>20.09</v>
       </c>
       <c r="K65" t="n">
-        <v>-95.61</v>
+        <v>-165.74</v>
       </c>
       <c r="L65" t="n">
-        <v>202.08</v>
+        <v>166.95</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>08:45:32</t>
+          <t>08:39:49</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>4.14</v>
+        <v>4.2</v>
       </c>
       <c r="F66" t="n">
-        <v>12.2</v>
+        <v>11.26</v>
       </c>
       <c r="G66" t="n">
-        <v>217.2</v>
+        <v>217.3</v>
       </c>
       <c r="H66" t="n">
-        <v>92.90000000000001</v>
+        <v>59.7</v>
       </c>
       <c r="I66" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J66" t="n">
-        <v>-220.67</v>
+        <v>-125.25</v>
       </c>
       <c r="K66" t="n">
-        <v>105</v>
+        <v>7.07</v>
       </c>
       <c r="L66" t="n">
-        <v>244.38</v>
+        <v>125.45</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>08:46:31</t>
+          <t>08:42:07</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>4.21</v>
+        <v>4.59</v>
       </c>
       <c r="F67" t="n">
-        <v>9.529999999999999</v>
+        <v>11.76</v>
       </c>
       <c r="G67" t="n">
-        <v>218.7</v>
+        <v>224.3</v>
       </c>
       <c r="H67" t="n">
-        <v>97.3</v>
+        <v>78.8</v>
       </c>
       <c r="I67" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J67" t="n">
-        <v>-157.35</v>
+        <v>83.97</v>
       </c>
       <c r="K67" t="n">
-        <v>-56.13</v>
+        <v>-104.58</v>
       </c>
       <c r="L67" t="n">
-        <v>167.06</v>
+        <v>134.12</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>08:53:05</t>
+          <t>08:46:08</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>4.81</v>
+        <v>4.54</v>
       </c>
       <c r="F68" t="n">
-        <v>12.3</v>
+        <v>11.14</v>
       </c>
       <c r="G68" t="n">
-        <v>228.3</v>
+        <v>207.8</v>
       </c>
       <c r="H68" t="n">
-        <v>95.40000000000001</v>
+        <v>63.7</v>
       </c>
       <c r="I68" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>-311.6</v>
+        <v>100.89</v>
       </c>
       <c r="K68" t="n">
-        <v>-218.45</v>
+        <v>-219.58</v>
       </c>
       <c r="L68" t="n">
-        <v>380.55</v>
+        <v>241.65</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>08:54:00</t>
+          <t>08:48:11</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>3.51</v>
+        <v>4.71</v>
       </c>
       <c r="F69" t="n">
         <v>12.3</v>
       </c>
       <c r="G69" t="n">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="H69" t="n">
-        <v>96.40000000000001</v>
+        <v>67.8</v>
       </c>
       <c r="I69" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="J69" t="n">
-        <v>229.75</v>
+        <v>-68.28</v>
       </c>
       <c r="K69" t="n">
-        <v>-13.56</v>
+        <v>-224.94</v>
       </c>
       <c r="L69" t="n">
-        <v>230.15</v>
+        <v>235.07</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>08:56:06</t>
+          <t>08:49:45</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>4.34</v>
+        <v>4.47</v>
       </c>
       <c r="F70" t="n">
         <v>12.3</v>
       </c>
       <c r="G70" t="n">
-        <v>228</v>
+        <v>221.9</v>
       </c>
       <c r="H70" t="n">
-        <v>95.59999999999999</v>
+        <v>49.3</v>
       </c>
       <c r="I70" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>-284.25</v>
+        <v>-259.2</v>
       </c>
       <c r="K70" t="n">
-        <v>-82.87</v>
+        <v>-194.63</v>
       </c>
       <c r="L70" t="n">
-        <v>296.09</v>
+        <v>324.14</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>09:01:29</t>
+          <t>08:53:58</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>4.84</v>
+        <v>4.44</v>
       </c>
       <c r="F71" t="n">
-        <v>12.07</v>
+        <v>10.08</v>
       </c>
       <c r="G71" t="n">
-        <v>227.8</v>
+        <v>213.7</v>
       </c>
       <c r="H71" t="n">
-        <v>99.5</v>
+        <v>60.5</v>
       </c>
       <c r="I71" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>-549.77</v>
+        <v>-312.02</v>
       </c>
       <c r="K71" t="n">
-        <v>415.47</v>
+        <v>-248.8</v>
       </c>
       <c r="L71" t="n">
-        <v>689.1</v>
+        <v>399.07</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>09:04:07</t>
+          <t>08:55:02</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>4.2</v>
+        <v>4.49</v>
       </c>
       <c r="F72" t="n">
         <v>12.3</v>
       </c>
       <c r="G72" t="n">
-        <v>241.1</v>
+        <v>233.7</v>
       </c>
       <c r="H72" t="n">
-        <v>95.3</v>
+        <v>99.7</v>
       </c>
       <c r="I72" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J72" t="n">
-        <v>-255.38</v>
+        <v>137.78</v>
       </c>
       <c r="K72" t="n">
-        <v>-257.98</v>
+        <v>-282.44</v>
       </c>
       <c r="L72" t="n">
-        <v>363.01</v>
+        <v>314.26</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>09:04:49</t>
+          <t>08:57:36</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>4.69</v>
+        <v>4.57</v>
       </c>
       <c r="F73" t="n">
-        <v>12.23</v>
+        <v>11.68</v>
       </c>
       <c r="G73" t="n">
-        <v>219.2</v>
+        <v>212.5</v>
       </c>
       <c r="H73" t="n">
-        <v>93.2</v>
+        <v>55.8</v>
       </c>
       <c r="I73" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J73" t="n">
-        <v>374.33</v>
+        <v>-129.24</v>
       </c>
       <c r="K73" t="n">
-        <v>-37.02</v>
+        <v>-244.77</v>
       </c>
       <c r="L73" t="n">
-        <v>376.16</v>
+        <v>276.79</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>09:14:23</t>
+          <t>09:05:20</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>4.18</v>
+        <v>4.8</v>
       </c>
       <c r="F74" t="n">
-        <v>10.91</v>
+        <v>12.3</v>
       </c>
       <c r="G74" t="n">
-        <v>227.1</v>
+        <v>212.1</v>
       </c>
       <c r="H74" t="n">
-        <v>100</v>
+        <v>66.8</v>
       </c>
       <c r="I74" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J74" t="n">
-        <v>16.81</v>
+        <v>91.51000000000001</v>
       </c>
       <c r="K74" t="n">
-        <v>-96.63</v>
+        <v>13.2</v>
       </c>
       <c r="L74" t="n">
-        <v>98.08</v>
+        <v>92.45999999999999</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09:16:15</t>
+          <t>09:06:31</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>4.41</v>
+        <v>4.56</v>
       </c>
       <c r="F75" t="n">
         <v>12.3</v>
       </c>
       <c r="G75" t="n">
-        <v>231.3</v>
+        <v>229</v>
       </c>
       <c r="H75" t="n">
-        <v>93.90000000000001</v>
+        <v>42.5</v>
       </c>
       <c r="I75" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>-13.87</v>
+        <v>56.93</v>
       </c>
       <c r="K75" t="n">
-        <v>-140.81</v>
+        <v>74.81</v>
       </c>
       <c r="L75" t="n">
-        <v>141.49</v>
+        <v>94.01000000000001</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09:17:33</t>
+          <t>09:07:17</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>5.16</v>
+        <v>4.86</v>
       </c>
       <c r="F76" t="n">
         <v>12.3</v>
       </c>
       <c r="G76" t="n">
-        <v>233.5</v>
+        <v>222.2</v>
       </c>
       <c r="H76" t="n">
-        <v>96.09999999999999</v>
+        <v>34.9</v>
       </c>
       <c r="I76" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J76" t="n">
-        <v>-21.32</v>
+        <v>71.75</v>
       </c>
       <c r="K76" t="n">
-        <v>-109.09</v>
+        <v>-64.19</v>
       </c>
       <c r="L76" t="n">
-        <v>111.15</v>
+        <v>96.27</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09:22:26</t>
+          <t>09:11:48</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>4.36</v>
+        <v>5.18</v>
       </c>
       <c r="F77" t="n">
         <v>12.3</v>
       </c>
       <c r="G77" t="n">
-        <v>219.4</v>
+        <v>235.6</v>
       </c>
       <c r="H77" t="n">
-        <v>94.5</v>
+        <v>88.8</v>
       </c>
       <c r="I77" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J77" t="n">
-        <v>121.38</v>
+        <v>-79.36</v>
       </c>
       <c r="K77" t="n">
-        <v>-226.52</v>
+        <v>135.14</v>
       </c>
       <c r="L77" t="n">
-        <v>256.99</v>
+        <v>156.72</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09:24:27</t>
+          <t>09:13:01</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>4.38</v>
+        <v>4.61</v>
       </c>
       <c r="F78" t="n">
-        <v>11.28</v>
+        <v>12.3</v>
       </c>
       <c r="G78" t="n">
-        <v>234.2</v>
+        <v>232.3</v>
       </c>
       <c r="H78" t="n">
-        <v>98.3</v>
+        <v>51.4</v>
       </c>
       <c r="I78" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J78" t="n">
-        <v>-78.81999999999999</v>
+        <v>70.56999999999999</v>
       </c>
       <c r="K78" t="n">
-        <v>92.65000000000001</v>
+        <v>85.33</v>
       </c>
       <c r="L78" t="n">
-        <v>121.64</v>
+        <v>110.73</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09:25:42</t>
+          <t>09:14:26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>4.57</v>
+        <v>4.31</v>
       </c>
       <c r="F79" t="n">
-        <v>9.43</v>
+        <v>12.3</v>
       </c>
       <c r="G79" t="n">
-        <v>232.5</v>
+        <v>227.2</v>
       </c>
       <c r="H79" t="n">
-        <v>98.59999999999999</v>
+        <v>24.1</v>
       </c>
       <c r="I79" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>40.47</v>
+        <v>-109.21</v>
       </c>
       <c r="K79" t="n">
-        <v>85.33</v>
+        <v>-60.07</v>
       </c>
       <c r="L79" t="n">
-        <v>94.44</v>
+        <v>124.64</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>09:30:07</t>
+          <t>09:18:19</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>4.26</v>
+        <v>4.42</v>
       </c>
       <c r="F80" t="n">
-        <v>10.17</v>
+        <v>10.07</v>
       </c>
       <c r="G80" t="n">
-        <v>230.9</v>
+        <v>216.8</v>
       </c>
       <c r="H80" t="n">
-        <v>95.7</v>
+        <v>54.4</v>
       </c>
       <c r="I80" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>168.3</v>
+        <v>-108.35</v>
       </c>
       <c r="K80" t="n">
-        <v>6.29</v>
+        <v>34.13</v>
       </c>
       <c r="L80" t="n">
-        <v>168.41</v>
+        <v>113.6</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>09:31:17</t>
+          <t>09:20:07</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>4.87</v>
+        <v>4.66</v>
       </c>
       <c r="F81" t="n">
         <v>12.3</v>
       </c>
       <c r="G81" t="n">
-        <v>226.7</v>
+        <v>220.7</v>
       </c>
       <c r="H81" t="n">
-        <v>95.5</v>
+        <v>87.7</v>
       </c>
       <c r="I81" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J81" t="n">
-        <v>252.24</v>
+        <v>170.15</v>
       </c>
       <c r="K81" t="n">
-        <v>-16.89</v>
+        <v>148.63</v>
       </c>
       <c r="L81" t="n">
-        <v>252.8</v>
+        <v>225.93</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>09:32:26</t>
+          <t>09:22:08</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>4.38</v>
+        <v>4.43</v>
       </c>
       <c r="F82" t="n">
-        <v>12.3</v>
+        <v>10.61</v>
       </c>
       <c r="G82" t="n">
-        <v>221.7</v>
+        <v>228.8</v>
       </c>
       <c r="H82" t="n">
-        <v>91.7</v>
+        <v>48.3</v>
       </c>
       <c r="I82" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J82" t="n">
-        <v>-184.15</v>
+        <v>-178.07</v>
       </c>
       <c r="K82" t="n">
-        <v>104.66</v>
+        <v>-43.16</v>
       </c>
       <c r="L82" t="n">
-        <v>211.81</v>
+        <v>183.23</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>09:36:16</t>
+          <t>09:26:43</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>4.44</v>
+        <v>4.94</v>
       </c>
       <c r="F83" t="n">
-        <v>12.08</v>
+        <v>12.3</v>
       </c>
       <c r="G83" t="n">
-        <v>212.7</v>
+        <v>226</v>
       </c>
       <c r="H83" t="n">
-        <v>96.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="I83" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="J83" t="n">
-        <v>-260.54</v>
+        <v>-235.98</v>
       </c>
       <c r="K83" t="n">
-        <v>-194.31</v>
+        <v>113.07</v>
       </c>
       <c r="L83" t="n">
-        <v>325.02</v>
+        <v>261.67</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>09:38:07</t>
+          <t>09:29:16</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>4.19</v>
+        <v>4.13</v>
       </c>
       <c r="F84" t="n">
-        <v>12.3</v>
+        <v>12.23</v>
       </c>
       <c r="G84" t="n">
-        <v>231.4</v>
+        <v>228.2</v>
       </c>
       <c r="H84" t="n">
-        <v>100</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="I84" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="J84" t="n">
-        <v>-60.99</v>
+        <v>24.16</v>
       </c>
       <c r="K84" t="n">
-        <v>-188.14</v>
+        <v>236.97</v>
       </c>
       <c r="L84" t="n">
-        <v>197.78</v>
+        <v>238.19</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>09:40:26</t>
+          <t>09:31:00</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>4.24</v>
+        <v>4.15</v>
       </c>
       <c r="F85" t="n">
-        <v>12.3</v>
+        <v>11.35</v>
       </c>
       <c r="G85" t="n">
-        <v>220.1</v>
+        <v>235</v>
       </c>
       <c r="H85" t="n">
-        <v>100</v>
+        <v>46.3</v>
       </c>
       <c r="I85" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>4.95</v>
+        <v>-93.64</v>
       </c>
       <c r="K85" t="n">
-        <v>245.52</v>
+        <v>209.73</v>
       </c>
       <c r="L85" t="n">
-        <v>245.57</v>
+        <v>229.69</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>09:44:23</t>
+          <t>09:35:44</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>4.55</v>
+        <v>4.22</v>
       </c>
       <c r="F86" t="n">
         <v>12.3</v>
       </c>
       <c r="G86" t="n">
-        <v>228.9</v>
+        <v>231.1</v>
       </c>
       <c r="H86" t="n">
-        <v>100</v>
+        <v>49.5</v>
       </c>
       <c r="I86" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="J86" t="n">
-        <v>-198.93</v>
+        <v>179.08</v>
       </c>
       <c r="K86" t="n">
-        <v>-441.82</v>
+        <v>-233.82</v>
       </c>
       <c r="L86" t="n">
-        <v>484.54</v>
+        <v>294.51</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>09:46:20</t>
+          <t>09:37:05</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>5.09</v>
+        <v>5.04</v>
       </c>
       <c r="F87" t="n">
         <v>12.3</v>
       </c>
       <c r="G87" t="n">
-        <v>219</v>
+        <v>216.3</v>
       </c>
       <c r="H87" t="n">
-        <v>94.2</v>
+        <v>91.7</v>
       </c>
       <c r="I87" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J87" t="n">
-        <v>207.08</v>
+        <v>-228.12</v>
       </c>
       <c r="K87" t="n">
-        <v>287.65</v>
+        <v>-335.88</v>
       </c>
       <c r="L87" t="n">
-        <v>354.43</v>
+        <v>406.03</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>09:48:37</t>
+          <t>09:38:09</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>4.66</v>
+        <v>4.42</v>
       </c>
       <c r="F88" t="n">
-        <v>12.3</v>
+        <v>9.93</v>
       </c>
       <c r="G88" t="n">
-        <v>220.6</v>
+        <v>231.2</v>
       </c>
       <c r="H88" t="n">
-        <v>100</v>
+        <v>45.9</v>
       </c>
       <c r="I88" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J88" t="n">
-        <v>309.76</v>
+        <v>-231.91</v>
       </c>
       <c r="K88" t="n">
-        <v>-149.19</v>
+        <v>-211.93</v>
       </c>
       <c r="L88" t="n">
-        <v>343.82</v>
+        <v>314.16</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-08-26.xlsx
+++ b/output/2025-08-26.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>3.38</v>
+        <v>3.64</v>
       </c>
       <c r="F14" t="n">
-        <v>9.99</v>
+        <v>7.33</v>
       </c>
       <c r="G14" t="n">
-        <v>246.1</v>
+        <v>242.8</v>
       </c>
       <c r="H14" t="n">
-        <v>48.9</v>
+        <v>26.2</v>
       </c>
       <c r="I14" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J14" t="n">
-        <v>-84.14</v>
+        <v>-54.75</v>
       </c>
       <c r="K14" t="n">
-        <v>-25.99</v>
+        <v>1.59</v>
       </c>
       <c r="L14" t="n">
-        <v>88.06999999999999</v>
+        <v>54.77</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06:10:07</t>
+          <t>06:08:56</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3.57</v>
+        <v>3.55</v>
       </c>
       <c r="F15" t="n">
-        <v>7.78</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>232.6</v>
+        <v>221.4</v>
       </c>
       <c r="H15" t="n">
-        <v>62.4</v>
+        <v>100</v>
       </c>
       <c r="I15" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J15" t="n">
-        <v>-66.79000000000001</v>
+        <v>-39.98</v>
       </c>
       <c r="K15" t="n">
-        <v>-18.22</v>
+        <v>44.36</v>
       </c>
       <c r="L15" t="n">
-        <v>69.23</v>
+        <v>59.72</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06:11:36</t>
+          <t>06:10:33</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>3.8</v>
+        <v>3.38</v>
       </c>
       <c r="F16" t="n">
-        <v>9.460000000000001</v>
+        <v>10.42</v>
       </c>
       <c r="G16" t="n">
-        <v>219.4</v>
+        <v>223.3</v>
       </c>
       <c r="H16" t="n">
-        <v>76.09999999999999</v>
+        <v>44.5</v>
       </c>
       <c r="I16" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J16" t="n">
-        <v>6.87</v>
+        <v>-12.02</v>
       </c>
       <c r="K16" t="n">
-        <v>-62.93</v>
+        <v>-79.56999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>63.3</v>
+        <v>80.47</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06:15:19</t>
+          <t>06:16:05</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="F17" t="n">
-        <v>6.69</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>227</v>
+        <v>223.1</v>
       </c>
       <c r="H17" t="n">
-        <v>66.90000000000001</v>
+        <v>41.3</v>
       </c>
       <c r="I17" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>3.58</v>
+        <v>-76.53</v>
       </c>
       <c r="K17" t="n">
-        <v>-91.62</v>
+        <v>20.59</v>
       </c>
       <c r="L17" t="n">
-        <v>91.69</v>
+        <v>79.25</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06:16:56</t>
+          <t>06:17:01</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>3.76</v>
+        <v>3.33</v>
       </c>
       <c r="F18" t="n">
-        <v>8.539999999999999</v>
+        <v>9.94</v>
       </c>
       <c r="G18" t="n">
-        <v>233.4</v>
+        <v>227.2</v>
       </c>
       <c r="H18" t="n">
-        <v>55.1</v>
+        <v>100</v>
       </c>
       <c r="I18" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J18" t="n">
-        <v>-58.27</v>
+        <v>66.09</v>
       </c>
       <c r="K18" t="n">
-        <v>-82.38</v>
+        <v>52.03</v>
       </c>
       <c r="L18" t="n">
-        <v>100.91</v>
+        <v>84.11</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06:19:28</t>
+          <t>06:17:59</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>3.92</v>
+        <v>4.3</v>
       </c>
       <c r="F19" t="n">
-        <v>9.9</v>
+        <v>12.22</v>
       </c>
       <c r="G19" t="n">
-        <v>217.6</v>
+        <v>209.4</v>
       </c>
       <c r="H19" t="n">
-        <v>76.90000000000001</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J19" t="n">
-        <v>-17.74</v>
+        <v>101.47</v>
       </c>
       <c r="K19" t="n">
-        <v>-90.33</v>
+        <v>-85.34999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>92.05</v>
+        <v>132.59</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06:25:13</t>
+          <t>06:22:29</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>3.91</v>
+        <v>3.68</v>
       </c>
       <c r="F20" t="n">
-        <v>10.39</v>
+        <v>5.88</v>
       </c>
       <c r="G20" t="n">
-        <v>211</v>
+        <v>216.5</v>
       </c>
       <c r="H20" t="n">
-        <v>81.2</v>
+        <v>59.5</v>
       </c>
       <c r="I20" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J20" t="n">
-        <v>-57.64</v>
+        <v>54.09</v>
       </c>
       <c r="K20" t="n">
-        <v>89.45999999999999</v>
+        <v>-135.56</v>
       </c>
       <c r="L20" t="n">
-        <v>106.42</v>
+        <v>145.96</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06:26:50</t>
+          <t>06:23:12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>4.2</v>
+        <v>4.18</v>
       </c>
       <c r="F21" t="n">
-        <v>9.91</v>
+        <v>10.45</v>
       </c>
       <c r="G21" t="n">
-        <v>231</v>
+        <v>229.2</v>
       </c>
       <c r="H21" t="n">
-        <v>87</v>
+        <v>62.9</v>
       </c>
       <c r="I21" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="J21" t="n">
-        <v>-63.02</v>
+        <v>-20.11</v>
       </c>
       <c r="K21" t="n">
-        <v>30.15</v>
+        <v>-158.67</v>
       </c>
       <c r="L21" t="n">
-        <v>69.86</v>
+        <v>159.94</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06:28:12</t>
+          <t>06:25:25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>3.96</v>
+        <v>4.02</v>
       </c>
       <c r="F22" t="n">
-        <v>8.869999999999999</v>
+        <v>9.91</v>
       </c>
       <c r="G22" t="n">
-        <v>209.3</v>
+        <v>231.3</v>
       </c>
       <c r="H22" t="n">
-        <v>61.7</v>
+        <v>69.3</v>
       </c>
       <c r="I22" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J22" t="n">
-        <v>-97.06999999999999</v>
+        <v>-80.59</v>
       </c>
       <c r="K22" t="n">
-        <v>-105.81</v>
+        <v>-102.46</v>
       </c>
       <c r="L22" t="n">
-        <v>143.59</v>
+        <v>130.36</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06:32:32</t>
+          <t>06:29:06</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>3.72</v>
+        <v>3.5</v>
       </c>
       <c r="F23" t="n">
-        <v>10.17</v>
+        <v>9.06</v>
       </c>
       <c r="G23" t="n">
-        <v>219.4</v>
+        <v>223.7</v>
       </c>
       <c r="H23" t="n">
-        <v>62.3</v>
+        <v>66.5</v>
       </c>
       <c r="I23" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J23" t="n">
-        <v>-181.34</v>
+        <v>133.24</v>
       </c>
       <c r="K23" t="n">
-        <v>-73.42</v>
+        <v>-81.16</v>
       </c>
       <c r="L23" t="n">
-        <v>195.64</v>
+        <v>156.01</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06:33:38</t>
+          <t>06:30:51</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>3.57</v>
+        <v>3.96</v>
       </c>
       <c r="F24" t="n">
-        <v>10.35</v>
+        <v>10.5</v>
       </c>
       <c r="G24" t="n">
-        <v>226.3</v>
+        <v>226</v>
       </c>
       <c r="H24" t="n">
-        <v>31.8</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J24" t="n">
-        <v>-154.33</v>
+        <v>78.23</v>
       </c>
       <c r="K24" t="n">
-        <v>-107.9</v>
+        <v>-197.94</v>
       </c>
       <c r="L24" t="n">
-        <v>188.31</v>
+        <v>212.84</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06:35:07</t>
+          <t>06:32:36</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>3.95</v>
+        <v>4.01</v>
       </c>
       <c r="F25" t="n">
-        <v>9.74</v>
+        <v>7.14</v>
       </c>
       <c r="G25" t="n">
-        <v>222</v>
+        <v>225.5</v>
       </c>
       <c r="H25" t="n">
-        <v>58.2</v>
+        <v>82.7</v>
       </c>
       <c r="I25" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J25" t="n">
-        <v>117.06</v>
+        <v>292.71</v>
       </c>
       <c r="K25" t="n">
-        <v>-181.39</v>
+        <v>-85.40000000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>215.88</v>
+        <v>304.91</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06:39:48</t>
+          <t>06:37:53</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>3.47</v>
+        <v>3.77</v>
       </c>
       <c r="F26" t="n">
-        <v>7.85</v>
+        <v>10.7</v>
       </c>
       <c r="G26" t="n">
-        <v>225.6</v>
+        <v>211.3</v>
       </c>
       <c r="H26" t="n">
-        <v>61.2</v>
+        <v>57.2</v>
       </c>
       <c r="I26" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J26" t="n">
-        <v>71.2</v>
+        <v>-263.21</v>
       </c>
       <c r="K26" t="n">
-        <v>215.64</v>
+        <v>64.17</v>
       </c>
       <c r="L26" t="n">
-        <v>227.09</v>
+        <v>270.92</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06:40:36</t>
+          <t>06:39:29</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>3.48</v>
+        <v>3.68</v>
       </c>
       <c r="F27" t="n">
-        <v>6.67</v>
+        <v>9.9</v>
       </c>
       <c r="G27" t="n">
-        <v>225.8</v>
+        <v>229.6</v>
       </c>
       <c r="H27" t="n">
-        <v>57.5</v>
+        <v>100</v>
       </c>
       <c r="I27" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J27" t="n">
-        <v>-30.92</v>
+        <v>124.44</v>
       </c>
       <c r="K27" t="n">
-        <v>-264.48</v>
+        <v>-259.69</v>
       </c>
       <c r="L27" t="n">
-        <v>266.28</v>
+        <v>287.97</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06:41:44</t>
+          <t>06:41:51</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>3.68</v>
+        <v>4.33</v>
       </c>
       <c r="F28" t="n">
-        <v>11.94</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="G28" t="n">
-        <v>219.7</v>
+        <v>229.2</v>
       </c>
       <c r="H28" t="n">
-        <v>33.3</v>
+        <v>49.3</v>
       </c>
       <c r="I28" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J28" t="n">
-        <v>-225.24</v>
+        <v>214.87</v>
       </c>
       <c r="K28" t="n">
-        <v>-35.67</v>
+        <v>251.49</v>
       </c>
       <c r="L28" t="n">
-        <v>228.05</v>
+        <v>330.78</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06:50:46</t>
+          <t>06:54:11</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>4.08</v>
+        <v>4.1</v>
       </c>
       <c r="F29" t="n">
-        <v>10.41</v>
+        <v>10.05</v>
       </c>
       <c r="G29" t="n">
-        <v>238.7</v>
+        <v>235.3</v>
       </c>
       <c r="H29" t="n">
-        <v>44.6</v>
+        <v>63.8</v>
       </c>
       <c r="I29" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J29" t="n">
-        <v>-1.7</v>
+        <v>-33.76</v>
       </c>
       <c r="K29" t="n">
-        <v>-48.85</v>
+        <v>-46.86</v>
       </c>
       <c r="L29" t="n">
-        <v>48.88</v>
+        <v>57.75</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06:52:47</t>
+          <t>06:55:31</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>4.01</v>
+        <v>4.08</v>
       </c>
       <c r="F30" t="n">
-        <v>10.14</v>
+        <v>10.55</v>
       </c>
       <c r="G30" t="n">
-        <v>210.7</v>
+        <v>215.7</v>
       </c>
       <c r="H30" t="n">
-        <v>64.09999999999999</v>
+        <v>69.8</v>
       </c>
       <c r="I30" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J30" t="n">
-        <v>-63.62</v>
+        <v>-67.37</v>
       </c>
       <c r="K30" t="n">
-        <v>35.14</v>
+        <v>3.73</v>
       </c>
       <c r="L30" t="n">
-        <v>72.68000000000001</v>
+        <v>67.48</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06:54:48</t>
+          <t>06:56:35</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>3.41</v>
+        <v>3.87</v>
       </c>
       <c r="F31" t="n">
-        <v>11.79</v>
+        <v>7.32</v>
       </c>
       <c r="G31" t="n">
-        <v>212.5</v>
+        <v>227.8</v>
       </c>
       <c r="H31" t="n">
-        <v>100</v>
+        <v>40.1</v>
       </c>
       <c r="I31" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>13.5</v>
+        <v>-38.13</v>
       </c>
       <c r="K31" t="n">
-        <v>-60.85</v>
+        <v>40.2</v>
       </c>
       <c r="L31" t="n">
-        <v>62.33</v>
+        <v>55.41</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06:59:34</t>
+          <t>07:01:11</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>3.55</v>
+        <v>4.58</v>
       </c>
       <c r="F32" t="n">
-        <v>9.130000000000001</v>
+        <v>12.3</v>
       </c>
       <c r="G32" t="n">
-        <v>220.8</v>
+        <v>227.9</v>
       </c>
       <c r="H32" t="n">
-        <v>79.2</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="I32" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J32" t="n">
-        <v>-7.2</v>
+        <v>-68.45</v>
       </c>
       <c r="K32" t="n">
-        <v>-83.45999999999999</v>
+        <v>-63.86</v>
       </c>
       <c r="L32" t="n">
-        <v>83.77</v>
+        <v>93.61</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07:01:09</t>
+          <t>07:02:06</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>3.61</v>
+        <v>4.94</v>
       </c>
       <c r="F33" t="n">
-        <v>7.84</v>
+        <v>12.3</v>
       </c>
       <c r="G33" t="n">
-        <v>224.4</v>
+        <v>230.2</v>
       </c>
       <c r="H33" t="n">
-        <v>65</v>
+        <v>72.5</v>
       </c>
       <c r="I33" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="J33" t="n">
-        <v>-97.98</v>
+        <v>129.72</v>
       </c>
       <c r="K33" t="n">
-        <v>1.37</v>
+        <v>46.02</v>
       </c>
       <c r="L33" t="n">
-        <v>97.98999999999999</v>
+        <v>137.64</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07:03:05</t>
+          <t>07:03:19</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>4.32</v>
+        <v>4.84</v>
       </c>
       <c r="F34" t="n">
         <v>12.3</v>
       </c>
       <c r="G34" t="n">
-        <v>223.2</v>
+        <v>222.3</v>
       </c>
       <c r="H34" t="n">
-        <v>40.2</v>
+        <v>100</v>
       </c>
       <c r="I34" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J34" t="n">
-        <v>-91.78</v>
+        <v>-110.42</v>
       </c>
       <c r="K34" t="n">
-        <v>22.57</v>
+        <v>-61.23</v>
       </c>
       <c r="L34" t="n">
-        <v>94.51000000000001</v>
+        <v>126.26</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07:07:26</t>
+          <t>07:08:22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>3.49</v>
+        <v>4.17</v>
       </c>
       <c r="F35" t="n">
-        <v>6.88</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="G35" t="n">
-        <v>219.7</v>
+        <v>240.1</v>
       </c>
       <c r="H35" t="n">
-        <v>88.5</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J35" t="n">
-        <v>82.65000000000001</v>
+        <v>164.21</v>
       </c>
       <c r="K35" t="n">
-        <v>-66.08</v>
+        <v>23.44</v>
       </c>
       <c r="L35" t="n">
-        <v>105.82</v>
+        <v>165.87</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07:09:39</t>
+          <t>07:09:17</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>4.48</v>
+        <v>3.75</v>
       </c>
       <c r="F36" t="n">
-        <v>12.3</v>
+        <v>9.52</v>
       </c>
       <c r="G36" t="n">
-        <v>225.3</v>
+        <v>212.8</v>
       </c>
       <c r="H36" t="n">
-        <v>43.8</v>
+        <v>52.9</v>
       </c>
       <c r="I36" t="n">
         <v>31</v>
       </c>
       <c r="J36" t="n">
-        <v>-44.79</v>
+        <v>85.73999999999999</v>
       </c>
       <c r="K36" t="n">
-        <v>-93.41</v>
+        <v>-68.41</v>
       </c>
       <c r="L36" t="n">
-        <v>103.59</v>
+        <v>109.69</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07:10:44</t>
+          <t>07:11:50</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>3.75</v>
+        <v>4.27</v>
       </c>
       <c r="F37" t="n">
-        <v>8.51</v>
+        <v>10.43</v>
       </c>
       <c r="G37" t="n">
-        <v>227.7</v>
+        <v>219</v>
       </c>
       <c r="H37" t="n">
-        <v>98.2</v>
+        <v>58.9</v>
       </c>
       <c r="I37" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J37" t="n">
-        <v>-112.54</v>
+        <v>117.55</v>
       </c>
       <c r="K37" t="n">
-        <v>-29.37</v>
+        <v>-55.81</v>
       </c>
       <c r="L37" t="n">
-        <v>116.31</v>
+        <v>130.12</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07:16:36</t>
+          <t>07:16:24</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>4.63</v>
+        <v>3.48</v>
       </c>
       <c r="F38" t="n">
-        <v>12.3</v>
+        <v>7.45</v>
       </c>
       <c r="G38" t="n">
-        <v>221.7</v>
+        <v>224.7</v>
       </c>
       <c r="H38" t="n">
-        <v>66.8</v>
+        <v>93</v>
       </c>
       <c r="I38" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J38" t="n">
-        <v>-240.16</v>
+        <v>-39.15</v>
       </c>
       <c r="K38" t="n">
-        <v>123.18</v>
+        <v>-156.53</v>
       </c>
       <c r="L38" t="n">
-        <v>269.91</v>
+        <v>161.35</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07:18:56</t>
+          <t>07:17:49</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1678,31 +1678,31 @@
         <v>3.76</v>
       </c>
       <c r="F39" t="n">
-        <v>10.31</v>
+        <v>8.81</v>
       </c>
       <c r="G39" t="n">
-        <v>224</v>
+        <v>222.2</v>
       </c>
       <c r="H39" t="n">
-        <v>47.2</v>
+        <v>53.2</v>
       </c>
       <c r="I39" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J39" t="n">
-        <v>8.16</v>
+        <v>-73.31</v>
       </c>
       <c r="K39" t="n">
-        <v>-173.93</v>
+        <v>-164.56</v>
       </c>
       <c r="L39" t="n">
-        <v>174.12</v>
+        <v>180.15</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07:20:39</t>
+          <t>07:19:14</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>4.2</v>
+        <v>4.91</v>
       </c>
       <c r="F40" t="n">
-        <v>10.56</v>
+        <v>12.3</v>
       </c>
       <c r="G40" t="n">
-        <v>226.5</v>
+        <v>225.8</v>
       </c>
       <c r="H40" t="n">
-        <v>61.5</v>
+        <v>70.2</v>
       </c>
       <c r="I40" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J40" t="n">
-        <v>180.26</v>
+        <v>252.47</v>
       </c>
       <c r="K40" t="n">
-        <v>-180.32</v>
+        <v>34.37</v>
       </c>
       <c r="L40" t="n">
-        <v>254.97</v>
+        <v>254.8</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07:24:43</t>
+          <t>07:23:41</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>3.67</v>
+        <v>3.34</v>
       </c>
       <c r="F41" t="n">
-        <v>6.61</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="G41" t="n">
-        <v>220.4</v>
+        <v>221.8</v>
       </c>
       <c r="H41" t="n">
-        <v>37.2</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="I41" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J41" t="n">
-        <v>-223.54</v>
+        <v>216.58</v>
       </c>
       <c r="K41" t="n">
-        <v>53.62</v>
+        <v>130.97</v>
       </c>
       <c r="L41" t="n">
-        <v>229.88</v>
+        <v>253.1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07:25:40</t>
+          <t>07:24:32</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>3.85</v>
+        <v>3.73</v>
       </c>
       <c r="F42" t="n">
-        <v>6.21</v>
+        <v>10.97</v>
       </c>
       <c r="G42" t="n">
-        <v>229.3</v>
+        <v>229.5</v>
       </c>
       <c r="H42" t="n">
-        <v>96.3</v>
+        <v>22.2</v>
       </c>
       <c r="I42" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="J42" t="n">
-        <v>64.34999999999999</v>
+        <v>272.99</v>
       </c>
       <c r="K42" t="n">
-        <v>-274.48</v>
+        <v>33.24</v>
       </c>
       <c r="L42" t="n">
-        <v>281.92</v>
+        <v>275.01</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07:27:43</t>
+          <t>07:26:05</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>4.11</v>
+        <v>3.3</v>
       </c>
       <c r="F43" t="n">
-        <v>9.35</v>
+        <v>9.27</v>
       </c>
       <c r="G43" t="n">
-        <v>212.4</v>
+        <v>223.8</v>
       </c>
       <c r="H43" t="n">
-        <v>25.3</v>
+        <v>76.5</v>
       </c>
       <c r="I43" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>62.82</v>
+        <v>-106.82</v>
       </c>
       <c r="K43" t="n">
-        <v>-211.37</v>
+        <v>-145.72</v>
       </c>
       <c r="L43" t="n">
-        <v>220.51</v>
+        <v>180.67</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07:38:46</t>
+          <t>07:35:34</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>3.94</v>
+        <v>4.38</v>
       </c>
       <c r="F44" t="n">
-        <v>9.140000000000001</v>
+        <v>8.92</v>
       </c>
       <c r="G44" t="n">
-        <v>230.1</v>
+        <v>212.6</v>
       </c>
       <c r="H44" t="n">
-        <v>83.3</v>
+        <v>52.4</v>
       </c>
       <c r="I44" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J44" t="n">
-        <v>-52.56</v>
+        <v>38.82</v>
       </c>
       <c r="K44" t="n">
-        <v>26.56</v>
+        <v>-81.48</v>
       </c>
       <c r="L44" t="n">
-        <v>58.89</v>
+        <v>90.26000000000001</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07:39:52</t>
+          <t>07:37:06</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>4.14</v>
+        <v>4.63</v>
       </c>
       <c r="F45" t="n">
-        <v>10.45</v>
+        <v>11.46</v>
       </c>
       <c r="G45" t="n">
-        <v>216.4</v>
+        <v>219</v>
       </c>
       <c r="H45" t="n">
-        <v>64.5</v>
+        <v>46.5</v>
       </c>
       <c r="I45" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J45" t="n">
-        <v>-50.52</v>
+        <v>83.36</v>
       </c>
       <c r="K45" t="n">
-        <v>-60.37</v>
+        <v>-79.98</v>
       </c>
       <c r="L45" t="n">
-        <v>78.72</v>
+        <v>115.52</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07:40:40</t>
+          <t>07:38:36</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>3.75</v>
+        <v>4.45</v>
       </c>
       <c r="F46" t="n">
-        <v>6.16</v>
+        <v>8.9</v>
       </c>
       <c r="G46" t="n">
-        <v>233.6</v>
+        <v>217.4</v>
       </c>
       <c r="H46" t="n">
-        <v>26.3</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="I46" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J46" t="n">
-        <v>-39.73</v>
+        <v>-1.45</v>
       </c>
       <c r="K46" t="n">
-        <v>-55.54</v>
+        <v>-89.13</v>
       </c>
       <c r="L46" t="n">
-        <v>68.29000000000001</v>
+        <v>89.14</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07:46:02</t>
+          <t>07:44:44</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>3.73</v>
+        <v>3.77</v>
       </c>
       <c r="F47" t="n">
-        <v>10.39</v>
+        <v>7.79</v>
       </c>
       <c r="G47" t="n">
-        <v>235.1</v>
+        <v>225.6</v>
       </c>
       <c r="H47" t="n">
-        <v>48.5</v>
+        <v>45.9</v>
       </c>
       <c r="I47" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J47" t="n">
-        <v>-75.36</v>
+        <v>32.6</v>
       </c>
       <c r="K47" t="n">
-        <v>-16.32</v>
+        <v>-116.96</v>
       </c>
       <c r="L47" t="n">
-        <v>77.09999999999999</v>
+        <v>121.42</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07:46:56</t>
+          <t>07:46:49</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>3.78</v>
+        <v>3.95</v>
       </c>
       <c r="F48" t="n">
-        <v>10.26</v>
+        <v>11.53</v>
       </c>
       <c r="G48" t="n">
-        <v>223.6</v>
+        <v>228.3</v>
       </c>
       <c r="H48" t="n">
-        <v>93.09999999999999</v>
+        <v>49.6</v>
       </c>
       <c r="I48" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J48" t="n">
-        <v>-73.44</v>
+        <v>87.91</v>
       </c>
       <c r="K48" t="n">
-        <v>4.21</v>
+        <v>-56.49</v>
       </c>
       <c r="L48" t="n">
-        <v>73.56</v>
+        <v>104.5</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07:48:55</t>
+          <t>07:48:58</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>3.78</v>
+        <v>4.26</v>
       </c>
       <c r="F49" t="n">
-        <v>9.83</v>
+        <v>11.8</v>
       </c>
       <c r="G49" t="n">
-        <v>215.7</v>
+        <v>230.6</v>
       </c>
       <c r="H49" t="n">
-        <v>29.1</v>
+        <v>63.8</v>
       </c>
       <c r="I49" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J49" t="n">
-        <v>87.56</v>
+        <v>-25.19</v>
       </c>
       <c r="K49" t="n">
-        <v>36.03</v>
+        <v>-108</v>
       </c>
       <c r="L49" t="n">
-        <v>94.68000000000001</v>
+        <v>110.9</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07:52:47</t>
+          <t>07:54:19</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="F50" t="n">
-        <v>9.17</v>
+        <v>10.47</v>
       </c>
       <c r="G50" t="n">
-        <v>229.4</v>
+        <v>239</v>
       </c>
       <c r="H50" t="n">
-        <v>60</v>
+        <v>29.8</v>
       </c>
       <c r="I50" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J50" t="n">
-        <v>-158.63</v>
+        <v>135.75</v>
       </c>
       <c r="K50" t="n">
-        <v>-13.59</v>
+        <v>-24.84</v>
       </c>
       <c r="L50" t="n">
-        <v>159.21</v>
+        <v>138.01</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07:53:48</t>
+          <t>07:55:43</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>4.22</v>
+        <v>4.01</v>
       </c>
       <c r="F51" t="n">
-        <v>12.3</v>
+        <v>10.87</v>
       </c>
       <c r="G51" t="n">
-        <v>221.5</v>
+        <v>222.2</v>
       </c>
       <c r="H51" t="n">
-        <v>54.6</v>
+        <v>52.8</v>
       </c>
       <c r="I51" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J51" t="n">
-        <v>-31.62</v>
+        <v>1.93</v>
       </c>
       <c r="K51" t="n">
-        <v>163.19</v>
+        <v>-148.5</v>
       </c>
       <c r="L51" t="n">
-        <v>166.22</v>
+        <v>148.52</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07:54:55</t>
+          <t>07:58:11</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>4.42</v>
+        <v>3.6</v>
       </c>
       <c r="F52" t="n">
-        <v>8.51</v>
+        <v>6.98</v>
       </c>
       <c r="G52" t="n">
-        <v>224.9</v>
+        <v>225.2</v>
       </c>
       <c r="H52" t="n">
-        <v>100</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="I52" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J52" t="n">
-        <v>-146.95</v>
+        <v>102.25</v>
       </c>
       <c r="K52" t="n">
-        <v>118.16</v>
+        <v>5.35</v>
       </c>
       <c r="L52" t="n">
-        <v>188.56</v>
+        <v>102.39</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07:59:52</t>
+          <t>08:01:35</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>3.61</v>
+        <v>4.12</v>
       </c>
       <c r="F53" t="n">
-        <v>7.81</v>
+        <v>11.74</v>
       </c>
       <c r="G53" t="n">
-        <v>227.2</v>
+        <v>232.7</v>
       </c>
       <c r="H53" t="n">
-        <v>66.5</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="I53" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J53" t="n">
-        <v>-112.53</v>
+        <v>93.03</v>
       </c>
       <c r="K53" t="n">
-        <v>-80.94</v>
+        <v>-267.7</v>
       </c>
       <c r="L53" t="n">
-        <v>138.62</v>
+        <v>283.4</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08:02:02</t>
+          <t>08:03:04</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>4.19</v>
+        <v>3.98</v>
       </c>
       <c r="F54" t="n">
         <v>12.3</v>
       </c>
       <c r="G54" t="n">
-        <v>224</v>
+        <v>216.7</v>
       </c>
       <c r="H54" t="n">
-        <v>70.90000000000001</v>
+        <v>55.5</v>
       </c>
       <c r="I54" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J54" t="n">
-        <v>-19.25</v>
+        <v>169.23</v>
       </c>
       <c r="K54" t="n">
-        <v>-188.49</v>
+        <v>-153.5</v>
       </c>
       <c r="L54" t="n">
-        <v>189.47</v>
+        <v>228.48</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08:03:21</t>
+          <t>08:04:50</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>4.57</v>
+        <v>3.93</v>
       </c>
       <c r="F55" t="n">
-        <v>10.63</v>
+        <v>7.35</v>
       </c>
       <c r="G55" t="n">
-        <v>218.2</v>
+        <v>226.2</v>
       </c>
       <c r="H55" t="n">
-        <v>39.7</v>
+        <v>45.7</v>
       </c>
       <c r="I55" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>-189.36</v>
+        <v>-20.14</v>
       </c>
       <c r="K55" t="n">
-        <v>-90.76000000000001</v>
+        <v>231.51</v>
       </c>
       <c r="L55" t="n">
-        <v>209.99</v>
+        <v>232.39</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08:08:43</t>
+          <t>08:08:39</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>4.03</v>
+        <v>4.07</v>
       </c>
       <c r="F56" t="n">
-        <v>8.98</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="G56" t="n">
-        <v>219.7</v>
+        <v>237.4</v>
       </c>
       <c r="H56" t="n">
-        <v>56.2</v>
+        <v>47.7</v>
       </c>
       <c r="I56" t="n">
         <v>32</v>
       </c>
       <c r="J56" t="n">
-        <v>-90.36</v>
+        <v>-176.98</v>
       </c>
       <c r="K56" t="n">
-        <v>203.66</v>
+        <v>217.15</v>
       </c>
       <c r="L56" t="n">
-        <v>222.81</v>
+        <v>280.14</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08:09:53</t>
+          <t>08:09:40</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>3.77</v>
+        <v>4.47</v>
       </c>
       <c r="F57" t="n">
-        <v>9.880000000000001</v>
+        <v>12.15</v>
       </c>
       <c r="G57" t="n">
-        <v>226.9</v>
+        <v>224.2</v>
       </c>
       <c r="H57" t="n">
-        <v>61</v>
+        <v>21.4</v>
       </c>
       <c r="I57" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J57" t="n">
-        <v>104.81</v>
+        <v>-253.48</v>
       </c>
       <c r="K57" t="n">
-        <v>-263.1</v>
+        <v>-350.7</v>
       </c>
       <c r="L57" t="n">
-        <v>283.21</v>
+        <v>432.71</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08:11:20</t>
+          <t>08:11:55</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>3.72</v>
+        <v>3.75</v>
       </c>
       <c r="F58" t="n">
-        <v>12.04</v>
+        <v>9.4</v>
       </c>
       <c r="G58" t="n">
-        <v>234.1</v>
+        <v>239.1</v>
       </c>
       <c r="H58" t="n">
-        <v>61.4</v>
+        <v>23.1</v>
       </c>
       <c r="I58" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="J58" t="n">
-        <v>-109.89</v>
+        <v>-247.77</v>
       </c>
       <c r="K58" t="n">
-        <v>-229</v>
+        <v>-77.76000000000001</v>
       </c>
       <c r="L58" t="n">
-        <v>254</v>
+        <v>259.69</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08:23:50</t>
+          <t>08:21:46</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>3.73</v>
+        <v>4.02</v>
       </c>
       <c r="F59" t="n">
-        <v>10.85</v>
+        <v>10.91</v>
       </c>
       <c r="G59" t="n">
-        <v>233.5</v>
+        <v>223.4</v>
       </c>
       <c r="H59" t="n">
-        <v>99.8</v>
+        <v>44.3</v>
       </c>
       <c r="I59" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>-52.1</v>
+        <v>57.58</v>
       </c>
       <c r="K59" t="n">
-        <v>1</v>
+        <v>17.08</v>
       </c>
       <c r="L59" t="n">
-        <v>52.11</v>
+        <v>60.06</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08:25:36</t>
+          <t>08:24:00</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>4.4</v>
+        <v>4.55</v>
       </c>
       <c r="F60" t="n">
-        <v>11.3</v>
+        <v>12.3</v>
       </c>
       <c r="G60" t="n">
-        <v>224.9</v>
+        <v>222.1</v>
       </c>
       <c r="H60" t="n">
-        <v>54.3</v>
+        <v>67.5</v>
       </c>
       <c r="I60" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>-20.09</v>
+        <v>-17.73</v>
       </c>
       <c r="K60" t="n">
-        <v>-74.48999999999999</v>
+        <v>-92.20999999999999</v>
       </c>
       <c r="L60" t="n">
-        <v>77.15000000000001</v>
+        <v>93.90000000000001</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08:26:41</t>
+          <t>08:24:51</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>4.31</v>
+        <v>4.8</v>
       </c>
       <c r="F61" t="n">
-        <v>12.3</v>
+        <v>11.85</v>
       </c>
       <c r="G61" t="n">
-        <v>217.3</v>
+        <v>219.5</v>
       </c>
       <c r="H61" t="n">
-        <v>4.4</v>
+        <v>42.8</v>
       </c>
       <c r="I61" t="n">
         <v>28</v>
       </c>
       <c r="J61" t="n">
-        <v>44.8</v>
+        <v>82.16</v>
       </c>
       <c r="K61" t="n">
-        <v>81.79000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="L61" t="n">
-        <v>93.26000000000001</v>
+        <v>108.26</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08:30:46</t>
+          <t>08:28:58</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>4.3</v>
+        <v>4.53</v>
       </c>
       <c r="F62" t="n">
-        <v>11.13</v>
+        <v>12.3</v>
       </c>
       <c r="G62" t="n">
-        <v>228.2</v>
+        <v>233</v>
       </c>
       <c r="H62" t="n">
-        <v>34</v>
+        <v>50.9</v>
       </c>
       <c r="I62" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="J62" t="n">
-        <v>18.12</v>
+        <v>-124.49</v>
       </c>
       <c r="K62" t="n">
-        <v>-125.48</v>
+        <v>-4.03</v>
       </c>
       <c r="L62" t="n">
-        <v>126.78</v>
+        <v>124.55</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08:31:27</t>
+          <t>08:30:40</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>4.54</v>
+        <v>3.62</v>
       </c>
       <c r="F63" t="n">
-        <v>11.61</v>
+        <v>7.76</v>
       </c>
       <c r="G63" t="n">
-        <v>224.7</v>
+        <v>231.8</v>
       </c>
       <c r="H63" t="n">
-        <v>84.59999999999999</v>
+        <v>58.7</v>
       </c>
       <c r="I63" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J63" t="n">
-        <v>-105.43</v>
+        <v>-62.59</v>
       </c>
       <c r="K63" t="n">
-        <v>21.66</v>
+        <v>-31.65</v>
       </c>
       <c r="L63" t="n">
-        <v>107.63</v>
+        <v>70.13</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>08:32:48</t>
+          <t>08:32:06</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>3.8</v>
+        <v>3.71</v>
       </c>
       <c r="F64" t="n">
-        <v>10.67</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G64" t="n">
-        <v>223.3</v>
+        <v>241.7</v>
       </c>
       <c r="H64" t="n">
-        <v>74.90000000000001</v>
+        <v>77</v>
       </c>
       <c r="I64" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J64" t="n">
-        <v>-41.81</v>
+        <v>46.11</v>
       </c>
       <c r="K64" t="n">
-        <v>-70.41</v>
+        <v>57.51</v>
       </c>
       <c r="L64" t="n">
-        <v>81.89</v>
+        <v>73.72</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>08:37:42</t>
+          <t>08:37:31</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>4.1</v>
+        <v>4.67</v>
       </c>
       <c r="F65" t="n">
-        <v>10.23</v>
+        <v>12.3</v>
       </c>
       <c r="G65" t="n">
-        <v>214.2</v>
+        <v>224</v>
       </c>
       <c r="H65" t="n">
-        <v>64.59999999999999</v>
+        <v>64</v>
       </c>
       <c r="I65" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J65" t="n">
-        <v>20.09</v>
+        <v>112.43</v>
       </c>
       <c r="K65" t="n">
-        <v>-165.74</v>
+        <v>94.16</v>
       </c>
       <c r="L65" t="n">
-        <v>166.95</v>
+        <v>146.65</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>08:39:49</t>
+          <t>08:38:34</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>4.2</v>
+        <v>4.52</v>
       </c>
       <c r="F66" t="n">
-        <v>11.26</v>
+        <v>12.3</v>
       </c>
       <c r="G66" t="n">
-        <v>217.3</v>
+        <v>229.5</v>
       </c>
       <c r="H66" t="n">
-        <v>59.7</v>
+        <v>63.7</v>
       </c>
       <c r="I66" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J66" t="n">
-        <v>-125.25</v>
+        <v>-138.32</v>
       </c>
       <c r="K66" t="n">
-        <v>7.07</v>
+        <v>72.95999999999999</v>
       </c>
       <c r="L66" t="n">
-        <v>125.45</v>
+        <v>156.38</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>08:42:07</t>
+          <t>08:39:38</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>4.59</v>
+        <v>4.54</v>
       </c>
       <c r="F67" t="n">
-        <v>11.76</v>
+        <v>11.07</v>
       </c>
       <c r="G67" t="n">
-        <v>224.3</v>
+        <v>224.1</v>
       </c>
       <c r="H67" t="n">
-        <v>78.8</v>
+        <v>61.6</v>
       </c>
       <c r="I67" t="n">
         <v>24</v>
       </c>
       <c r="J67" t="n">
-        <v>83.97</v>
+        <v>126.31</v>
       </c>
       <c r="K67" t="n">
-        <v>-104.58</v>
+        <v>31.89</v>
       </c>
       <c r="L67" t="n">
-        <v>134.12</v>
+        <v>130.27</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>08:46:08</t>
+          <t>08:43:54</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>4.54</v>
+        <v>3.84</v>
       </c>
       <c r="F68" t="n">
-        <v>11.14</v>
+        <v>9.57</v>
       </c>
       <c r="G68" t="n">
-        <v>207.8</v>
+        <v>225.5</v>
       </c>
       <c r="H68" t="n">
-        <v>63.7</v>
+        <v>57.4</v>
       </c>
       <c r="I68" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J68" t="n">
-        <v>100.89</v>
+        <v>169.56</v>
       </c>
       <c r="K68" t="n">
-        <v>-219.58</v>
+        <v>99.23</v>
       </c>
       <c r="L68" t="n">
-        <v>241.65</v>
+        <v>196.46</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>08:48:11</t>
+          <t>08:44:49</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>4.71</v>
+        <v>5.03</v>
       </c>
       <c r="F69" t="n">
         <v>12.3</v>
       </c>
       <c r="G69" t="n">
-        <v>236</v>
+        <v>227.5</v>
       </c>
       <c r="H69" t="n">
-        <v>67.8</v>
+        <v>48</v>
       </c>
       <c r="I69" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J69" t="n">
-        <v>-68.28</v>
+        <v>-179.12</v>
       </c>
       <c r="K69" t="n">
-        <v>-224.94</v>
+        <v>-248.01</v>
       </c>
       <c r="L69" t="n">
-        <v>235.07</v>
+        <v>305.93</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>08:49:45</t>
+          <t>08:45:21</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>4.47</v>
+        <v>4.28</v>
       </c>
       <c r="F70" t="n">
         <v>12.3</v>
       </c>
       <c r="G70" t="n">
-        <v>221.9</v>
+        <v>233.6</v>
       </c>
       <c r="H70" t="n">
-        <v>49.3</v>
+        <v>41.9</v>
       </c>
       <c r="I70" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J70" t="n">
-        <v>-259.2</v>
+        <v>72.19</v>
       </c>
       <c r="K70" t="n">
-        <v>-194.63</v>
+        <v>191.81</v>
       </c>
       <c r="L70" t="n">
-        <v>324.14</v>
+        <v>204.94</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>08:53:58</t>
+          <t>08:51:04</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>4.44</v>
+        <v>3.36</v>
       </c>
       <c r="F71" t="n">
-        <v>10.08</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="G71" t="n">
-        <v>213.7</v>
+        <v>240.2</v>
       </c>
       <c r="H71" t="n">
-        <v>60.5</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="I71" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J71" t="n">
-        <v>-312.02</v>
+        <v>39.21</v>
       </c>
       <c r="K71" t="n">
-        <v>-248.8</v>
+        <v>163.92</v>
       </c>
       <c r="L71" t="n">
-        <v>399.07</v>
+        <v>168.55</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>08:55:02</t>
+          <t>08:53:34</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>4.49</v>
+        <v>4.43</v>
       </c>
       <c r="F72" t="n">
-        <v>12.3</v>
+        <v>11.61</v>
       </c>
       <c r="G72" t="n">
-        <v>233.7</v>
+        <v>230.3</v>
       </c>
       <c r="H72" t="n">
-        <v>99.7</v>
+        <v>68.8</v>
       </c>
       <c r="I72" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J72" t="n">
-        <v>137.78</v>
+        <v>52.03</v>
       </c>
       <c r="K72" t="n">
-        <v>-282.44</v>
+        <v>-304.78</v>
       </c>
       <c r="L72" t="n">
-        <v>314.26</v>
+        <v>309.19</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>08:57:36</t>
+          <t>08:55:07</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>4.57</v>
+        <v>4.64</v>
       </c>
       <c r="F73" t="n">
-        <v>11.68</v>
+        <v>11.84</v>
       </c>
       <c r="G73" t="n">
-        <v>212.5</v>
+        <v>221.7</v>
       </c>
       <c r="H73" t="n">
-        <v>55.8</v>
+        <v>43.7</v>
       </c>
       <c r="I73" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J73" t="n">
-        <v>-129.24</v>
+        <v>-237.34</v>
       </c>
       <c r="K73" t="n">
-        <v>-244.77</v>
+        <v>116.57</v>
       </c>
       <c r="L73" t="n">
-        <v>276.79</v>
+        <v>264.42</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>09:05:20</t>
+          <t>09:02:21</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>4.8</v>
+        <v>4.39</v>
       </c>
       <c r="F74" t="n">
-        <v>12.3</v>
+        <v>11.58</v>
       </c>
       <c r="G74" t="n">
-        <v>212.1</v>
+        <v>221.8</v>
       </c>
       <c r="H74" t="n">
-        <v>66.8</v>
+        <v>33.3</v>
       </c>
       <c r="I74" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J74" t="n">
-        <v>91.51000000000001</v>
+        <v>-85.23999999999999</v>
       </c>
       <c r="K74" t="n">
-        <v>13.2</v>
+        <v>-54.2</v>
       </c>
       <c r="L74" t="n">
-        <v>92.45999999999999</v>
+        <v>101.01</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09:06:31</t>
+          <t>09:04:04</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>4.56</v>
+        <v>4.58</v>
       </c>
       <c r="F75" t="n">
-        <v>12.3</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="G75" t="n">
-        <v>229</v>
+        <v>223.5</v>
       </c>
       <c r="H75" t="n">
-        <v>42.5</v>
+        <v>68.8</v>
       </c>
       <c r="I75" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J75" t="n">
-        <v>56.93</v>
+        <v>-62.03</v>
       </c>
       <c r="K75" t="n">
-        <v>74.81</v>
+        <v>-14.19</v>
       </c>
       <c r="L75" t="n">
-        <v>94.01000000000001</v>
+        <v>63.63</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09:07:17</t>
+          <t>09:05:09</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>4.86</v>
+        <v>3.88</v>
       </c>
       <c r="F76" t="n">
-        <v>12.3</v>
+        <v>10.08</v>
       </c>
       <c r="G76" t="n">
-        <v>222.2</v>
+        <v>222.6</v>
       </c>
       <c r="H76" t="n">
-        <v>34.9</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="I76" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>71.75</v>
+        <v>67.33</v>
       </c>
       <c r="K76" t="n">
-        <v>-64.19</v>
+        <v>-32.23</v>
       </c>
       <c r="L76" t="n">
-        <v>96.27</v>
+        <v>74.65000000000001</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09:11:48</t>
+          <t>09:10:42</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>5.18</v>
+        <v>4.18</v>
       </c>
       <c r="F77" t="n">
-        <v>12.3</v>
+        <v>10.54</v>
       </c>
       <c r="G77" t="n">
-        <v>235.6</v>
+        <v>214.3</v>
       </c>
       <c r="H77" t="n">
-        <v>88.8</v>
+        <v>67.3</v>
       </c>
       <c r="I77" t="n">
         <v>32</v>
       </c>
       <c r="J77" t="n">
-        <v>-79.36</v>
+        <v>-95.41</v>
       </c>
       <c r="K77" t="n">
-        <v>135.14</v>
+        <v>32.67</v>
       </c>
       <c r="L77" t="n">
-        <v>156.72</v>
+        <v>100.85</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09:13:01</t>
+          <t>09:13:16</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>4.61</v>
+        <v>5.09</v>
       </c>
       <c r="F78" t="n">
         <v>12.3</v>
       </c>
       <c r="G78" t="n">
-        <v>232.3</v>
+        <v>245.5</v>
       </c>
       <c r="H78" t="n">
-        <v>51.4</v>
+        <v>44.6</v>
       </c>
       <c r="I78" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J78" t="n">
-        <v>70.56999999999999</v>
+        <v>131.88</v>
       </c>
       <c r="K78" t="n">
-        <v>85.33</v>
+        <v>98.8</v>
       </c>
       <c r="L78" t="n">
-        <v>110.73</v>
+        <v>164.78</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09:14:26</t>
+          <t>09:14:08</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>4.31</v>
+        <v>4.49</v>
       </c>
       <c r="F79" t="n">
         <v>12.3</v>
       </c>
       <c r="G79" t="n">
-        <v>227.2</v>
+        <v>228.1</v>
       </c>
       <c r="H79" t="n">
-        <v>24.1</v>
+        <v>59.6</v>
       </c>
       <c r="I79" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J79" t="n">
-        <v>-109.21</v>
+        <v>-71.81999999999999</v>
       </c>
       <c r="K79" t="n">
-        <v>-60.07</v>
+        <v>-114.44</v>
       </c>
       <c r="L79" t="n">
-        <v>124.64</v>
+        <v>135.11</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>09:18:19</t>
+          <t>09:17:55</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>4.42</v>
+        <v>4.12</v>
       </c>
       <c r="F80" t="n">
-        <v>10.07</v>
+        <v>12.3</v>
       </c>
       <c r="G80" t="n">
-        <v>216.8</v>
+        <v>208.9</v>
       </c>
       <c r="H80" t="n">
-        <v>54.4</v>
+        <v>24.5</v>
       </c>
       <c r="I80" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J80" t="n">
-        <v>-108.35</v>
+        <v>101.59</v>
       </c>
       <c r="K80" t="n">
-        <v>34.13</v>
+        <v>-100.44</v>
       </c>
       <c r="L80" t="n">
-        <v>113.6</v>
+        <v>142.86</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>09:20:07</t>
+          <t>09:20:17</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>4.66</v>
+        <v>3.81</v>
       </c>
       <c r="F81" t="n">
-        <v>12.3</v>
+        <v>9.52</v>
       </c>
       <c r="G81" t="n">
-        <v>220.7</v>
+        <v>218</v>
       </c>
       <c r="H81" t="n">
-        <v>87.7</v>
+        <v>44.7</v>
       </c>
       <c r="I81" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J81" t="n">
-        <v>170.15</v>
+        <v>-130.92</v>
       </c>
       <c r="K81" t="n">
-        <v>148.63</v>
+        <v>9.1</v>
       </c>
       <c r="L81" t="n">
-        <v>225.93</v>
+        <v>131.24</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>09:22:08</t>
+          <t>09:22:05</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>4.43</v>
+        <v>4.31</v>
       </c>
       <c r="F82" t="n">
-        <v>10.61</v>
+        <v>11.66</v>
       </c>
       <c r="G82" t="n">
-        <v>228.8</v>
+        <v>229</v>
       </c>
       <c r="H82" t="n">
-        <v>48.3</v>
+        <v>65.3</v>
       </c>
       <c r="I82" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>-178.07</v>
+        <v>-108.2</v>
       </c>
       <c r="K82" t="n">
-        <v>-43.16</v>
+        <v>77.53</v>
       </c>
       <c r="L82" t="n">
-        <v>183.23</v>
+        <v>133.11</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>09:26:43</t>
+          <t>09:28:05</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>4.94</v>
+        <v>4.81</v>
       </c>
       <c r="F83" t="n">
         <v>12.3</v>
       </c>
       <c r="G83" t="n">
-        <v>226</v>
+        <v>224.7</v>
       </c>
       <c r="H83" t="n">
-        <v>100</v>
+        <v>85.3</v>
       </c>
       <c r="I83" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="J83" t="n">
-        <v>-235.98</v>
+        <v>-315.61</v>
       </c>
       <c r="K83" t="n">
-        <v>113.07</v>
+        <v>-38.05</v>
       </c>
       <c r="L83" t="n">
-        <v>261.67</v>
+        <v>317.89</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>09:29:16</t>
+          <t>09:29:17</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>4.13</v>
+        <v>4</v>
       </c>
       <c r="F84" t="n">
-        <v>12.23</v>
+        <v>12.3</v>
       </c>
       <c r="G84" t="n">
-        <v>228.2</v>
+        <v>219.7</v>
       </c>
       <c r="H84" t="n">
-        <v>74.90000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="I84" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J84" t="n">
-        <v>24.16</v>
+        <v>-95.41</v>
       </c>
       <c r="K84" t="n">
-        <v>236.97</v>
+        <v>-223.49</v>
       </c>
       <c r="L84" t="n">
-        <v>238.19</v>
+        <v>243</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>09:31:00</t>
+          <t>09:30:27</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>4.15</v>
+        <v>5</v>
       </c>
       <c r="F85" t="n">
-        <v>11.35</v>
+        <v>12.2</v>
       </c>
       <c r="G85" t="n">
-        <v>235</v>
+        <v>223.8</v>
       </c>
       <c r="H85" t="n">
-        <v>46.3</v>
+        <v>32.2</v>
       </c>
       <c r="I85" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J85" t="n">
-        <v>-93.64</v>
+        <v>-211.57</v>
       </c>
       <c r="K85" t="n">
-        <v>209.73</v>
+        <v>-192.89</v>
       </c>
       <c r="L85" t="n">
-        <v>229.69</v>
+        <v>286.3</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>09:35:44</t>
+          <t>09:34:30</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>4.22</v>
+        <v>3.93</v>
       </c>
       <c r="F86" t="n">
-        <v>12.3</v>
+        <v>7.79</v>
       </c>
       <c r="G86" t="n">
-        <v>231.1</v>
+        <v>226.4</v>
       </c>
       <c r="H86" t="n">
-        <v>49.5</v>
+        <v>74</v>
       </c>
       <c r="I86" t="n">
         <v>32</v>
       </c>
       <c r="J86" t="n">
-        <v>179.08</v>
+        <v>275.7</v>
       </c>
       <c r="K86" t="n">
-        <v>-233.82</v>
+        <v>83.72</v>
       </c>
       <c r="L86" t="n">
-        <v>294.51</v>
+        <v>288.13</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>09:37:05</t>
+          <t>09:36:04</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>5.04</v>
+        <v>4.16</v>
       </c>
       <c r="F87" t="n">
-        <v>12.3</v>
+        <v>11.97</v>
       </c>
       <c r="G87" t="n">
-        <v>216.3</v>
+        <v>224.1</v>
       </c>
       <c r="H87" t="n">
-        <v>91.7</v>
+        <v>87.5</v>
       </c>
       <c r="I87" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J87" t="n">
-        <v>-228.12</v>
+        <v>34.48</v>
       </c>
       <c r="K87" t="n">
-        <v>-335.88</v>
+        <v>-237.92</v>
       </c>
       <c r="L87" t="n">
-        <v>406.03</v>
+        <v>240.4</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>09:38:09</t>
+          <t>09:37:08</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>4.42</v>
+        <v>4.18</v>
       </c>
       <c r="F88" t="n">
-        <v>9.93</v>
+        <v>11.65</v>
       </c>
       <c r="G88" t="n">
-        <v>231.2</v>
+        <v>221.9</v>
       </c>
       <c r="H88" t="n">
-        <v>45.9</v>
+        <v>40.6</v>
       </c>
       <c r="I88" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J88" t="n">
-        <v>-231.91</v>
+        <v>243.75</v>
       </c>
       <c r="K88" t="n">
-        <v>-211.93</v>
+        <v>128.64</v>
       </c>
       <c r="L88" t="n">
-        <v>314.16</v>
+        <v>275.61</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-08-26.xlsx
+++ b/output/2025-08-26.xlsx
@@ -640,13 +640,13 @@
         <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>63.6</v>
+        <v>71.92</v>
       </c>
       <c r="K14" t="n">
-        <v>-46.28</v>
+        <v>-52.33</v>
       </c>
       <c r="L14" t="n">
-        <v>78.66</v>
+        <v>88.94</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>-104.64</v>
+        <v>-115.35</v>
       </c>
       <c r="K15" t="n">
-        <v>-7.97</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>104.94</v>
+        <v>115.69</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>16</v>
       </c>
       <c r="J16" t="n">
-        <v>-86.64</v>
+        <v>-97.08</v>
       </c>
       <c r="K16" t="n">
-        <v>-20</v>
+        <v>-22.41</v>
       </c>
       <c r="L16" t="n">
-        <v>88.92</v>
+        <v>99.63</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>97.5</v>
+        <v>104.71</v>
       </c>
       <c r="K17" t="n">
-        <v>109.44</v>
+        <v>117.53</v>
       </c>
       <c r="L17" t="n">
-        <v>146.57</v>
+        <v>157.4</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>20</v>
       </c>
       <c r="J18" t="n">
-        <v>-98.34</v>
+        <v>-112.15</v>
       </c>
       <c r="K18" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="L18" t="n">
-        <v>98.34</v>
+        <v>112.15</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>58.86</v>
+        <v>70.42</v>
       </c>
       <c r="K19" t="n">
-        <v>-72.72</v>
+        <v>-87</v>
       </c>
       <c r="L19" t="n">
-        <v>93.56</v>
+        <v>111.93</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>19</v>
       </c>
       <c r="J20" t="n">
-        <v>-51.24</v>
+        <v>-66.45</v>
       </c>
       <c r="K20" t="n">
-        <v>-82.52</v>
+        <v>-107.03</v>
       </c>
       <c r="L20" t="n">
-        <v>97.14</v>
+        <v>125.98</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>16</v>
       </c>
       <c r="J21" t="n">
-        <v>-108.71</v>
+        <v>-130.04</v>
       </c>
       <c r="K21" t="n">
-        <v>-122.41</v>
+        <v>-146.44</v>
       </c>
       <c r="L21" t="n">
-        <v>163.71</v>
+        <v>195.85</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>18</v>
       </c>
       <c r="J22" t="n">
-        <v>160.39</v>
+        <v>186.12</v>
       </c>
       <c r="K22" t="n">
-        <v>-30.05</v>
+        <v>-34.87</v>
       </c>
       <c r="L22" t="n">
-        <v>163.18</v>
+        <v>189.36</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>20</v>
       </c>
       <c r="J23" t="n">
-        <v>-289.9</v>
+        <v>-343.91</v>
       </c>
       <c r="K23" t="n">
-        <v>4.29</v>
+        <v>5.09</v>
       </c>
       <c r="L23" t="n">
-        <v>289.93</v>
+        <v>343.95</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>266.46</v>
+        <v>304.36</v>
       </c>
       <c r="K24" t="n">
-        <v>-174.72</v>
+        <v>-199.57</v>
       </c>
       <c r="L24" t="n">
-        <v>318.63</v>
+        <v>363.95</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>16</v>
       </c>
       <c r="J25" t="n">
-        <v>-141.38</v>
+        <v>-189.55</v>
       </c>
       <c r="K25" t="n">
-        <v>-48.9</v>
+        <v>-65.56</v>
       </c>
       <c r="L25" t="n">
-        <v>149.6</v>
+        <v>200.57</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>19</v>
       </c>
       <c r="J26" t="n">
-        <v>34.78</v>
+        <v>49.28</v>
       </c>
       <c r="K26" t="n">
-        <v>-15.76</v>
+        <v>-22.32</v>
       </c>
       <c r="L26" t="n">
-        <v>38.18</v>
+        <v>54.1</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>20</v>
       </c>
       <c r="J27" t="n">
-        <v>283.78</v>
+        <v>367.27</v>
       </c>
       <c r="K27" t="n">
-        <v>-155.79</v>
+        <v>-201.63</v>
       </c>
       <c r="L27" t="n">
-        <v>323.73</v>
+        <v>418.98</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>19</v>
       </c>
       <c r="J28" t="n">
-        <v>185.15</v>
+        <v>261.81</v>
       </c>
       <c r="K28" t="n">
-        <v>37.63</v>
+        <v>53.21</v>
       </c>
       <c r="L28" t="n">
-        <v>188.94</v>
+        <v>267.17</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>-28.34</v>
+        <v>-32.82</v>
       </c>
       <c r="K29" t="n">
-        <v>80.02</v>
+        <v>92.67</v>
       </c>
       <c r="L29" t="n">
-        <v>84.89</v>
+        <v>98.31</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>17</v>
       </c>
       <c r="J30" t="n">
-        <v>-10.12</v>
+        <v>-12.6</v>
       </c>
       <c r="K30" t="n">
-        <v>14.2</v>
+        <v>17.69</v>
       </c>
       <c r="L30" t="n">
-        <v>17.44</v>
+        <v>21.72</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>-72.56</v>
+        <v>-83.56999999999999</v>
       </c>
       <c r="K31" t="n">
-        <v>36.56</v>
+        <v>42.1</v>
       </c>
       <c r="L31" t="n">
-        <v>81.25</v>
+        <v>93.58</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>16</v>
       </c>
       <c r="J32" t="n">
-        <v>85.04000000000001</v>
+        <v>93.16</v>
       </c>
       <c r="K32" t="n">
-        <v>-94.70999999999999</v>
+        <v>-103.75</v>
       </c>
       <c r="L32" t="n">
-        <v>127.28</v>
+        <v>139.44</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>18</v>
       </c>
       <c r="J33" t="n">
-        <v>45.78</v>
+        <v>54.23</v>
       </c>
       <c r="K33" t="n">
-        <v>79.55</v>
+        <v>94.23999999999999</v>
       </c>
       <c r="L33" t="n">
-        <v>91.78</v>
+        <v>108.73</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>17</v>
       </c>
       <c r="J34" t="n">
-        <v>78.44</v>
+        <v>93.69</v>
       </c>
       <c r="K34" t="n">
-        <v>-49.35</v>
+        <v>-58.94</v>
       </c>
       <c r="L34" t="n">
-        <v>92.67</v>
+        <v>110.69</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>20</v>
       </c>
       <c r="J35" t="n">
-        <v>-56.42</v>
+        <v>-73.66</v>
       </c>
       <c r="K35" t="n">
-        <v>80.5</v>
+        <v>105.1</v>
       </c>
       <c r="L35" t="n">
-        <v>98.3</v>
+        <v>128.35</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>16</v>
       </c>
       <c r="J36" t="n">
-        <v>-148.79</v>
+        <v>-185.08</v>
       </c>
       <c r="K36" t="n">
-        <v>1.89</v>
+        <v>2.35</v>
       </c>
       <c r="L36" t="n">
-        <v>148.8</v>
+        <v>185.09</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>-1.09</v>
+        <v>-1.29</v>
       </c>
       <c r="K37" t="n">
-        <v>203.93</v>
+        <v>241.4</v>
       </c>
       <c r="L37" t="n">
-        <v>203.93</v>
+        <v>241.4</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>19</v>
       </c>
       <c r="J38" t="n">
-        <v>-115.39</v>
+        <v>-156.96</v>
       </c>
       <c r="K38" t="n">
-        <v>-90.70999999999999</v>
+        <v>-123.38</v>
       </c>
       <c r="L38" t="n">
-        <v>146.78</v>
+        <v>199.65</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>17</v>
       </c>
       <c r="J39" t="n">
-        <v>-144.34</v>
+        <v>-181.37</v>
       </c>
       <c r="K39" t="n">
-        <v>-121.11</v>
+        <v>-152.18</v>
       </c>
       <c r="L39" t="n">
-        <v>188.42</v>
+        <v>236.76</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>-96.51000000000001</v>
+        <v>-115.29</v>
       </c>
       <c r="K40" t="n">
-        <v>-220.86</v>
+        <v>-263.82</v>
       </c>
       <c r="L40" t="n">
-        <v>241.02</v>
+        <v>287.91</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>0.77</v>
+        <v>0.96</v>
       </c>
       <c r="K41" t="n">
-        <v>309.57</v>
+        <v>389.54</v>
       </c>
       <c r="L41" t="n">
-        <v>309.57</v>
+        <v>389.54</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>16</v>
       </c>
       <c r="J42" t="n">
-        <v>-24.06</v>
+        <v>-30.51</v>
       </c>
       <c r="K42" t="n">
-        <v>-279.45</v>
+        <v>-354.44</v>
       </c>
       <c r="L42" t="n">
-        <v>280.49</v>
+        <v>355.75</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>16</v>
       </c>
       <c r="J43" t="n">
-        <v>22.83</v>
+        <v>29.81</v>
       </c>
       <c r="K43" t="n">
-        <v>-295.89</v>
+        <v>-386.24</v>
       </c>
       <c r="L43" t="n">
-        <v>296.77</v>
+        <v>387.38</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>-51.02</v>
+        <v>-56.99</v>
       </c>
       <c r="K44" t="n">
-        <v>69.79000000000001</v>
+        <v>77.95999999999999</v>
       </c>
       <c r="L44" t="n">
-        <v>86.45</v>
+        <v>96.56999999999999</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>53.99</v>
+        <v>63.56</v>
       </c>
       <c r="K45" t="n">
-        <v>46.41</v>
+        <v>54.64</v>
       </c>
       <c r="L45" t="n">
-        <v>71.2</v>
+        <v>83.81999999999999</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>16</v>
       </c>
       <c r="J46" t="n">
-        <v>-55.17</v>
+        <v>-68.11</v>
       </c>
       <c r="K46" t="n">
-        <v>34.67</v>
+        <v>42.8</v>
       </c>
       <c r="L46" t="n">
-        <v>65.16</v>
+        <v>80.45</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>16</v>
       </c>
       <c r="J47" t="n">
-        <v>93.41</v>
+        <v>114.65</v>
       </c>
       <c r="K47" t="n">
-        <v>1.91</v>
+        <v>2.34</v>
       </c>
       <c r="L47" t="n">
-        <v>93.43000000000001</v>
+        <v>114.67</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>-19.49</v>
+        <v>-22.69</v>
       </c>
       <c r="K48" t="n">
-        <v>92.8</v>
+        <v>108.04</v>
       </c>
       <c r="L48" t="n">
-        <v>94.81999999999999</v>
+        <v>110.39</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>17</v>
       </c>
       <c r="J49" t="n">
-        <v>-100.8</v>
+        <v>-112.36</v>
       </c>
       <c r="K49" t="n">
-        <v>-81.08</v>
+        <v>-90.38</v>
       </c>
       <c r="L49" t="n">
-        <v>129.36</v>
+        <v>144.2</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>-109.65</v>
+        <v>-143.73</v>
       </c>
       <c r="K50" t="n">
-        <v>-26.99</v>
+        <v>-35.38</v>
       </c>
       <c r="L50" t="n">
-        <v>112.92</v>
+        <v>148.02</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>19</v>
       </c>
       <c r="J51" t="n">
-        <v>108.28</v>
+        <v>142.45</v>
       </c>
       <c r="K51" t="n">
-        <v>10.98</v>
+        <v>14.45</v>
       </c>
       <c r="L51" t="n">
-        <v>108.84</v>
+        <v>143.19</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>111.33</v>
+        <v>148.01</v>
       </c>
       <c r="K52" t="n">
-        <v>-47.15</v>
+        <v>-62.68</v>
       </c>
       <c r="L52" t="n">
-        <v>120.9</v>
+        <v>160.73</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>19</v>
       </c>
       <c r="J53" t="n">
-        <v>157.4</v>
+        <v>229.67</v>
       </c>
       <c r="K53" t="n">
-        <v>-123.45</v>
+        <v>-180.13</v>
       </c>
       <c r="L53" t="n">
-        <v>200.03</v>
+        <v>291.88</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>45.77</v>
+        <v>60.94</v>
       </c>
       <c r="K54" t="n">
-        <v>145.38</v>
+        <v>193.56</v>
       </c>
       <c r="L54" t="n">
-        <v>152.42</v>
+        <v>202.93</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>-155.39</v>
+        <v>-189.94</v>
       </c>
       <c r="K55" t="n">
-        <v>213.05</v>
+        <v>260.42</v>
       </c>
       <c r="L55" t="n">
-        <v>263.69</v>
+        <v>322.34</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>17</v>
       </c>
       <c r="J56" t="n">
-        <v>206.2</v>
+        <v>275.08</v>
       </c>
       <c r="K56" t="n">
-        <v>112.74</v>
+        <v>150.4</v>
       </c>
       <c r="L56" t="n">
-        <v>235.01</v>
+        <v>313.51</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>-188.87</v>
+        <v>-256.94</v>
       </c>
       <c r="K57" t="n">
-        <v>198.32</v>
+        <v>269.81</v>
       </c>
       <c r="L57" t="n">
-        <v>273.87</v>
+        <v>372.58</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>17</v>
       </c>
       <c r="J58" t="n">
-        <v>-228.71</v>
+        <v>-304.47</v>
       </c>
       <c r="K58" t="n">
-        <v>-262.34</v>
+        <v>-349.25</v>
       </c>
       <c r="L58" t="n">
-        <v>348.04</v>
+        <v>463.34</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>20</v>
       </c>
       <c r="J59" t="n">
-        <v>-76.83</v>
+        <v>-86.51000000000001</v>
       </c>
       <c r="K59" t="n">
-        <v>-39.87</v>
+        <v>-44.89</v>
       </c>
       <c r="L59" t="n">
-        <v>86.56</v>
+        <v>97.45999999999999</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>17</v>
       </c>
       <c r="J60" t="n">
-        <v>73</v>
+        <v>81.95999999999999</v>
       </c>
       <c r="K60" t="n">
-        <v>53.85</v>
+        <v>60.46</v>
       </c>
       <c r="L60" t="n">
-        <v>90.70999999999999</v>
+        <v>101.85</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>28.86</v>
+        <v>34.87</v>
       </c>
       <c r="K61" t="n">
-        <v>-66.45</v>
+        <v>-80.3</v>
       </c>
       <c r="L61" t="n">
-        <v>72.44</v>
+        <v>87.54000000000001</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>16</v>
       </c>
       <c r="J62" t="n">
-        <v>-53.57</v>
+        <v>-66.62</v>
       </c>
       <c r="K62" t="n">
-        <v>50.34</v>
+        <v>62.61</v>
       </c>
       <c r="L62" t="n">
-        <v>73.51000000000001</v>
+        <v>91.42</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>-72.92</v>
+        <v>-83.12</v>
       </c>
       <c r="K63" t="n">
-        <v>-86.23999999999999</v>
+        <v>-98.31</v>
       </c>
       <c r="L63" t="n">
-        <v>112.94</v>
+        <v>128.74</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>20</v>
       </c>
       <c r="J64" t="n">
-        <v>-28.41</v>
+        <v>-33.13</v>
       </c>
       <c r="K64" t="n">
-        <v>87.95</v>
+        <v>102.56</v>
       </c>
       <c r="L64" t="n">
-        <v>92.43000000000001</v>
+        <v>107.78</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>16</v>
       </c>
       <c r="J65" t="n">
-        <v>-99.06999999999999</v>
+        <v>-129.98</v>
       </c>
       <c r="K65" t="n">
-        <v>63.45</v>
+        <v>83.25</v>
       </c>
       <c r="L65" t="n">
-        <v>117.65</v>
+        <v>154.35</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>-195.35</v>
+        <v>-225.45</v>
       </c>
       <c r="K66" t="n">
-        <v>85.33</v>
+        <v>98.48</v>
       </c>
       <c r="L66" t="n">
-        <v>213.17</v>
+        <v>246.02</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>19</v>
       </c>
       <c r="J67" t="n">
-        <v>-138.65</v>
+        <v>-170</v>
       </c>
       <c r="K67" t="n">
-        <v>-37.83</v>
+        <v>-46.39</v>
       </c>
       <c r="L67" t="n">
-        <v>143.72</v>
+        <v>176.22</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>20</v>
       </c>
       <c r="J68" t="n">
-        <v>-224.26</v>
+        <v>-281.88</v>
       </c>
       <c r="K68" t="n">
-        <v>-155.72</v>
+        <v>-195.74</v>
       </c>
       <c r="L68" t="n">
-        <v>273.02</v>
+        <v>343.18</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>19</v>
       </c>
       <c r="J69" t="n">
-        <v>161.34</v>
+        <v>207.21</v>
       </c>
       <c r="K69" t="n">
-        <v>20.77</v>
+        <v>26.67</v>
       </c>
       <c r="L69" t="n">
-        <v>162.67</v>
+        <v>208.92</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>19</v>
       </c>
       <c r="J70" t="n">
-        <v>-219.26</v>
+        <v>-268.16</v>
       </c>
       <c r="K70" t="n">
-        <v>-51.66</v>
+        <v>-63.18</v>
       </c>
       <c r="L70" t="n">
-        <v>225.26</v>
+        <v>275.5</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>19</v>
       </c>
       <c r="J71" t="n">
-        <v>-388.26</v>
+        <v>-491.26</v>
       </c>
       <c r="K71" t="n">
-        <v>330.98</v>
+        <v>418.79</v>
       </c>
       <c r="L71" t="n">
-        <v>510.19</v>
+        <v>645.54</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>17</v>
       </c>
       <c r="J72" t="n">
-        <v>-132.27</v>
+        <v>-187.78</v>
       </c>
       <c r="K72" t="n">
-        <v>-194.53</v>
+        <v>-276.17</v>
       </c>
       <c r="L72" t="n">
-        <v>235.23</v>
+        <v>333.97</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>19</v>
       </c>
       <c r="J73" t="n">
-        <v>282.33</v>
+        <v>401.39</v>
       </c>
       <c r="K73" t="n">
-        <v>18.24</v>
+        <v>25.93</v>
       </c>
       <c r="L73" t="n">
-        <v>282.92</v>
+        <v>402.23</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>17</v>
       </c>
       <c r="J74" t="n">
-        <v>14.69</v>
+        <v>17.35</v>
       </c>
       <c r="K74" t="n">
-        <v>-76.34</v>
+        <v>-90.17</v>
       </c>
       <c r="L74" t="n">
-        <v>77.73999999999999</v>
+        <v>91.81999999999999</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>20</v>
       </c>
       <c r="J75" t="n">
-        <v>-11.09</v>
+        <v>-11.68</v>
       </c>
       <c r="K75" t="n">
-        <v>-122.97</v>
+        <v>-129.57</v>
       </c>
       <c r="L75" t="n">
-        <v>123.47</v>
+        <v>130.1</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>-17.97</v>
+        <v>-20.45</v>
       </c>
       <c r="K76" t="n">
-        <v>-100.25</v>
+        <v>-114.1</v>
       </c>
       <c r="L76" t="n">
-        <v>101.85</v>
+        <v>115.92</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>100.33</v>
+        <v>103.64</v>
       </c>
       <c r="K77" t="n">
-        <v>-181.74</v>
+        <v>-187.74</v>
       </c>
       <c r="L77" t="n">
-        <v>207.59</v>
+        <v>214.44</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>-63.03</v>
+        <v>-74.33</v>
       </c>
       <c r="K78" t="n">
-        <v>81.84999999999999</v>
+        <v>96.53</v>
       </c>
       <c r="L78" t="n">
-        <v>103.3</v>
+        <v>121.83</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>19</v>
       </c>
       <c r="J79" t="n">
-        <v>37.66</v>
+        <v>47.17</v>
       </c>
       <c r="K79" t="n">
-        <v>69.70999999999999</v>
+        <v>87.3</v>
       </c>
       <c r="L79" t="n">
-        <v>79.23</v>
+        <v>99.23</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>18</v>
       </c>
       <c r="J80" t="n">
-        <v>130.25</v>
+        <v>165.81</v>
       </c>
       <c r="K80" t="n">
-        <v>18.72</v>
+        <v>23.82</v>
       </c>
       <c r="L80" t="n">
-        <v>131.59</v>
+        <v>167.51</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>216.6</v>
+        <v>260.67</v>
       </c>
       <c r="K81" t="n">
-        <v>-0.23</v>
+        <v>-0.28</v>
       </c>
       <c r="L81" t="n">
-        <v>216.6</v>
+        <v>260.67</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>20</v>
       </c>
       <c r="J82" t="n">
-        <v>-118.87</v>
+        <v>-146.64</v>
       </c>
       <c r="K82" t="n">
-        <v>90.27</v>
+        <v>111.36</v>
       </c>
       <c r="L82" t="n">
-        <v>149.26</v>
+        <v>184.13</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>-215.18</v>
+        <v>-268.56</v>
       </c>
       <c r="K83" t="n">
-        <v>-140.21</v>
+        <v>-174.99</v>
       </c>
       <c r="L83" t="n">
-        <v>256.83</v>
+        <v>320.54</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>19</v>
       </c>
       <c r="J84" t="n">
-        <v>29.07</v>
+        <v>40.51</v>
       </c>
       <c r="K84" t="n">
-        <v>-54.51</v>
+        <v>-75.95</v>
       </c>
       <c r="L84" t="n">
-        <v>61.77</v>
+        <v>86.06999999999999</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>19</v>
       </c>
       <c r="J85" t="n">
-        <v>22.11</v>
+        <v>27.34</v>
       </c>
       <c r="K85" t="n">
-        <v>211.13</v>
+        <v>261.03</v>
       </c>
       <c r="L85" t="n">
-        <v>212.28</v>
+        <v>262.46</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>19</v>
       </c>
       <c r="J86" t="n">
-        <v>-160.26</v>
+        <v>-209.52</v>
       </c>
       <c r="K86" t="n">
-        <v>-385.98</v>
+        <v>-504.62</v>
       </c>
       <c r="L86" t="n">
-        <v>417.93</v>
+        <v>546.39</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>180.24</v>
+        <v>270.98</v>
       </c>
       <c r="K87" t="n">
-        <v>249.71</v>
+        <v>375.41</v>
       </c>
       <c r="L87" t="n">
-        <v>307.96</v>
+        <v>462.99</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>294.07</v>
+        <v>424.58</v>
       </c>
       <c r="K88" t="n">
-        <v>-60.72</v>
+        <v>-87.67</v>
       </c>
       <c r="L88" t="n">
-        <v>300.27</v>
+        <v>433.54</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-08-26.xlsx
+++ b/output/2025-08-26.xlsx
@@ -640,13 +640,13 @@
         <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>71.92</v>
+        <v>72.42</v>
       </c>
       <c r="K14" t="n">
-        <v>-52.33</v>
+        <v>-52.7</v>
       </c>
       <c r="L14" t="n">
-        <v>88.94</v>
+        <v>89.56999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>-115.35</v>
+        <v>-132.97</v>
       </c>
       <c r="K15" t="n">
-        <v>-8.789999999999999</v>
+        <v>-10.13</v>
       </c>
       <c r="L15" t="n">
-        <v>115.69</v>
+        <v>133.36</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>16</v>
       </c>
       <c r="J16" t="n">
-        <v>-97.08</v>
+        <v>-102.95</v>
       </c>
       <c r="K16" t="n">
-        <v>-22.41</v>
+        <v>-23.76</v>
       </c>
       <c r="L16" t="n">
-        <v>99.63</v>
+        <v>105.65</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>104.71</v>
+        <v>110.61</v>
       </c>
       <c r="K17" t="n">
-        <v>117.53</v>
+        <v>124.15</v>
       </c>
       <c r="L17" t="n">
-        <v>157.4</v>
+        <v>166.28</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>20</v>
       </c>
       <c r="J18" t="n">
-        <v>-112.15</v>
+        <v>-124.95</v>
       </c>
       <c r="K18" t="n">
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
       <c r="L18" t="n">
-        <v>112.15</v>
+        <v>124.95</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>70.42</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>-87</v>
+        <v>-101.18</v>
       </c>
       <c r="L19" t="n">
-        <v>111.93</v>
+        <v>130.17</v>
       </c>
     </row>
     <row r="20">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>-32.82</v>
+        <v>-40.89</v>
       </c>
       <c r="K29" t="n">
-        <v>92.67</v>
+        <v>115.46</v>
       </c>
       <c r="L29" t="n">
-        <v>98.31</v>
+        <v>122.49</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>17</v>
       </c>
       <c r="J30" t="n">
-        <v>-12.6</v>
+        <v>-13.39</v>
       </c>
       <c r="K30" t="n">
-        <v>17.69</v>
+        <v>18.79</v>
       </c>
       <c r="L30" t="n">
-        <v>21.72</v>
+        <v>23.07</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>-83.56999999999999</v>
+        <v>-98.53</v>
       </c>
       <c r="K31" t="n">
-        <v>42.1</v>
+        <v>49.64</v>
       </c>
       <c r="L31" t="n">
-        <v>93.58</v>
+        <v>110.32</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>16</v>
       </c>
       <c r="J32" t="n">
-        <v>93.16</v>
+        <v>103.17</v>
       </c>
       <c r="K32" t="n">
-        <v>-103.75</v>
+        <v>-114.9</v>
       </c>
       <c r="L32" t="n">
-        <v>139.44</v>
+        <v>154.42</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>18</v>
       </c>
       <c r="J33" t="n">
-        <v>54.23</v>
+        <v>62.97</v>
       </c>
       <c r="K33" t="n">
-        <v>94.23999999999999</v>
+        <v>109.43</v>
       </c>
       <c r="L33" t="n">
-        <v>108.73</v>
+        <v>126.26</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>17</v>
       </c>
       <c r="J34" t="n">
-        <v>93.69</v>
+        <v>113.78</v>
       </c>
       <c r="K34" t="n">
-        <v>-58.94</v>
+        <v>-71.58</v>
       </c>
       <c r="L34" t="n">
-        <v>110.69</v>
+        <v>134.43</v>
       </c>
     </row>
     <row r="35">
@@ -1900,13 +1900,13 @@
         <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>-56.99</v>
+        <v>-68.58</v>
       </c>
       <c r="K44" t="n">
-        <v>77.95999999999999</v>
+        <v>93.81</v>
       </c>
       <c r="L44" t="n">
-        <v>96.56999999999999</v>
+        <v>116.21</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>63.56</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="K45" t="n">
-        <v>54.64</v>
+        <v>56.37</v>
       </c>
       <c r="L45" t="n">
-        <v>83.81999999999999</v>
+        <v>86.47</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>16</v>
       </c>
       <c r="J46" t="n">
-        <v>-68.11</v>
+        <v>-79.65000000000001</v>
       </c>
       <c r="K46" t="n">
-        <v>42.8</v>
+        <v>50.05</v>
       </c>
       <c r="L46" t="n">
-        <v>80.45</v>
+        <v>94.06999999999999</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>16</v>
       </c>
       <c r="J47" t="n">
-        <v>114.65</v>
+        <v>151.75</v>
       </c>
       <c r="K47" t="n">
-        <v>2.34</v>
+        <v>3.1</v>
       </c>
       <c r="L47" t="n">
-        <v>114.67</v>
+        <v>151.78</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>-22.69</v>
+        <v>-24.61</v>
       </c>
       <c r="K48" t="n">
-        <v>108.04</v>
+        <v>117.16</v>
       </c>
       <c r="L48" t="n">
-        <v>110.39</v>
+        <v>119.72</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>17</v>
       </c>
       <c r="J49" t="n">
-        <v>-112.36</v>
+        <v>-142.71</v>
       </c>
       <c r="K49" t="n">
-        <v>-90.38</v>
+        <v>-114.79</v>
       </c>
       <c r="L49" t="n">
-        <v>144.2</v>
+        <v>183.15</v>
       </c>
     </row>
     <row r="50">
@@ -2530,13 +2530,13 @@
         <v>20</v>
       </c>
       <c r="J59" t="n">
-        <v>-86.51000000000001</v>
+        <v>-113.17</v>
       </c>
       <c r="K59" t="n">
-        <v>-44.89</v>
+        <v>-58.72</v>
       </c>
       <c r="L59" t="n">
-        <v>97.45999999999999</v>
+        <v>127.5</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>17</v>
       </c>
       <c r="J60" t="n">
-        <v>81.95999999999999</v>
+        <v>100.05</v>
       </c>
       <c r="K60" t="n">
-        <v>60.46</v>
+        <v>73.81</v>
       </c>
       <c r="L60" t="n">
-        <v>101.85</v>
+        <v>124.33</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>34.87</v>
+        <v>46.73</v>
       </c>
       <c r="K61" t="n">
-        <v>-80.3</v>
+        <v>-107.61</v>
       </c>
       <c r="L61" t="n">
-        <v>87.54000000000001</v>
+        <v>117.32</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>16</v>
       </c>
       <c r="J62" t="n">
-        <v>-66.62</v>
+        <v>-74.68000000000001</v>
       </c>
       <c r="K62" t="n">
-        <v>62.61</v>
+        <v>70.18000000000001</v>
       </c>
       <c r="L62" t="n">
-        <v>91.42</v>
+        <v>102.48</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>-83.12</v>
+        <v>-104.6</v>
       </c>
       <c r="K63" t="n">
-        <v>-98.31</v>
+        <v>-123.71</v>
       </c>
       <c r="L63" t="n">
-        <v>128.74</v>
+        <v>162</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>20</v>
       </c>
       <c r="J64" t="n">
-        <v>-33.13</v>
+        <v>-40.24</v>
       </c>
       <c r="K64" t="n">
-        <v>102.56</v>
+        <v>124.56</v>
       </c>
       <c r="L64" t="n">
-        <v>107.78</v>
+        <v>130.9</v>
       </c>
     </row>
     <row r="65">
@@ -3160,13 +3160,13 @@
         <v>17</v>
       </c>
       <c r="J74" t="n">
-        <v>17.35</v>
+        <v>21.66</v>
       </c>
       <c r="K74" t="n">
-        <v>-90.17</v>
+        <v>-112.57</v>
       </c>
       <c r="L74" t="n">
-        <v>91.81999999999999</v>
+        <v>114.64</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>20</v>
       </c>
       <c r="J75" t="n">
-        <v>-11.68</v>
+        <v>-15.28</v>
       </c>
       <c r="K75" t="n">
-        <v>-129.57</v>
+        <v>-169.5</v>
       </c>
       <c r="L75" t="n">
-        <v>130.1</v>
+        <v>170.19</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>-20.45</v>
+        <v>-31</v>
       </c>
       <c r="K76" t="n">
-        <v>-114.1</v>
+        <v>-172.94</v>
       </c>
       <c r="L76" t="n">
-        <v>115.92</v>
+        <v>175.69</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>103.64</v>
+        <v>125.48</v>
       </c>
       <c r="K77" t="n">
-        <v>-187.74</v>
+        <v>-227.3</v>
       </c>
       <c r="L77" t="n">
-        <v>214.44</v>
+        <v>259.63</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>-74.33</v>
+        <v>-90.27</v>
       </c>
       <c r="K78" t="n">
-        <v>96.53</v>
+        <v>117.23</v>
       </c>
       <c r="L78" t="n">
-        <v>121.83</v>
+        <v>147.96</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>19</v>
       </c>
       <c r="J79" t="n">
-        <v>47.17</v>
+        <v>58.99</v>
       </c>
       <c r="K79" t="n">
-        <v>87.3</v>
+        <v>109.18</v>
       </c>
       <c r="L79" t="n">
-        <v>99.23</v>
+        <v>124.1</v>
       </c>
     </row>
     <row r="80">
